--- a/master_data.xlsx
+++ b/master_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\000_專案計畫\20260107_學分學程查詢功能\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA7EBF8-90C7-4ECA-A67D-7A8B9D1504F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{922EBC95-E643-4AEC-A77F-BDA1CE915FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2419E411-9130-4528-BB63-D18464EFCFCF}"/>
+    <workbookView xWindow="6915" yWindow="4185" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{2419E411-9130-4528-BB63-D18464EFCFCF}"/>
   </bookViews>
   <sheets>
     <sheet name="科目表" sheetId="1" r:id="rId1"/>
@@ -276,11 +276,11 @@
     <t>備註 (模組要求)</t>
   </si>
   <si>
-    <t>無</t>
+    <t>選修模組</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>選修模組</t>
+    <t>我來測試一下</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -796,7 +796,7 @@
         <v>22</v>
       </c>
       <c r="J4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -825,7 +825,7 @@
         <v>22</v>
       </c>
       <c r="J5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -854,7 +854,7 @@
         <v>22</v>
       </c>
       <c r="J6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -883,7 +883,7 @@
         <v>17</v>
       </c>
       <c r="J7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -912,7 +912,7 @@
         <v>17</v>
       </c>
       <c r="J8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -941,7 +941,7 @@
         <v>17</v>
       </c>
       <c r="J9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -970,7 +970,7 @@
         <v>17</v>
       </c>
       <c r="J10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -999,7 +999,7 @@
         <v>17</v>
       </c>
       <c r="J11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -1028,7 +1028,7 @@
         <v>17</v>
       </c>
       <c r="J12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1057,7 +1057,7 @@
         <v>17</v>
       </c>
       <c r="J13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1086,7 +1086,7 @@
         <v>17</v>
       </c>
       <c r="J14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -1115,7 +1115,7 @@
         <v>17</v>
       </c>
       <c r="J15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1144,7 +1144,7 @@
         <v>17</v>
       </c>
       <c r="J16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -1173,7 +1173,7 @@
         <v>17</v>
       </c>
       <c r="J17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -1202,7 +1202,7 @@
         <v>17</v>
       </c>
       <c r="J18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -1231,7 +1231,7 @@
         <v>19</v>
       </c>
       <c r="J19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -1260,7 +1260,7 @@
         <v>19</v>
       </c>
       <c r="J20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -1289,7 +1289,7 @@
         <v>19</v>
       </c>
       <c r="J21" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -1318,7 +1318,7 @@
         <v>19</v>
       </c>
       <c r="J22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -1347,7 +1347,7 @@
         <v>19</v>
       </c>
       <c r="J23" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1376,7 +1376,7 @@
         <v>19</v>
       </c>
       <c r="J24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -1405,7 +1405,7 @@
         <v>19</v>
       </c>
       <c r="J25" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -1434,7 +1434,7 @@
         <v>19</v>
       </c>
       <c r="J26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -1463,7 +1463,7 @@
         <v>19</v>
       </c>
       <c r="J27" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -1492,7 +1492,7 @@
         <v>19</v>
       </c>
       <c r="J28" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -1521,7 +1521,7 @@
         <v>19</v>
       </c>
       <c r="J29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -1550,7 +1550,7 @@
         <v>19</v>
       </c>
       <c r="J30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -1579,7 +1579,7 @@
         <v>19</v>
       </c>
       <c r="J31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -1608,7 +1608,7 @@
         <v>19</v>
       </c>
       <c r="J32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -1637,7 +1637,7 @@
         <v>19</v>
       </c>
       <c r="J33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -1666,7 +1666,7 @@
         <v>19</v>
       </c>
       <c r="J34" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -1695,7 +1695,7 @@
         <v>54</v>
       </c>
       <c r="J35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -1724,7 +1724,7 @@
         <v>56</v>
       </c>
       <c r="J36" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -1753,7 +1753,7 @@
         <v>56</v>
       </c>
       <c r="J37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -1782,7 +1782,7 @@
         <v>56</v>
       </c>
       <c r="J38" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -1811,7 +1811,7 @@
         <v>56</v>
       </c>
       <c r="J39" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -1840,7 +1840,7 @@
         <v>56</v>
       </c>
       <c r="J40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -1869,7 +1869,7 @@
         <v>56</v>
       </c>
       <c r="J41" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -1898,7 +1898,7 @@
         <v>56</v>
       </c>
       <c r="J42" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -1927,7 +1927,7 @@
         <v>56</v>
       </c>
       <c r="J43" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L43" t="s">
         <v>64</v>
@@ -1959,7 +1959,7 @@
         <v>56</v>
       </c>
       <c r="J44" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L44" t="s">
         <v>64</v>
@@ -1991,7 +1991,7 @@
         <v>56</v>
       </c>
       <c r="J45" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L45" t="s">
         <v>67</v>
@@ -2023,7 +2023,7 @@
         <v>56</v>
       </c>
       <c r="J46" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L46" t="s">
         <v>67</v>
@@ -2055,7 +2055,7 @@
         <v>70</v>
       </c>
       <c r="J47" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -2084,7 +2084,7 @@
         <v>70</v>
       </c>
       <c r="J48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -2113,7 +2113,7 @@
         <v>70</v>
       </c>
       <c r="J49" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
@@ -2142,7 +2142,7 @@
         <v>70</v>
       </c>
       <c r="J50" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2206,7 +2206,7 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/master_data.xlsx
+++ b/master_data.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\000_專案計畫\20260107_學分學程查詢功能\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{922EBC95-E643-4AEC-A77F-BDA1CE915FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DB5EB78-01F7-4B2D-BA62-2ACDD2246CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6915" yWindow="4185" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{2419E411-9130-4528-BB63-D18464EFCFCF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C32469BD-056E-459F-8F49-ECC8EEE0EE91}"/>
   </bookViews>
   <sheets>
-    <sheet name="科目表" sheetId="1" r:id="rId1"/>
-    <sheet name="學程規範總額" sheetId="2" r:id="rId2"/>
+    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="123">
   <si>
     <t>學院</t>
   </si>
@@ -109,179 +108,310 @@
   </si>
   <si>
     <t>圖資系碩士班</t>
-  </si>
-  <si>
-    <t>古籍整理與利用</t>
-  </si>
-  <si>
-    <t>數位典藏理論與實務專題</t>
-  </si>
-  <si>
-    <t>版本學與古籍保護</t>
-  </si>
-  <si>
-    <t>數位典藏與數位學習</t>
-  </si>
-  <si>
-    <t>檔案管理與加值行銷</t>
-  </si>
-  <si>
-    <t>圖書館推廣與行銷</t>
-  </si>
-  <si>
-    <t>圖書資訊學導論</t>
-  </si>
-  <si>
-    <t>參考資源</t>
-  </si>
-  <si>
-    <t>資訊組織</t>
-  </si>
-  <si>
-    <t>主題分析</t>
-  </si>
-  <si>
-    <t>館藏發展</t>
-  </si>
-  <si>
-    <t>人文學資源</t>
-  </si>
-  <si>
-    <t>社會科學資源</t>
-  </si>
-  <si>
-    <t>圖書館實務</t>
-  </si>
-  <si>
-    <t>禮記</t>
-  </si>
-  <si>
-    <t>尚書</t>
-  </si>
-  <si>
-    <t>老子</t>
-  </si>
-  <si>
-    <t>莊子</t>
-  </si>
-  <si>
-    <t>詩經</t>
-  </si>
-  <si>
-    <t>荀子</t>
-  </si>
-  <si>
-    <t>左傳</t>
-  </si>
-  <si>
-    <t>語法修辭學</t>
-  </si>
-  <si>
-    <t>文獻知識</t>
-  </si>
-  <si>
-    <t>聲韻學</t>
-  </si>
-  <si>
-    <t>訓詁學</t>
-  </si>
-  <si>
-    <t>文字學</t>
-  </si>
-  <si>
-    <t>中國傳統小說</t>
-  </si>
-  <si>
-    <t>中國古典戲曲</t>
-  </si>
-  <si>
-    <t>中國文學史</t>
-  </si>
-  <si>
-    <t>史記</t>
-  </si>
-  <si>
-    <t>易經</t>
-  </si>
-  <si>
-    <t>中文系or哲學系</t>
-  </si>
-  <si>
-    <t>先秦諸子哲學</t>
-  </si>
-  <si>
-    <t>哲學系</t>
-  </si>
-  <si>
-    <t>魏晉哲學</t>
-  </si>
-  <si>
-    <t>儒家哲學</t>
-  </si>
-  <si>
-    <t>兩漢哲學</t>
-  </si>
-  <si>
-    <t>五經思想/五經思想：易經</t>
-  </si>
-  <si>
-    <t>佛學概論</t>
-  </si>
-  <si>
-    <t>宋明理學</t>
-  </si>
-  <si>
-    <t>清代哲學</t>
-  </si>
-  <si>
-    <t>chin_ph</t>
-  </si>
-  <si>
-    <t>清代哲學研究</t>
-  </si>
-  <si>
-    <t>道家哲學</t>
-  </si>
-  <si>
-    <t>dao_ph</t>
-  </si>
-  <si>
-    <t>先秦道家哲學</t>
-  </si>
-  <si>
-    <t>西洋博物館史</t>
-  </si>
-  <si>
-    <t>歷史系</t>
-  </si>
-  <si>
-    <t>台灣博物館史</t>
-  </si>
-  <si>
-    <t>檔案與口述歷史</t>
-  </si>
-  <si>
-    <t>中國史學史</t>
-  </si>
-  <si>
-    <t>必修總學分</t>
-  </si>
-  <si>
-    <t>選修總學分</t>
-  </si>
-  <si>
-    <t>總計應修學分</t>
-  </si>
-  <si>
-    <t>備註 (模組要求)</t>
   </si>
   <si>
     <t>選修模組</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>我來測試一下</t>
+    <t>古籍整理與利用</t>
+  </si>
+  <si>
+    <t>數位典藏理論與實務專題</t>
+  </si>
+  <si>
+    <t>版本學與古籍保護</t>
+  </si>
+  <si>
+    <t>數位典藏與數位學習</t>
+  </si>
+  <si>
+    <t>檔案管理與加值行銷</t>
+  </si>
+  <si>
+    <t>圖書館推廣與行銷</t>
+  </si>
+  <si>
+    <t>圖書資訊學導論</t>
+  </si>
+  <si>
+    <t>參考資源</t>
+  </si>
+  <si>
+    <t>資訊組織</t>
+  </si>
+  <si>
+    <t>主題分析</t>
+  </si>
+  <si>
+    <t>館藏發展</t>
+  </si>
+  <si>
+    <t>人文學資源</t>
+  </si>
+  <si>
+    <t>社會科學資源</t>
+  </si>
+  <si>
+    <t>圖書館實務</t>
+  </si>
+  <si>
+    <t>禮記</t>
+  </si>
+  <si>
+    <t>尚書</t>
+  </si>
+  <si>
+    <t>老子</t>
+  </si>
+  <si>
+    <t>莊子</t>
+  </si>
+  <si>
+    <t>詩經</t>
+  </si>
+  <si>
+    <t>荀子</t>
+  </si>
+  <si>
+    <t>左傳</t>
+  </si>
+  <si>
+    <t>語法修辭學</t>
+  </si>
+  <si>
+    <t>文獻知識</t>
+  </si>
+  <si>
+    <t>聲韻學</t>
+  </si>
+  <si>
+    <t>訓詁學</t>
+  </si>
+  <si>
+    <t>文字學</t>
+  </si>
+  <si>
+    <t>中國傳統小說</t>
+  </si>
+  <si>
+    <t>中國古典戲曲</t>
+  </si>
+  <si>
+    <t>中國文學史</t>
+  </si>
+  <si>
+    <t>史記</t>
+  </si>
+  <si>
+    <t>易經</t>
+  </si>
+  <si>
+    <t>中文系or哲學系</t>
+  </si>
+  <si>
+    <t>先秦諸子哲學</t>
+  </si>
+  <si>
+    <t>哲學系</t>
+  </si>
+  <si>
+    <t>魏晉哲學</t>
+  </si>
+  <si>
+    <t>儒家哲學</t>
+  </si>
+  <si>
+    <t>兩漢哲學</t>
+  </si>
+  <si>
+    <t>五經思想/五經思想：易經</t>
+  </si>
+  <si>
+    <t>佛學概論</t>
+  </si>
+  <si>
+    <t>宋明理學</t>
+  </si>
+  <si>
+    <t>清代哲學</t>
+  </si>
+  <si>
+    <t>chin_ph</t>
+  </si>
+  <si>
+    <t>清代哲學研究</t>
+  </si>
+  <si>
+    <t>道家哲學</t>
+  </si>
+  <si>
+    <t>dao_ph</t>
+  </si>
+  <si>
+    <t>先秦道家哲學</t>
+  </si>
+  <si>
+    <t>西洋博物館史</t>
+  </si>
+  <si>
+    <t>歷史系</t>
+  </si>
+  <si>
+    <t>台灣博物館史</t>
+  </si>
+  <si>
+    <t>檔案與口述歷史</t>
+  </si>
+  <si>
+    <t>中國史學史</t>
+  </si>
+  <si>
+    <t>K260</t>
+  </si>
+  <si>
+    <t>哲學諮商與輔導學分學程</t>
+  </si>
+  <si>
+    <t>必修</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>哲學諮商理論與實務</t>
+  </si>
+  <si>
+    <t>哲學諮商方法論</t>
+  </si>
+  <si>
+    <t>哲學諮商：實習</t>
+  </si>
+  <si>
+    <t>哲學系、心理學系、臨床心理學系共同負責</t>
+  </si>
+  <si>
+    <t>知識論</t>
+  </si>
+  <si>
+    <t>哲學系學生不得列為選修課程。</t>
+  </si>
+  <si>
+    <t>倫理學</t>
+  </si>
+  <si>
+    <t>哲學人學</t>
+  </si>
+  <si>
+    <t>兒童哲學</t>
+  </si>
+  <si>
+    <t>蘇格拉底對話</t>
+  </si>
+  <si>
+    <t>現象學導論</t>
+  </si>
+  <si>
+    <t>敘事符號學</t>
+  </si>
+  <si>
+    <t>詮釋學</t>
+  </si>
+  <si>
+    <t>方法論</t>
+  </si>
+  <si>
+    <t>行動哲學</t>
+  </si>
+  <si>
+    <t>存在主義</t>
+  </si>
+  <si>
+    <t>兒童哲學：理論與實務</t>
+  </si>
+  <si>
+    <t>哲學諮商與社會實踐</t>
+  </si>
+  <si>
+    <t>哲學諮商的倫理學基礎</t>
+  </si>
+  <si>
+    <t>亞里斯多德的哲學諮商</t>
+  </si>
+  <si>
+    <t>哲學諮商實務</t>
+  </si>
+  <si>
+    <t>哲學諮商的批判與思考</t>
+  </si>
+  <si>
+    <t>五經思想：易經</t>
+  </si>
+  <si>
+    <t>中國哲學的方法論</t>
+  </si>
+  <si>
+    <t>先秦儒家與情感哲學</t>
+  </si>
+  <si>
+    <t>中國哲學專題：人性論</t>
+  </si>
+  <si>
+    <t>敘說、反應與實踐導論</t>
+  </si>
+  <si>
+    <t>心理系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>輔導與諮商概論</t>
+  </si>
+  <si>
+    <t>電影、心理與人生</t>
+  </si>
+  <si>
+    <t>性別經驗與心理學</t>
+  </si>
+  <si>
+    <t>變態心理學</t>
+  </si>
+  <si>
+    <t>家庭關係與個人發展</t>
+  </si>
+  <si>
+    <t>諮商與心理治療理論</t>
+  </si>
+  <si>
+    <t>批判心理學導論</t>
+  </si>
+  <si>
+    <t>生命敘說與自我發展</t>
+  </si>
+  <si>
+    <t>戲劇治療</t>
+  </si>
+  <si>
+    <t>社會生活與社會治療</t>
+  </si>
+  <si>
+    <t>心理衛生</t>
+  </si>
+  <si>
+    <t>臨心系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>團體諮商</t>
+  </si>
+  <si>
+    <t>人本心理學</t>
+  </si>
+  <si>
+    <t>完形治療法</t>
+  </si>
+  <si>
+    <t>遊戲治療法</t>
+  </si>
+  <si>
+    <t>舞蹈治療實務</t>
   </si>
 </sst>
 </file>
@@ -664,21 +794,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64589823-D3C8-45DA-9C5E-2E7B269696D6}">
-  <dimension ref="A1:L50"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94A09248-8F3E-4F54-B236-07AA808331C3}">
+  <dimension ref="A1:L91"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.875" customWidth="1"/>
-    <col min="12" max="12" width="9.5" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -796,7 +914,7 @@
         <v>22</v>
       </c>
       <c r="J4" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -816,7 +934,7 @@
         <v>20</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -825,7 +943,7 @@
         <v>22</v>
       </c>
       <c r="J5" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -845,7 +963,7 @@
         <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H6">
         <v>2</v>
@@ -854,7 +972,7 @@
         <v>22</v>
       </c>
       <c r="J6" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -874,7 +992,7 @@
         <v>20</v>
       </c>
       <c r="G7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H7">
         <v>4</v>
@@ -883,7 +1001,7 @@
         <v>17</v>
       </c>
       <c r="J7" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -903,7 +1021,7 @@
         <v>20</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -912,7 +1030,7 @@
         <v>17</v>
       </c>
       <c r="J8" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -932,7 +1050,7 @@
         <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H9">
         <v>4</v>
@@ -941,7 +1059,7 @@
         <v>17</v>
       </c>
       <c r="J9" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -961,7 +1079,7 @@
         <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H10">
         <v>4</v>
@@ -970,7 +1088,7 @@
         <v>17</v>
       </c>
       <c r="J10" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -990,7 +1108,7 @@
         <v>20</v>
       </c>
       <c r="G11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H11">
         <v>4</v>
@@ -999,7 +1117,7 @@
         <v>17</v>
       </c>
       <c r="J11" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -1019,7 +1137,7 @@
         <v>20</v>
       </c>
       <c r="G12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H12">
         <v>4</v>
@@ -1028,7 +1146,7 @@
         <v>17</v>
       </c>
       <c r="J12" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -1048,7 +1166,7 @@
         <v>20</v>
       </c>
       <c r="G13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H13">
         <v>4</v>
@@ -1057,7 +1175,7 @@
         <v>17</v>
       </c>
       <c r="J13" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -1077,7 +1195,7 @@
         <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H14">
         <v>4</v>
@@ -1086,7 +1204,7 @@
         <v>17</v>
       </c>
       <c r="J14" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -1106,7 +1224,7 @@
         <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H15">
         <v>4</v>
@@ -1115,7 +1233,7 @@
         <v>17</v>
       </c>
       <c r="J15" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -1135,7 +1253,7 @@
         <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H16">
         <v>4</v>
@@ -1144,7 +1262,7 @@
         <v>17</v>
       </c>
       <c r="J16" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -1164,7 +1282,7 @@
         <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H17">
         <v>4</v>
@@ -1173,7 +1291,7 @@
         <v>17</v>
       </c>
       <c r="J17" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -1193,7 +1311,7 @@
         <v>20</v>
       </c>
       <c r="G18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H18">
         <v>2</v>
@@ -1202,7 +1320,7 @@
         <v>17</v>
       </c>
       <c r="J18" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -1222,7 +1340,7 @@
         <v>20</v>
       </c>
       <c r="G19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H19">
         <v>4</v>
@@ -1231,7 +1349,7 @@
         <v>19</v>
       </c>
       <c r="J19" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -1251,7 +1369,7 @@
         <v>20</v>
       </c>
       <c r="G20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H20">
         <v>4</v>
@@ -1260,7 +1378,7 @@
         <v>19</v>
       </c>
       <c r="J20" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -1280,7 +1398,7 @@
         <v>20</v>
       </c>
       <c r="G21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H21">
         <v>4</v>
@@ -1289,7 +1407,7 @@
         <v>19</v>
       </c>
       <c r="J21" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -1309,7 +1427,7 @@
         <v>20</v>
       </c>
       <c r="G22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H22">
         <v>4</v>
@@ -1318,7 +1436,7 @@
         <v>19</v>
       </c>
       <c r="J22" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -1338,7 +1456,7 @@
         <v>20</v>
       </c>
       <c r="G23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H23">
         <v>4</v>
@@ -1347,7 +1465,7 @@
         <v>19</v>
       </c>
       <c r="J23" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1367,7 +1485,7 @@
         <v>20</v>
       </c>
       <c r="G24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H24">
         <v>4</v>
@@ -1376,7 +1494,7 @@
         <v>19</v>
       </c>
       <c r="J24" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -1396,7 +1514,7 @@
         <v>20</v>
       </c>
       <c r="G25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H25">
         <v>4</v>
@@ -1405,7 +1523,7 @@
         <v>19</v>
       </c>
       <c r="J25" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -1425,7 +1543,7 @@
         <v>20</v>
       </c>
       <c r="G26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H26">
         <v>4</v>
@@ -1434,7 +1552,7 @@
         <v>19</v>
       </c>
       <c r="J26" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -1454,7 +1572,7 @@
         <v>20</v>
       </c>
       <c r="G27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H27">
         <v>4</v>
@@ -1463,7 +1581,7 @@
         <v>19</v>
       </c>
       <c r="J27" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -1483,7 +1601,7 @@
         <v>20</v>
       </c>
       <c r="G28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H28">
         <v>4</v>
@@ -1492,7 +1610,7 @@
         <v>19</v>
       </c>
       <c r="J28" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -1512,7 +1630,7 @@
         <v>20</v>
       </c>
       <c r="G29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H29">
         <v>4</v>
@@ -1521,7 +1639,7 @@
         <v>19</v>
       </c>
       <c r="J29" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -1541,7 +1659,7 @@
         <v>20</v>
       </c>
       <c r="G30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H30">
         <v>4</v>
@@ -1550,7 +1668,7 @@
         <v>19</v>
       </c>
       <c r="J30" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -1570,7 +1688,7 @@
         <v>20</v>
       </c>
       <c r="G31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H31">
         <v>4</v>
@@ -1579,7 +1697,7 @@
         <v>19</v>
       </c>
       <c r="J31" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -1599,7 +1717,7 @@
         <v>20</v>
       </c>
       <c r="G32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H32">
         <v>4</v>
@@ -1608,7 +1726,7 @@
         <v>19</v>
       </c>
       <c r="J32" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -1628,7 +1746,7 @@
         <v>20</v>
       </c>
       <c r="G33" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H33">
         <v>6</v>
@@ -1637,7 +1755,7 @@
         <v>19</v>
       </c>
       <c r="J33" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -1657,7 +1775,7 @@
         <v>20</v>
       </c>
       <c r="G34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H34">
         <v>4</v>
@@ -1666,7 +1784,7 @@
         <v>19</v>
       </c>
       <c r="J34" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -1686,16 +1804,16 @@
         <v>20</v>
       </c>
       <c r="G35" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H35">
         <v>4</v>
       </c>
       <c r="I35" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J35" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -1715,16 +1833,16 @@
         <v>20</v>
       </c>
       <c r="G36" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H36">
         <v>4</v>
       </c>
       <c r="I36" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J36" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -1744,16 +1862,16 @@
         <v>20</v>
       </c>
       <c r="G37" t="s">
+        <v>58</v>
+      </c>
+      <c r="H37">
+        <v>4</v>
+      </c>
+      <c r="I37" t="s">
         <v>57</v>
       </c>
-      <c r="H37">
-        <v>4</v>
-      </c>
-      <c r="I37" t="s">
-        <v>56</v>
-      </c>
       <c r="J37" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -1773,16 +1891,16 @@
         <v>20</v>
       </c>
       <c r="G38" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H38">
         <v>4</v>
       </c>
       <c r="I38" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J38" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -1802,16 +1920,16 @@
         <v>20</v>
       </c>
       <c r="G39" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H39">
         <v>4</v>
       </c>
       <c r="I39" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J39" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -1831,16 +1949,16 @@
         <v>20</v>
       </c>
       <c r="G40" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H40">
         <v>4</v>
       </c>
       <c r="I40" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J40" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -1860,16 +1978,16 @@
         <v>20</v>
       </c>
       <c r="G41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H41">
         <v>4</v>
       </c>
       <c r="I41" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J41" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -1889,16 +2007,16 @@
         <v>20</v>
       </c>
       <c r="G42" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H42">
         <v>4</v>
       </c>
       <c r="I42" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J42" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -1918,19 +2036,19 @@
         <v>20</v>
       </c>
       <c r="G43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H43">
         <v>4</v>
       </c>
       <c r="I43" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J43" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="L43" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -1950,19 +2068,19 @@
         <v>20</v>
       </c>
       <c r="G44" t="s">
+        <v>66</v>
+      </c>
+      <c r="H44">
+        <v>4</v>
+      </c>
+      <c r="I44" t="s">
+        <v>57</v>
+      </c>
+      <c r="J44" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" t="s">
         <v>65</v>
-      </c>
-      <c r="H44">
-        <v>4</v>
-      </c>
-      <c r="I44" t="s">
-        <v>56</v>
-      </c>
-      <c r="J44" t="s">
-        <v>78</v>
-      </c>
-      <c r="L44" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -1982,19 +2100,19 @@
         <v>20</v>
       </c>
       <c r="G45" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H45">
         <v>4</v>
       </c>
       <c r="I45" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J45" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="L45" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -2014,19 +2132,19 @@
         <v>20</v>
       </c>
       <c r="G46" t="s">
+        <v>69</v>
+      </c>
+      <c r="H46">
+        <v>4</v>
+      </c>
+      <c r="I46" t="s">
+        <v>57</v>
+      </c>
+      <c r="J46" t="s">
+        <v>23</v>
+      </c>
+      <c r="L46" t="s">
         <v>68</v>
-      </c>
-      <c r="H46">
-        <v>4</v>
-      </c>
-      <c r="I46" t="s">
-        <v>56</v>
-      </c>
-      <c r="J46" t="s">
-        <v>78</v>
-      </c>
-      <c r="L46" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -2046,16 +2164,16 @@
         <v>20</v>
       </c>
       <c r="G47" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H47">
         <v>2</v>
       </c>
       <c r="I47" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J47" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -2075,19 +2193,19 @@
         <v>20</v>
       </c>
       <c r="G48" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H48">
         <v>2</v>
       </c>
       <c r="I48" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J48" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>12</v>
       </c>
@@ -2104,114 +2222,1238 @@
         <v>20</v>
       </c>
       <c r="G49" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H49">
         <v>2</v>
       </c>
       <c r="I49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J49" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" t="s">
+        <v>14</v>
+      </c>
+      <c r="D50">
+        <v>114</v>
+      </c>
+      <c r="E50" t="s">
+        <v>20</v>
+      </c>
+      <c r="G50" t="s">
+        <v>74</v>
+      </c>
+      <c r="H50">
+        <v>4</v>
+      </c>
+      <c r="I50" t="s">
+        <v>71</v>
+      </c>
+      <c r="J50" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" t="s">
+        <v>75</v>
+      </c>
+      <c r="C51" t="s">
+        <v>76</v>
+      </c>
+      <c r="D51">
+        <v>114</v>
+      </c>
+      <c r="E51" t="s">
+        <v>77</v>
+      </c>
+      <c r="G51" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>12</v>
-      </c>
-      <c r="B50" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" t="s">
-        <v>14</v>
-      </c>
-      <c r="D50">
-        <v>114</v>
-      </c>
-      <c r="E50" t="s">
-        <v>20</v>
-      </c>
-      <c r="G50" t="s">
-        <v>73</v>
-      </c>
-      <c r="H50">
-        <v>4</v>
-      </c>
-      <c r="I50" t="s">
-        <v>70</v>
-      </c>
-      <c r="J50" t="s">
-        <v>78</v>
+      <c r="H51">
+        <v>4</v>
+      </c>
+      <c r="I51" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>12</v>
+      </c>
+      <c r="B52" t="s">
+        <v>75</v>
+      </c>
+      <c r="C52" t="s">
+        <v>76</v>
+      </c>
+      <c r="D52">
+        <v>114</v>
+      </c>
+      <c r="E52" t="s">
+        <v>77</v>
+      </c>
+      <c r="G52" t="s">
+        <v>79</v>
+      </c>
+      <c r="H52">
+        <v>4</v>
+      </c>
+      <c r="I52" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>12</v>
+      </c>
+      <c r="B53" t="s">
+        <v>75</v>
+      </c>
+      <c r="C53" t="s">
+        <v>76</v>
+      </c>
+      <c r="D53">
+        <v>114</v>
+      </c>
+      <c r="E53" t="s">
+        <v>77</v>
+      </c>
+      <c r="G53" t="s">
+        <v>80</v>
+      </c>
+      <c r="H53">
+        <v>2</v>
+      </c>
+      <c r="I53" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>12</v>
+      </c>
+      <c r="B54" t="s">
+        <v>75</v>
+      </c>
+      <c r="C54" t="s">
+        <v>76</v>
+      </c>
+      <c r="D54">
+        <v>114</v>
+      </c>
+      <c r="E54" t="s">
+        <v>20</v>
+      </c>
+      <c r="G54" t="s">
+        <v>82</v>
+      </c>
+      <c r="H54">
+        <v>4</v>
+      </c>
+      <c r="I54" t="s">
+        <v>57</v>
+      </c>
+      <c r="J54" t="s">
+        <v>23</v>
+      </c>
+      <c r="K54" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>12</v>
+      </c>
+      <c r="B55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C55" t="s">
+        <v>76</v>
+      </c>
+      <c r="D55">
+        <v>114</v>
+      </c>
+      <c r="E55" t="s">
+        <v>20</v>
+      </c>
+      <c r="G55" t="s">
+        <v>84</v>
+      </c>
+      <c r="H55">
+        <v>4</v>
+      </c>
+      <c r="I55" t="s">
+        <v>57</v>
+      </c>
+      <c r="J55" t="s">
+        <v>23</v>
+      </c>
+      <c r="K55" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>12</v>
+      </c>
+      <c r="B56" t="s">
+        <v>75</v>
+      </c>
+      <c r="C56" t="s">
+        <v>76</v>
+      </c>
+      <c r="D56">
+        <v>114</v>
+      </c>
+      <c r="E56" t="s">
+        <v>20</v>
+      </c>
+      <c r="G56" t="s">
+        <v>85</v>
+      </c>
+      <c r="H56">
+        <v>4</v>
+      </c>
+      <c r="I56" t="s">
+        <v>57</v>
+      </c>
+      <c r="J56" t="s">
+        <v>23</v>
+      </c>
+      <c r="K56" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>12</v>
+      </c>
+      <c r="B57" t="s">
+        <v>75</v>
+      </c>
+      <c r="C57" t="s">
+        <v>76</v>
+      </c>
+      <c r="D57">
+        <v>114</v>
+      </c>
+      <c r="E57" t="s">
+        <v>20</v>
+      </c>
+      <c r="G57" t="s">
+        <v>86</v>
+      </c>
+      <c r="H57">
+        <v>2</v>
+      </c>
+      <c r="I57" t="s">
+        <v>57</v>
+      </c>
+      <c r="J57" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>12</v>
+      </c>
+      <c r="B58" t="s">
+        <v>75</v>
+      </c>
+      <c r="C58" t="s">
+        <v>76</v>
+      </c>
+      <c r="D58">
+        <v>114</v>
+      </c>
+      <c r="E58" t="s">
+        <v>20</v>
+      </c>
+      <c r="G58" t="s">
+        <v>87</v>
+      </c>
+      <c r="H58">
+        <v>2</v>
+      </c>
+      <c r="I58" t="s">
+        <v>57</v>
+      </c>
+      <c r="J58" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>12</v>
+      </c>
+      <c r="B59" t="s">
+        <v>75</v>
+      </c>
+      <c r="C59" t="s">
+        <v>76</v>
+      </c>
+      <c r="D59">
+        <v>114</v>
+      </c>
+      <c r="E59" t="s">
+        <v>20</v>
+      </c>
+      <c r="G59" t="s">
+        <v>88</v>
+      </c>
+      <c r="H59">
+        <v>2</v>
+      </c>
+      <c r="I59" t="s">
+        <v>57</v>
+      </c>
+      <c r="J59" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>12</v>
+      </c>
+      <c r="B60" t="s">
+        <v>75</v>
+      </c>
+      <c r="C60" t="s">
+        <v>76</v>
+      </c>
+      <c r="D60">
+        <v>114</v>
+      </c>
+      <c r="E60" t="s">
+        <v>20</v>
+      </c>
+      <c r="G60" t="s">
+        <v>89</v>
+      </c>
+      <c r="H60">
+        <v>2</v>
+      </c>
+      <c r="I60" t="s">
+        <v>57</v>
+      </c>
+      <c r="J60" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>12</v>
+      </c>
+      <c r="B61" t="s">
+        <v>75</v>
+      </c>
+      <c r="C61" t="s">
+        <v>76</v>
+      </c>
+      <c r="D61">
+        <v>114</v>
+      </c>
+      <c r="E61" t="s">
+        <v>20</v>
+      </c>
+      <c r="G61" t="s">
+        <v>90</v>
+      </c>
+      <c r="H61">
+        <v>2</v>
+      </c>
+      <c r="I61" t="s">
+        <v>57</v>
+      </c>
+      <c r="J61" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>12</v>
+      </c>
+      <c r="B62" t="s">
+        <v>75</v>
+      </c>
+      <c r="C62" t="s">
+        <v>76</v>
+      </c>
+      <c r="D62">
+        <v>114</v>
+      </c>
+      <c r="E62" t="s">
+        <v>20</v>
+      </c>
+      <c r="G62" t="s">
+        <v>91</v>
+      </c>
+      <c r="H62">
+        <v>4</v>
+      </c>
+      <c r="I62" t="s">
+        <v>57</v>
+      </c>
+      <c r="J62" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>12</v>
+      </c>
+      <c r="B63" t="s">
+        <v>75</v>
+      </c>
+      <c r="C63" t="s">
+        <v>76</v>
+      </c>
+      <c r="D63">
+        <v>114</v>
+      </c>
+      <c r="E63" t="s">
+        <v>20</v>
+      </c>
+      <c r="G63" t="s">
+        <v>92</v>
+      </c>
+      <c r="H63">
+        <v>2</v>
+      </c>
+      <c r="I63" t="s">
+        <v>57</v>
+      </c>
+      <c r="J63" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>12</v>
+      </c>
+      <c r="B64" t="s">
+        <v>75</v>
+      </c>
+      <c r="C64" t="s">
+        <v>76</v>
+      </c>
+      <c r="D64">
+        <v>114</v>
+      </c>
+      <c r="E64" t="s">
+        <v>20</v>
+      </c>
+      <c r="G64" t="s">
+        <v>93</v>
+      </c>
+      <c r="H64">
+        <v>4</v>
+      </c>
+      <c r="I64" t="s">
+        <v>57</v>
+      </c>
+      <c r="J64" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" t="s">
+        <v>75</v>
+      </c>
+      <c r="C65" t="s">
+        <v>76</v>
+      </c>
+      <c r="D65">
+        <v>114</v>
+      </c>
+      <c r="E65" t="s">
+        <v>20</v>
+      </c>
+      <c r="G65" t="s">
+        <v>94</v>
+      </c>
+      <c r="H65">
+        <v>4</v>
+      </c>
+      <c r="I65" t="s">
+        <v>57</v>
+      </c>
+      <c r="J65" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>12</v>
+      </c>
+      <c r="B66" t="s">
+        <v>75</v>
+      </c>
+      <c r="C66" t="s">
+        <v>76</v>
+      </c>
+      <c r="D66">
+        <v>114</v>
+      </c>
+      <c r="E66" t="s">
+        <v>20</v>
+      </c>
+      <c r="G66" t="s">
+        <v>95</v>
+      </c>
+      <c r="H66">
+        <v>2</v>
+      </c>
+      <c r="I66" t="s">
+        <v>57</v>
+      </c>
+      <c r="J66" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>12</v>
+      </c>
+      <c r="B67" t="s">
+        <v>75</v>
+      </c>
+      <c r="C67" t="s">
+        <v>76</v>
+      </c>
+      <c r="D67">
+        <v>114</v>
+      </c>
+      <c r="E67" t="s">
+        <v>20</v>
+      </c>
+      <c r="G67" t="s">
+        <v>96</v>
+      </c>
+      <c r="H67">
+        <v>2</v>
+      </c>
+      <c r="I67" t="s">
+        <v>57</v>
+      </c>
+      <c r="J67" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>12</v>
+      </c>
+      <c r="B68" t="s">
+        <v>75</v>
+      </c>
+      <c r="C68" t="s">
+        <v>76</v>
+      </c>
+      <c r="D68">
+        <v>114</v>
+      </c>
+      <c r="E68" t="s">
+        <v>20</v>
+      </c>
+      <c r="G68" t="s">
+        <v>97</v>
+      </c>
+      <c r="H68">
+        <v>2</v>
+      </c>
+      <c r="I68" t="s">
+        <v>57</v>
+      </c>
+      <c r="J68" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>12</v>
+      </c>
+      <c r="B69" t="s">
+        <v>75</v>
+      </c>
+      <c r="C69" t="s">
+        <v>76</v>
+      </c>
+      <c r="D69">
+        <v>114</v>
+      </c>
+      <c r="E69" t="s">
+        <v>20</v>
+      </c>
+      <c r="G69" t="s">
+        <v>98</v>
+      </c>
+      <c r="H69">
+        <v>2</v>
+      </c>
+      <c r="I69" t="s">
+        <v>57</v>
+      </c>
+      <c r="J69" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>12</v>
+      </c>
+      <c r="B70" t="s">
+        <v>75</v>
+      </c>
+      <c r="C70" t="s">
+        <v>76</v>
+      </c>
+      <c r="D70">
+        <v>114</v>
+      </c>
+      <c r="E70" t="s">
+        <v>20</v>
+      </c>
+      <c r="G70" t="s">
+        <v>99</v>
+      </c>
+      <c r="H70">
+        <v>2</v>
+      </c>
+      <c r="I70" t="s">
+        <v>57</v>
+      </c>
+      <c r="J70" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>12</v>
+      </c>
+      <c r="B71" t="s">
+        <v>75</v>
+      </c>
+      <c r="C71" t="s">
+        <v>76</v>
+      </c>
+      <c r="D71">
+        <v>114</v>
+      </c>
+      <c r="E71" t="s">
+        <v>20</v>
+      </c>
+      <c r="G71" t="s">
+        <v>100</v>
+      </c>
+      <c r="H71">
+        <v>4</v>
+      </c>
+      <c r="I71" t="s">
+        <v>57</v>
+      </c>
+      <c r="J71" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>12</v>
+      </c>
+      <c r="B72" t="s">
+        <v>75</v>
+      </c>
+      <c r="C72" t="s">
+        <v>76</v>
+      </c>
+      <c r="D72">
+        <v>114</v>
+      </c>
+      <c r="E72" t="s">
+        <v>20</v>
+      </c>
+      <c r="G72" t="s">
+        <v>101</v>
+      </c>
+      <c r="H72">
+        <v>4</v>
+      </c>
+      <c r="I72" t="s">
+        <v>57</v>
+      </c>
+      <c r="J72" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>12</v>
+      </c>
+      <c r="B73" t="s">
+        <v>75</v>
+      </c>
+      <c r="C73" t="s">
+        <v>76</v>
+      </c>
+      <c r="D73">
+        <v>114</v>
+      </c>
+      <c r="E73" t="s">
+        <v>20</v>
+      </c>
+      <c r="G73" t="s">
+        <v>102</v>
+      </c>
+      <c r="H73">
+        <v>2</v>
+      </c>
+      <c r="I73" t="s">
+        <v>57</v>
+      </c>
+      <c r="J73" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>12</v>
+      </c>
+      <c r="B74" t="s">
+        <v>75</v>
+      </c>
+      <c r="C74" t="s">
+        <v>76</v>
+      </c>
+      <c r="D74">
+        <v>114</v>
+      </c>
+      <c r="E74" t="s">
+        <v>20</v>
+      </c>
+      <c r="G74" t="s">
+        <v>103</v>
+      </c>
+      <c r="H74">
+        <v>2</v>
+      </c>
+      <c r="I74" t="s">
+        <v>57</v>
+      </c>
+      <c r="J74" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>12</v>
+      </c>
+      <c r="B75" t="s">
+        <v>75</v>
+      </c>
+      <c r="C75" t="s">
+        <v>76</v>
+      </c>
+      <c r="D75">
+        <v>114</v>
+      </c>
+      <c r="E75" t="s">
+        <v>20</v>
+      </c>
+      <c r="G75" t="s">
+        <v>104</v>
+      </c>
+      <c r="H75">
+        <v>3</v>
+      </c>
+      <c r="I75" t="s">
+        <v>105</v>
+      </c>
+      <c r="J75" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>12</v>
+      </c>
+      <c r="B76" t="s">
+        <v>75</v>
+      </c>
+      <c r="C76" t="s">
+        <v>76</v>
+      </c>
+      <c r="D76">
+        <v>114</v>
+      </c>
+      <c r="E76" t="s">
+        <v>20</v>
+      </c>
+      <c r="G76" t="s">
+        <v>106</v>
+      </c>
+      <c r="H76">
+        <v>3</v>
+      </c>
+      <c r="I76" t="s">
+        <v>105</v>
+      </c>
+      <c r="J76" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>12</v>
+      </c>
+      <c r="B77" t="s">
+        <v>75</v>
+      </c>
+      <c r="C77" t="s">
+        <v>76</v>
+      </c>
+      <c r="D77">
+        <v>114</v>
+      </c>
+      <c r="E77" t="s">
+        <v>20</v>
+      </c>
+      <c r="G77" t="s">
+        <v>107</v>
+      </c>
+      <c r="H77">
+        <v>3</v>
+      </c>
+      <c r="I77" t="s">
+        <v>105</v>
+      </c>
+      <c r="J77" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>12</v>
+      </c>
+      <c r="B78" t="s">
+        <v>75</v>
+      </c>
+      <c r="C78" t="s">
+        <v>76</v>
+      </c>
+      <c r="D78">
+        <v>114</v>
+      </c>
+      <c r="E78" t="s">
+        <v>20</v>
+      </c>
+      <c r="G78" t="s">
+        <v>108</v>
+      </c>
+      <c r="H78">
+        <v>3</v>
+      </c>
+      <c r="I78" t="s">
+        <v>105</v>
+      </c>
+      <c r="J78" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>12</v>
+      </c>
+      <c r="B79" t="s">
+        <v>75</v>
+      </c>
+      <c r="C79" t="s">
+        <v>76</v>
+      </c>
+      <c r="D79">
+        <v>114</v>
+      </c>
+      <c r="E79" t="s">
+        <v>20</v>
+      </c>
+      <c r="G79" t="s">
+        <v>109</v>
+      </c>
+      <c r="H79">
+        <v>3</v>
+      </c>
+      <c r="I79" t="s">
+        <v>105</v>
+      </c>
+      <c r="J79" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>12</v>
+      </c>
+      <c r="B80" t="s">
+        <v>75</v>
+      </c>
+      <c r="C80" t="s">
+        <v>76</v>
+      </c>
+      <c r="D80">
+        <v>114</v>
+      </c>
+      <c r="E80" t="s">
+        <v>20</v>
+      </c>
+      <c r="G80" t="s">
+        <v>110</v>
+      </c>
+      <c r="H80">
+        <v>3</v>
+      </c>
+      <c r="I80" t="s">
+        <v>105</v>
+      </c>
+      <c r="J80" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>12</v>
+      </c>
+      <c r="B81" t="s">
+        <v>75</v>
+      </c>
+      <c r="C81" t="s">
+        <v>76</v>
+      </c>
+      <c r="D81">
+        <v>114</v>
+      </c>
+      <c r="E81" t="s">
+        <v>20</v>
+      </c>
+      <c r="G81" t="s">
+        <v>111</v>
+      </c>
+      <c r="H81">
+        <v>3</v>
+      </c>
+      <c r="I81" t="s">
+        <v>105</v>
+      </c>
+      <c r="J81" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>12</v>
+      </c>
+      <c r="B82" t="s">
+        <v>75</v>
+      </c>
+      <c r="C82" t="s">
+        <v>76</v>
+      </c>
+      <c r="D82">
+        <v>114</v>
+      </c>
+      <c r="E82" t="s">
+        <v>20</v>
+      </c>
+      <c r="G82" t="s">
+        <v>112</v>
+      </c>
+      <c r="H82">
+        <v>3</v>
+      </c>
+      <c r="I82" t="s">
+        <v>105</v>
+      </c>
+      <c r="J82" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>12</v>
+      </c>
+      <c r="B83" t="s">
+        <v>75</v>
+      </c>
+      <c r="C83" t="s">
+        <v>76</v>
+      </c>
+      <c r="D83">
+        <v>114</v>
+      </c>
+      <c r="E83" t="s">
+        <v>20</v>
+      </c>
+      <c r="G83" t="s">
+        <v>113</v>
+      </c>
+      <c r="H83">
+        <v>3</v>
+      </c>
+      <c r="I83" t="s">
+        <v>105</v>
+      </c>
+      <c r="J83" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>12</v>
+      </c>
+      <c r="B84" t="s">
+        <v>75</v>
+      </c>
+      <c r="C84" t="s">
+        <v>76</v>
+      </c>
+      <c r="D84">
+        <v>114</v>
+      </c>
+      <c r="E84" t="s">
+        <v>20</v>
+      </c>
+      <c r="G84" t="s">
+        <v>114</v>
+      </c>
+      <c r="H84">
+        <v>3</v>
+      </c>
+      <c r="I84" t="s">
+        <v>105</v>
+      </c>
+      <c r="J84" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>12</v>
+      </c>
+      <c r="B85" t="s">
+        <v>75</v>
+      </c>
+      <c r="C85" t="s">
+        <v>76</v>
+      </c>
+      <c r="D85">
+        <v>114</v>
+      </c>
+      <c r="E85" t="s">
+        <v>20</v>
+      </c>
+      <c r="G85" t="s">
+        <v>115</v>
+      </c>
+      <c r="H85">
+        <v>3</v>
+      </c>
+      <c r="I85" t="s">
+        <v>105</v>
+      </c>
+      <c r="J85" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>12</v>
+      </c>
+      <c r="B86" t="s">
+        <v>75</v>
+      </c>
+      <c r="C86" t="s">
+        <v>76</v>
+      </c>
+      <c r="D86">
+        <v>114</v>
+      </c>
+      <c r="E86" t="s">
+        <v>20</v>
+      </c>
+      <c r="G86" t="s">
+        <v>116</v>
+      </c>
+      <c r="H86">
+        <v>2</v>
+      </c>
+      <c r="I86" t="s">
+        <v>117</v>
+      </c>
+      <c r="J86" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>12</v>
+      </c>
+      <c r="B87" t="s">
+        <v>75</v>
+      </c>
+      <c r="C87" t="s">
+        <v>76</v>
+      </c>
+      <c r="D87">
+        <v>114</v>
+      </c>
+      <c r="E87" t="s">
+        <v>20</v>
+      </c>
+      <c r="G87" t="s">
+        <v>118</v>
+      </c>
+      <c r="H87">
+        <v>2</v>
+      </c>
+      <c r="I87" t="s">
+        <v>117</v>
+      </c>
+      <c r="J87" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>12</v>
+      </c>
+      <c r="B88" t="s">
+        <v>75</v>
+      </c>
+      <c r="C88" t="s">
+        <v>76</v>
+      </c>
+      <c r="D88">
+        <v>114</v>
+      </c>
+      <c r="E88" t="s">
+        <v>20</v>
+      </c>
+      <c r="G88" t="s">
+        <v>119</v>
+      </c>
+      <c r="H88">
+        <v>2</v>
+      </c>
+      <c r="I88" t="s">
+        <v>117</v>
+      </c>
+      <c r="J88" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>12</v>
+      </c>
+      <c r="B89" t="s">
+        <v>75</v>
+      </c>
+      <c r="C89" t="s">
+        <v>76</v>
+      </c>
+      <c r="D89">
+        <v>114</v>
+      </c>
+      <c r="E89" t="s">
+        <v>20</v>
+      </c>
+      <c r="G89" t="s">
+        <v>120</v>
+      </c>
+      <c r="H89">
+        <v>2</v>
+      </c>
+      <c r="I89" t="s">
+        <v>117</v>
+      </c>
+      <c r="J89" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>12</v>
+      </c>
+      <c r="B90" t="s">
+        <v>75</v>
+      </c>
+      <c r="C90" t="s">
+        <v>76</v>
+      </c>
+      <c r="D90">
+        <v>114</v>
+      </c>
+      <c r="E90" t="s">
+        <v>20</v>
+      </c>
+      <c r="G90" t="s">
+        <v>121</v>
+      </c>
+      <c r="H90">
+        <v>2</v>
+      </c>
+      <c r="I90" t="s">
+        <v>117</v>
+      </c>
+      <c r="J90" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>12</v>
+      </c>
+      <c r="B91" t="s">
+        <v>75</v>
+      </c>
+      <c r="C91" t="s">
+        <v>76</v>
+      </c>
+      <c r="D91">
+        <v>114</v>
+      </c>
+      <c r="E91" t="s">
+        <v>20</v>
+      </c>
+      <c r="G91" t="s">
+        <v>122</v>
+      </c>
+      <c r="H91">
+        <v>2</v>
+      </c>
+      <c r="I91" t="s">
+        <v>117</v>
+      </c>
+      <c r="J91" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E67BA04-2B14-462A-AE57-A607CB882528}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="22.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2">
-        <v>114</v>
-      </c>
-      <c r="D2">
-        <v>8</v>
-      </c>
-      <c r="E2">
-        <v>12</v>
-      </c>
-      <c r="F2">
-        <v>20</v>
-      </c>
-      <c r="G2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/master_data.xlsx
+++ b/master_data.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\000_專案計畫\20260107_學分學程查詢功能\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DB5EB78-01F7-4B2D-BA62-2ACDD2246CFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D58FAC94-0DB1-40A4-9E11-AFF2F90AA187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C32469BD-056E-459F-8F49-ECC8EEE0EE91}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FFE4C370-C0A9-478E-9CE1-7346844BA6EF}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="科目表" sheetId="1" r:id="rId1"/>
+    <sheet name="學程規範總額" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="129">
   <si>
     <t>學院</t>
   </si>
@@ -412,6 +413,27 @@
   </si>
   <si>
     <t>舞蹈治療實務</t>
+  </si>
+  <si>
+    <t>必修總學分</t>
+  </si>
+  <si>
+    <t>選修總學分</t>
+  </si>
+  <si>
+    <t>總計應修學分</t>
+  </si>
+  <si>
+    <t>備註 (模組要求)</t>
+  </si>
+  <si>
+    <t>我來測試一下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>必修核心課程(共十學分) /n 選修課程(至少須修讀十學分) 
+開設課程及開放選修名額以當年度課表為準</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -457,9 +479,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -794,9 +819,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94A09248-8F3E-4F54-B236-07AA808331C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72D8DFEF-04BC-4EC8-AF3C-DEBFBDC1D1D9}">
   <dimension ref="A1:L91"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.875" customWidth="1"/>
+    <col min="12" max="12" width="9.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -3456,4 +3493,92 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20ADBEC6-416B-4F00-8AE1-CD593204EE73}">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="22.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2">
+        <v>114</v>
+      </c>
+      <c r="D2">
+        <v>8</v>
+      </c>
+      <c r="E2">
+        <v>12</v>
+      </c>
+      <c r="F2">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3">
+        <v>114</v>
+      </c>
+      <c r="D3">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>20</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/master_data.xlsx
+++ b/master_data.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\000_專案計畫\20260107_學分學程查詢功能\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D58FAC94-0DB1-40A4-9E11-AFF2F90AA187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EF6255C-9312-46E6-BA93-7541BBC5AF06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FFE4C370-C0A9-478E-9CE1-7346844BA6EF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B70EB7C3-9A6E-4253-8A93-DDDC10397334}"/>
   </bookViews>
   <sheets>
     <sheet name="科目表" sheetId="1" r:id="rId1"/>
     <sheet name="學程規範總額" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">科目表!$A$1:$L$109</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="162">
   <si>
     <t>學院</t>
   </si>
@@ -293,9 +296,6 @@
     <t>知識論</t>
   </si>
   <si>
-    <t>哲學系學生不得列為選修課程。</t>
-  </si>
-  <si>
     <t>倫理學</t>
   </si>
   <si>
@@ -415,6 +415,115 @@
     <t>舞蹈治療實務</t>
   </si>
   <si>
+    <t>跨領域學院</t>
+  </si>
+  <si>
+    <t>K860</t>
+  </si>
+  <si>
+    <t>教育大數據微學程</t>
+  </si>
+  <si>
+    <t>程式設計概論</t>
+  </si>
+  <si>
+    <t>資管系
+經濟系
+金企系
+企管系
+統資系</t>
+  </si>
+  <si>
+    <t>基礎(至少2學分)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>計算機概論</t>
+  </si>
+  <si>
+    <t>程式設計</t>
+  </si>
+  <si>
+    <t>物理系</t>
+  </si>
+  <si>
+    <t>機器學習</t>
+  </si>
+  <si>
+    <t>重點(至少6學分)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>資料探索及資訊視覺化</t>
+  </si>
+  <si>
+    <t>資料庫系統設計</t>
+  </si>
+  <si>
+    <t>專業/進階課程(至少2學分)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI與永續</t>
+  </si>
+  <si>
+    <t>大數據資料分析與應用</t>
+  </si>
+  <si>
+    <t>AI學士後系</t>
+  </si>
+  <si>
+    <t>生成式AI與生活</t>
+  </si>
+  <si>
+    <t>資創學程</t>
+  </si>
+  <si>
+    <t>教育科技發展趨勢</t>
+  </si>
+  <si>
+    <t>領科學程三</t>
+  </si>
+  <si>
+    <t xml:space="preserve">特殊教育與適性教學
+</t>
+  </si>
+  <si>
+    <t>中等教育學程</t>
+  </si>
+  <si>
+    <t>資料庫系統概論</t>
+  </si>
+  <si>
+    <t>資工系</t>
+  </si>
+  <si>
+    <t>資料庫</t>
+  </si>
+  <si>
+    <t>資數系</t>
+  </si>
+  <si>
+    <t>資料庫管理</t>
+  </si>
+  <si>
+    <t>統資系
+資管系</t>
+  </si>
+  <si>
+    <t>統資系</t>
+  </si>
+  <si>
+    <t>會計系</t>
+  </si>
+  <si>
+    <t>教育大數據專題</t>
+  </si>
+  <si>
+    <t>總整課程(至少2學分)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>必修總學分</t>
   </si>
   <si>
@@ -433,6 +542,10 @@
   <si>
     <t>必修核心課程(共十學分) /n 選修課程(至少須修讀十學分) 
 開設課程及開放選修名額以當年度課表為準</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>本微學程應修學分數 12 學分。包括基礎課程(2 學分)、重點課程(6 學分)專業/進階課程(2 學分)、總整課程(2 學分)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -819,8 +932,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72D8DFEF-04BC-4EC8-AF3C-DEBFBDC1D1D9}">
-  <dimension ref="A1:L91"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C00A167-E895-40EC-94CE-4E0040707CC8}">
+  <dimension ref="A1:L108"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
@@ -830,7 +943,7 @@
     <col min="7" max="7" width="25.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.75" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.875" customWidth="1"/>
     <col min="12" max="12" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
@@ -953,6 +1066,9 @@
       <c r="J4" t="s">
         <v>23</v>
       </c>
+      <c r="K4">
+        <v>12</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -982,6 +1098,9 @@
       <c r="J5" t="s">
         <v>23</v>
       </c>
+      <c r="K5">
+        <v>12</v>
+      </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -1011,6 +1130,9 @@
       <c r="J6" t="s">
         <v>23</v>
       </c>
+      <c r="K6">
+        <v>12</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -1040,6 +1162,9 @@
       <c r="J7" t="s">
         <v>23</v>
       </c>
+      <c r="K7">
+        <v>12</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -1069,6 +1194,9 @@
       <c r="J8" t="s">
         <v>23</v>
       </c>
+      <c r="K8">
+        <v>12</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -1098,6 +1226,9 @@
       <c r="J9" t="s">
         <v>23</v>
       </c>
+      <c r="K9">
+        <v>12</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -1127,6 +1258,9 @@
       <c r="J10" t="s">
         <v>23</v>
       </c>
+      <c r="K10">
+        <v>12</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -1156,6 +1290,9 @@
       <c r="J11" t="s">
         <v>23</v>
       </c>
+      <c r="K11">
+        <v>12</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -1185,6 +1322,9 @@
       <c r="J12" t="s">
         <v>23</v>
       </c>
+      <c r="K12">
+        <v>12</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -1214,6 +1354,9 @@
       <c r="J13" t="s">
         <v>23</v>
       </c>
+      <c r="K13">
+        <v>12</v>
+      </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -1243,6 +1386,9 @@
       <c r="J14" t="s">
         <v>23</v>
       </c>
+      <c r="K14">
+        <v>12</v>
+      </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -1272,6 +1418,9 @@
       <c r="J15" t="s">
         <v>23</v>
       </c>
+      <c r="K15">
+        <v>12</v>
+      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -1301,8 +1450,11 @@
       <c r="J16" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -1330,8 +1482,11 @@
       <c r="J17" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -1359,8 +1514,11 @@
       <c r="J18" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K18">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -1388,8 +1546,11 @@
       <c r="J19" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K19">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -1417,8 +1578,11 @@
       <c r="J20" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K20">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -1446,8 +1610,11 @@
       <c r="J21" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K21">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -1475,8 +1642,11 @@
       <c r="J22" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K22">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -1504,8 +1674,11 @@
       <c r="J23" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K23">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -1533,8 +1706,11 @@
       <c r="J24" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K24">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -1562,8 +1738,11 @@
       <c r="J25" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -1591,8 +1770,11 @@
       <c r="J26" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K26">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -1620,8 +1802,11 @@
       <c r="J27" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K27">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -1649,8 +1834,11 @@
       <c r="J28" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K28">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -1678,8 +1866,11 @@
       <c r="J29" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K29">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -1707,8 +1898,11 @@
       <c r="J30" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K30">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -1736,8 +1930,11 @@
       <c r="J31" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K31">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -1765,6 +1962,9 @@
       <c r="J32" t="s">
         <v>23</v>
       </c>
+      <c r="K32">
+        <v>12</v>
+      </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
@@ -1794,6 +1994,9 @@
       <c r="J33" t="s">
         <v>23</v>
       </c>
+      <c r="K33">
+        <v>12</v>
+      </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
@@ -1823,6 +2026,9 @@
       <c r="J34" t="s">
         <v>23</v>
       </c>
+      <c r="K34">
+        <v>12</v>
+      </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
@@ -1852,6 +2058,9 @@
       <c r="J35" t="s">
         <v>23</v>
       </c>
+      <c r="K35">
+        <v>12</v>
+      </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
@@ -1881,6 +2090,9 @@
       <c r="J36" t="s">
         <v>23</v>
       </c>
+      <c r="K36">
+        <v>12</v>
+      </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
@@ -1910,6 +2122,9 @@
       <c r="J37" t="s">
         <v>23</v>
       </c>
+      <c r="K37">
+        <v>12</v>
+      </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
@@ -1939,6 +2154,9 @@
       <c r="J38" t="s">
         <v>23</v>
       </c>
+      <c r="K38">
+        <v>12</v>
+      </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
@@ -1968,6 +2186,9 @@
       <c r="J39" t="s">
         <v>23</v>
       </c>
+      <c r="K39">
+        <v>12</v>
+      </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
@@ -1997,6 +2218,9 @@
       <c r="J40" t="s">
         <v>23</v>
       </c>
+      <c r="K40">
+        <v>12</v>
+      </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
@@ -2026,6 +2250,9 @@
       <c r="J41" t="s">
         <v>23</v>
       </c>
+      <c r="K41">
+        <v>12</v>
+      </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
@@ -2055,6 +2282,9 @@
       <c r="J42" t="s">
         <v>23</v>
       </c>
+      <c r="K42">
+        <v>12</v>
+      </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
@@ -2084,6 +2314,9 @@
       <c r="J43" t="s">
         <v>23</v>
       </c>
+      <c r="K43">
+        <v>12</v>
+      </c>
       <c r="L43" t="s">
         <v>65</v>
       </c>
@@ -2116,6 +2349,9 @@
       <c r="J44" t="s">
         <v>23</v>
       </c>
+      <c r="K44">
+        <v>12</v>
+      </c>
       <c r="L44" t="s">
         <v>65</v>
       </c>
@@ -2148,6 +2384,9 @@
       <c r="J45" t="s">
         <v>23</v>
       </c>
+      <c r="K45">
+        <v>12</v>
+      </c>
       <c r="L45" t="s">
         <v>68</v>
       </c>
@@ -2180,6 +2419,9 @@
       <c r="J46" t="s">
         <v>23</v>
       </c>
+      <c r="K46">
+        <v>12</v>
+      </c>
       <c r="L46" t="s">
         <v>68</v>
       </c>
@@ -2212,6 +2454,9 @@
       <c r="J47" t="s">
         <v>23</v>
       </c>
+      <c r="K47">
+        <v>12</v>
+      </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
@@ -2241,6 +2486,9 @@
       <c r="J48" t="s">
         <v>23</v>
       </c>
+      <c r="K48">
+        <v>12</v>
+      </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
@@ -2270,6 +2518,9 @@
       <c r="J49" t="s">
         <v>23</v>
       </c>
+      <c r="K49">
+        <v>12</v>
+      </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
@@ -2299,6 +2550,9 @@
       <c r="J50" t="s">
         <v>23</v>
       </c>
+      <c r="K50">
+        <v>12</v>
+      </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
@@ -2406,8 +2660,8 @@
       <c r="J54" t="s">
         <v>23</v>
       </c>
-      <c r="K54" t="s">
-        <v>83</v>
+      <c r="K54">
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -2427,7 +2681,7 @@
         <v>20</v>
       </c>
       <c r="G55" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H55">
         <v>4</v>
@@ -2438,8 +2692,8 @@
       <c r="J55" t="s">
         <v>23</v>
       </c>
-      <c r="K55" t="s">
-        <v>83</v>
+      <c r="K55">
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -2459,7 +2713,7 @@
         <v>20</v>
       </c>
       <c r="G56" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H56">
         <v>4</v>
@@ -2470,8 +2724,8 @@
       <c r="J56" t="s">
         <v>23</v>
       </c>
-      <c r="K56" t="s">
-        <v>83</v>
+      <c r="K56">
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -2491,7 +2745,7 @@
         <v>20</v>
       </c>
       <c r="G57" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H57">
         <v>2</v>
@@ -2502,6 +2756,9 @@
       <c r="J57" t="s">
         <v>23</v>
       </c>
+      <c r="K57">
+        <v>10</v>
+      </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
@@ -2520,7 +2777,7 @@
         <v>20</v>
       </c>
       <c r="G58" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H58">
         <v>2</v>
@@ -2531,6 +2788,9 @@
       <c r="J58" t="s">
         <v>23</v>
       </c>
+      <c r="K58">
+        <v>10</v>
+      </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
@@ -2549,7 +2809,7 @@
         <v>20</v>
       </c>
       <c r="G59" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H59">
         <v>2</v>
@@ -2560,6 +2820,9 @@
       <c r="J59" t="s">
         <v>23</v>
       </c>
+      <c r="K59">
+        <v>10</v>
+      </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
@@ -2578,7 +2841,7 @@
         <v>20</v>
       </c>
       <c r="G60" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H60">
         <v>2</v>
@@ -2589,6 +2852,9 @@
       <c r="J60" t="s">
         <v>23</v>
       </c>
+      <c r="K60">
+        <v>10</v>
+      </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
@@ -2607,7 +2873,7 @@
         <v>20</v>
       </c>
       <c r="G61" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H61">
         <v>2</v>
@@ -2618,6 +2884,9 @@
       <c r="J61" t="s">
         <v>23</v>
       </c>
+      <c r="K61">
+        <v>10</v>
+      </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
@@ -2636,7 +2905,7 @@
         <v>20</v>
       </c>
       <c r="G62" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H62">
         <v>4</v>
@@ -2647,6 +2916,9 @@
       <c r="J62" t="s">
         <v>23</v>
       </c>
+      <c r="K62">
+        <v>10</v>
+      </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
@@ -2665,7 +2937,7 @@
         <v>20</v>
       </c>
       <c r="G63" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H63">
         <v>2</v>
@@ -2676,6 +2948,9 @@
       <c r="J63" t="s">
         <v>23</v>
       </c>
+      <c r="K63">
+        <v>10</v>
+      </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
@@ -2694,7 +2969,7 @@
         <v>20</v>
       </c>
       <c r="G64" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H64">
         <v>4</v>
@@ -2705,8 +2980,11 @@
       <c r="J64" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K64">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>12</v>
       </c>
@@ -2723,7 +3001,7 @@
         <v>20</v>
       </c>
       <c r="G65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H65">
         <v>4</v>
@@ -2734,8 +3012,11 @@
       <c r="J65" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K65">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>12</v>
       </c>
@@ -2752,7 +3033,7 @@
         <v>20</v>
       </c>
       <c r="G66" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H66">
         <v>2</v>
@@ -2763,8 +3044,11 @@
       <c r="J66" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K66">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>12</v>
       </c>
@@ -2781,7 +3065,7 @@
         <v>20</v>
       </c>
       <c r="G67" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H67">
         <v>2</v>
@@ -2792,8 +3076,11 @@
       <c r="J67" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K67">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>12</v>
       </c>
@@ -2810,7 +3097,7 @@
         <v>20</v>
       </c>
       <c r="G68" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H68">
         <v>2</v>
@@ -2821,8 +3108,11 @@
       <c r="J68" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K68">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>12</v>
       </c>
@@ -2839,7 +3129,7 @@
         <v>20</v>
       </c>
       <c r="G69" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H69">
         <v>2</v>
@@ -2850,8 +3140,11 @@
       <c r="J69" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K69">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>12</v>
       </c>
@@ -2868,7 +3161,7 @@
         <v>20</v>
       </c>
       <c r="G70" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H70">
         <v>2</v>
@@ -2879,8 +3172,11 @@
       <c r="J70" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K70">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>12</v>
       </c>
@@ -2897,7 +3193,7 @@
         <v>20</v>
       </c>
       <c r="G71" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H71">
         <v>4</v>
@@ -2908,8 +3204,11 @@
       <c r="J71" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K71">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>12</v>
       </c>
@@ -2926,7 +3225,7 @@
         <v>20</v>
       </c>
       <c r="G72" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H72">
         <v>4</v>
@@ -2937,8 +3236,11 @@
       <c r="J72" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K72">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>12</v>
       </c>
@@ -2955,7 +3257,7 @@
         <v>20</v>
       </c>
       <c r="G73" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H73">
         <v>2</v>
@@ -2966,8 +3268,11 @@
       <c r="J73" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K73">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>12</v>
       </c>
@@ -2984,7 +3289,7 @@
         <v>20</v>
       </c>
       <c r="G74" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H74">
         <v>2</v>
@@ -2995,8 +3300,11 @@
       <c r="J74" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K74">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>12</v>
       </c>
@@ -3013,19 +3321,22 @@
         <v>20</v>
       </c>
       <c r="G75" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H75">
         <v>3</v>
       </c>
       <c r="I75" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J75" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K75">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>12</v>
       </c>
@@ -3042,19 +3353,22 @@
         <v>20</v>
       </c>
       <c r="G76" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H76">
         <v>3</v>
       </c>
       <c r="I76" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J76" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K76">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>12</v>
       </c>
@@ -3071,19 +3385,22 @@
         <v>20</v>
       </c>
       <c r="G77" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H77">
         <v>3</v>
       </c>
       <c r="I77" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J77" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K77">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>12</v>
       </c>
@@ -3100,19 +3417,22 @@
         <v>20</v>
       </c>
       <c r="G78" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H78">
         <v>3</v>
       </c>
       <c r="I78" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J78" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K78">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>12</v>
       </c>
@@ -3129,19 +3449,22 @@
         <v>20</v>
       </c>
       <c r="G79" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H79">
         <v>3</v>
       </c>
       <c r="I79" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J79" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K79">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>12</v>
       </c>
@@ -3158,19 +3481,22 @@
         <v>20</v>
       </c>
       <c r="G80" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H80">
         <v>3</v>
       </c>
       <c r="I80" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J80" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K80">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>12</v>
       </c>
@@ -3187,19 +3513,22 @@
         <v>20</v>
       </c>
       <c r="G81" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H81">
         <v>3</v>
       </c>
       <c r="I81" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J81" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K81">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>12</v>
       </c>
@@ -3216,19 +3545,22 @@
         <v>20</v>
       </c>
       <c r="G82" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H82">
         <v>3</v>
       </c>
       <c r="I82" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J82" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K82">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>12</v>
       </c>
@@ -3245,19 +3577,22 @@
         <v>20</v>
       </c>
       <c r="G83" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H83">
         <v>3</v>
       </c>
       <c r="I83" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J83" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K83">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>12</v>
       </c>
@@ -3274,19 +3609,22 @@
         <v>20</v>
       </c>
       <c r="G84" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H84">
         <v>3</v>
       </c>
       <c r="I84" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J84" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K84">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>12</v>
       </c>
@@ -3303,19 +3641,22 @@
         <v>20</v>
       </c>
       <c r="G85" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H85">
         <v>3</v>
       </c>
       <c r="I85" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J85" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>12</v>
       </c>
@@ -3332,19 +3673,22 @@
         <v>20</v>
       </c>
       <c r="G86" t="s">
+        <v>115</v>
+      </c>
+      <c r="H86">
+        <v>2</v>
+      </c>
+      <c r="I86" t="s">
         <v>116</v>
       </c>
-      <c r="H86">
-        <v>2</v>
-      </c>
-      <c r="I86" t="s">
-        <v>117</v>
-      </c>
       <c r="J86" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K86">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>12</v>
       </c>
@@ -3361,19 +3705,22 @@
         <v>20</v>
       </c>
       <c r="G87" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H87">
         <v>2</v>
       </c>
       <c r="I87" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J87" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K87">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>12</v>
       </c>
@@ -3390,19 +3737,22 @@
         <v>20</v>
       </c>
       <c r="G88" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H88">
         <v>2</v>
       </c>
       <c r="I88" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J88" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K88">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>12</v>
       </c>
@@ -3419,19 +3769,22 @@
         <v>20</v>
       </c>
       <c r="G89" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H89">
         <v>2</v>
       </c>
       <c r="I89" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J89" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K89">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>12</v>
       </c>
@@ -3448,19 +3801,22 @@
         <v>20</v>
       </c>
       <c r="G90" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H90">
         <v>2</v>
       </c>
       <c r="I90" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J90" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K90">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>12</v>
       </c>
@@ -3477,16 +3833,557 @@
         <v>20</v>
       </c>
       <c r="G91" t="s">
+        <v>121</v>
+      </c>
+      <c r="H91">
+        <v>2</v>
+      </c>
+      <c r="I91" t="s">
+        <v>116</v>
+      </c>
+      <c r="J91" t="s">
+        <v>23</v>
+      </c>
+      <c r="K91">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>122</v>
       </c>
-      <c r="H91">
-        <v>2</v>
-      </c>
-      <c r="I91" t="s">
-        <v>117</v>
-      </c>
-      <c r="J91" t="s">
-        <v>23</v>
+      <c r="B92" t="s">
+        <v>123</v>
+      </c>
+      <c r="C92" t="s">
+        <v>124</v>
+      </c>
+      <c r="D92">
+        <v>114</v>
+      </c>
+      <c r="E92" t="s">
+        <v>20</v>
+      </c>
+      <c r="G92" t="s">
+        <v>125</v>
+      </c>
+      <c r="H92">
+        <v>3</v>
+      </c>
+      <c r="I92" t="s">
+        <v>126</v>
+      </c>
+      <c r="J92" t="s">
+        <v>127</v>
+      </c>
+      <c r="K92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>122</v>
+      </c>
+      <c r="B93" t="s">
+        <v>123</v>
+      </c>
+      <c r="C93" t="s">
+        <v>124</v>
+      </c>
+      <c r="D93">
+        <v>114</v>
+      </c>
+      <c r="E93" t="s">
+        <v>20</v>
+      </c>
+      <c r="G93" t="s">
+        <v>128</v>
+      </c>
+      <c r="H93">
+        <v>6</v>
+      </c>
+      <c r="I93" t="s">
+        <v>17</v>
+      </c>
+      <c r="J93" t="s">
+        <v>127</v>
+      </c>
+      <c r="K93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>122</v>
+      </c>
+      <c r="B94" t="s">
+        <v>123</v>
+      </c>
+      <c r="C94" t="s">
+        <v>124</v>
+      </c>
+      <c r="D94">
+        <v>114</v>
+      </c>
+      <c r="E94" t="s">
+        <v>20</v>
+      </c>
+      <c r="G94" t="s">
+        <v>129</v>
+      </c>
+      <c r="H94">
+        <v>6</v>
+      </c>
+      <c r="I94" t="s">
+        <v>130</v>
+      </c>
+      <c r="J94" t="s">
+        <v>127</v>
+      </c>
+      <c r="K94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>122</v>
+      </c>
+      <c r="B95" t="s">
+        <v>123</v>
+      </c>
+      <c r="C95" t="s">
+        <v>124</v>
+      </c>
+      <c r="D95">
+        <v>114</v>
+      </c>
+      <c r="E95" t="s">
+        <v>77</v>
+      </c>
+      <c r="G95" t="s">
+        <v>131</v>
+      </c>
+      <c r="H95">
+        <v>3</v>
+      </c>
+      <c r="I95" t="s">
+        <v>122</v>
+      </c>
+      <c r="J95" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>122</v>
+      </c>
+      <c r="B96" t="s">
+        <v>123</v>
+      </c>
+      <c r="C96" t="s">
+        <v>124</v>
+      </c>
+      <c r="D96">
+        <v>114</v>
+      </c>
+      <c r="E96" t="s">
+        <v>77</v>
+      </c>
+      <c r="G96" t="s">
+        <v>133</v>
+      </c>
+      <c r="H96">
+        <v>3</v>
+      </c>
+      <c r="I96" t="s">
+        <v>122</v>
+      </c>
+      <c r="J96" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>122</v>
+      </c>
+      <c r="B97" t="s">
+        <v>123</v>
+      </c>
+      <c r="C97" t="s">
+        <v>124</v>
+      </c>
+      <c r="D97">
+        <v>114</v>
+      </c>
+      <c r="E97" t="s">
+        <v>20</v>
+      </c>
+      <c r="G97" t="s">
+        <v>134</v>
+      </c>
+      <c r="H97">
+        <v>2</v>
+      </c>
+      <c r="I97" t="s">
+        <v>122</v>
+      </c>
+      <c r="J97" t="s">
+        <v>135</v>
+      </c>
+      <c r="K97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>122</v>
+      </c>
+      <c r="B98" t="s">
+        <v>123</v>
+      </c>
+      <c r="C98" t="s">
+        <v>124</v>
+      </c>
+      <c r="D98">
+        <v>114</v>
+      </c>
+      <c r="E98" t="s">
+        <v>20</v>
+      </c>
+      <c r="G98" t="s">
+        <v>136</v>
+      </c>
+      <c r="H98">
+        <v>2</v>
+      </c>
+      <c r="I98" t="s">
+        <v>122</v>
+      </c>
+      <c r="J98" t="s">
+        <v>135</v>
+      </c>
+      <c r="K98">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>122</v>
+      </c>
+      <c r="B99" t="s">
+        <v>123</v>
+      </c>
+      <c r="C99" t="s">
+        <v>124</v>
+      </c>
+      <c r="D99">
+        <v>114</v>
+      </c>
+      <c r="E99" t="s">
+        <v>20</v>
+      </c>
+      <c r="G99" t="s">
+        <v>137</v>
+      </c>
+      <c r="H99">
+        <v>3</v>
+      </c>
+      <c r="I99" t="s">
+        <v>138</v>
+      </c>
+      <c r="J99" t="s">
+        <v>135</v>
+      </c>
+      <c r="K99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>122</v>
+      </c>
+      <c r="B100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C100" t="s">
+        <v>124</v>
+      </c>
+      <c r="D100">
+        <v>114</v>
+      </c>
+      <c r="E100" t="s">
+        <v>20</v>
+      </c>
+      <c r="G100" t="s">
+        <v>139</v>
+      </c>
+      <c r="H100">
+        <v>2</v>
+      </c>
+      <c r="I100" t="s">
+        <v>140</v>
+      </c>
+      <c r="J100" t="s">
+        <v>135</v>
+      </c>
+      <c r="K100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>122</v>
+      </c>
+      <c r="B101" t="s">
+        <v>123</v>
+      </c>
+      <c r="C101" t="s">
+        <v>124</v>
+      </c>
+      <c r="D101">
+        <v>114</v>
+      </c>
+      <c r="E101" t="s">
+        <v>20</v>
+      </c>
+      <c r="G101" t="s">
+        <v>141</v>
+      </c>
+      <c r="H101">
+        <v>2</v>
+      </c>
+      <c r="I101" t="s">
+        <v>142</v>
+      </c>
+      <c r="J101" t="s">
+        <v>135</v>
+      </c>
+      <c r="K101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>122</v>
+      </c>
+      <c r="B102" t="s">
+        <v>123</v>
+      </c>
+      <c r="C102" t="s">
+        <v>124</v>
+      </c>
+      <c r="D102">
+        <v>114</v>
+      </c>
+      <c r="E102" t="s">
+        <v>20</v>
+      </c>
+      <c r="G102" t="s">
+        <v>143</v>
+      </c>
+      <c r="H102">
+        <v>3</v>
+      </c>
+      <c r="I102" t="s">
+        <v>144</v>
+      </c>
+      <c r="J102" t="s">
+        <v>135</v>
+      </c>
+      <c r="K102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>122</v>
+      </c>
+      <c r="B103" t="s">
+        <v>123</v>
+      </c>
+      <c r="C103" t="s">
+        <v>124</v>
+      </c>
+      <c r="D103">
+        <v>114</v>
+      </c>
+      <c r="E103" t="s">
+        <v>20</v>
+      </c>
+      <c r="G103" t="s">
+        <v>145</v>
+      </c>
+      <c r="H103">
+        <v>3</v>
+      </c>
+      <c r="I103" t="s">
+        <v>146</v>
+      </c>
+      <c r="J103" t="s">
+        <v>135</v>
+      </c>
+      <c r="K103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>122</v>
+      </c>
+      <c r="B104" t="s">
+        <v>123</v>
+      </c>
+      <c r="C104" t="s">
+        <v>124</v>
+      </c>
+      <c r="D104">
+        <v>114</v>
+      </c>
+      <c r="E104" t="s">
+        <v>20</v>
+      </c>
+      <c r="G104" t="s">
+        <v>147</v>
+      </c>
+      <c r="H104">
+        <v>3</v>
+      </c>
+      <c r="I104" t="s">
+        <v>148</v>
+      </c>
+      <c r="J104" t="s">
+        <v>135</v>
+      </c>
+      <c r="K104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>122</v>
+      </c>
+      <c r="B105" t="s">
+        <v>123</v>
+      </c>
+      <c r="C105" t="s">
+        <v>124</v>
+      </c>
+      <c r="D105">
+        <v>114</v>
+      </c>
+      <c r="E105" t="s">
+        <v>20</v>
+      </c>
+      <c r="G105" t="s">
+        <v>149</v>
+      </c>
+      <c r="H105">
+        <v>3</v>
+      </c>
+      <c r="I105" t="s">
+        <v>150</v>
+      </c>
+      <c r="J105" t="s">
+        <v>135</v>
+      </c>
+      <c r="K105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>122</v>
+      </c>
+      <c r="B106" t="s">
+        <v>123</v>
+      </c>
+      <c r="C106" t="s">
+        <v>124</v>
+      </c>
+      <c r="D106">
+        <v>114</v>
+      </c>
+      <c r="E106" t="s">
+        <v>20</v>
+      </c>
+      <c r="G106" t="s">
+        <v>149</v>
+      </c>
+      <c r="H106">
+        <v>3</v>
+      </c>
+      <c r="I106" t="s">
+        <v>151</v>
+      </c>
+      <c r="J106" t="s">
+        <v>135</v>
+      </c>
+      <c r="K106">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>122</v>
+      </c>
+      <c r="B107" t="s">
+        <v>123</v>
+      </c>
+      <c r="C107" t="s">
+        <v>124</v>
+      </c>
+      <c r="D107">
+        <v>114</v>
+      </c>
+      <c r="E107" t="s">
+        <v>20</v>
+      </c>
+      <c r="G107" t="s">
+        <v>149</v>
+      </c>
+      <c r="H107">
+        <v>3</v>
+      </c>
+      <c r="I107" t="s">
+        <v>152</v>
+      </c>
+      <c r="J107" t="s">
+        <v>135</v>
+      </c>
+      <c r="K107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>122</v>
+      </c>
+      <c r="B108" t="s">
+        <v>123</v>
+      </c>
+      <c r="C108" t="s">
+        <v>124</v>
+      </c>
+      <c r="D108">
+        <v>114</v>
+      </c>
+      <c r="E108" t="s">
+        <v>20</v>
+      </c>
+      <c r="G108" t="s">
+        <v>153</v>
+      </c>
+      <c r="H108">
+        <v>3</v>
+      </c>
+      <c r="I108" t="s">
+        <v>122</v>
+      </c>
+      <c r="J108" t="s">
+        <v>154</v>
+      </c>
+      <c r="K108">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3496,8 +4393,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20ADBEC6-416B-4F00-8AE1-CD593204EE73}">
-  <dimension ref="A1:G3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F00DE9E-18A2-47AD-8A9D-EC1159415896}">
+  <dimension ref="A1:K108"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22.75" bestFit="1" customWidth="1"/>
@@ -3505,6 +4402,7 @@
     <col min="4" max="5" width="11.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -3518,16 +4416,16 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="E1" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="F1" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="G1" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -3550,7 +4448,7 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>127</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="66" x14ac:dyDescent="0.25">
@@ -3573,7 +4471,523 @@
         <v>20</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4">
+        <v>114</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+      <c r="F4">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>122</v>
+      </c>
+      <c r="B92" t="s">
+        <v>123</v>
+      </c>
+      <c r="C92" t="s">
+        <v>124</v>
+      </c>
+      <c r="D92">
+        <v>114</v>
+      </c>
+      <c r="G92" t="s">
+        <v>125</v>
+      </c>
+      <c r="H92">
+        <v>3</v>
+      </c>
+      <c r="I92" t="s">
+        <v>126</v>
+      </c>
+      <c r="J92" t="s">
+        <v>127</v>
+      </c>
+      <c r="K92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>122</v>
+      </c>
+      <c r="B93" t="s">
+        <v>123</v>
+      </c>
+      <c r="C93" t="s">
+        <v>124</v>
+      </c>
+      <c r="D93">
+        <v>114</v>
+      </c>
+      <c r="G93" t="s">
         <v>128</v>
+      </c>
+      <c r="H93">
+        <v>6</v>
+      </c>
+      <c r="I93" t="s">
+        <v>17</v>
+      </c>
+      <c r="J93" t="s">
+        <v>127</v>
+      </c>
+      <c r="K93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>122</v>
+      </c>
+      <c r="B94" t="s">
+        <v>123</v>
+      </c>
+      <c r="C94" t="s">
+        <v>124</v>
+      </c>
+      <c r="D94">
+        <v>114</v>
+      </c>
+      <c r="G94" t="s">
+        <v>129</v>
+      </c>
+      <c r="H94">
+        <v>6</v>
+      </c>
+      <c r="I94" t="s">
+        <v>130</v>
+      </c>
+      <c r="J94" t="s">
+        <v>127</v>
+      </c>
+      <c r="K94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>122</v>
+      </c>
+      <c r="B95" t="s">
+        <v>123</v>
+      </c>
+      <c r="C95" t="s">
+        <v>124</v>
+      </c>
+      <c r="D95">
+        <v>114</v>
+      </c>
+      <c r="E95" t="s">
+        <v>77</v>
+      </c>
+      <c r="G95" t="s">
+        <v>131</v>
+      </c>
+      <c r="H95">
+        <v>3</v>
+      </c>
+      <c r="I95" t="s">
+        <v>122</v>
+      </c>
+      <c r="J95" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>122</v>
+      </c>
+      <c r="B96" t="s">
+        <v>123</v>
+      </c>
+      <c r="C96" t="s">
+        <v>124</v>
+      </c>
+      <c r="D96">
+        <v>114</v>
+      </c>
+      <c r="E96" t="s">
+        <v>77</v>
+      </c>
+      <c r="G96" t="s">
+        <v>133</v>
+      </c>
+      <c r="H96">
+        <v>3</v>
+      </c>
+      <c r="I96" t="s">
+        <v>122</v>
+      </c>
+      <c r="J96" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>122</v>
+      </c>
+      <c r="B97" t="s">
+        <v>123</v>
+      </c>
+      <c r="C97" t="s">
+        <v>124</v>
+      </c>
+      <c r="D97">
+        <v>114</v>
+      </c>
+      <c r="G97" t="s">
+        <v>134</v>
+      </c>
+      <c r="H97">
+        <v>2</v>
+      </c>
+      <c r="I97" t="s">
+        <v>122</v>
+      </c>
+      <c r="J97" t="s">
+        <v>135</v>
+      </c>
+      <c r="K97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>122</v>
+      </c>
+      <c r="B98" t="s">
+        <v>123</v>
+      </c>
+      <c r="C98" t="s">
+        <v>124</v>
+      </c>
+      <c r="D98">
+        <v>114</v>
+      </c>
+      <c r="G98" t="s">
+        <v>136</v>
+      </c>
+      <c r="H98">
+        <v>2</v>
+      </c>
+      <c r="I98" t="s">
+        <v>122</v>
+      </c>
+      <c r="J98" t="s">
+        <v>135</v>
+      </c>
+      <c r="K98">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>122</v>
+      </c>
+      <c r="B99" t="s">
+        <v>123</v>
+      </c>
+      <c r="C99" t="s">
+        <v>124</v>
+      </c>
+      <c r="D99">
+        <v>114</v>
+      </c>
+      <c r="G99" t="s">
+        <v>137</v>
+      </c>
+      <c r="H99">
+        <v>3</v>
+      </c>
+      <c r="I99" t="s">
+        <v>138</v>
+      </c>
+      <c r="J99" t="s">
+        <v>135</v>
+      </c>
+      <c r="K99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>122</v>
+      </c>
+      <c r="B100" t="s">
+        <v>123</v>
+      </c>
+      <c r="C100" t="s">
+        <v>124</v>
+      </c>
+      <c r="D100">
+        <v>114</v>
+      </c>
+      <c r="G100" t="s">
+        <v>139</v>
+      </c>
+      <c r="H100">
+        <v>2</v>
+      </c>
+      <c r="I100" t="s">
+        <v>140</v>
+      </c>
+      <c r="J100" t="s">
+        <v>135</v>
+      </c>
+      <c r="K100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>122</v>
+      </c>
+      <c r="B101" t="s">
+        <v>123</v>
+      </c>
+      <c r="C101" t="s">
+        <v>124</v>
+      </c>
+      <c r="D101">
+        <v>114</v>
+      </c>
+      <c r="G101" t="s">
+        <v>141</v>
+      </c>
+      <c r="H101">
+        <v>2</v>
+      </c>
+      <c r="I101" t="s">
+        <v>142</v>
+      </c>
+      <c r="J101" t="s">
+        <v>135</v>
+      </c>
+      <c r="K101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>122</v>
+      </c>
+      <c r="B102" t="s">
+        <v>123</v>
+      </c>
+      <c r="C102" t="s">
+        <v>124</v>
+      </c>
+      <c r="D102">
+        <v>114</v>
+      </c>
+      <c r="G102" t="s">
+        <v>143</v>
+      </c>
+      <c r="H102">
+        <v>3</v>
+      </c>
+      <c r="I102" t="s">
+        <v>144</v>
+      </c>
+      <c r="J102" t="s">
+        <v>135</v>
+      </c>
+      <c r="K102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>122</v>
+      </c>
+      <c r="B103" t="s">
+        <v>123</v>
+      </c>
+      <c r="C103" t="s">
+        <v>124</v>
+      </c>
+      <c r="D103">
+        <v>114</v>
+      </c>
+      <c r="G103" t="s">
+        <v>145</v>
+      </c>
+      <c r="H103">
+        <v>3</v>
+      </c>
+      <c r="I103" t="s">
+        <v>146</v>
+      </c>
+      <c r="J103" t="s">
+        <v>135</v>
+      </c>
+      <c r="K103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>122</v>
+      </c>
+      <c r="B104" t="s">
+        <v>123</v>
+      </c>
+      <c r="C104" t="s">
+        <v>124</v>
+      </c>
+      <c r="D104">
+        <v>114</v>
+      </c>
+      <c r="G104" t="s">
+        <v>147</v>
+      </c>
+      <c r="H104">
+        <v>3</v>
+      </c>
+      <c r="I104" t="s">
+        <v>148</v>
+      </c>
+      <c r="J104" t="s">
+        <v>135</v>
+      </c>
+      <c r="K104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>122</v>
+      </c>
+      <c r="B105" t="s">
+        <v>123</v>
+      </c>
+      <c r="C105" t="s">
+        <v>124</v>
+      </c>
+      <c r="D105">
+        <v>114</v>
+      </c>
+      <c r="G105" t="s">
+        <v>149</v>
+      </c>
+      <c r="H105">
+        <v>3</v>
+      </c>
+      <c r="I105" t="s">
+        <v>150</v>
+      </c>
+      <c r="J105" t="s">
+        <v>135</v>
+      </c>
+      <c r="K105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>122</v>
+      </c>
+      <c r="B106" t="s">
+        <v>123</v>
+      </c>
+      <c r="C106" t="s">
+        <v>124</v>
+      </c>
+      <c r="D106">
+        <v>114</v>
+      </c>
+      <c r="G106" t="s">
+        <v>149</v>
+      </c>
+      <c r="H106">
+        <v>3</v>
+      </c>
+      <c r="I106" t="s">
+        <v>151</v>
+      </c>
+      <c r="J106" t="s">
+        <v>135</v>
+      </c>
+      <c r="K106">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>122</v>
+      </c>
+      <c r="B107" t="s">
+        <v>123</v>
+      </c>
+      <c r="C107" t="s">
+        <v>124</v>
+      </c>
+      <c r="D107">
+        <v>114</v>
+      </c>
+      <c r="G107" t="s">
+        <v>149</v>
+      </c>
+      <c r="H107">
+        <v>3</v>
+      </c>
+      <c r="I107" t="s">
+        <v>152</v>
+      </c>
+      <c r="J107" t="s">
+        <v>135</v>
+      </c>
+      <c r="K107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>122</v>
+      </c>
+      <c r="B108" t="s">
+        <v>123</v>
+      </c>
+      <c r="C108" t="s">
+        <v>124</v>
+      </c>
+      <c r="D108">
+        <v>114</v>
+      </c>
+      <c r="G108" t="s">
+        <v>153</v>
+      </c>
+      <c r="H108">
+        <v>3</v>
+      </c>
+      <c r="I108" t="s">
+        <v>122</v>
+      </c>
+      <c r="J108" t="s">
+        <v>154</v>
+      </c>
+      <c r="K108">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/master_data.xlsx
+++ b/master_data.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\000_專案計畫\20260107_學分學程查詢功能\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EF6255C-9312-46E6-BA93-7541BBC5AF06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7866313E-F0F3-4E40-8AC2-26BD6A1A607A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B70EB7C3-9A6E-4253-8A93-DDDC10397334}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D4E4C608-F7C5-457E-9559-0A0A39C60FDD}"/>
   </bookViews>
   <sheets>
     <sheet name="科目表" sheetId="1" r:id="rId1"/>
     <sheet name="學程規範總額" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">科目表!$A$1:$L$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">科目表!$A$1:$M$107</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="160">
   <si>
     <t>學院</t>
   </si>
@@ -60,6 +60,10 @@
     <t>科目類別</t>
   </si>
   <si>
+    <t>模組名稱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>課程代碼</t>
   </si>
   <si>
@@ -112,10 +116,6 @@
   </si>
   <si>
     <t>圖資系碩士班</t>
-  </si>
-  <si>
-    <t>選修模組</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>古籍整理與利用</t>
@@ -424,20 +424,17 @@
     <t>教育大數據微學程</t>
   </si>
   <si>
-    <t>程式設計概論</t>
-  </si>
-  <si>
-    <t>資管系
-經濟系
-金企系
-企管系
-統資系</t>
-  </si>
-  <si>
     <t>基礎(至少2學分)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>程式設計概論</t>
+  </si>
+  <si>
+    <t>經濟系、資管系、金企系、企管系、統資系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>計算機概論</t>
   </si>
   <si>
@@ -445,25 +442,25 @@
   </si>
   <si>
     <t>物理系</t>
-  </si>
-  <si>
-    <t>機器學習</t>
   </si>
   <si>
     <t>重點(至少6學分)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>機器學習</t>
+  </si>
+  <si>
     <t>資料探索及資訊視覺化</t>
-  </si>
-  <si>
-    <t>資料庫系統設計</t>
   </si>
   <si>
     <t>專業/進階課程(至少2學分)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>資料庫系統設計</t>
+  </si>
+  <si>
     <t>AI與永續</t>
   </si>
   <si>
@@ -505,23 +502,18 @@
   </si>
   <si>
     <t>資料庫管理</t>
-  </si>
-  <si>
-    <t>統資系
-資管系</t>
-  </si>
-  <si>
-    <t>統資系</t>
-  </si>
-  <si>
-    <t>會計系</t>
-  </si>
-  <si>
-    <t>教育大數據專題</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>會計系、資管系、統資系</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>總整課程(至少2學分)</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教育大數據專題</t>
   </si>
   <si>
     <t>必修總學分</t>
@@ -932,23 +924,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C00A167-E895-40EC-94CE-4E0040707CC8}">
-  <dimension ref="A1:L108"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAD85608-43B1-478F-B47D-E9EA75A115A0}">
+  <dimension ref="A1:M106"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.875" customWidth="1"/>
-    <col min="12" max="12" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.75" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.875" customWidth="1"/>
+    <col min="13" max="13" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -985,1578 +979,1446 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>114</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
         <v>16</v>
       </c>
-      <c r="H2">
-        <v>4</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="H2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3">
         <v>114</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="I3">
+        <v>4</v>
+      </c>
+      <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>114</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" t="s">
         <v>22</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
       </c>
       <c r="J4" t="s">
         <v>23</v>
       </c>
-      <c r="K4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>114</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" t="s">
         <v>24</v>
       </c>
-      <c r="H5">
-        <v>2</v>
-      </c>
-      <c r="I5" t="s">
-        <v>22</v>
+      <c r="I5">
+        <v>2</v>
       </c>
       <c r="J5" t="s">
         <v>23</v>
       </c>
-      <c r="K5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>114</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" t="s">
         <v>25</v>
       </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6" t="s">
-        <v>22</v>
+      <c r="I6">
+        <v>2</v>
       </c>
       <c r="J6" t="s">
         <v>23</v>
       </c>
-      <c r="K6">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D7">
         <v>114</v>
       </c>
       <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8">
+        <v>114</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8" t="s">
+        <v>18</v>
+      </c>
+      <c r="L8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9">
+        <v>114</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9">
+        <v>4</v>
+      </c>
+      <c r="J9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10">
+        <v>114</v>
+      </c>
+      <c r="E10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10">
+        <v>4</v>
+      </c>
+      <c r="J10" t="s">
+        <v>18</v>
+      </c>
+      <c r="L10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11">
+        <v>114</v>
+      </c>
+      <c r="E11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11">
+        <v>4</v>
+      </c>
+      <c r="J11" t="s">
+        <v>18</v>
+      </c>
+      <c r="L11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12">
+        <v>114</v>
+      </c>
+      <c r="E12" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I12">
+        <v>4</v>
+      </c>
+      <c r="J12" t="s">
+        <v>18</v>
+      </c>
+      <c r="L12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13">
+        <v>114</v>
+      </c>
+      <c r="E13" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13">
+        <v>4</v>
+      </c>
+      <c r="J13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14">
+        <v>114</v>
+      </c>
+      <c r="E14" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14">
+        <v>4</v>
+      </c>
+      <c r="J14" t="s">
+        <v>18</v>
+      </c>
+      <c r="L14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15">
+        <v>114</v>
+      </c>
+      <c r="E15" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" t="s">
+        <v>34</v>
+      </c>
+      <c r="I15">
+        <v>4</v>
+      </c>
+      <c r="J15" t="s">
+        <v>18</v>
+      </c>
+      <c r="L15">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16">
+        <v>114</v>
+      </c>
+      <c r="E16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16">
+        <v>4</v>
+      </c>
+      <c r="J16" t="s">
+        <v>18</v>
+      </c>
+      <c r="L16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>15</v>
+      </c>
+      <c r="D17">
+        <v>114</v>
+      </c>
+      <c r="E17" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" t="s">
+        <v>36</v>
+      </c>
+      <c r="I17">
+        <v>4</v>
+      </c>
+      <c r="J17" t="s">
+        <v>18</v>
+      </c>
+      <c r="L17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18">
+        <v>114</v>
+      </c>
+      <c r="E18" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18">
+        <v>2</v>
+      </c>
+      <c r="J18" t="s">
+        <v>18</v>
+      </c>
+      <c r="L18">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19">
+        <v>114</v>
+      </c>
+      <c r="E19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" t="s">
+        <v>38</v>
+      </c>
+      <c r="I19">
+        <v>4</v>
+      </c>
+      <c r="J19" t="s">
         <v>20</v>
       </c>
-      <c r="G7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="I7" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" t="s">
-        <v>23</v>
-      </c>
-      <c r="K7">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8">
-        <v>114</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="L19">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20">
+        <v>114</v>
+      </c>
+      <c r="E20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" t="s">
+        <v>39</v>
+      </c>
+      <c r="I20">
+        <v>4</v>
+      </c>
+      <c r="J20" t="s">
         <v>20</v>
       </c>
-      <c r="G8" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8">
-        <v>2</v>
-      </c>
-      <c r="I8" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9">
-        <v>114</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="L20">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21">
+        <v>114</v>
+      </c>
+      <c r="E21" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" t="s">
+        <v>40</v>
+      </c>
+      <c r="I21">
+        <v>4</v>
+      </c>
+      <c r="J21" t="s">
         <v>20</v>
       </c>
-      <c r="G9" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9">
-        <v>4</v>
-      </c>
-      <c r="I9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10">
-        <v>114</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="L21">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22">
+        <v>114</v>
+      </c>
+      <c r="E22" t="s">
+        <v>21</v>
+      </c>
+      <c r="H22" t="s">
+        <v>41</v>
+      </c>
+      <c r="I22">
+        <v>4</v>
+      </c>
+      <c r="J22" t="s">
         <v>20</v>
       </c>
-      <c r="G10" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10">
-        <v>4</v>
-      </c>
-      <c r="I10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" t="s">
-        <v>23</v>
-      </c>
-      <c r="K10">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11">
-        <v>114</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="L22">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23">
+        <v>114</v>
+      </c>
+      <c r="E23" t="s">
+        <v>21</v>
+      </c>
+      <c r="H23" t="s">
+        <v>42</v>
+      </c>
+      <c r="I23">
+        <v>4</v>
+      </c>
+      <c r="J23" t="s">
         <v>20</v>
       </c>
-      <c r="G11" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11">
-        <v>4</v>
-      </c>
-      <c r="I11" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" t="s">
-        <v>23</v>
-      </c>
-      <c r="K11">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12">
-        <v>114</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="L23">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24">
+        <v>114</v>
+      </c>
+      <c r="E24" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" t="s">
+        <v>43</v>
+      </c>
+      <c r="I24">
+        <v>4</v>
+      </c>
+      <c r="J24" t="s">
         <v>20</v>
       </c>
-      <c r="G12" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12">
-        <v>4</v>
-      </c>
-      <c r="I12" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" t="s">
-        <v>23</v>
-      </c>
-      <c r="K12">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D13">
-        <v>114</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="L24">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>13</v>
+      </c>
+      <c r="B25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25">
+        <v>114</v>
+      </c>
+      <c r="E25" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" t="s">
+        <v>44</v>
+      </c>
+      <c r="I25">
+        <v>4</v>
+      </c>
+      <c r="J25" t="s">
         <v>20</v>
       </c>
-      <c r="G13" t="s">
-        <v>32</v>
-      </c>
-      <c r="H13">
-        <v>4</v>
-      </c>
-      <c r="I13" t="s">
-        <v>17</v>
-      </c>
-      <c r="J13" t="s">
-        <v>23</v>
-      </c>
-      <c r="K13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D14">
-        <v>114</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="L25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" t="s">
+        <v>15</v>
+      </c>
+      <c r="D26">
+        <v>114</v>
+      </c>
+      <c r="E26" t="s">
+        <v>21</v>
+      </c>
+      <c r="H26" t="s">
+        <v>45</v>
+      </c>
+      <c r="I26">
+        <v>4</v>
+      </c>
+      <c r="J26" t="s">
         <v>20</v>
       </c>
-      <c r="G14" t="s">
-        <v>33</v>
-      </c>
-      <c r="H14">
-        <v>4</v>
-      </c>
-      <c r="I14" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" t="s">
-        <v>23</v>
-      </c>
-      <c r="K14">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15">
-        <v>114</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="L26">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27">
+        <v>114</v>
+      </c>
+      <c r="E27" t="s">
+        <v>21</v>
+      </c>
+      <c r="H27" t="s">
+        <v>46</v>
+      </c>
+      <c r="I27">
+        <v>4</v>
+      </c>
+      <c r="J27" t="s">
         <v>20</v>
       </c>
-      <c r="G15" t="s">
-        <v>34</v>
-      </c>
-      <c r="H15">
-        <v>4</v>
-      </c>
-      <c r="I15" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" t="s">
-        <v>23</v>
-      </c>
-      <c r="K15">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16">
-        <v>114</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="L27">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28">
+        <v>114</v>
+      </c>
+      <c r="E28" t="s">
+        <v>21</v>
+      </c>
+      <c r="H28" t="s">
+        <v>47</v>
+      </c>
+      <c r="I28">
+        <v>4</v>
+      </c>
+      <c r="J28" t="s">
         <v>20</v>
       </c>
-      <c r="G16" t="s">
-        <v>35</v>
-      </c>
-      <c r="H16">
-        <v>4</v>
-      </c>
-      <c r="I16" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" t="s">
-        <v>23</v>
-      </c>
-      <c r="K16">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17">
-        <v>114</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="L28">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29">
+        <v>114</v>
+      </c>
+      <c r="E29" t="s">
+        <v>21</v>
+      </c>
+      <c r="H29" t="s">
+        <v>48</v>
+      </c>
+      <c r="I29">
+        <v>4</v>
+      </c>
+      <c r="J29" t="s">
         <v>20</v>
       </c>
-      <c r="G17" t="s">
-        <v>36</v>
-      </c>
-      <c r="H17">
-        <v>4</v>
-      </c>
-      <c r="I17" t="s">
-        <v>17</v>
-      </c>
-      <c r="J17" t="s">
-        <v>23</v>
-      </c>
-      <c r="K17">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" t="s">
-        <v>14</v>
-      </c>
-      <c r="D18">
-        <v>114</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="L29">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30">
+        <v>114</v>
+      </c>
+      <c r="E30" t="s">
+        <v>21</v>
+      </c>
+      <c r="H30" t="s">
+        <v>49</v>
+      </c>
+      <c r="I30">
+        <v>4</v>
+      </c>
+      <c r="J30" t="s">
         <v>20</v>
       </c>
-      <c r="G18" t="s">
-        <v>37</v>
-      </c>
-      <c r="H18">
-        <v>2</v>
-      </c>
-      <c r="I18" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" t="s">
-        <v>23</v>
-      </c>
-      <c r="K18">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D19">
-        <v>114</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="L30">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31">
+        <v>114</v>
+      </c>
+      <c r="E31" t="s">
+        <v>21</v>
+      </c>
+      <c r="H31" t="s">
+        <v>50</v>
+      </c>
+      <c r="I31">
+        <v>4</v>
+      </c>
+      <c r="J31" t="s">
         <v>20</v>
       </c>
-      <c r="G19" t="s">
-        <v>38</v>
-      </c>
-      <c r="H19">
-        <v>4</v>
-      </c>
-      <c r="I19" t="s">
-        <v>19</v>
-      </c>
-      <c r="J19" t="s">
-        <v>23</v>
-      </c>
-      <c r="K19">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>12</v>
-      </c>
-      <c r="B20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20">
-        <v>114</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="L31">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32">
+        <v>114</v>
+      </c>
+      <c r="E32" t="s">
+        <v>21</v>
+      </c>
+      <c r="H32" t="s">
+        <v>51</v>
+      </c>
+      <c r="I32">
+        <v>4</v>
+      </c>
+      <c r="J32" t="s">
         <v>20</v>
       </c>
-      <c r="G20" t="s">
-        <v>39</v>
-      </c>
-      <c r="H20">
-        <v>4</v>
-      </c>
-      <c r="I20" t="s">
-        <v>19</v>
-      </c>
-      <c r="J20" t="s">
-        <v>23</v>
-      </c>
-      <c r="K20">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21">
-        <v>114</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="L32">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33">
+        <v>114</v>
+      </c>
+      <c r="E33" t="s">
+        <v>21</v>
+      </c>
+      <c r="H33" t="s">
+        <v>52</v>
+      </c>
+      <c r="I33">
+        <v>6</v>
+      </c>
+      <c r="J33" t="s">
         <v>20</v>
       </c>
-      <c r="G21" t="s">
-        <v>40</v>
-      </c>
-      <c r="H21">
-        <v>4</v>
-      </c>
-      <c r="I21" t="s">
-        <v>19</v>
-      </c>
-      <c r="J21" t="s">
-        <v>23</v>
-      </c>
-      <c r="K21">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22">
-        <v>114</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="L33">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34">
+        <v>114</v>
+      </c>
+      <c r="E34" t="s">
+        <v>21</v>
+      </c>
+      <c r="H34" t="s">
+        <v>53</v>
+      </c>
+      <c r="I34">
+        <v>4</v>
+      </c>
+      <c r="J34" t="s">
         <v>20</v>
       </c>
-      <c r="G22" t="s">
-        <v>41</v>
-      </c>
-      <c r="H22">
-        <v>4</v>
-      </c>
-      <c r="I22" t="s">
-        <v>19</v>
-      </c>
-      <c r="J22" t="s">
-        <v>23</v>
-      </c>
-      <c r="K22">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23">
-        <v>114</v>
-      </c>
-      <c r="E23" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" t="s">
-        <v>42</v>
-      </c>
-      <c r="H23">
-        <v>4</v>
-      </c>
-      <c r="I23" t="s">
-        <v>19</v>
-      </c>
-      <c r="J23" t="s">
-        <v>23</v>
-      </c>
-      <c r="K23">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24">
-        <v>114</v>
-      </c>
-      <c r="E24" t="s">
-        <v>20</v>
-      </c>
-      <c r="G24" t="s">
-        <v>43</v>
-      </c>
-      <c r="H24">
-        <v>4</v>
-      </c>
-      <c r="I24" t="s">
-        <v>19</v>
-      </c>
-      <c r="J24" t="s">
-        <v>23</v>
-      </c>
-      <c r="K24">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D25">
-        <v>114</v>
-      </c>
-      <c r="E25" t="s">
-        <v>20</v>
-      </c>
-      <c r="G25" t="s">
-        <v>44</v>
-      </c>
-      <c r="H25">
-        <v>4</v>
-      </c>
-      <c r="I25" t="s">
-        <v>19</v>
-      </c>
-      <c r="J25" t="s">
-        <v>23</v>
-      </c>
-      <c r="K25">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>12</v>
-      </c>
-      <c r="B26" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" t="s">
-        <v>14</v>
-      </c>
-      <c r="D26">
-        <v>114</v>
-      </c>
-      <c r="E26" t="s">
-        <v>20</v>
-      </c>
-      <c r="G26" t="s">
-        <v>45</v>
-      </c>
-      <c r="H26">
-        <v>4</v>
-      </c>
-      <c r="I26" t="s">
-        <v>19</v>
-      </c>
-      <c r="J26" t="s">
-        <v>23</v>
-      </c>
-      <c r="K26">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>12</v>
-      </c>
-      <c r="B27" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27">
-        <v>114</v>
-      </c>
-      <c r="E27" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" t="s">
-        <v>46</v>
-      </c>
-      <c r="H27">
-        <v>4</v>
-      </c>
-      <c r="I27" t="s">
-        <v>19</v>
-      </c>
-      <c r="J27" t="s">
-        <v>23</v>
-      </c>
-      <c r="K27">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" t="s">
-        <v>13</v>
-      </c>
-      <c r="C28" t="s">
-        <v>14</v>
-      </c>
-      <c r="D28">
-        <v>114</v>
-      </c>
-      <c r="E28" t="s">
-        <v>20</v>
-      </c>
-      <c r="G28" t="s">
-        <v>47</v>
-      </c>
-      <c r="H28">
-        <v>4</v>
-      </c>
-      <c r="I28" t="s">
-        <v>19</v>
-      </c>
-      <c r="J28" t="s">
-        <v>23</v>
-      </c>
-      <c r="K28">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" t="s">
-        <v>14</v>
-      </c>
-      <c r="D29">
-        <v>114</v>
-      </c>
-      <c r="E29" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" t="s">
-        <v>48</v>
-      </c>
-      <c r="H29">
-        <v>4</v>
-      </c>
-      <c r="I29" t="s">
-        <v>19</v>
-      </c>
-      <c r="J29" t="s">
-        <v>23</v>
-      </c>
-      <c r="K29">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>12</v>
-      </c>
-      <c r="B30" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" t="s">
-        <v>14</v>
-      </c>
-      <c r="D30">
-        <v>114</v>
-      </c>
-      <c r="E30" t="s">
-        <v>20</v>
-      </c>
-      <c r="G30" t="s">
-        <v>49</v>
-      </c>
-      <c r="H30">
-        <v>4</v>
-      </c>
-      <c r="I30" t="s">
-        <v>19</v>
-      </c>
-      <c r="J30" t="s">
-        <v>23</v>
-      </c>
-      <c r="K30">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" t="s">
-        <v>13</v>
-      </c>
-      <c r="C31" t="s">
-        <v>14</v>
-      </c>
-      <c r="D31">
-        <v>114</v>
-      </c>
-      <c r="E31" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" t="s">
-        <v>50</v>
-      </c>
-      <c r="H31">
-        <v>4</v>
-      </c>
-      <c r="I31" t="s">
-        <v>19</v>
-      </c>
-      <c r="J31" t="s">
-        <v>23</v>
-      </c>
-      <c r="K31">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" t="s">
-        <v>13</v>
-      </c>
-      <c r="C32" t="s">
-        <v>14</v>
-      </c>
-      <c r="D32">
-        <v>114</v>
-      </c>
-      <c r="E32" t="s">
-        <v>20</v>
-      </c>
-      <c r="G32" t="s">
-        <v>51</v>
-      </c>
-      <c r="H32">
-        <v>4</v>
-      </c>
-      <c r="I32" t="s">
-        <v>19</v>
-      </c>
-      <c r="J32" t="s">
-        <v>23</v>
-      </c>
-      <c r="K32">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>12</v>
-      </c>
-      <c r="B33" t="s">
-        <v>13</v>
-      </c>
-      <c r="C33" t="s">
-        <v>14</v>
-      </c>
-      <c r="D33">
-        <v>114</v>
-      </c>
-      <c r="E33" t="s">
-        <v>20</v>
-      </c>
-      <c r="G33" t="s">
-        <v>52</v>
-      </c>
-      <c r="H33">
-        <v>6</v>
-      </c>
-      <c r="I33" t="s">
-        <v>19</v>
-      </c>
-      <c r="J33" t="s">
-        <v>23</v>
-      </c>
-      <c r="K33">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>12</v>
-      </c>
-      <c r="B34" t="s">
-        <v>13</v>
-      </c>
-      <c r="C34" t="s">
-        <v>14</v>
-      </c>
-      <c r="D34">
-        <v>114</v>
-      </c>
-      <c r="E34" t="s">
-        <v>20</v>
-      </c>
-      <c r="G34" t="s">
-        <v>53</v>
-      </c>
-      <c r="H34">
-        <v>4</v>
-      </c>
-      <c r="I34" t="s">
-        <v>19</v>
-      </c>
-      <c r="J34" t="s">
-        <v>23</v>
-      </c>
-      <c r="K34">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L34">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D35">
         <v>114</v>
       </c>
       <c r="E35" t="s">
-        <v>20</v>
-      </c>
-      <c r="G35" t="s">
+        <v>21</v>
+      </c>
+      <c r="H35" t="s">
         <v>54</v>
       </c>
-      <c r="H35">
-        <v>4</v>
-      </c>
-      <c r="I35" t="s">
+      <c r="I35">
+        <v>4</v>
+      </c>
+      <c r="J35" t="s">
         <v>55</v>
       </c>
-      <c r="J35" t="s">
-        <v>23</v>
-      </c>
-      <c r="K35">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D36">
         <v>114</v>
       </c>
       <c r="E36" t="s">
-        <v>20</v>
-      </c>
-      <c r="G36" t="s">
+        <v>21</v>
+      </c>
+      <c r="H36" t="s">
         <v>56</v>
       </c>
-      <c r="H36">
-        <v>4</v>
-      </c>
-      <c r="I36" t="s">
+      <c r="I36">
+        <v>4</v>
+      </c>
+      <c r="J36" t="s">
         <v>57</v>
       </c>
-      <c r="J36" t="s">
-        <v>23</v>
-      </c>
-      <c r="K36">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L36">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C37" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D37">
         <v>114</v>
       </c>
       <c r="E37" t="s">
-        <v>20</v>
-      </c>
-      <c r="G37" t="s">
+        <v>21</v>
+      </c>
+      <c r="H37" t="s">
         <v>58</v>
       </c>
-      <c r="H37">
-        <v>4</v>
-      </c>
-      <c r="I37" t="s">
+      <c r="I37">
+        <v>4</v>
+      </c>
+      <c r="J37" t="s">
         <v>57</v>
       </c>
-      <c r="J37" t="s">
-        <v>23</v>
-      </c>
-      <c r="K37">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L37">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C38" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D38">
         <v>114</v>
       </c>
       <c r="E38" t="s">
-        <v>20</v>
-      </c>
-      <c r="G38" t="s">
+        <v>21</v>
+      </c>
+      <c r="H38" t="s">
         <v>59</v>
       </c>
-      <c r="H38">
-        <v>4</v>
-      </c>
-      <c r="I38" t="s">
+      <c r="I38">
+        <v>4</v>
+      </c>
+      <c r="J38" t="s">
         <v>57</v>
       </c>
-      <c r="J38" t="s">
-        <v>23</v>
-      </c>
-      <c r="K38">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L38">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C39" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D39">
         <v>114</v>
       </c>
       <c r="E39" t="s">
-        <v>20</v>
-      </c>
-      <c r="G39" t="s">
+        <v>21</v>
+      </c>
+      <c r="H39" t="s">
         <v>60</v>
       </c>
-      <c r="H39">
-        <v>4</v>
-      </c>
-      <c r="I39" t="s">
+      <c r="I39">
+        <v>4</v>
+      </c>
+      <c r="J39" t="s">
         <v>57</v>
       </c>
-      <c r="J39" t="s">
-        <v>23</v>
-      </c>
-      <c r="K39">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L39">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B40" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C40" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D40">
         <v>114</v>
       </c>
       <c r="E40" t="s">
-        <v>20</v>
-      </c>
-      <c r="G40" t="s">
+        <v>21</v>
+      </c>
+      <c r="H40" t="s">
         <v>61</v>
       </c>
-      <c r="H40">
-        <v>4</v>
-      </c>
-      <c r="I40" t="s">
+      <c r="I40">
+        <v>4</v>
+      </c>
+      <c r="J40" t="s">
         <v>57</v>
       </c>
-      <c r="J40" t="s">
-        <v>23</v>
-      </c>
-      <c r="K40">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L40">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C41" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D41">
         <v>114</v>
       </c>
       <c r="E41" t="s">
-        <v>20</v>
-      </c>
-      <c r="G41" t="s">
+        <v>21</v>
+      </c>
+      <c r="H41" t="s">
         <v>62</v>
       </c>
-      <c r="H41">
-        <v>4</v>
-      </c>
-      <c r="I41" t="s">
+      <c r="I41">
+        <v>4</v>
+      </c>
+      <c r="J41" t="s">
         <v>57</v>
       </c>
-      <c r="J41" t="s">
-        <v>23</v>
-      </c>
-      <c r="K41">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L41">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D42">
         <v>114</v>
       </c>
       <c r="E42" t="s">
-        <v>20</v>
-      </c>
-      <c r="G42" t="s">
+        <v>21</v>
+      </c>
+      <c r="H42" t="s">
         <v>63</v>
       </c>
-      <c r="H42">
-        <v>4</v>
-      </c>
-      <c r="I42" t="s">
+      <c r="I42">
+        <v>4</v>
+      </c>
+      <c r="J42" t="s">
         <v>57</v>
       </c>
-      <c r="J42" t="s">
-        <v>23</v>
-      </c>
-      <c r="K42">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L42">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B43" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C43" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D43">
         <v>114</v>
       </c>
       <c r="E43" t="s">
-        <v>20</v>
-      </c>
-      <c r="G43" t="s">
+        <v>21</v>
+      </c>
+      <c r="H43" t="s">
         <v>64</v>
       </c>
-      <c r="H43">
-        <v>4</v>
-      </c>
-      <c r="I43" t="s">
+      <c r="I43">
+        <v>4</v>
+      </c>
+      <c r="J43" t="s">
         <v>57</v>
       </c>
-      <c r="J43" t="s">
-        <v>23</v>
-      </c>
-      <c r="K43">
-        <v>12</v>
-      </c>
-      <c r="L43" t="s">
+      <c r="L43">
+        <v>12</v>
+      </c>
+      <c r="M43" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C44" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D44">
         <v>114</v>
       </c>
       <c r="E44" t="s">
-        <v>20</v>
-      </c>
-      <c r="G44" t="s">
+        <v>21</v>
+      </c>
+      <c r="H44" t="s">
         <v>66</v>
       </c>
-      <c r="H44">
-        <v>4</v>
-      </c>
-      <c r="I44" t="s">
+      <c r="I44">
+        <v>4</v>
+      </c>
+      <c r="J44" t="s">
         <v>57</v>
       </c>
-      <c r="J44" t="s">
-        <v>23</v>
-      </c>
-      <c r="K44">
-        <v>12</v>
-      </c>
-      <c r="L44" t="s">
+      <c r="L44">
+        <v>12</v>
+      </c>
+      <c r="M44" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C45" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D45">
         <v>114</v>
       </c>
       <c r="E45" t="s">
-        <v>20</v>
-      </c>
-      <c r="G45" t="s">
+        <v>21</v>
+      </c>
+      <c r="H45" t="s">
         <v>67</v>
       </c>
-      <c r="H45">
-        <v>4</v>
-      </c>
-      <c r="I45" t="s">
+      <c r="I45">
+        <v>4</v>
+      </c>
+      <c r="J45" t="s">
         <v>57</v>
       </c>
-      <c r="J45" t="s">
-        <v>23</v>
-      </c>
-      <c r="K45">
-        <v>12</v>
-      </c>
-      <c r="L45" t="s">
+      <c r="L45">
+        <v>12</v>
+      </c>
+      <c r="M45" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C46" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D46">
         <v>114</v>
       </c>
       <c r="E46" t="s">
-        <v>20</v>
-      </c>
-      <c r="G46" t="s">
+        <v>21</v>
+      </c>
+      <c r="H46" t="s">
         <v>69</v>
       </c>
-      <c r="H46">
-        <v>4</v>
-      </c>
-      <c r="I46" t="s">
+      <c r="I46">
+        <v>4</v>
+      </c>
+      <c r="J46" t="s">
         <v>57</v>
       </c>
-      <c r="J46" t="s">
-        <v>23</v>
-      </c>
-      <c r="K46">
-        <v>12</v>
-      </c>
-      <c r="L46" t="s">
+      <c r="L46">
+        <v>12</v>
+      </c>
+      <c r="M46" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B47" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C47" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D47">
         <v>114</v>
       </c>
       <c r="E47" t="s">
-        <v>20</v>
-      </c>
-      <c r="G47" t="s">
+        <v>21</v>
+      </c>
+      <c r="H47" t="s">
         <v>70</v>
       </c>
-      <c r="H47">
-        <v>2</v>
-      </c>
-      <c r="I47" t="s">
+      <c r="I47">
+        <v>2</v>
+      </c>
+      <c r="J47" t="s">
         <v>71</v>
       </c>
-      <c r="J47" t="s">
-        <v>23</v>
-      </c>
-      <c r="K47">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L47">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C48" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D48">
         <v>114</v>
       </c>
       <c r="E48" t="s">
-        <v>20</v>
-      </c>
-      <c r="G48" t="s">
+        <v>21</v>
+      </c>
+      <c r="H48" t="s">
         <v>72</v>
       </c>
-      <c r="H48">
-        <v>2</v>
-      </c>
-      <c r="I48" t="s">
+      <c r="I48">
+        <v>2</v>
+      </c>
+      <c r="J48" t="s">
         <v>71</v>
       </c>
-      <c r="J48" t="s">
-        <v>23</v>
-      </c>
-      <c r="K48">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L48">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C49" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D49">
         <v>114</v>
       </c>
       <c r="E49" t="s">
-        <v>20</v>
-      </c>
-      <c r="G49" t="s">
+        <v>21</v>
+      </c>
+      <c r="H49" t="s">
         <v>73</v>
       </c>
-      <c r="H49">
-        <v>2</v>
-      </c>
-      <c r="I49" t="s">
+      <c r="I49">
+        <v>2</v>
+      </c>
+      <c r="J49" t="s">
         <v>71</v>
       </c>
-      <c r="J49" t="s">
-        <v>23</v>
-      </c>
-      <c r="K49">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L49">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D50">
         <v>114</v>
       </c>
       <c r="E50" t="s">
-        <v>20</v>
-      </c>
-      <c r="G50" t="s">
+        <v>21</v>
+      </c>
+      <c r="H50" t="s">
         <v>74</v>
       </c>
-      <c r="H50">
-        <v>4</v>
-      </c>
-      <c r="I50" t="s">
+      <c r="I50">
+        <v>4</v>
+      </c>
+      <c r="J50" t="s">
         <v>71</v>
       </c>
-      <c r="J50" t="s">
-        <v>23</v>
-      </c>
-      <c r="K50">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L50">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B51" t="s">
         <v>75</v>
@@ -2570,19 +2432,22 @@
       <c r="E51" t="s">
         <v>77</v>
       </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
         <v>78</v>
       </c>
-      <c r="H51">
-        <v>4</v>
-      </c>
-      <c r="I51" t="s">
+      <c r="I51">
+        <v>4</v>
+      </c>
+      <c r="J51" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L51">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B52" t="s">
         <v>75</v>
@@ -2596,19 +2461,22 @@
       <c r="E52" t="s">
         <v>77</v>
       </c>
-      <c r="G52" t="s">
+      <c r="H52" t="s">
         <v>79</v>
       </c>
-      <c r="H52">
-        <v>4</v>
-      </c>
-      <c r="I52" t="s">
+      <c r="I52">
+        <v>4</v>
+      </c>
+      <c r="J52" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L52">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B53" t="s">
         <v>75</v>
@@ -2622,19 +2490,22 @@
       <c r="E53" t="s">
         <v>77</v>
       </c>
-      <c r="G53" t="s">
+      <c r="H53" t="s">
         <v>80</v>
       </c>
-      <c r="H53">
-        <v>2</v>
-      </c>
-      <c r="I53" t="s">
+      <c r="I53">
+        <v>2</v>
+      </c>
+      <c r="J53" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L53">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B54" t="s">
         <v>75</v>
@@ -2646,27 +2517,24 @@
         <v>114</v>
       </c>
       <c r="E54" t="s">
-        <v>20</v>
-      </c>
-      <c r="G54" t="s">
+        <v>21</v>
+      </c>
+      <c r="H54" t="s">
         <v>82</v>
       </c>
-      <c r="H54">
-        <v>4</v>
-      </c>
-      <c r="I54" t="s">
+      <c r="I54">
+        <v>4</v>
+      </c>
+      <c r="J54" t="s">
         <v>57</v>
       </c>
-      <c r="J54" t="s">
-        <v>23</v>
-      </c>
-      <c r="K54">
+      <c r="L54">
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B55" t="s">
         <v>75</v>
@@ -2678,27 +2546,24 @@
         <v>114</v>
       </c>
       <c r="E55" t="s">
-        <v>20</v>
-      </c>
-      <c r="G55" t="s">
+        <v>21</v>
+      </c>
+      <c r="H55" t="s">
         <v>83</v>
       </c>
-      <c r="H55">
-        <v>4</v>
-      </c>
-      <c r="I55" t="s">
+      <c r="I55">
+        <v>4</v>
+      </c>
+      <c r="J55" t="s">
         <v>57</v>
       </c>
-      <c r="J55" t="s">
-        <v>23</v>
-      </c>
-      <c r="K55">
+      <c r="L55">
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B56" t="s">
         <v>75</v>
@@ -2710,27 +2575,24 @@
         <v>114</v>
       </c>
       <c r="E56" t="s">
-        <v>20</v>
-      </c>
-      <c r="G56" t="s">
+        <v>21</v>
+      </c>
+      <c r="H56" t="s">
         <v>84</v>
       </c>
-      <c r="H56">
-        <v>4</v>
-      </c>
-      <c r="I56" t="s">
+      <c r="I56">
+        <v>4</v>
+      </c>
+      <c r="J56" t="s">
         <v>57</v>
       </c>
-      <c r="J56" t="s">
-        <v>23</v>
-      </c>
-      <c r="K56">
+      <c r="L56">
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B57" t="s">
         <v>75</v>
@@ -2742,27 +2604,24 @@
         <v>114</v>
       </c>
       <c r="E57" t="s">
-        <v>20</v>
-      </c>
-      <c r="G57" t="s">
+        <v>21</v>
+      </c>
+      <c r="H57" t="s">
         <v>85</v>
       </c>
-      <c r="H57">
-        <v>2</v>
-      </c>
-      <c r="I57" t="s">
+      <c r="I57">
+        <v>2</v>
+      </c>
+      <c r="J57" t="s">
         <v>57</v>
       </c>
-      <c r="J57" t="s">
-        <v>23</v>
-      </c>
-      <c r="K57">
+      <c r="L57">
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B58" t="s">
         <v>75</v>
@@ -2774,27 +2633,24 @@
         <v>114</v>
       </c>
       <c r="E58" t="s">
-        <v>20</v>
-      </c>
-      <c r="G58" t="s">
+        <v>21</v>
+      </c>
+      <c r="H58" t="s">
         <v>86</v>
       </c>
-      <c r="H58">
-        <v>2</v>
-      </c>
-      <c r="I58" t="s">
+      <c r="I58">
+        <v>2</v>
+      </c>
+      <c r="J58" t="s">
         <v>57</v>
       </c>
-      <c r="J58" t="s">
-        <v>23</v>
-      </c>
-      <c r="K58">
+      <c r="L58">
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B59" t="s">
         <v>75</v>
@@ -2806,27 +2662,24 @@
         <v>114</v>
       </c>
       <c r="E59" t="s">
-        <v>20</v>
-      </c>
-      <c r="G59" t="s">
+        <v>21</v>
+      </c>
+      <c r="H59" t="s">
         <v>87</v>
       </c>
-      <c r="H59">
-        <v>2</v>
-      </c>
-      <c r="I59" t="s">
+      <c r="I59">
+        <v>2</v>
+      </c>
+      <c r="J59" t="s">
         <v>57</v>
       </c>
-      <c r="J59" t="s">
-        <v>23</v>
-      </c>
-      <c r="K59">
+      <c r="L59">
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B60" t="s">
         <v>75</v>
@@ -2838,27 +2691,24 @@
         <v>114</v>
       </c>
       <c r="E60" t="s">
-        <v>20</v>
-      </c>
-      <c r="G60" t="s">
+        <v>21</v>
+      </c>
+      <c r="H60" t="s">
         <v>88</v>
       </c>
-      <c r="H60">
-        <v>2</v>
-      </c>
-      <c r="I60" t="s">
+      <c r="I60">
+        <v>2</v>
+      </c>
+      <c r="J60" t="s">
         <v>57</v>
       </c>
-      <c r="J60" t="s">
-        <v>23</v>
-      </c>
-      <c r="K60">
+      <c r="L60">
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B61" t="s">
         <v>75</v>
@@ -2870,27 +2720,24 @@
         <v>114</v>
       </c>
       <c r="E61" t="s">
-        <v>20</v>
-      </c>
-      <c r="G61" t="s">
+        <v>21</v>
+      </c>
+      <c r="H61" t="s">
         <v>89</v>
       </c>
-      <c r="H61">
-        <v>2</v>
-      </c>
-      <c r="I61" t="s">
+      <c r="I61">
+        <v>2</v>
+      </c>
+      <c r="J61" t="s">
         <v>57</v>
       </c>
-      <c r="J61" t="s">
-        <v>23</v>
-      </c>
-      <c r="K61">
+      <c r="L61">
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B62" t="s">
         <v>75</v>
@@ -2902,27 +2749,24 @@
         <v>114</v>
       </c>
       <c r="E62" t="s">
-        <v>20</v>
-      </c>
-      <c r="G62" t="s">
+        <v>21</v>
+      </c>
+      <c r="H62" t="s">
         <v>90</v>
       </c>
-      <c r="H62">
-        <v>4</v>
-      </c>
-      <c r="I62" t="s">
+      <c r="I62">
+        <v>4</v>
+      </c>
+      <c r="J62" t="s">
         <v>57</v>
       </c>
-      <c r="J62" t="s">
-        <v>23</v>
-      </c>
-      <c r="K62">
+      <c r="L62">
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B63" t="s">
         <v>75</v>
@@ -2934,27 +2778,24 @@
         <v>114</v>
       </c>
       <c r="E63" t="s">
-        <v>20</v>
-      </c>
-      <c r="G63" t="s">
+        <v>21</v>
+      </c>
+      <c r="H63" t="s">
         <v>91</v>
       </c>
-      <c r="H63">
-        <v>2</v>
-      </c>
-      <c r="I63" t="s">
+      <c r="I63">
+        <v>2</v>
+      </c>
+      <c r="J63" t="s">
         <v>57</v>
       </c>
-      <c r="J63" t="s">
-        <v>23</v>
-      </c>
-      <c r="K63">
+      <c r="L63">
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B64" t="s">
         <v>75</v>
@@ -2966,27 +2807,24 @@
         <v>114</v>
       </c>
       <c r="E64" t="s">
-        <v>20</v>
-      </c>
-      <c r="G64" t="s">
+        <v>21</v>
+      </c>
+      <c r="H64" t="s">
         <v>92</v>
       </c>
-      <c r="H64">
-        <v>4</v>
-      </c>
-      <c r="I64" t="s">
+      <c r="I64">
+        <v>4</v>
+      </c>
+      <c r="J64" t="s">
         <v>57</v>
       </c>
-      <c r="J64" t="s">
-        <v>23</v>
-      </c>
-      <c r="K64">
+      <c r="L64">
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B65" t="s">
         <v>75</v>
@@ -2998,27 +2836,24 @@
         <v>114</v>
       </c>
       <c r="E65" t="s">
-        <v>20</v>
-      </c>
-      <c r="G65" t="s">
+        <v>21</v>
+      </c>
+      <c r="H65" t="s">
         <v>93</v>
       </c>
-      <c r="H65">
-        <v>4</v>
-      </c>
-      <c r="I65" t="s">
+      <c r="I65">
+        <v>4</v>
+      </c>
+      <c r="J65" t="s">
         <v>57</v>
       </c>
-      <c r="J65" t="s">
-        <v>23</v>
-      </c>
-      <c r="K65">
+      <c r="L65">
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B66" t="s">
         <v>75</v>
@@ -3030,27 +2865,24 @@
         <v>114</v>
       </c>
       <c r="E66" t="s">
-        <v>20</v>
-      </c>
-      <c r="G66" t="s">
+        <v>21</v>
+      </c>
+      <c r="H66" t="s">
         <v>94</v>
       </c>
-      <c r="H66">
-        <v>2</v>
-      </c>
-      <c r="I66" t="s">
+      <c r="I66">
+        <v>2</v>
+      </c>
+      <c r="J66" t="s">
         <v>57</v>
       </c>
-      <c r="J66" t="s">
-        <v>23</v>
-      </c>
-      <c r="K66">
+      <c r="L66">
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B67" t="s">
         <v>75</v>
@@ -3062,27 +2894,24 @@
         <v>114</v>
       </c>
       <c r="E67" t="s">
-        <v>20</v>
-      </c>
-      <c r="G67" t="s">
+        <v>21</v>
+      </c>
+      <c r="H67" t="s">
         <v>95</v>
       </c>
-      <c r="H67">
-        <v>2</v>
-      </c>
-      <c r="I67" t="s">
+      <c r="I67">
+        <v>2</v>
+      </c>
+      <c r="J67" t="s">
         <v>57</v>
       </c>
-      <c r="J67" t="s">
-        <v>23</v>
-      </c>
-      <c r="K67">
+      <c r="L67">
         <v>10</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B68" t="s">
         <v>75</v>
@@ -3094,27 +2923,24 @@
         <v>114</v>
       </c>
       <c r="E68" t="s">
-        <v>20</v>
-      </c>
-      <c r="G68" t="s">
+        <v>21</v>
+      </c>
+      <c r="H68" t="s">
         <v>96</v>
       </c>
-      <c r="H68">
-        <v>2</v>
-      </c>
-      <c r="I68" t="s">
+      <c r="I68">
+        <v>2</v>
+      </c>
+      <c r="J68" t="s">
         <v>57</v>
       </c>
-      <c r="J68" t="s">
-        <v>23</v>
-      </c>
-      <c r="K68">
+      <c r="L68">
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B69" t="s">
         <v>75</v>
@@ -3126,27 +2952,24 @@
         <v>114</v>
       </c>
       <c r="E69" t="s">
-        <v>20</v>
-      </c>
-      <c r="G69" t="s">
+        <v>21</v>
+      </c>
+      <c r="H69" t="s">
         <v>97</v>
       </c>
-      <c r="H69">
-        <v>2</v>
-      </c>
-      <c r="I69" t="s">
+      <c r="I69">
+        <v>2</v>
+      </c>
+      <c r="J69" t="s">
         <v>57</v>
       </c>
-      <c r="J69" t="s">
-        <v>23</v>
-      </c>
-      <c r="K69">
+      <c r="L69">
         <v>10</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B70" t="s">
         <v>75</v>
@@ -3158,27 +2981,24 @@
         <v>114</v>
       </c>
       <c r="E70" t="s">
-        <v>20</v>
-      </c>
-      <c r="G70" t="s">
+        <v>21</v>
+      </c>
+      <c r="H70" t="s">
         <v>98</v>
       </c>
-      <c r="H70">
-        <v>2</v>
-      </c>
-      <c r="I70" t="s">
+      <c r="I70">
+        <v>2</v>
+      </c>
+      <c r="J70" t="s">
         <v>57</v>
       </c>
-      <c r="J70" t="s">
-        <v>23</v>
-      </c>
-      <c r="K70">
+      <c r="L70">
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B71" t="s">
         <v>75</v>
@@ -3190,27 +3010,24 @@
         <v>114</v>
       </c>
       <c r="E71" t="s">
-        <v>20</v>
-      </c>
-      <c r="G71" t="s">
+        <v>21</v>
+      </c>
+      <c r="H71" t="s">
         <v>99</v>
       </c>
-      <c r="H71">
-        <v>4</v>
-      </c>
-      <c r="I71" t="s">
+      <c r="I71">
+        <v>4</v>
+      </c>
+      <c r="J71" t="s">
         <v>57</v>
       </c>
-      <c r="J71" t="s">
-        <v>23</v>
-      </c>
-      <c r="K71">
+      <c r="L71">
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B72" t="s">
         <v>75</v>
@@ -3222,27 +3039,24 @@
         <v>114</v>
       </c>
       <c r="E72" t="s">
-        <v>20</v>
-      </c>
-      <c r="G72" t="s">
+        <v>21</v>
+      </c>
+      <c r="H72" t="s">
         <v>100</v>
       </c>
-      <c r="H72">
-        <v>4</v>
-      </c>
-      <c r="I72" t="s">
+      <c r="I72">
+        <v>4</v>
+      </c>
+      <c r="J72" t="s">
         <v>57</v>
       </c>
-      <c r="J72" t="s">
-        <v>23</v>
-      </c>
-      <c r="K72">
+      <c r="L72">
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B73" t="s">
         <v>75</v>
@@ -3254,27 +3068,24 @@
         <v>114</v>
       </c>
       <c r="E73" t="s">
-        <v>20</v>
-      </c>
-      <c r="G73" t="s">
+        <v>21</v>
+      </c>
+      <c r="H73" t="s">
         <v>101</v>
       </c>
-      <c r="H73">
-        <v>2</v>
-      </c>
-      <c r="I73" t="s">
+      <c r="I73">
+        <v>2</v>
+      </c>
+      <c r="J73" t="s">
         <v>57</v>
       </c>
-      <c r="J73" t="s">
-        <v>23</v>
-      </c>
-      <c r="K73">
+      <c r="L73">
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B74" t="s">
         <v>75</v>
@@ -3286,27 +3097,24 @@
         <v>114</v>
       </c>
       <c r="E74" t="s">
-        <v>20</v>
-      </c>
-      <c r="G74" t="s">
+        <v>21</v>
+      </c>
+      <c r="H74" t="s">
         <v>102</v>
       </c>
-      <c r="H74">
-        <v>2</v>
-      </c>
-      <c r="I74" t="s">
+      <c r="I74">
+        <v>2</v>
+      </c>
+      <c r="J74" t="s">
         <v>57</v>
       </c>
-      <c r="J74" t="s">
-        <v>23</v>
-      </c>
-      <c r="K74">
+      <c r="L74">
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B75" t="s">
         <v>75</v>
@@ -3318,27 +3126,24 @@
         <v>114</v>
       </c>
       <c r="E75" t="s">
-        <v>20</v>
-      </c>
-      <c r="G75" t="s">
+        <v>21</v>
+      </c>
+      <c r="H75" t="s">
         <v>103</v>
       </c>
-      <c r="H75">
+      <c r="I75">
         <v>3</v>
       </c>
-      <c r="I75" t="s">
+      <c r="J75" t="s">
         <v>104</v>
       </c>
-      <c r="J75" t="s">
-        <v>23</v>
-      </c>
-      <c r="K75">
+      <c r="L75">
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B76" t="s">
         <v>75</v>
@@ -3350,27 +3155,24 @@
         <v>114</v>
       </c>
       <c r="E76" t="s">
-        <v>20</v>
-      </c>
-      <c r="G76" t="s">
+        <v>21</v>
+      </c>
+      <c r="H76" t="s">
         <v>105</v>
       </c>
-      <c r="H76">
+      <c r="I76">
         <v>3</v>
       </c>
-      <c r="I76" t="s">
+      <c r="J76" t="s">
         <v>104</v>
       </c>
-      <c r="J76" t="s">
-        <v>23</v>
-      </c>
-      <c r="K76">
+      <c r="L76">
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B77" t="s">
         <v>75</v>
@@ -3382,27 +3184,24 @@
         <v>114</v>
       </c>
       <c r="E77" t="s">
-        <v>20</v>
-      </c>
-      <c r="G77" t="s">
+        <v>21</v>
+      </c>
+      <c r="H77" t="s">
         <v>106</v>
       </c>
-      <c r="H77">
+      <c r="I77">
         <v>3</v>
       </c>
-      <c r="I77" t="s">
+      <c r="J77" t="s">
         <v>104</v>
       </c>
-      <c r="J77" t="s">
-        <v>23</v>
-      </c>
-      <c r="K77">
+      <c r="L77">
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B78" t="s">
         <v>75</v>
@@ -3414,27 +3213,24 @@
         <v>114</v>
       </c>
       <c r="E78" t="s">
-        <v>20</v>
-      </c>
-      <c r="G78" t="s">
+        <v>21</v>
+      </c>
+      <c r="H78" t="s">
         <v>107</v>
       </c>
-      <c r="H78">
+      <c r="I78">
         <v>3</v>
       </c>
-      <c r="I78" t="s">
+      <c r="J78" t="s">
         <v>104</v>
       </c>
-      <c r="J78" t="s">
-        <v>23</v>
-      </c>
-      <c r="K78">
+      <c r="L78">
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B79" t="s">
         <v>75</v>
@@ -3446,27 +3242,24 @@
         <v>114</v>
       </c>
       <c r="E79" t="s">
-        <v>20</v>
-      </c>
-      <c r="G79" t="s">
+        <v>21</v>
+      </c>
+      <c r="H79" t="s">
         <v>108</v>
       </c>
-      <c r="H79">
+      <c r="I79">
         <v>3</v>
       </c>
-      <c r="I79" t="s">
+      <c r="J79" t="s">
         <v>104</v>
       </c>
-      <c r="J79" t="s">
-        <v>23</v>
-      </c>
-      <c r="K79">
+      <c r="L79">
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B80" t="s">
         <v>75</v>
@@ -3478,27 +3271,24 @@
         <v>114</v>
       </c>
       <c r="E80" t="s">
-        <v>20</v>
-      </c>
-      <c r="G80" t="s">
+        <v>21</v>
+      </c>
+      <c r="H80" t="s">
         <v>109</v>
       </c>
-      <c r="H80">
+      <c r="I80">
         <v>3</v>
       </c>
-      <c r="I80" t="s">
+      <c r="J80" t="s">
         <v>104</v>
       </c>
-      <c r="J80" t="s">
-        <v>23</v>
-      </c>
-      <c r="K80">
+      <c r="L80">
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B81" t="s">
         <v>75</v>
@@ -3510,27 +3300,24 @@
         <v>114</v>
       </c>
       <c r="E81" t="s">
-        <v>20</v>
-      </c>
-      <c r="G81" t="s">
+        <v>21</v>
+      </c>
+      <c r="H81" t="s">
         <v>110</v>
       </c>
-      <c r="H81">
+      <c r="I81">
         <v>3</v>
       </c>
-      <c r="I81" t="s">
+      <c r="J81" t="s">
         <v>104</v>
       </c>
-      <c r="J81" t="s">
-        <v>23</v>
-      </c>
-      <c r="K81">
+      <c r="L81">
         <v>10</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B82" t="s">
         <v>75</v>
@@ -3542,27 +3329,24 @@
         <v>114</v>
       </c>
       <c r="E82" t="s">
-        <v>20</v>
-      </c>
-      <c r="G82" t="s">
+        <v>21</v>
+      </c>
+      <c r="H82" t="s">
         <v>111</v>
       </c>
-      <c r="H82">
+      <c r="I82">
         <v>3</v>
       </c>
-      <c r="I82" t="s">
+      <c r="J82" t="s">
         <v>104</v>
       </c>
-      <c r="J82" t="s">
-        <v>23</v>
-      </c>
-      <c r="K82">
+      <c r="L82">
         <v>10</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B83" t="s">
         <v>75</v>
@@ -3574,27 +3358,24 @@
         <v>114</v>
       </c>
       <c r="E83" t="s">
-        <v>20</v>
-      </c>
-      <c r="G83" t="s">
+        <v>21</v>
+      </c>
+      <c r="H83" t="s">
         <v>112</v>
       </c>
-      <c r="H83">
+      <c r="I83">
         <v>3</v>
       </c>
-      <c r="I83" t="s">
+      <c r="J83" t="s">
         <v>104</v>
       </c>
-      <c r="J83" t="s">
-        <v>23</v>
-      </c>
-      <c r="K83">
+      <c r="L83">
         <v>10</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B84" t="s">
         <v>75</v>
@@ -3606,27 +3387,24 @@
         <v>114</v>
       </c>
       <c r="E84" t="s">
-        <v>20</v>
-      </c>
-      <c r="G84" t="s">
+        <v>21</v>
+      </c>
+      <c r="H84" t="s">
         <v>113</v>
       </c>
-      <c r="H84">
+      <c r="I84">
         <v>3</v>
       </c>
-      <c r="I84" t="s">
+      <c r="J84" t="s">
         <v>104</v>
       </c>
-      <c r="J84" t="s">
-        <v>23</v>
-      </c>
-      <c r="K84">
+      <c r="L84">
         <v>10</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B85" t="s">
         <v>75</v>
@@ -3638,27 +3416,24 @@
         <v>114</v>
       </c>
       <c r="E85" t="s">
-        <v>20</v>
-      </c>
-      <c r="G85" t="s">
-        <v>114</v>
-      </c>
-      <c r="H85">
+        <v>21</v>
+      </c>
+      <c r="H85" t="s">
+        <v>114</v>
+      </c>
+      <c r="I85">
         <v>3</v>
       </c>
-      <c r="I85" t="s">
+      <c r="J85" t="s">
         <v>104</v>
       </c>
-      <c r="J85" t="s">
-        <v>23</v>
-      </c>
-      <c r="K85">
+      <c r="L85">
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B86" t="s">
         <v>75</v>
@@ -3670,27 +3445,24 @@
         <v>114</v>
       </c>
       <c r="E86" t="s">
-        <v>20</v>
-      </c>
-      <c r="G86" t="s">
+        <v>21</v>
+      </c>
+      <c r="H86" t="s">
         <v>115</v>
       </c>
-      <c r="H86">
-        <v>2</v>
-      </c>
-      <c r="I86" t="s">
+      <c r="I86">
+        <v>2</v>
+      </c>
+      <c r="J86" t="s">
         <v>116</v>
       </c>
-      <c r="J86" t="s">
-        <v>23</v>
-      </c>
-      <c r="K86">
+      <c r="L86">
         <v>10</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B87" t="s">
         <v>75</v>
@@ -3702,27 +3474,24 @@
         <v>114</v>
       </c>
       <c r="E87" t="s">
-        <v>20</v>
-      </c>
-      <c r="G87" t="s">
+        <v>21</v>
+      </c>
+      <c r="H87" t="s">
         <v>117</v>
       </c>
-      <c r="H87">
-        <v>2</v>
-      </c>
-      <c r="I87" t="s">
+      <c r="I87">
+        <v>2</v>
+      </c>
+      <c r="J87" t="s">
         <v>116</v>
       </c>
-      <c r="J87" t="s">
-        <v>23</v>
-      </c>
-      <c r="K87">
+      <c r="L87">
         <v>10</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B88" t="s">
         <v>75</v>
@@ -3734,27 +3503,24 @@
         <v>114</v>
       </c>
       <c r="E88" t="s">
-        <v>20</v>
-      </c>
-      <c r="G88" t="s">
+        <v>21</v>
+      </c>
+      <c r="H88" t="s">
         <v>118</v>
       </c>
-      <c r="H88">
-        <v>2</v>
-      </c>
-      <c r="I88" t="s">
+      <c r="I88">
+        <v>2</v>
+      </c>
+      <c r="J88" t="s">
         <v>116</v>
       </c>
-      <c r="J88" t="s">
-        <v>23</v>
-      </c>
-      <c r="K88">
+      <c r="L88">
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B89" t="s">
         <v>75</v>
@@ -3766,27 +3532,24 @@
         <v>114</v>
       </c>
       <c r="E89" t="s">
-        <v>20</v>
-      </c>
-      <c r="G89" t="s">
+        <v>21</v>
+      </c>
+      <c r="H89" t="s">
         <v>119</v>
       </c>
-      <c r="H89">
-        <v>2</v>
-      </c>
-      <c r="I89" t="s">
+      <c r="I89">
+        <v>2</v>
+      </c>
+      <c r="J89" t="s">
         <v>116</v>
       </c>
-      <c r="J89" t="s">
-        <v>23</v>
-      </c>
-      <c r="K89">
+      <c r="L89">
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B90" t="s">
         <v>75</v>
@@ -3798,27 +3561,24 @@
         <v>114</v>
       </c>
       <c r="E90" t="s">
-        <v>20</v>
-      </c>
-      <c r="G90" t="s">
+        <v>21</v>
+      </c>
+      <c r="H90" t="s">
         <v>120</v>
       </c>
-      <c r="H90">
-        <v>2</v>
-      </c>
-      <c r="I90" t="s">
+      <c r="I90">
+        <v>2</v>
+      </c>
+      <c r="J90" t="s">
         <v>116</v>
       </c>
-      <c r="J90" t="s">
-        <v>23</v>
-      </c>
-      <c r="K90">
+      <c r="L90">
         <v>10</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B91" t="s">
         <v>75</v>
@@ -3830,25 +3590,22 @@
         <v>114</v>
       </c>
       <c r="E91" t="s">
-        <v>20</v>
-      </c>
-      <c r="G91" t="s">
+        <v>21</v>
+      </c>
+      <c r="H91" t="s">
         <v>121</v>
       </c>
-      <c r="H91">
-        <v>2</v>
-      </c>
-      <c r="I91" t="s">
+      <c r="I91">
+        <v>2</v>
+      </c>
+      <c r="J91" t="s">
         <v>116</v>
       </c>
-      <c r="J91" t="s">
-        <v>23</v>
-      </c>
-      <c r="K91">
+      <c r="L91">
         <v>10</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>122</v>
       </c>
@@ -3862,25 +3619,25 @@
         <v>114</v>
       </c>
       <c r="E92" t="s">
-        <v>20</v>
-      </c>
-      <c r="G92" t="s">
+        <v>21</v>
+      </c>
+      <c r="F92" t="s">
         <v>125</v>
       </c>
-      <c r="H92">
+      <c r="H92" t="s">
+        <v>126</v>
+      </c>
+      <c r="I92">
         <v>3</v>
-      </c>
-      <c r="I92" t="s">
-        <v>126</v>
       </c>
       <c r="J92" t="s">
         <v>127</v>
       </c>
-      <c r="K92">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>122</v>
       </c>
@@ -3894,25 +3651,25 @@
         <v>114</v>
       </c>
       <c r="E93" t="s">
-        <v>20</v>
-      </c>
-      <c r="G93" t="s">
+        <v>21</v>
+      </c>
+      <c r="F93" t="s">
+        <v>125</v>
+      </c>
+      <c r="H93" t="s">
         <v>128</v>
       </c>
-      <c r="H93">
+      <c r="I93">
         <v>6</v>
       </c>
-      <c r="I93" t="s">
-        <v>17</v>
-      </c>
       <c r="J93" t="s">
-        <v>127</v>
-      </c>
-      <c r="K93">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="L93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>122</v>
       </c>
@@ -3926,25 +3683,25 @@
         <v>114</v>
       </c>
       <c r="E94" t="s">
-        <v>20</v>
-      </c>
-      <c r="G94" t="s">
+        <v>21</v>
+      </c>
+      <c r="F94" t="s">
+        <v>125</v>
+      </c>
+      <c r="H94" t="s">
         <v>129</v>
       </c>
-      <c r="H94">
+      <c r="I94">
         <v>6</v>
       </c>
-      <c r="I94" t="s">
+      <c r="J94" t="s">
         <v>130</v>
       </c>
-      <c r="J94" t="s">
-        <v>127</v>
-      </c>
-      <c r="K94">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>122</v>
       </c>
@@ -3960,20 +3717,23 @@
       <c r="E95" t="s">
         <v>77</v>
       </c>
-      <c r="G95" t="s">
+      <c r="F95" t="s">
         <v>131</v>
       </c>
-      <c r="H95">
+      <c r="H95" t="s">
+        <v>132</v>
+      </c>
+      <c r="I95">
         <v>3</v>
       </c>
-      <c r="I95" t="s">
+      <c r="J95" t="s">
         <v>122</v>
       </c>
-      <c r="J95" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L95">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>122</v>
       </c>
@@ -3989,20 +3749,23 @@
       <c r="E96" t="s">
         <v>77</v>
       </c>
-      <c r="G96" t="s">
+      <c r="F96" t="s">
+        <v>131</v>
+      </c>
+      <c r="H96" t="s">
         <v>133</v>
       </c>
-      <c r="H96">
+      <c r="I96">
         <v>3</v>
       </c>
-      <c r="I96" t="s">
+      <c r="J96" t="s">
         <v>122</v>
       </c>
-      <c r="J96" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L96">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>122</v>
       </c>
@@ -4016,25 +3779,25 @@
         <v>114</v>
       </c>
       <c r="E97" t="s">
-        <v>20</v>
-      </c>
-      <c r="G97" t="s">
+        <v>21</v>
+      </c>
+      <c r="F97" t="s">
         <v>134</v>
       </c>
-      <c r="H97">
-        <v>2</v>
-      </c>
-      <c r="I97" t="s">
+      <c r="H97" t="s">
+        <v>135</v>
+      </c>
+      <c r="I97">
+        <v>2</v>
+      </c>
+      <c r="J97" t="s">
         <v>122</v>
       </c>
-      <c r="J97" t="s">
-        <v>135</v>
-      </c>
-      <c r="K97">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>122</v>
       </c>
@@ -4048,25 +3811,25 @@
         <v>114</v>
       </c>
       <c r="E98" t="s">
-        <v>20</v>
-      </c>
-      <c r="G98" t="s">
+        <v>21</v>
+      </c>
+      <c r="F98" t="s">
+        <v>134</v>
+      </c>
+      <c r="H98" t="s">
         <v>136</v>
       </c>
-      <c r="H98">
-        <v>2</v>
-      </c>
-      <c r="I98" t="s">
+      <c r="I98">
+        <v>2</v>
+      </c>
+      <c r="J98" t="s">
         <v>122</v>
       </c>
-      <c r="J98" t="s">
-        <v>135</v>
-      </c>
-      <c r="K98">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L98">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>122</v>
       </c>
@@ -4080,25 +3843,25 @@
         <v>114</v>
       </c>
       <c r="E99" t="s">
-        <v>20</v>
-      </c>
-      <c r="G99" t="s">
+        <v>21</v>
+      </c>
+      <c r="F99" t="s">
+        <v>134</v>
+      </c>
+      <c r="H99" t="s">
         <v>137</v>
       </c>
-      <c r="H99">
+      <c r="I99">
         <v>3</v>
       </c>
-      <c r="I99" t="s">
+      <c r="J99" t="s">
         <v>138</v>
       </c>
-      <c r="J99" t="s">
-        <v>135</v>
-      </c>
-      <c r="K99">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>122</v>
       </c>
@@ -4112,25 +3875,25 @@
         <v>114</v>
       </c>
       <c r="E100" t="s">
-        <v>20</v>
-      </c>
-      <c r="G100" t="s">
+        <v>21</v>
+      </c>
+      <c r="F100" t="s">
+        <v>134</v>
+      </c>
+      <c r="H100" t="s">
         <v>139</v>
       </c>
-      <c r="H100">
-        <v>2</v>
-      </c>
-      <c r="I100" t="s">
+      <c r="I100">
+        <v>2</v>
+      </c>
+      <c r="J100" t="s">
         <v>140</v>
       </c>
-      <c r="J100" t="s">
-        <v>135</v>
-      </c>
-      <c r="K100">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>122</v>
       </c>
@@ -4144,25 +3907,25 @@
         <v>114</v>
       </c>
       <c r="E101" t="s">
-        <v>20</v>
-      </c>
-      <c r="G101" t="s">
+        <v>21</v>
+      </c>
+      <c r="F101" t="s">
+        <v>134</v>
+      </c>
+      <c r="H101" t="s">
         <v>141</v>
       </c>
-      <c r="H101">
-        <v>2</v>
-      </c>
-      <c r="I101" t="s">
+      <c r="I101">
+        <v>2</v>
+      </c>
+      <c r="J101" t="s">
         <v>142</v>
       </c>
-      <c r="J101" t="s">
-        <v>135</v>
-      </c>
-      <c r="K101">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>122</v>
       </c>
@@ -4176,25 +3939,25 @@
         <v>114</v>
       </c>
       <c r="E102" t="s">
-        <v>20</v>
-      </c>
-      <c r="G102" t="s">
+        <v>21</v>
+      </c>
+      <c r="F102" t="s">
+        <v>134</v>
+      </c>
+      <c r="H102" t="s">
         <v>143</v>
       </c>
-      <c r="H102">
+      <c r="I102">
         <v>3</v>
       </c>
-      <c r="I102" t="s">
+      <c r="J102" t="s">
         <v>144</v>
       </c>
-      <c r="J102" t="s">
-        <v>135</v>
-      </c>
-      <c r="K102">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>122</v>
       </c>
@@ -4208,25 +3971,25 @@
         <v>114</v>
       </c>
       <c r="E103" t="s">
-        <v>20</v>
-      </c>
-      <c r="G103" t="s">
+        <v>21</v>
+      </c>
+      <c r="F103" t="s">
+        <v>134</v>
+      </c>
+      <c r="H103" t="s">
         <v>145</v>
       </c>
-      <c r="H103">
+      <c r="I103">
         <v>3</v>
       </c>
-      <c r="I103" t="s">
+      <c r="J103" t="s">
         <v>146</v>
       </c>
-      <c r="J103" t="s">
-        <v>135</v>
-      </c>
-      <c r="K103">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>122</v>
       </c>
@@ -4240,25 +4003,25 @@
         <v>114</v>
       </c>
       <c r="E104" t="s">
-        <v>20</v>
-      </c>
-      <c r="G104" t="s">
+        <v>21</v>
+      </c>
+      <c r="F104" t="s">
+        <v>134</v>
+      </c>
+      <c r="H104" t="s">
         <v>147</v>
       </c>
-      <c r="H104">
+      <c r="I104">
         <v>3</v>
       </c>
-      <c r="I104" t="s">
+      <c r="J104" t="s">
         <v>148</v>
       </c>
-      <c r="J104" t="s">
-        <v>135</v>
-      </c>
-      <c r="K104">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>122</v>
       </c>
@@ -4272,25 +4035,25 @@
         <v>114</v>
       </c>
       <c r="E105" t="s">
-        <v>20</v>
-      </c>
-      <c r="G105" t="s">
+        <v>21</v>
+      </c>
+      <c r="F105" t="s">
+        <v>134</v>
+      </c>
+      <c r="H105" t="s">
         <v>149</v>
       </c>
-      <c r="H105">
+      <c r="I105">
         <v>3</v>
       </c>
-      <c r="I105" t="s">
+      <c r="J105" t="s">
         <v>150</v>
       </c>
-      <c r="J105" t="s">
-        <v>135</v>
-      </c>
-      <c r="K105">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>122</v>
       </c>
@@ -4304,85 +4067,21 @@
         <v>114</v>
       </c>
       <c r="E106" t="s">
-        <v>20</v>
-      </c>
-      <c r="G106" t="s">
-        <v>149</v>
-      </c>
-      <c r="H106">
+        <v>21</v>
+      </c>
+      <c r="F106" t="s">
+        <v>151</v>
+      </c>
+      <c r="H106" t="s">
+        <v>152</v>
+      </c>
+      <c r="I106">
         <v>3</v>
       </c>
-      <c r="I106" t="s">
-        <v>151</v>
-      </c>
       <c r="J106" t="s">
-        <v>135</v>
-      </c>
-      <c r="K106">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
         <v>122</v>
       </c>
-      <c r="B107" t="s">
-        <v>123</v>
-      </c>
-      <c r="C107" t="s">
-        <v>124</v>
-      </c>
-      <c r="D107">
-        <v>114</v>
-      </c>
-      <c r="E107" t="s">
-        <v>20</v>
-      </c>
-      <c r="G107" t="s">
-        <v>149</v>
-      </c>
-      <c r="H107">
-        <v>3</v>
-      </c>
-      <c r="I107" t="s">
-        <v>152</v>
-      </c>
-      <c r="J107" t="s">
-        <v>135</v>
-      </c>
-      <c r="K107">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>122</v>
-      </c>
-      <c r="B108" t="s">
-        <v>123</v>
-      </c>
-      <c r="C108" t="s">
-        <v>124</v>
-      </c>
-      <c r="D108">
-        <v>114</v>
-      </c>
-      <c r="E108" t="s">
-        <v>20</v>
-      </c>
-      <c r="G108" t="s">
-        <v>153</v>
-      </c>
-      <c r="H108">
-        <v>3</v>
-      </c>
-      <c r="I108" t="s">
-        <v>122</v>
-      </c>
-      <c r="J108" t="s">
-        <v>154</v>
-      </c>
-      <c r="K108">
+      <c r="L106">
         <v>2</v>
       </c>
     </row>
@@ -4393,19 +4092,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F00DE9E-18A2-47AD-8A9D-EC1159415896}">
-  <dimension ref="A1:K108"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD235D7-F693-4BA5-B6AA-3E11869424DE}">
+  <dimension ref="A1:L106"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.5" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -4416,24 +4116,27 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
         <v>155</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>156</v>
       </c>
-      <c r="F1" t="s">
-        <v>157</v>
-      </c>
-      <c r="G1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2">
         <v>114</v>
@@ -4444,14 +4147,17 @@
       <c r="E2">
         <v>12</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>20</v>
       </c>
-      <c r="G2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+      <c r="H2" t="s">
+        <v>157</v>
+      </c>
+      <c r="L2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="66" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>75</v>
       </c>
@@ -4467,14 +4173,17 @@
       <c r="E3">
         <v>10</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>20</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="L3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>123</v>
       </c>
@@ -4490,14 +4199,29 @@
       <c r="E4">
         <v>6</v>
       </c>
-      <c r="F4">
-        <v>12</v>
-      </c>
-      <c r="G4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G4">
+        <v>12</v>
+      </c>
+      <c r="H4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="51" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L51">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L52">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="12:12" x14ac:dyDescent="0.25">
+      <c r="L53">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>122</v>
       </c>
@@ -4510,23 +4234,23 @@
       <c r="D92">
         <v>114</v>
       </c>
-      <c r="G92" t="s">
+      <c r="F92" t="s">
         <v>125</v>
       </c>
-      <c r="H92">
+      <c r="H92" t="s">
+        <v>126</v>
+      </c>
+      <c r="I92">
         <v>3</v>
-      </c>
-      <c r="I92" t="s">
-        <v>126</v>
       </c>
       <c r="J92" t="s">
         <v>127</v>
       </c>
-      <c r="K92">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>122</v>
       </c>
@@ -4539,23 +4263,23 @@
       <c r="D93">
         <v>114</v>
       </c>
-      <c r="G93" t="s">
+      <c r="F93" t="s">
+        <v>125</v>
+      </c>
+      <c r="H93" t="s">
         <v>128</v>
       </c>
-      <c r="H93">
+      <c r="I93">
         <v>6</v>
       </c>
-      <c r="I93" t="s">
-        <v>17</v>
-      </c>
       <c r="J93" t="s">
-        <v>127</v>
-      </c>
-      <c r="K93">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="L93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>122</v>
       </c>
@@ -4568,23 +4292,23 @@
       <c r="D94">
         <v>114</v>
       </c>
-      <c r="G94" t="s">
+      <c r="F94" t="s">
+        <v>125</v>
+      </c>
+      <c r="H94" t="s">
         <v>129</v>
       </c>
-      <c r="H94">
+      <c r="I94">
         <v>6</v>
       </c>
-      <c r="I94" t="s">
+      <c r="J94" t="s">
         <v>130</v>
       </c>
-      <c r="J94" t="s">
-        <v>127</v>
-      </c>
-      <c r="K94">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>122</v>
       </c>
@@ -4600,20 +4324,23 @@
       <c r="E95" t="s">
         <v>77</v>
       </c>
-      <c r="G95" t="s">
+      <c r="F95" t="s">
         <v>131</v>
       </c>
-      <c r="H95">
+      <c r="H95" t="s">
+        <v>132</v>
+      </c>
+      <c r="I95">
         <v>3</v>
       </c>
-      <c r="I95" t="s">
+      <c r="J95" t="s">
         <v>122</v>
       </c>
-      <c r="J95" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L95">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>122</v>
       </c>
@@ -4629,20 +4356,23 @@
       <c r="E96" t="s">
         <v>77</v>
       </c>
-      <c r="G96" t="s">
+      <c r="F96" t="s">
+        <v>131</v>
+      </c>
+      <c r="H96" t="s">
         <v>133</v>
       </c>
-      <c r="H96">
+      <c r="I96">
         <v>3</v>
       </c>
-      <c r="I96" t="s">
+      <c r="J96" t="s">
         <v>122</v>
       </c>
-      <c r="J96" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L96">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>122</v>
       </c>
@@ -4655,23 +4385,23 @@
       <c r="D97">
         <v>114</v>
       </c>
-      <c r="G97" t="s">
+      <c r="F97" t="s">
         <v>134</v>
       </c>
-      <c r="H97">
-        <v>2</v>
-      </c>
-      <c r="I97" t="s">
+      <c r="H97" t="s">
+        <v>135</v>
+      </c>
+      <c r="I97">
+        <v>2</v>
+      </c>
+      <c r="J97" t="s">
         <v>122</v>
       </c>
-      <c r="J97" t="s">
-        <v>135</v>
-      </c>
-      <c r="K97">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>122</v>
       </c>
@@ -4684,23 +4414,23 @@
       <c r="D98">
         <v>114</v>
       </c>
-      <c r="G98" t="s">
+      <c r="F98" t="s">
+        <v>134</v>
+      </c>
+      <c r="H98" t="s">
         <v>136</v>
       </c>
-      <c r="H98">
-        <v>2</v>
-      </c>
-      <c r="I98" t="s">
+      <c r="I98">
+        <v>2</v>
+      </c>
+      <c r="J98" t="s">
         <v>122</v>
       </c>
-      <c r="J98" t="s">
-        <v>135</v>
-      </c>
-      <c r="K98">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L98">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>122</v>
       </c>
@@ -4713,23 +4443,23 @@
       <c r="D99">
         <v>114</v>
       </c>
-      <c r="G99" t="s">
+      <c r="F99" t="s">
+        <v>134</v>
+      </c>
+      <c r="H99" t="s">
         <v>137</v>
       </c>
-      <c r="H99">
+      <c r="I99">
         <v>3</v>
       </c>
-      <c r="I99" t="s">
+      <c r="J99" t="s">
         <v>138</v>
       </c>
-      <c r="J99" t="s">
-        <v>135</v>
-      </c>
-      <c r="K99">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>122</v>
       </c>
@@ -4742,23 +4472,23 @@
       <c r="D100">
         <v>114</v>
       </c>
-      <c r="G100" t="s">
+      <c r="F100" t="s">
+        <v>134</v>
+      </c>
+      <c r="H100" t="s">
         <v>139</v>
       </c>
-      <c r="H100">
-        <v>2</v>
-      </c>
-      <c r="I100" t="s">
+      <c r="I100">
+        <v>2</v>
+      </c>
+      <c r="J100" t="s">
         <v>140</v>
       </c>
-      <c r="J100" t="s">
-        <v>135</v>
-      </c>
-      <c r="K100">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>122</v>
       </c>
@@ -4771,23 +4501,23 @@
       <c r="D101">
         <v>114</v>
       </c>
-      <c r="G101" t="s">
+      <c r="F101" t="s">
+        <v>134</v>
+      </c>
+      <c r="H101" t="s">
         <v>141</v>
       </c>
-      <c r="H101">
-        <v>2</v>
-      </c>
-      <c r="I101" t="s">
+      <c r="I101">
+        <v>2</v>
+      </c>
+      <c r="J101" t="s">
         <v>142</v>
       </c>
-      <c r="J101" t="s">
-        <v>135</v>
-      </c>
-      <c r="K101">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>122</v>
       </c>
@@ -4800,23 +4530,23 @@
       <c r="D102">
         <v>114</v>
       </c>
-      <c r="G102" t="s">
+      <c r="F102" t="s">
+        <v>134</v>
+      </c>
+      <c r="H102" t="s">
         <v>143</v>
       </c>
-      <c r="H102">
+      <c r="I102">
         <v>3</v>
       </c>
-      <c r="I102" t="s">
+      <c r="J102" t="s">
         <v>144</v>
       </c>
-      <c r="J102" t="s">
-        <v>135</v>
-      </c>
-      <c r="K102">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>122</v>
       </c>
@@ -4829,23 +4559,23 @@
       <c r="D103">
         <v>114</v>
       </c>
-      <c r="G103" t="s">
+      <c r="F103" t="s">
+        <v>134</v>
+      </c>
+      <c r="H103" t="s">
         <v>145</v>
       </c>
-      <c r="H103">
+      <c r="I103">
         <v>3</v>
       </c>
-      <c r="I103" t="s">
+      <c r="J103" t="s">
         <v>146</v>
       </c>
-      <c r="J103" t="s">
-        <v>135</v>
-      </c>
-      <c r="K103">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>122</v>
       </c>
@@ -4858,23 +4588,23 @@
       <c r="D104">
         <v>114</v>
       </c>
-      <c r="G104" t="s">
+      <c r="F104" t="s">
+        <v>134</v>
+      </c>
+      <c r="H104" t="s">
         <v>147</v>
       </c>
-      <c r="H104">
+      <c r="I104">
         <v>3</v>
       </c>
-      <c r="I104" t="s">
+      <c r="J104" t="s">
         <v>148</v>
       </c>
-      <c r="J104" t="s">
-        <v>135</v>
-      </c>
-      <c r="K104">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>122</v>
       </c>
@@ -4887,23 +4617,23 @@
       <c r="D105">
         <v>114</v>
       </c>
-      <c r="G105" t="s">
+      <c r="F105" t="s">
+        <v>134</v>
+      </c>
+      <c r="H105" t="s">
         <v>149</v>
       </c>
-      <c r="H105">
+      <c r="I105">
         <v>3</v>
       </c>
-      <c r="I105" t="s">
+      <c r="J105" t="s">
         <v>150</v>
       </c>
-      <c r="J105" t="s">
-        <v>135</v>
-      </c>
-      <c r="K105">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>122</v>
       </c>
@@ -4916,77 +4646,19 @@
       <c r="D106">
         <v>114</v>
       </c>
-      <c r="G106" t="s">
-        <v>149</v>
-      </c>
-      <c r="H106">
+      <c r="F106" t="s">
+        <v>151</v>
+      </c>
+      <c r="H106" t="s">
+        <v>152</v>
+      </c>
+      <c r="I106">
         <v>3</v>
       </c>
-      <c r="I106" t="s">
-        <v>151</v>
-      </c>
       <c r="J106" t="s">
-        <v>135</v>
-      </c>
-      <c r="K106">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
         <v>122</v>
       </c>
-      <c r="B107" t="s">
-        <v>123</v>
-      </c>
-      <c r="C107" t="s">
-        <v>124</v>
-      </c>
-      <c r="D107">
-        <v>114</v>
-      </c>
-      <c r="G107" t="s">
-        <v>149</v>
-      </c>
-      <c r="H107">
-        <v>3</v>
-      </c>
-      <c r="I107" t="s">
-        <v>152</v>
-      </c>
-      <c r="J107" t="s">
-        <v>135</v>
-      </c>
-      <c r="K107">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>122</v>
-      </c>
-      <c r="B108" t="s">
-        <v>123</v>
-      </c>
-      <c r="C108" t="s">
-        <v>124</v>
-      </c>
-      <c r="D108">
-        <v>114</v>
-      </c>
-      <c r="G108" t="s">
-        <v>153</v>
-      </c>
-      <c r="H108">
-        <v>3</v>
-      </c>
-      <c r="I108" t="s">
-        <v>122</v>
-      </c>
-      <c r="J108" t="s">
-        <v>154</v>
-      </c>
-      <c r="K108">
+      <c r="L106">
         <v>2</v>
       </c>
     </row>

--- a/master_data.xlsx
+++ b/master_data.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\000_專案計畫\20260107_學分學程查詢功能\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7866313E-F0F3-4E40-8AC2-26BD6A1A607A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{29635E56-EF64-4245-809E-FF394D74D934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D4E4C608-F7C5-457E-9559-0A0A39C60FDD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6EDA1B97-6CCA-429F-BA7D-376AE58494D3}"/>
   </bookViews>
   <sheets>
     <sheet name="科目表" sheetId="1" r:id="rId1"/>
     <sheet name="學程規範總額" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">科目表!$A$1:$M$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">科目表!$A$1:$M$108</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,10 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="160">
-  <si>
-    <t>學院</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="885" uniqueCount="268">
   <si>
     <t>學程代碼</t>
   </si>
@@ -61,7 +58,7 @@
   </si>
   <si>
     <t>模組名稱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>課程代碼</t>
@@ -229,7 +226,16 @@
     <t>兩漢哲學</t>
   </si>
   <si>
-    <t>五經思想/五經思想：易經</t>
+    <t>五經思想</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>five_classics</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>五經思想：易經</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>佛學概論</t>
@@ -262,7 +268,8 @@
     <t>歷史系</t>
   </si>
   <si>
-    <t>台灣博物館史</t>
+    <t>臺灣博物館史</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>檔案與口述歷史</t>
@@ -278,16 +285,18 @@
   </si>
   <si>
     <t>必修</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>哲學諮商理論與實務</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>哲學諮商:理論與實務</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>哲學諮商方法論</t>
   </si>
   <si>
-    <t>哲學諮商：實習</t>
+    <t>哲學諮商:實習</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>哲學系、心理學系、臨床心理學系共同負責</t>
@@ -335,13 +344,15 @@
     <t>哲學諮商的倫理學基礎</t>
   </si>
   <si>
-    <t>亞里斯多德的哲學諮商</t>
+    <t>亞里斯多德式的哲學諮商</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>哲學諮商實務</t>
   </si>
   <si>
-    <t>哲學諮商的批判與思考</t>
+    <t>哲學諮商的批判思考</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>五經思想：易經</t>
@@ -356,11 +367,11 @@
     <t>中國哲學專題：人性論</t>
   </si>
   <si>
-    <t>敘說、反應與實踐導論</t>
+    <t>敘說、反映與實踐導論</t>
   </si>
   <si>
     <t>心理系</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>輔導與諮商概論</t>
@@ -397,7 +408,7 @@
   </si>
   <si>
     <t>臨心系</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>團體諮商</t>
@@ -425,14 +436,14 @@
   </si>
   <si>
     <t>基礎(至少2學分)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>程式設計概論</t>
   </si>
   <si>
     <t>經濟系、資管系、金企系、企管系、統資系</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>計算機概論</t>
@@ -445,7 +456,7 @@
   </si>
   <si>
     <t>重點(至少6學分)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>機器學習</t>
@@ -455,7 +466,7 @@
   </si>
   <si>
     <t>專業/進階課程(至少2學分)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>資料庫系統設計</t>
@@ -480,75 +491,406 @@
   </si>
   <si>
     <t>領科學程三</t>
+  </si>
+  <si>
+    <t>特殊教育與適性教學</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中等教育學程</t>
+  </si>
+  <si>
+    <t>資料庫系統概論</t>
+  </si>
+  <si>
+    <t>資工系</t>
+  </si>
+  <si>
+    <t>資料庫</t>
+  </si>
+  <si>
+    <t>資數系</t>
+  </si>
+  <si>
+    <t>資料庫管理</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>會計系、資管系、統資系</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>總整課程(至少2學分)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>教育大數據專題</t>
+  </si>
+  <si>
+    <t>必修總學分</t>
+  </si>
+  <si>
+    <t>選修總學分</t>
+  </si>
+  <si>
+    <t>總計應修學分</t>
+  </si>
+  <si>
+    <t>備註 (模組要求)</t>
+  </si>
+  <si>
+    <t>我來測試一下</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>必修核心課程(共十學分) /n 選修課程(至少須修讀十學分) 
+開設課程及開放選修名額以當年度課表為準</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本微學程應修學分數 12 學分。包括基礎課程(2 學分)、重點課程(6 學分)專業/進階課程(2 學分)、總整課程(2 學分)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">特殊教育與適性教學
 </t>
   </si>
   <si>
-    <t>中等教育學程</t>
-  </si>
-  <si>
-    <t>資料庫系統概論</t>
-  </si>
-  <si>
-    <t>資工系</t>
-  </si>
-  <si>
-    <t>資料庫</t>
-  </si>
-  <si>
-    <t>資數系</t>
-  </si>
-  <si>
-    <t>資料庫管理</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>會計系、資管系、統資系</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>總整課程(至少2學分)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>教育大數據專題</t>
-  </si>
-  <si>
-    <t>必修總學分</t>
-  </si>
-  <si>
-    <t>選修總學分</t>
-  </si>
-  <si>
-    <t>總計應修學分</t>
-  </si>
-  <si>
-    <t>備註 (模組要求)</t>
-  </si>
-  <si>
-    <t>我來測試一下</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>必修核心課程(共十學分) /n 選修課程(至少須修讀十學分) 
-開設課程及開放選修名額以當年度課表為準</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>本微學程應修學分數 12 學分。包括基礎課程(2 學分)、重點課程(6 學分)專業/進階課程(2 學分)、總整課程(2 學分)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>17624</t>
+  </si>
+  <si>
+    <t>02109</t>
+  </si>
+  <si>
+    <t>18087</t>
+  </si>
+  <si>
+    <t>18981</t>
+  </si>
+  <si>
+    <t>21877</t>
+  </si>
+  <si>
+    <t>32707</t>
+  </si>
+  <si>
+    <t>21256</t>
+  </si>
+  <si>
+    <t>31502</t>
+  </si>
+  <si>
+    <t>11230</t>
+  </si>
+  <si>
+    <t>11059</t>
+  </si>
+  <si>
+    <t>07253</t>
+  </si>
+  <si>
+    <t>07254</t>
+  </si>
+  <si>
+    <t>07269</t>
+  </si>
+  <si>
+    <t>07272</t>
+  </si>
+  <si>
+    <t>10035</t>
+  </si>
+  <si>
+    <t>08021</t>
+  </si>
+  <si>
+    <t>07268</t>
+  </si>
+  <si>
+    <t>02905</t>
+  </si>
+  <si>
+    <t>01625</t>
+  </si>
+  <si>
+    <t>01466</t>
+  </si>
+  <si>
+    <t>02243</t>
+  </si>
+  <si>
+    <t>02480</t>
+  </si>
+  <si>
+    <t>01977</t>
+  </si>
+  <si>
+    <t>01313</t>
+  </si>
+  <si>
+    <t>21269</t>
+  </si>
+  <si>
+    <t>22433</t>
+  </si>
+  <si>
+    <t>02894</t>
+  </si>
+  <si>
+    <t>01979</t>
+  </si>
+  <si>
+    <t>01203</t>
+  </si>
+  <si>
+    <t>01146</t>
+  </si>
+  <si>
+    <t>01119</t>
+  </si>
+  <si>
+    <t>01113</t>
+  </si>
+  <si>
+    <t>01299</t>
+  </si>
+  <si>
+    <t>01635</t>
+  </si>
+  <si>
+    <t>15998</t>
+  </si>
+  <si>
+    <t>02938</t>
+  </si>
+  <si>
+    <t>04534</t>
+  </si>
+  <si>
+    <t>01608</t>
+  </si>
+  <si>
+    <t>12724</t>
+  </si>
+  <si>
+    <t>22515</t>
+  </si>
+  <si>
+    <t>01556</t>
+  </si>
+  <si>
+    <t>01565</t>
+  </si>
+  <si>
+    <t>04538</t>
+  </si>
+  <si>
+    <t>15903</t>
+  </si>
+  <si>
+    <t>05163</t>
+  </si>
+  <si>
+    <t>23401</t>
+  </si>
+  <si>
+    <t>20178</t>
+  </si>
+  <si>
+    <t>20179</t>
+  </si>
+  <si>
+    <t>16324</t>
+  </si>
+  <si>
+    <t>01121</t>
+  </si>
+  <si>
+    <t>12728</t>
+  </si>
+  <si>
+    <t>15294</t>
+  </si>
+  <si>
+    <t>13644</t>
+  </si>
+  <si>
+    <t>01699</t>
+  </si>
+  <si>
+    <t>01913</t>
+  </si>
+  <si>
+    <t>09994</t>
+  </si>
+  <si>
+    <t>01600</t>
+  </si>
+  <si>
+    <t>17555</t>
+  </si>
+  <si>
+    <t>04868</t>
+  </si>
+  <si>
+    <t>16261</t>
+  </si>
+  <si>
+    <t>04189</t>
+  </si>
+  <si>
+    <t>01221</t>
+  </si>
+  <si>
+    <t>16785</t>
+  </si>
+  <si>
+    <t>03940</t>
+  </si>
+  <si>
+    <t>13737</t>
+  </si>
+  <si>
+    <t>30449</t>
+  </si>
+  <si>
+    <t>31407</t>
+  </si>
+  <si>
+    <t>30443</t>
+  </si>
+  <si>
+    <t>34280</t>
+  </si>
+  <si>
+    <t>35014</t>
+  </si>
+  <si>
+    <t>04254</t>
+  </si>
+  <si>
+    <t>35268</t>
+  </si>
+  <si>
+    <t>23660</t>
+  </si>
+  <si>
+    <t>12798</t>
+  </si>
+  <si>
+    <t>05752</t>
+  </si>
+  <si>
+    <t>07070</t>
+  </si>
+  <si>
+    <t>10467</t>
+  </si>
+  <si>
+    <t>02962</t>
+  </si>
+  <si>
+    <t>07603</t>
+  </si>
+  <si>
+    <t>06184</t>
+  </si>
+  <si>
+    <t>13769</t>
+  </si>
+  <si>
+    <t>18958</t>
+  </si>
+  <si>
+    <t>19781</t>
+  </si>
+  <si>
+    <t>19758</t>
+  </si>
+  <si>
+    <t>01194</t>
+  </si>
+  <si>
+    <t>03400</t>
+  </si>
+  <si>
+    <t>05444</t>
+  </si>
+  <si>
+    <t>07050</t>
+  </si>
+  <si>
+    <t>07422</t>
+  </si>
+  <si>
+    <t>22492</t>
+  </si>
+  <si>
+    <t>24495</t>
+  </si>
+  <si>
+    <t>01863</t>
+  </si>
+  <si>
+    <t>03056</t>
+  </si>
+  <si>
+    <t>13027</t>
+  </si>
+  <si>
+    <t>24327</t>
+  </si>
+  <si>
+    <t>36024</t>
+  </si>
+  <si>
+    <t>36025</t>
+  </si>
+  <si>
+    <t>31441</t>
+  </si>
+  <si>
+    <t>36739</t>
+  </si>
+  <si>
+    <t>24565</t>
+  </si>
+  <si>
+    <t>32392</t>
+  </si>
+  <si>
+    <t>03001</t>
+  </si>
+  <si>
+    <t>05347</t>
+  </si>
+  <si>
+    <t>02490</t>
+  </si>
+  <si>
+    <t>36029</t>
+  </si>
+  <si>
+    <t>學院</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -584,8 +926,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -924,8 +1269,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAD85608-43B1-478F-B47D-E9EA75A115A0}">
-  <dimension ref="A1:M106"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5337EBCA-7F9A-44C4-88C1-9A3DAE96CBE3}">
+  <dimension ref="A1:M107"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
@@ -944,69 +1289,72 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
       <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2">
+        <v>114</v>
+      </c>
+      <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="D2">
-        <v>114</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
+        <v>162</v>
+      </c>
+      <c r="H2" t="s">
         <v>16</v>
-      </c>
-      <c r="H2" t="s">
-        <v>17</v>
       </c>
       <c r="I2">
         <v>4</v>
       </c>
       <c r="J2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L2">
         <v>8</v>
@@ -1014,28 +1362,31 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3">
+        <v>114</v>
+      </c>
+      <c r="E3" t="s">
         <v>15</v>
       </c>
-      <c r="D3">
-        <v>114</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
+      <c r="G3" t="s">
+        <v>163</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I3">
         <v>4</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L3">
         <v>8</v>
@@ -1043,28 +1394,31 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
       <c r="D4">
         <v>114</v>
       </c>
       <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>164</v>
+      </c>
+      <c r="H4" t="s">
         <v>21</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4" t="s">
         <v>22</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4" t="s">
-        <v>23</v>
       </c>
       <c r="L4">
         <v>12</v>
@@ -1072,28 +1426,31 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
       <c r="D5">
         <v>114</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G5" t="s">
+        <v>165</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I5">
         <v>2</v>
       </c>
       <c r="J5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L5">
         <v>12</v>
@@ -1101,28 +1458,31 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
         <v>13</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="s">
-        <v>15</v>
-      </c>
       <c r="D6">
         <v>114</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G6" t="s">
+        <v>166</v>
       </c>
       <c r="H6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I6">
         <v>2</v>
       </c>
       <c r="J6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L6">
         <v>12</v>
@@ -1130,28 +1490,31 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>14</v>
       </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
       <c r="D7">
         <v>114</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G7" t="s">
+        <v>167</v>
       </c>
       <c r="H7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I7">
         <v>4</v>
       </c>
       <c r="J7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L7">
         <v>12</v>
@@ -1159,28 +1522,31 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>14</v>
       </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
       <c r="D8">
         <v>114</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G8" t="s">
+        <v>168</v>
       </c>
       <c r="H8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
       <c r="J8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L8">
         <v>12</v>
@@ -1188,28 +1554,31 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
         <v>13</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>14</v>
       </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
       <c r="D9">
         <v>114</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G9" t="s">
+        <v>169</v>
       </c>
       <c r="H9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I9">
         <v>4</v>
       </c>
       <c r="J9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L9">
         <v>12</v>
@@ -1217,28 +1586,31 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>14</v>
       </c>
-      <c r="C10" t="s">
-        <v>15</v>
-      </c>
       <c r="D10">
         <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G10" t="s">
+        <v>170</v>
       </c>
       <c r="H10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I10">
         <v>4</v>
       </c>
       <c r="J10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L10">
         <v>12</v>
@@ -1246,28 +1618,31 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
         <v>13</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>14</v>
       </c>
-      <c r="C11" t="s">
-        <v>15</v>
-      </c>
       <c r="D11">
         <v>114</v>
       </c>
       <c r="E11" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G11" t="s">
+        <v>171</v>
       </c>
       <c r="H11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I11">
         <v>4</v>
       </c>
       <c r="J11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L11">
         <v>12</v>
@@ -1275,28 +1650,31 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
         <v>13</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>14</v>
       </c>
-      <c r="C12" t="s">
-        <v>15</v>
-      </c>
       <c r="D12">
         <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G12" t="s">
+        <v>172</v>
       </c>
       <c r="H12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I12">
         <v>4</v>
       </c>
       <c r="J12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L12">
         <v>12</v>
@@ -1304,28 +1682,31 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
         <v>13</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>14</v>
       </c>
-      <c r="C13" t="s">
-        <v>15</v>
-      </c>
       <c r="D13">
         <v>114</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G13" t="s">
+        <v>173</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I13">
         <v>4</v>
       </c>
       <c r="J13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L13">
         <v>12</v>
@@ -1333,28 +1714,31 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>14</v>
       </c>
-      <c r="C14" t="s">
-        <v>15</v>
-      </c>
       <c r="D14">
         <v>114</v>
       </c>
       <c r="E14" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G14" t="s">
+        <v>174</v>
       </c>
       <c r="H14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I14">
         <v>4</v>
       </c>
       <c r="J14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L14">
         <v>12</v>
@@ -1362,28 +1746,31 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
         <v>13</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>14</v>
       </c>
-      <c r="C15" t="s">
-        <v>15</v>
-      </c>
       <c r="D15">
         <v>114</v>
       </c>
       <c r="E15" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G15" t="s">
+        <v>175</v>
       </c>
       <c r="H15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I15">
         <v>4</v>
       </c>
       <c r="J15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L15">
         <v>12</v>
@@ -1391,28 +1778,31 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s">
         <v>13</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>14</v>
       </c>
-      <c r="C16" t="s">
-        <v>15</v>
-      </c>
       <c r="D16">
         <v>114</v>
       </c>
       <c r="E16" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G16" t="s">
+        <v>176</v>
       </c>
       <c r="H16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I16">
         <v>4</v>
       </c>
       <c r="J16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L16">
         <v>12</v>
@@ -1420,28 +1810,31 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
         <v>13</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>14</v>
       </c>
-      <c r="C17" t="s">
-        <v>15</v>
-      </c>
       <c r="D17">
         <v>114</v>
       </c>
       <c r="E17" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G17" t="s">
+        <v>177</v>
       </c>
       <c r="H17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I17">
         <v>4</v>
       </c>
       <c r="J17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L17">
         <v>12</v>
@@ -1449,28 +1842,31 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" t="s">
         <v>13</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>14</v>
       </c>
-      <c r="C18" t="s">
-        <v>15</v>
-      </c>
       <c r="D18">
         <v>114</v>
       </c>
       <c r="E18" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G18" t="s">
+        <v>178</v>
       </c>
       <c r="H18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I18">
         <v>2</v>
       </c>
       <c r="J18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L18">
         <v>12</v>
@@ -1478,28 +1874,31 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
         <v>13</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>14</v>
       </c>
-      <c r="C19" t="s">
-        <v>15</v>
-      </c>
       <c r="D19">
         <v>114</v>
       </c>
       <c r="E19" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G19" t="s">
+        <v>179</v>
       </c>
       <c r="H19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I19">
         <v>4</v>
       </c>
       <c r="J19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L19">
         <v>12</v>
@@ -1507,28 +1906,31 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" t="s">
         <v>13</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>14</v>
       </c>
-      <c r="C20" t="s">
-        <v>15</v>
-      </c>
       <c r="D20">
         <v>114</v>
       </c>
       <c r="E20" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G20" t="s">
+        <v>180</v>
       </c>
       <c r="H20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I20">
         <v>4</v>
       </c>
       <c r="J20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L20">
         <v>12</v>
@@ -1536,28 +1938,31 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
         <v>13</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>14</v>
       </c>
-      <c r="C21" t="s">
-        <v>15</v>
-      </c>
       <c r="D21">
         <v>114</v>
       </c>
       <c r="E21" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G21" t="s">
+        <v>181</v>
       </c>
       <c r="H21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I21">
         <v>4</v>
       </c>
       <c r="J21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L21">
         <v>12</v>
@@ -1565,28 +1970,31 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" t="s">
         <v>13</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>14</v>
       </c>
-      <c r="C22" t="s">
-        <v>15</v>
-      </c>
       <c r="D22">
         <v>114</v>
       </c>
       <c r="E22" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G22" t="s">
+        <v>182</v>
       </c>
       <c r="H22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I22">
         <v>4</v>
       </c>
       <c r="J22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L22">
         <v>12</v>
@@ -1594,28 +2002,31 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" t="s">
         <v>13</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>14</v>
       </c>
-      <c r="C23" t="s">
-        <v>15</v>
-      </c>
       <c r="D23">
         <v>114</v>
       </c>
       <c r="E23" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G23" t="s">
+        <v>183</v>
       </c>
       <c r="H23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I23">
         <v>4</v>
       </c>
       <c r="J23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L23">
         <v>12</v>
@@ -1623,28 +2034,31 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" t="s">
         <v>13</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>14</v>
       </c>
-      <c r="C24" t="s">
-        <v>15</v>
-      </c>
       <c r="D24">
         <v>114</v>
       </c>
       <c r="E24" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G24" t="s">
+        <v>184</v>
       </c>
       <c r="H24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I24">
         <v>4</v>
       </c>
       <c r="J24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L24">
         <v>12</v>
@@ -1652,28 +2066,31 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" t="s">
         <v>13</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>14</v>
       </c>
-      <c r="C25" t="s">
-        <v>15</v>
-      </c>
       <c r="D25">
         <v>114</v>
       </c>
       <c r="E25" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G25" t="s">
+        <v>185</v>
       </c>
       <c r="H25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I25">
         <v>4</v>
       </c>
       <c r="J25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L25">
         <v>12</v>
@@ -1681,28 +2098,31 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" t="s">
         <v>13</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>14</v>
       </c>
-      <c r="C26" t="s">
-        <v>15</v>
-      </c>
       <c r="D26">
         <v>114</v>
       </c>
       <c r="E26" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G26" t="s">
+        <v>186</v>
       </c>
       <c r="H26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I26">
         <v>4</v>
       </c>
       <c r="J26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L26">
         <v>12</v>
@@ -1710,28 +2130,31 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" t="s">
         <v>13</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>14</v>
       </c>
-      <c r="C27" t="s">
-        <v>15</v>
-      </c>
       <c r="D27">
         <v>114</v>
       </c>
       <c r="E27" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G27" t="s">
+        <v>187</v>
       </c>
       <c r="H27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I27">
         <v>4</v>
       </c>
       <c r="J27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L27">
         <v>12</v>
@@ -1739,28 +2162,31 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" t="s">
         <v>13</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>14</v>
       </c>
-      <c r="C28" t="s">
-        <v>15</v>
-      </c>
       <c r="D28">
         <v>114</v>
       </c>
       <c r="E28" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G28" t="s">
+        <v>188</v>
       </c>
       <c r="H28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I28">
         <v>4</v>
       </c>
       <c r="J28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L28">
         <v>12</v>
@@ -1768,28 +2194,31 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s">
         <v>13</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>14</v>
       </c>
-      <c r="C29" t="s">
-        <v>15</v>
-      </c>
       <c r="D29">
         <v>114</v>
       </c>
       <c r="E29" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G29" t="s">
+        <v>189</v>
       </c>
       <c r="H29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I29">
         <v>4</v>
       </c>
       <c r="J29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L29">
         <v>12</v>
@@ -1797,28 +2226,31 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" t="s">
         <v>13</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>14</v>
       </c>
-      <c r="C30" t="s">
-        <v>15</v>
-      </c>
       <c r="D30">
         <v>114</v>
       </c>
       <c r="E30" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G30" t="s">
+        <v>190</v>
       </c>
       <c r="H30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I30">
         <v>4</v>
       </c>
       <c r="J30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L30">
         <v>12</v>
@@ -1826,28 +2258,31 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" t="s">
         <v>13</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>14</v>
       </c>
-      <c r="C31" t="s">
-        <v>15</v>
-      </c>
       <c r="D31">
         <v>114</v>
       </c>
       <c r="E31" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G31" t="s">
+        <v>191</v>
       </c>
       <c r="H31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I31">
         <v>4</v>
       </c>
       <c r="J31" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L31">
         <v>12</v>
@@ -1855,28 +2290,31 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>12</v>
+      </c>
+      <c r="B32" t="s">
         <v>13</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>14</v>
       </c>
-      <c r="C32" t="s">
-        <v>15</v>
-      </c>
       <c r="D32">
         <v>114</v>
       </c>
       <c r="E32" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G32" t="s">
+        <v>192</v>
       </c>
       <c r="H32" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I32">
         <v>4</v>
       </c>
       <c r="J32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L32">
         <v>12</v>
@@ -1884,28 +2322,31 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" t="s">
         <v>13</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>14</v>
       </c>
-      <c r="C33" t="s">
-        <v>15</v>
-      </c>
       <c r="D33">
         <v>114</v>
       </c>
       <c r="E33" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G33" t="s">
+        <v>193</v>
       </c>
       <c r="H33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I33">
         <v>6</v>
       </c>
       <c r="J33" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L33">
         <v>12</v>
@@ -1913,28 +2354,31 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" t="s">
         <v>13</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>14</v>
       </c>
-      <c r="C34" t="s">
-        <v>15</v>
-      </c>
       <c r="D34">
         <v>114</v>
       </c>
       <c r="E34" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G34" t="s">
+        <v>194</v>
       </c>
       <c r="H34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I34">
         <v>4</v>
       </c>
       <c r="J34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L34">
         <v>12</v>
@@ -1942,28 +2386,31 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" t="s">
         <v>13</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>14</v>
       </c>
-      <c r="C35" t="s">
-        <v>15</v>
-      </c>
       <c r="D35">
         <v>114</v>
       </c>
       <c r="E35" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G35" t="s">
+        <v>195</v>
       </c>
       <c r="H35" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I35">
         <v>4</v>
       </c>
       <c r="J35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L35">
         <v>12</v>
@@ -1971,28 +2418,31 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" t="s">
         <v>13</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>14</v>
       </c>
-      <c r="C36" t="s">
-        <v>15</v>
-      </c>
       <c r="D36">
         <v>114</v>
       </c>
       <c r="E36" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G36" t="s">
+        <v>196</v>
       </c>
       <c r="H36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I36">
         <v>4</v>
       </c>
       <c r="J36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L36">
         <v>12</v>
@@ -2000,28 +2450,31 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" t="s">
         <v>13</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>14</v>
       </c>
-      <c r="C37" t="s">
-        <v>15</v>
-      </c>
       <c r="D37">
         <v>114</v>
       </c>
       <c r="E37" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G37" t="s">
+        <v>197</v>
       </c>
       <c r="H37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I37">
         <v>4</v>
       </c>
       <c r="J37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L37">
         <v>12</v>
@@ -2029,28 +2482,31 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B38" t="s">
         <v>13</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>14</v>
       </c>
-      <c r="C38" t="s">
-        <v>15</v>
-      </c>
       <c r="D38">
         <v>114</v>
       </c>
       <c r="E38" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G38" t="s">
+        <v>198</v>
       </c>
       <c r="H38" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I38">
         <v>4</v>
       </c>
       <c r="J38" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L38">
         <v>12</v>
@@ -2058,28 +2514,31 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" t="s">
         <v>13</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>14</v>
       </c>
-      <c r="C39" t="s">
-        <v>15</v>
-      </c>
       <c r="D39">
         <v>114</v>
       </c>
       <c r="E39" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G39" t="s">
+        <v>199</v>
       </c>
       <c r="H39" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I39">
         <v>4</v>
       </c>
       <c r="J39" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L39">
         <v>12</v>
@@ -2087,48 +2546,57 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" t="s">
         <v>13</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>14</v>
       </c>
-      <c r="C40" t="s">
-        <v>15</v>
-      </c>
       <c r="D40">
         <v>114</v>
       </c>
       <c r="E40" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G40" t="s">
+        <v>200</v>
       </c>
       <c r="H40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I40">
         <v>4</v>
       </c>
       <c r="J40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L40">
         <v>12</v>
+      </c>
+      <c r="M40" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" t="s">
         <v>13</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>14</v>
       </c>
-      <c r="C41" t="s">
-        <v>15</v>
-      </c>
       <c r="D41">
         <v>114</v>
       </c>
       <c r="E41" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G41" t="s">
+        <v>201</v>
       </c>
       <c r="H41" t="s">
         <v>62</v>
@@ -2137,27 +2605,33 @@
         <v>4</v>
       </c>
       <c r="J41" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L41">
         <v>12</v>
+      </c>
+      <c r="M41" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>12</v>
+      </c>
+      <c r="B42" t="s">
         <v>13</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>14</v>
       </c>
-      <c r="C42" t="s">
-        <v>15</v>
-      </c>
       <c r="D42">
         <v>114</v>
       </c>
       <c r="E42" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G42" t="s">
+        <v>202</v>
       </c>
       <c r="H42" t="s">
         <v>63</v>
@@ -2166,7 +2640,7 @@
         <v>4</v>
       </c>
       <c r="J42" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L42">
         <v>12</v>
@@ -2174,19 +2648,22 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" t="s">
         <v>13</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>14</v>
       </c>
-      <c r="C43" t="s">
-        <v>15</v>
-      </c>
       <c r="D43">
         <v>114</v>
       </c>
       <c r="E43" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G43" t="s">
+        <v>203</v>
       </c>
       <c r="H43" t="s">
         <v>64</v>
@@ -2195,62 +2672,65 @@
         <v>4</v>
       </c>
       <c r="J43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L43">
         <v>12</v>
-      </c>
-      <c r="M43" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>12</v>
+      </c>
+      <c r="B44" t="s">
         <v>13</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>14</v>
       </c>
-      <c r="C44" t="s">
-        <v>15</v>
-      </c>
       <c r="D44">
         <v>114</v>
       </c>
       <c r="E44" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G44" t="s">
+        <v>204</v>
       </c>
       <c r="H44" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I44">
         <v>4</v>
       </c>
       <c r="J44" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L44">
         <v>12</v>
       </c>
       <c r="M44" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45" t="s">
         <v>13</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>14</v>
       </c>
-      <c r="C45" t="s">
-        <v>15</v>
-      </c>
       <c r="D45">
         <v>114</v>
       </c>
       <c r="E45" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G45" t="s">
+        <v>205</v>
       </c>
       <c r="H45" t="s">
         <v>67</v>
@@ -2259,100 +2739,112 @@
         <v>4</v>
       </c>
       <c r="J45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L45">
         <v>12</v>
       </c>
       <c r="M45" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" t="s">
         <v>13</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>14</v>
       </c>
-      <c r="C46" t="s">
-        <v>15</v>
-      </c>
       <c r="D46">
         <v>114</v>
       </c>
       <c r="E46" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G46" t="s">
+        <v>206</v>
       </c>
       <c r="H46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I46">
         <v>4</v>
       </c>
       <c r="J46" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L46">
         <v>12</v>
       </c>
       <c r="M46" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" t="s">
         <v>13</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>14</v>
       </c>
-      <c r="C47" t="s">
-        <v>15</v>
-      </c>
       <c r="D47">
         <v>114</v>
       </c>
       <c r="E47" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G47" t="s">
+        <v>207</v>
       </c>
       <c r="H47" t="s">
         <v>70</v>
       </c>
       <c r="I47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J47" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="L47">
         <v>12</v>
+      </c>
+      <c r="M47" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>12</v>
+      </c>
+      <c r="B48" t="s">
         <v>13</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>14</v>
       </c>
-      <c r="C48" t="s">
-        <v>15</v>
-      </c>
       <c r="D48">
         <v>114</v>
       </c>
       <c r="E48" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G48" t="s">
+        <v>208</v>
       </c>
       <c r="H48" t="s">
+        <v>71</v>
+      </c>
+      <c r="I48">
+        <v>2</v>
+      </c>
+      <c r="J48" t="s">
         <v>72</v>
-      </c>
-      <c r="I48">
-        <v>2</v>
-      </c>
-      <c r="J48" t="s">
-        <v>71</v>
       </c>
       <c r="L48">
         <v>12</v>
@@ -2360,19 +2852,22 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>12</v>
+      </c>
+      <c r="B49" t="s">
         <v>13</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>14</v>
       </c>
-      <c r="C49" t="s">
-        <v>15</v>
-      </c>
       <c r="D49">
         <v>114</v>
       </c>
       <c r="E49" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G49" t="s">
+        <v>209</v>
       </c>
       <c r="H49" t="s">
         <v>73</v>
@@ -2381,7 +2876,7 @@
         <v>2</v>
       </c>
       <c r="J49" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L49">
         <v>12</v>
@@ -2389,28 +2884,31 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>12</v>
+      </c>
+      <c r="B50" t="s">
         <v>13</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>14</v>
       </c>
-      <c r="C50" t="s">
-        <v>15</v>
-      </c>
       <c r="D50">
         <v>114</v>
       </c>
       <c r="E50" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G50" t="s">
+        <v>210</v>
       </c>
       <c r="H50" t="s">
         <v>74</v>
       </c>
       <c r="I50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J50" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L50">
         <v>12</v>
@@ -2418,48 +2916,54 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" t="s">
         <v>13</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51">
+        <v>114</v>
+      </c>
+      <c r="E51" t="s">
+        <v>20</v>
+      </c>
+      <c r="G51" t="s">
+        <v>211</v>
+      </c>
+      <c r="H51" t="s">
         <v>75</v>
-      </c>
-      <c r="C51" t="s">
-        <v>76</v>
-      </c>
-      <c r="D51">
-        <v>114</v>
-      </c>
-      <c r="E51" t="s">
-        <v>77</v>
-      </c>
-      <c r="H51" t="s">
-        <v>78</v>
       </c>
       <c r="I51">
         <v>4</v>
       </c>
       <c r="J51" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="L51">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C52" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D52">
         <v>114</v>
       </c>
       <c r="E52" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="G52" t="s">
+        <v>212</v>
       </c>
       <c r="H52" t="s">
         <v>79</v>
@@ -2468,7 +2972,7 @@
         <v>4</v>
       </c>
       <c r="J52" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L52">
         <v>10</v>
@@ -2476,28 +2980,31 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C53" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D53">
         <v>114</v>
       </c>
       <c r="E53" t="s">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="G53" t="s">
+        <v>213</v>
       </c>
       <c r="H53" t="s">
         <v>80</v>
       </c>
       <c r="I53">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J53" t="s">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="L53">
         <v>10</v>
@@ -2505,28 +3012,31 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C54" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D54">
         <v>114</v>
       </c>
       <c r="E54" t="s">
-        <v>21</v>
+        <v>78</v>
+      </c>
+      <c r="G54" t="s">
+        <v>214</v>
       </c>
       <c r="H54" t="s">
+        <v>81</v>
+      </c>
+      <c r="I54">
+        <v>2</v>
+      </c>
+      <c r="J54" t="s">
         <v>82</v>
-      </c>
-      <c r="I54">
-        <v>4</v>
-      </c>
-      <c r="J54" t="s">
-        <v>57</v>
       </c>
       <c r="L54">
         <v>10</v>
@@ -2534,19 +3044,22 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C55" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D55">
         <v>114</v>
       </c>
       <c r="E55" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G55" t="s">
+        <v>215</v>
       </c>
       <c r="H55" t="s">
         <v>83</v>
@@ -2555,7 +3068,7 @@
         <v>4</v>
       </c>
       <c r="J55" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L55">
         <v>10</v>
@@ -2563,19 +3076,22 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C56" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D56">
         <v>114</v>
       </c>
       <c r="E56" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G56" t="s">
+        <v>216</v>
       </c>
       <c r="H56" t="s">
         <v>84</v>
@@ -2584,7 +3100,7 @@
         <v>4</v>
       </c>
       <c r="J56" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L56">
         <v>10</v>
@@ -2592,28 +3108,31 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C57" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D57">
         <v>114</v>
       </c>
       <c r="E57" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G57" t="s">
+        <v>217</v>
       </c>
       <c r="H57" t="s">
         <v>85</v>
       </c>
       <c r="I57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J57" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L57">
         <v>10</v>
@@ -2621,19 +3140,22 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C58" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D58">
         <v>114</v>
       </c>
       <c r="E58" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G58" t="s">
+        <v>218</v>
       </c>
       <c r="H58" t="s">
         <v>86</v>
@@ -2642,7 +3164,7 @@
         <v>2</v>
       </c>
       <c r="J58" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L58">
         <v>10</v>
@@ -2650,19 +3172,22 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C59" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D59">
         <v>114</v>
       </c>
       <c r="E59" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G59" t="s">
+        <v>219</v>
       </c>
       <c r="H59" t="s">
         <v>87</v>
@@ -2671,7 +3196,7 @@
         <v>2</v>
       </c>
       <c r="J59" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L59">
         <v>10</v>
@@ -2679,19 +3204,22 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C60" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D60">
         <v>114</v>
       </c>
       <c r="E60" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G60" t="s">
+        <v>220</v>
       </c>
       <c r="H60" t="s">
         <v>88</v>
@@ -2700,7 +3228,7 @@
         <v>2</v>
       </c>
       <c r="J60" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L60">
         <v>10</v>
@@ -2708,19 +3236,22 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C61" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D61">
         <v>114</v>
       </c>
       <c r="E61" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G61" t="s">
+        <v>221</v>
       </c>
       <c r="H61" t="s">
         <v>89</v>
@@ -2729,7 +3260,7 @@
         <v>2</v>
       </c>
       <c r="J61" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L61">
         <v>10</v>
@@ -2737,28 +3268,31 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C62" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D62">
         <v>114</v>
       </c>
       <c r="E62" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G62" t="s">
+        <v>222</v>
       </c>
       <c r="H62" t="s">
         <v>90</v>
       </c>
       <c r="I62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J62" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L62">
         <v>10</v>
@@ -2766,28 +3300,31 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C63" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D63">
         <v>114</v>
       </c>
       <c r="E63" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G63" t="s">
+        <v>223</v>
       </c>
       <c r="H63" t="s">
         <v>91</v>
       </c>
       <c r="I63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J63" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L63">
         <v>10</v>
@@ -2795,28 +3332,31 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C64" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D64">
         <v>114</v>
       </c>
       <c r="E64" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G64" t="s">
+        <v>224</v>
       </c>
       <c r="H64" t="s">
         <v>92</v>
       </c>
       <c r="I64">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J64" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L64">
         <v>10</v>
@@ -2824,19 +3364,22 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C65" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D65">
         <v>114</v>
       </c>
       <c r="E65" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G65" t="s">
+        <v>225</v>
       </c>
       <c r="H65" t="s">
         <v>93</v>
@@ -2845,7 +3388,7 @@
         <v>4</v>
       </c>
       <c r="J65" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L65">
         <v>10</v>
@@ -2853,28 +3396,31 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C66" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D66">
         <v>114</v>
       </c>
       <c r="E66" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G66" t="s">
+        <v>226</v>
       </c>
       <c r="H66" t="s">
         <v>94</v>
       </c>
       <c r="I66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J66" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L66">
         <v>10</v>
@@ -2882,19 +3428,22 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C67" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D67">
         <v>114</v>
       </c>
       <c r="E67" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G67" t="s">
+        <v>227</v>
       </c>
       <c r="H67" t="s">
         <v>95</v>
@@ -2903,7 +3452,7 @@
         <v>2</v>
       </c>
       <c r="J67" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L67">
         <v>10</v>
@@ -2911,19 +3460,22 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C68" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D68">
         <v>114</v>
       </c>
       <c r="E68" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G68" t="s">
+        <v>228</v>
       </c>
       <c r="H68" t="s">
         <v>96</v>
@@ -2932,7 +3484,7 @@
         <v>2</v>
       </c>
       <c r="J68" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L68">
         <v>10</v>
@@ -2940,28 +3492,31 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C69" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D69">
         <v>114</v>
       </c>
       <c r="E69" t="s">
-        <v>21</v>
-      </c>
-      <c r="H69" t="s">
+        <v>20</v>
+      </c>
+      <c r="G69" t="s">
+        <v>229</v>
+      </c>
+      <c r="H69" s="1" t="s">
         <v>97</v>
       </c>
       <c r="I69">
         <v>2</v>
       </c>
       <c r="J69" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L69">
         <v>10</v>
@@ -2969,19 +3524,22 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C70" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D70">
         <v>114</v>
       </c>
       <c r="E70" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G70" t="s">
+        <v>230</v>
       </c>
       <c r="H70" t="s">
         <v>98</v>
@@ -2990,7 +3548,7 @@
         <v>2</v>
       </c>
       <c r="J70" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L70">
         <v>10</v>
@@ -2998,28 +3556,31 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C71" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D71">
         <v>114</v>
       </c>
       <c r="E71" t="s">
-        <v>21</v>
-      </c>
-      <c r="H71" t="s">
+        <v>20</v>
+      </c>
+      <c r="G71" t="s">
+        <v>231</v>
+      </c>
+      <c r="H71" s="1" t="s">
         <v>99</v>
       </c>
       <c r="I71">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J71" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L71">
         <v>10</v>
@@ -3027,19 +3588,22 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C72" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D72">
         <v>114</v>
       </c>
       <c r="E72" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G72" t="s">
+        <v>201</v>
       </c>
       <c r="H72" t="s">
         <v>100</v>
@@ -3048,7 +3612,7 @@
         <v>4</v>
       </c>
       <c r="J72" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L72">
         <v>10</v>
@@ -3056,28 +3620,31 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C73" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D73">
         <v>114</v>
       </c>
       <c r="E73" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G73" t="s">
+        <v>232</v>
       </c>
       <c r="H73" t="s">
         <v>101</v>
       </c>
       <c r="I73">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J73" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L73">
         <v>10</v>
@@ -3085,19 +3652,22 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C74" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D74">
         <v>114</v>
       </c>
       <c r="E74" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G74" t="s">
+        <v>233</v>
       </c>
       <c r="H74" t="s">
         <v>102</v>
@@ -3106,7 +3676,7 @@
         <v>2</v>
       </c>
       <c r="J74" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L74">
         <v>10</v>
@@ -3114,28 +3684,31 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C75" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D75">
         <v>114</v>
       </c>
       <c r="E75" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G75" t="s">
+        <v>234</v>
       </c>
       <c r="H75" t="s">
         <v>103</v>
       </c>
       <c r="I75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J75" t="s">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="L75">
         <v>10</v>
@@ -3143,28 +3716,31 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C76" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D76">
         <v>114</v>
       </c>
       <c r="E76" t="s">
-        <v>21</v>
-      </c>
-      <c r="H76" t="s">
-        <v>105</v>
+        <v>20</v>
+      </c>
+      <c r="G76" t="s">
+        <v>235</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="I76">
         <v>3</v>
       </c>
       <c r="J76" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L76">
         <v>10</v>
@@ -3172,19 +3748,22 @@
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C77" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D77">
         <v>114</v>
       </c>
       <c r="E77" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G77" t="s">
+        <v>236</v>
       </c>
       <c r="H77" t="s">
         <v>106</v>
@@ -3193,7 +3772,7 @@
         <v>3</v>
       </c>
       <c r="J77" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L77">
         <v>10</v>
@@ -3201,19 +3780,22 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C78" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D78">
         <v>114</v>
       </c>
       <c r="E78" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G78" t="s">
+        <v>237</v>
       </c>
       <c r="H78" t="s">
         <v>107</v>
@@ -3222,7 +3804,7 @@
         <v>3</v>
       </c>
       <c r="J78" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L78">
         <v>10</v>
@@ -3230,19 +3812,22 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C79" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D79">
         <v>114</v>
       </c>
       <c r="E79" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G79" t="s">
+        <v>238</v>
       </c>
       <c r="H79" t="s">
         <v>108</v>
@@ -3251,7 +3836,7 @@
         <v>3</v>
       </c>
       <c r="J79" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L79">
         <v>10</v>
@@ -3259,19 +3844,22 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C80" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D80">
         <v>114</v>
       </c>
       <c r="E80" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G80" t="s">
+        <v>239</v>
       </c>
       <c r="H80" t="s">
         <v>109</v>
@@ -3280,7 +3868,7 @@
         <v>3</v>
       </c>
       <c r="J80" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L80">
         <v>10</v>
@@ -3288,19 +3876,22 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C81" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D81">
         <v>114</v>
       </c>
       <c r="E81" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G81" t="s">
+        <v>240</v>
       </c>
       <c r="H81" t="s">
         <v>110</v>
@@ -3309,7 +3900,7 @@
         <v>3</v>
       </c>
       <c r="J81" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L81">
         <v>10</v>
@@ -3317,19 +3908,22 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C82" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D82">
         <v>114</v>
       </c>
       <c r="E82" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G82" t="s">
+        <v>241</v>
       </c>
       <c r="H82" t="s">
         <v>111</v>
@@ -3338,7 +3932,7 @@
         <v>3</v>
       </c>
       <c r="J82" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L82">
         <v>10</v>
@@ -3346,19 +3940,22 @@
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C83" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D83">
         <v>114</v>
       </c>
       <c r="E83" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G83" t="s">
+        <v>242</v>
       </c>
       <c r="H83" t="s">
         <v>112</v>
@@ -3367,7 +3964,7 @@
         <v>3</v>
       </c>
       <c r="J83" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L83">
         <v>10</v>
@@ -3375,19 +3972,22 @@
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C84" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D84">
         <v>114</v>
       </c>
       <c r="E84" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G84" t="s">
+        <v>243</v>
       </c>
       <c r="H84" t="s">
         <v>113</v>
@@ -3396,7 +3996,7 @@
         <v>3</v>
       </c>
       <c r="J84" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L84">
         <v>10</v>
@@ -3404,19 +4004,22 @@
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C85" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D85">
         <v>114</v>
       </c>
       <c r="E85" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G85" t="s">
+        <v>244</v>
       </c>
       <c r="H85" t="s">
         <v>114</v>
@@ -3425,7 +4028,7 @@
         <v>3</v>
       </c>
       <c r="J85" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L85">
         <v>10</v>
@@ -3433,28 +4036,31 @@
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C86" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D86">
         <v>114</v>
       </c>
       <c r="E86" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G86" t="s">
+        <v>245</v>
       </c>
       <c r="H86" t="s">
         <v>115</v>
       </c>
       <c r="I86">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J86" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="L86">
         <v>10</v>
@@ -3462,28 +4068,31 @@
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C87" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D87">
         <v>114</v>
       </c>
       <c r="E87" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G87" t="s">
+        <v>246</v>
       </c>
       <c r="H87" t="s">
+        <v>116</v>
+      </c>
+      <c r="I87">
+        <v>2</v>
+      </c>
+      <c r="J87" t="s">
         <v>117</v>
-      </c>
-      <c r="I87">
-        <v>2</v>
-      </c>
-      <c r="J87" t="s">
-        <v>116</v>
       </c>
       <c r="L87">
         <v>10</v>
@@ -3491,19 +4100,22 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C88" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D88">
         <v>114</v>
       </c>
       <c r="E88" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G88" t="s">
+        <v>247</v>
       </c>
       <c r="H88" t="s">
         <v>118</v>
@@ -3512,7 +4124,7 @@
         <v>2</v>
       </c>
       <c r="J88" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L88">
         <v>10</v>
@@ -3520,19 +4132,22 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C89" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D89">
         <v>114</v>
       </c>
       <c r="E89" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G89" t="s">
+        <v>248</v>
       </c>
       <c r="H89" t="s">
         <v>119</v>
@@ -3541,7 +4156,7 @@
         <v>2</v>
       </c>
       <c r="J89" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L89">
         <v>10</v>
@@ -3549,19 +4164,22 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C90" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D90">
         <v>114</v>
       </c>
       <c r="E90" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G90" t="s">
+        <v>249</v>
       </c>
       <c r="H90" t="s">
         <v>120</v>
@@ -3570,7 +4188,7 @@
         <v>2</v>
       </c>
       <c r="J90" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L90">
         <v>10</v>
@@ -3578,19 +4196,22 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C91" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D91">
         <v>114</v>
       </c>
       <c r="E91" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="G91" t="s">
+        <v>250</v>
       </c>
       <c r="H91" t="s">
         <v>121</v>
@@ -3599,7 +4220,7 @@
         <v>2</v>
       </c>
       <c r="J91" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L91">
         <v>10</v>
@@ -3607,63 +4228,66 @@
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>12</v>
+      </c>
+      <c r="B92" t="s">
+        <v>76</v>
+      </c>
+      <c r="C92" t="s">
+        <v>77</v>
+      </c>
+      <c r="D92">
+        <v>114</v>
+      </c>
+      <c r="E92" t="s">
+        <v>20</v>
+      </c>
+      <c r="G92" t="s">
+        <v>251</v>
+      </c>
+      <c r="H92" t="s">
         <v>122</v>
       </c>
-      <c r="B92" t="s">
-        <v>123</v>
-      </c>
-      <c r="C92" t="s">
-        <v>124</v>
-      </c>
-      <c r="D92">
-        <v>114</v>
-      </c>
-      <c r="E92" t="s">
-        <v>21</v>
-      </c>
-      <c r="F92" t="s">
-        <v>125</v>
-      </c>
-      <c r="H92" t="s">
-        <v>126</v>
-      </c>
       <c r="I92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J92" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="L92">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B93" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C93" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D93">
         <v>114</v>
       </c>
       <c r="E93" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F93" t="s">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="G93" t="s">
+        <v>252</v>
       </c>
       <c r="H93" t="s">
+        <v>127</v>
+      </c>
+      <c r="I93">
+        <v>3</v>
+      </c>
+      <c r="J93" t="s">
         <v>128</v>
-      </c>
-      <c r="I93">
-        <v>6</v>
-      </c>
-      <c r="J93" t="s">
-        <v>18</v>
       </c>
       <c r="L93">
         <v>2</v>
@@ -3671,22 +4295,25 @@
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B94" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C94" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D94">
         <v>114</v>
       </c>
       <c r="E94" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F94" t="s">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="G94" t="s">
+        <v>253</v>
       </c>
       <c r="H94" t="s">
         <v>129</v>
@@ -3695,7 +4322,7 @@
         <v>6</v>
       </c>
       <c r="J94" t="s">
-        <v>130</v>
+        <v>17</v>
       </c>
       <c r="L94">
         <v>2</v>
@@ -3703,54 +4330,60 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B95" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C95" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D95">
         <v>114</v>
       </c>
       <c r="E95" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="F95" t="s">
+        <v>126</v>
+      </c>
+      <c r="G95" t="s">
+        <v>254</v>
+      </c>
+      <c r="H95" t="s">
+        <v>130</v>
+      </c>
+      <c r="I95">
+        <v>6</v>
+      </c>
+      <c r="J95" t="s">
         <v>131</v>
       </c>
-      <c r="H95" t="s">
-        <v>132</v>
-      </c>
-      <c r="I95">
-        <v>3</v>
-      </c>
-      <c r="J95" t="s">
-        <v>122</v>
-      </c>
       <c r="L95">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B96" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C96" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D96">
         <v>114</v>
       </c>
       <c r="E96" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F96" t="s">
-        <v>131</v>
+        <v>132</v>
+      </c>
+      <c r="G96" t="s">
+        <v>255</v>
       </c>
       <c r="H96" t="s">
         <v>133</v>
@@ -3759,7 +4392,7 @@
         <v>3</v>
       </c>
       <c r="J96" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L96">
         <v>6</v>
@@ -3767,54 +4400,60 @@
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B97" t="s">
+        <v>124</v>
+      </c>
+      <c r="C97" t="s">
+        <v>125</v>
+      </c>
+      <c r="D97">
+        <v>114</v>
+      </c>
+      <c r="E97" t="s">
+        <v>78</v>
+      </c>
+      <c r="F97" t="s">
+        <v>132</v>
+      </c>
+      <c r="G97" t="s">
+        <v>256</v>
+      </c>
+      <c r="H97" t="s">
+        <v>134</v>
+      </c>
+      <c r="I97">
+        <v>3</v>
+      </c>
+      <c r="J97" t="s">
         <v>123</v>
       </c>
-      <c r="C97" t="s">
-        <v>124</v>
-      </c>
-      <c r="D97">
-        <v>114</v>
-      </c>
-      <c r="E97" t="s">
-        <v>21</v>
-      </c>
-      <c r="F97" t="s">
-        <v>134</v>
-      </c>
-      <c r="H97" t="s">
-        <v>135</v>
-      </c>
-      <c r="I97">
-        <v>2</v>
-      </c>
-      <c r="J97" t="s">
-        <v>122</v>
-      </c>
       <c r="L97">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B98" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C98" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D98">
         <v>114</v>
       </c>
       <c r="E98" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F98" t="s">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="G98" t="s">
+        <v>257</v>
       </c>
       <c r="H98" t="s">
         <v>136</v>
@@ -3823,7 +4462,7 @@
         <v>2</v>
       </c>
       <c r="J98" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L98">
         <v>2</v>
@@ -3831,31 +4470,34 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B99" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C99" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D99">
         <v>114</v>
       </c>
       <c r="E99" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F99" t="s">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="G99" t="s">
+        <v>258</v>
       </c>
       <c r="H99" t="s">
         <v>137</v>
       </c>
       <c r="I99">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J99" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="L99">
         <v>2</v>
@@ -3863,31 +4505,34 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B100" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C100" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D100">
         <v>114</v>
       </c>
       <c r="E100" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F100" t="s">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="G100" t="s">
+        <v>259</v>
       </c>
       <c r="H100" t="s">
+        <v>138</v>
+      </c>
+      <c r="I100">
+        <v>3</v>
+      </c>
+      <c r="J100" t="s">
         <v>139</v>
-      </c>
-      <c r="I100">
-        <v>2</v>
-      </c>
-      <c r="J100" t="s">
-        <v>140</v>
       </c>
       <c r="L100">
         <v>2</v>
@@ -3895,31 +4540,34 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B101" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C101" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D101">
         <v>114</v>
       </c>
       <c r="E101" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F101" t="s">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="G101" t="s">
+        <v>260</v>
       </c>
       <c r="H101" t="s">
+        <v>140</v>
+      </c>
+      <c r="I101">
+        <v>2</v>
+      </c>
+      <c r="J101" t="s">
         <v>141</v>
-      </c>
-      <c r="I101">
-        <v>2</v>
-      </c>
-      <c r="J101" t="s">
-        <v>142</v>
       </c>
       <c r="L101">
         <v>2</v>
@@ -3927,31 +4575,34 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B102" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C102" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D102">
         <v>114</v>
       </c>
       <c r="E102" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F102" t="s">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="G102" t="s">
+        <v>261</v>
       </c>
       <c r="H102" t="s">
+        <v>142</v>
+      </c>
+      <c r="I102">
+        <v>2</v>
+      </c>
+      <c r="J102" t="s">
         <v>143</v>
-      </c>
-      <c r="I102">
-        <v>3</v>
-      </c>
-      <c r="J102" t="s">
-        <v>144</v>
       </c>
       <c r="L102">
         <v>2</v>
@@ -3959,31 +4610,34 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B103" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C103" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D103">
         <v>114</v>
       </c>
       <c r="E103" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F103" t="s">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="G103" t="s">
+        <v>262</v>
       </c>
       <c r="H103" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I103">
         <v>3</v>
       </c>
       <c r="J103" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L103">
         <v>2</v>
@@ -3991,31 +4645,34 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B104" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C104" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D104">
         <v>114</v>
       </c>
       <c r="E104" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F104" t="s">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="G104" t="s">
+        <v>263</v>
       </c>
       <c r="H104" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I104">
         <v>3</v>
       </c>
       <c r="J104" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L104">
         <v>2</v>
@@ -4023,31 +4680,34 @@
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B105" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C105" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D105">
         <v>114</v>
       </c>
       <c r="E105" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F105" t="s">
-        <v>134</v>
+        <v>135</v>
+      </c>
+      <c r="G105" t="s">
+        <v>264</v>
       </c>
       <c r="H105" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I105">
         <v>3</v>
       </c>
       <c r="J105" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L105">
         <v>2</v>
@@ -4055,44 +4715,82 @@
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B106" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C106" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D106">
         <v>114</v>
       </c>
       <c r="E106" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F106" t="s">
-        <v>151</v>
+        <v>135</v>
+      </c>
+      <c r="G106" t="s">
+        <v>265</v>
       </c>
       <c r="H106" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="I106">
         <v>3</v>
       </c>
       <c r="J106" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="L106">
         <v>2</v>
       </c>
     </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>123</v>
+      </c>
+      <c r="B107" t="s">
+        <v>124</v>
+      </c>
+      <c r="C107" t="s">
+        <v>125</v>
+      </c>
+      <c r="D107">
+        <v>114</v>
+      </c>
+      <c r="E107" t="s">
+        <v>20</v>
+      </c>
+      <c r="F107" t="s">
+        <v>152</v>
+      </c>
+      <c r="G107" t="s">
+        <v>266</v>
+      </c>
+      <c r="H107" t="s">
+        <v>153</v>
+      </c>
+      <c r="I107">
+        <v>3</v>
+      </c>
+      <c r="J107" t="s">
+        <v>123</v>
+      </c>
+      <c r="L107">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD235D7-F693-4BA5-B6AA-3E11869424DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5116334-EAA1-4028-A382-0588E219C2C4}">
   <dimension ref="A1:L106"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4107,36 +4805,36 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
       <c r="C1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
         <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
       </c>
       <c r="C2">
         <v>114</v>
@@ -4151,7 +4849,7 @@
         <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L2">
         <v>8</v>
@@ -4159,10 +4857,10 @@
     </row>
     <row r="3" spans="1:12" ht="66" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3">
         <v>114</v>
@@ -4176,8 +4874,8 @@
       <c r="G3">
         <v>20</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>158</v>
+      <c r="H3" s="2" t="s">
+        <v>159</v>
       </c>
       <c r="L3">
         <v>8</v>
@@ -4185,10 +4883,10 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C4">
         <v>114</v>
@@ -4203,7 +4901,7 @@
         <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="51" spans="12:12" x14ac:dyDescent="0.25">
@@ -4223,28 +4921,28 @@
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B92" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C92" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D92">
         <v>114</v>
       </c>
       <c r="F92" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H92" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I92">
         <v>3</v>
       </c>
       <c r="J92" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L92">
         <v>2</v>
@@ -4252,28 +4950,28 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B93" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C93" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D93">
         <v>114</v>
       </c>
       <c r="F93" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H93" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I93">
         <v>6</v>
       </c>
       <c r="J93" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L93">
         <v>2</v>
@@ -4281,28 +4979,28 @@
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B94" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C94" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D94">
         <v>114</v>
       </c>
       <c r="F94" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H94" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I94">
         <v>6</v>
       </c>
       <c r="J94" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L94">
         <v>2</v>
@@ -4310,31 +5008,31 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B95" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C95" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D95">
         <v>114</v>
       </c>
       <c r="E95" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F95" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H95" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I95">
         <v>3</v>
       </c>
       <c r="J95" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L95">
         <v>6</v>
@@ -4342,31 +5040,31 @@
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B96" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C96" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D96">
         <v>114</v>
       </c>
       <c r="E96" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F96" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H96" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I96">
         <v>3</v>
       </c>
       <c r="J96" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L96">
         <v>6</v>
@@ -4374,28 +5072,28 @@
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B97" t="s">
+        <v>124</v>
+      </c>
+      <c r="C97" t="s">
+        <v>125</v>
+      </c>
+      <c r="D97">
+        <v>114</v>
+      </c>
+      <c r="F97" t="s">
+        <v>135</v>
+      </c>
+      <c r="H97" t="s">
+        <v>136</v>
+      </c>
+      <c r="I97">
+        <v>2</v>
+      </c>
+      <c r="J97" t="s">
         <v>123</v>
-      </c>
-      <c r="C97" t="s">
-        <v>124</v>
-      </c>
-      <c r="D97">
-        <v>114</v>
-      </c>
-      <c r="F97" t="s">
-        <v>134</v>
-      </c>
-      <c r="H97" t="s">
-        <v>135</v>
-      </c>
-      <c r="I97">
-        <v>2</v>
-      </c>
-      <c r="J97" t="s">
-        <v>122</v>
       </c>
       <c r="L97">
         <v>2</v>
@@ -4403,28 +5101,28 @@
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B98" t="s">
+        <v>124</v>
+      </c>
+      <c r="C98" t="s">
+        <v>125</v>
+      </c>
+      <c r="D98">
+        <v>114</v>
+      </c>
+      <c r="F98" t="s">
+        <v>135</v>
+      </c>
+      <c r="H98" t="s">
+        <v>137</v>
+      </c>
+      <c r="I98">
+        <v>2</v>
+      </c>
+      <c r="J98" t="s">
         <v>123</v>
-      </c>
-      <c r="C98" t="s">
-        <v>124</v>
-      </c>
-      <c r="D98">
-        <v>114</v>
-      </c>
-      <c r="F98" t="s">
-        <v>134</v>
-      </c>
-      <c r="H98" t="s">
-        <v>136</v>
-      </c>
-      <c r="I98">
-        <v>2</v>
-      </c>
-      <c r="J98" t="s">
-        <v>122</v>
       </c>
       <c r="L98">
         <v>2</v>
@@ -4432,28 +5130,28 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B99" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C99" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D99">
         <v>114</v>
       </c>
       <c r="F99" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H99" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I99">
         <v>3</v>
       </c>
       <c r="J99" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L99">
         <v>2</v>
@@ -4461,28 +5159,28 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B100" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C100" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D100">
         <v>114</v>
       </c>
       <c r="F100" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H100" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I100">
         <v>2</v>
       </c>
       <c r="J100" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L100">
         <v>2</v>
@@ -4490,28 +5188,28 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B101" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C101" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D101">
         <v>114</v>
       </c>
       <c r="F101" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H101" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I101">
         <v>2</v>
       </c>
       <c r="J101" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L101">
         <v>2</v>
@@ -4519,28 +5217,28 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B102" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C102" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D102">
         <v>114</v>
       </c>
       <c r="F102" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H102" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="I102">
         <v>3</v>
       </c>
       <c r="J102" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L102">
         <v>2</v>
@@ -4548,28 +5246,28 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B103" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C103" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D103">
         <v>114</v>
       </c>
       <c r="F103" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H103" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I103">
         <v>3</v>
       </c>
       <c r="J103" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L103">
         <v>2</v>
@@ -4577,28 +5275,28 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B104" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C104" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D104">
         <v>114</v>
       </c>
       <c r="F104" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H104" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I104">
         <v>3</v>
       </c>
       <c r="J104" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L104">
         <v>2</v>
@@ -4606,28 +5304,28 @@
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B105" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C105" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D105">
         <v>114</v>
       </c>
       <c r="F105" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H105" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I105">
         <v>3</v>
       </c>
       <c r="J105" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L105">
         <v>2</v>
@@ -4635,35 +5333,35 @@
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B106" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C106" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D106">
         <v>114</v>
       </c>
       <c r="F106" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H106" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I106">
         <v>3</v>
       </c>
       <c r="J106" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L106">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/master_data.xlsx
+++ b/master_data.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\000_專案計畫\20260107_學分學程查詢功能\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{15817F7B-165C-44F3-AC8F-2AC404DBE885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C8A36E-D882-4479-902A-3D176D27F7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{08D0A2CF-AB20-4F18-B6B3-AB47673F728A}"/>
   </bookViews>
   <sheets>
     <sheet name="科目表" sheetId="1" r:id="rId1"/>
-    <sheet name="學程規範總額" sheetId="2" r:id="rId2"/>
+    <sheet name="學程規範總額" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">科目表!$A$1:$K$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">科目表!$A$1:$K$107</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="269">
   <si>
     <t>學院</t>
   </si>
@@ -552,336 +552,329 @@
     <t>備註 (模組要求)</t>
   </si>
   <si>
+    <t>17624</t>
+  </si>
+  <si>
+    <t>02109</t>
+  </si>
+  <si>
+    <t>18087</t>
+  </si>
+  <si>
+    <t>18981</t>
+  </si>
+  <si>
+    <t>21877</t>
+  </si>
+  <si>
+    <t>32707</t>
+  </si>
+  <si>
+    <t>21256</t>
+  </si>
+  <si>
+    <t>31502</t>
+  </si>
+  <si>
+    <t>11230</t>
+  </si>
+  <si>
+    <t>11059</t>
+  </si>
+  <si>
+    <t>07253</t>
+  </si>
+  <si>
+    <t>07254</t>
+  </si>
+  <si>
+    <t>07269</t>
+  </si>
+  <si>
+    <t>07272</t>
+  </si>
+  <si>
+    <t>10035</t>
+  </si>
+  <si>
+    <t>08021</t>
+  </si>
+  <si>
+    <t>07268</t>
+  </si>
+  <si>
+    <t>02905</t>
+  </si>
+  <si>
+    <t>01625</t>
+  </si>
+  <si>
+    <t>01466</t>
+  </si>
+  <si>
+    <t>02243</t>
+  </si>
+  <si>
+    <t>02480</t>
+  </si>
+  <si>
+    <t>01977</t>
+  </si>
+  <si>
+    <t>01313</t>
+  </si>
+  <si>
+    <t>21269</t>
+  </si>
+  <si>
+    <t>22433</t>
+  </si>
+  <si>
+    <t>02894</t>
+  </si>
+  <si>
+    <t>01979</t>
+  </si>
+  <si>
+    <t>01203</t>
+  </si>
+  <si>
+    <t>01146</t>
+  </si>
+  <si>
+    <t>01119</t>
+  </si>
+  <si>
+    <t>01113</t>
+  </si>
+  <si>
+    <t>01299</t>
+  </si>
+  <si>
+    <t>01635</t>
+  </si>
+  <si>
+    <t>15998</t>
+  </si>
+  <si>
+    <t>02938</t>
+  </si>
+  <si>
+    <t>04534</t>
+  </si>
+  <si>
+    <t>01608</t>
+  </si>
+  <si>
+    <t>12724</t>
+  </si>
+  <si>
+    <t>22515</t>
+  </si>
+  <si>
+    <t>01556</t>
+  </si>
+  <si>
+    <t>01565</t>
+  </si>
+  <si>
+    <t>04538</t>
+  </si>
+  <si>
+    <t>15903</t>
+  </si>
+  <si>
+    <t>05163</t>
+  </si>
+  <si>
+    <t>23401</t>
+  </si>
+  <si>
+    <t>20178</t>
+  </si>
+  <si>
+    <t>20179</t>
+  </si>
+  <si>
+    <t>16324</t>
+  </si>
+  <si>
+    <t>01121</t>
+  </si>
+  <si>
+    <t>12728</t>
+  </si>
+  <si>
+    <t>15294</t>
+  </si>
+  <si>
+    <t>13644</t>
+  </si>
+  <si>
+    <t>01699</t>
+  </si>
+  <si>
+    <t>01913</t>
+  </si>
+  <si>
+    <t>09994</t>
+  </si>
+  <si>
+    <t>01600</t>
+  </si>
+  <si>
+    <t>17555</t>
+  </si>
+  <si>
+    <t>04868</t>
+  </si>
+  <si>
+    <t>16261</t>
+  </si>
+  <si>
+    <t>04189</t>
+  </si>
+  <si>
+    <t>01221</t>
+  </si>
+  <si>
+    <t>16785</t>
+  </si>
+  <si>
+    <t>03940</t>
+  </si>
+  <si>
+    <t>13737</t>
+  </si>
+  <si>
+    <t>30449</t>
+  </si>
+  <si>
+    <t>31407</t>
+  </si>
+  <si>
+    <t>30443</t>
+  </si>
+  <si>
+    <t>34280</t>
+  </si>
+  <si>
+    <t>35014</t>
+  </si>
+  <si>
+    <t>04254</t>
+  </si>
+  <si>
+    <t>35268</t>
+  </si>
+  <si>
+    <t>23660</t>
+  </si>
+  <si>
+    <t>12798</t>
+  </si>
+  <si>
+    <t>05752</t>
+  </si>
+  <si>
+    <t>07070</t>
+  </si>
+  <si>
+    <t>10467</t>
+  </si>
+  <si>
+    <t>02962</t>
+  </si>
+  <si>
+    <t>07603</t>
+  </si>
+  <si>
+    <t>06184</t>
+  </si>
+  <si>
+    <t>13769</t>
+  </si>
+  <si>
+    <t>18958</t>
+  </si>
+  <si>
+    <t>19781</t>
+  </si>
+  <si>
+    <t>19758</t>
+  </si>
+  <si>
+    <t>01194</t>
+  </si>
+  <si>
+    <t>03400</t>
+  </si>
+  <si>
+    <t>05444</t>
+  </si>
+  <si>
+    <t>07050</t>
+  </si>
+  <si>
+    <t>07422</t>
+  </si>
+  <si>
+    <t>22492</t>
+  </si>
+  <si>
+    <t>24495</t>
+  </si>
+  <si>
+    <t>01863</t>
+  </si>
+  <si>
+    <t>03056</t>
+  </si>
+  <si>
+    <t>13027</t>
+  </si>
+  <si>
+    <t>24327</t>
+  </si>
+  <si>
+    <t>36024</t>
+  </si>
+  <si>
+    <t>36025</t>
+  </si>
+  <si>
+    <t>31441</t>
+  </si>
+  <si>
+    <t>36739</t>
+  </si>
+  <si>
+    <t>24565</t>
+  </si>
+  <si>
+    <t>32392</t>
+  </si>
+  <si>
+    <t>03001</t>
+  </si>
+  <si>
+    <t>05347</t>
+  </si>
+  <si>
+    <t>02490</t>
+  </si>
+  <si>
+    <t>36029</t>
+  </si>
+  <si>
     <t>必修8學分，選修12學分</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>必修核心課程(共十學分) ,選修課程(至少須修讀十學分) ,
 開設課程及開放選修名額以當年度課表為準</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>本微學程應修學分數 12 學分。包括基礎課程(2 學分)、重點課程(6 學分)、專業/進階課程(2 學分)、總整課程(2 學分)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">特殊教育與適性教學
-</t>
-  </si>
-  <si>
-    <t>17624</t>
-  </si>
-  <si>
-    <t>02109</t>
-  </si>
-  <si>
-    <t>18087</t>
-  </si>
-  <si>
-    <t>18981</t>
-  </si>
-  <si>
-    <t>21877</t>
-  </si>
-  <si>
-    <t>32707</t>
-  </si>
-  <si>
-    <t>21256</t>
-  </si>
-  <si>
-    <t>31502</t>
-  </si>
-  <si>
-    <t>11230</t>
-  </si>
-  <si>
-    <t>11059</t>
-  </si>
-  <si>
-    <t>07253</t>
-  </si>
-  <si>
-    <t>07254</t>
-  </si>
-  <si>
-    <t>07269</t>
-  </si>
-  <si>
-    <t>07272</t>
-  </si>
-  <si>
-    <t>10035</t>
-  </si>
-  <si>
-    <t>08021</t>
-  </si>
-  <si>
-    <t>07268</t>
-  </si>
-  <si>
-    <t>02905</t>
-  </si>
-  <si>
-    <t>01625</t>
-  </si>
-  <si>
-    <t>01466</t>
-  </si>
-  <si>
-    <t>02243</t>
-  </si>
-  <si>
-    <t>02480</t>
-  </si>
-  <si>
-    <t>01977</t>
-  </si>
-  <si>
-    <t>01313</t>
-  </si>
-  <si>
-    <t>21269</t>
-  </si>
-  <si>
-    <t>22433</t>
-  </si>
-  <si>
-    <t>02894</t>
-  </si>
-  <si>
-    <t>01979</t>
-  </si>
-  <si>
-    <t>01203</t>
-  </si>
-  <si>
-    <t>01146</t>
-  </si>
-  <si>
-    <t>01119</t>
-  </si>
-  <si>
-    <t>01113</t>
-  </si>
-  <si>
-    <t>01299</t>
-  </si>
-  <si>
-    <t>01635</t>
-  </si>
-  <si>
-    <t>15998</t>
-  </si>
-  <si>
-    <t>02938</t>
-  </si>
-  <si>
-    <t>04534</t>
-  </si>
-  <si>
-    <t>01608</t>
-  </si>
-  <si>
-    <t>12724</t>
-  </si>
-  <si>
-    <t>22515</t>
-  </si>
-  <si>
-    <t>01556</t>
-  </si>
-  <si>
-    <t>01565</t>
-  </si>
-  <si>
-    <t>04538</t>
-  </si>
-  <si>
-    <t>15903</t>
-  </si>
-  <si>
-    <t>05163</t>
-  </si>
-  <si>
-    <t>23401</t>
-  </si>
-  <si>
-    <t>20178</t>
-  </si>
-  <si>
-    <t>20179</t>
-  </si>
-  <si>
-    <t>16324</t>
-  </si>
-  <si>
-    <t>01121</t>
-  </si>
-  <si>
-    <t>12728</t>
-  </si>
-  <si>
-    <t>15294</t>
-  </si>
-  <si>
-    <t>13644</t>
-  </si>
-  <si>
-    <t>01699</t>
-  </si>
-  <si>
-    <t>01913</t>
-  </si>
-  <si>
-    <t>09994</t>
-  </si>
-  <si>
-    <t>01600</t>
-  </si>
-  <si>
-    <t>17555</t>
-  </si>
-  <si>
-    <t>04868</t>
-  </si>
-  <si>
-    <t>16261</t>
-  </si>
-  <si>
-    <t>04189</t>
-  </si>
-  <si>
-    <t>01221</t>
-  </si>
-  <si>
-    <t>16785</t>
-  </si>
-  <si>
-    <t>03940</t>
-  </si>
-  <si>
-    <t>13737</t>
-  </si>
-  <si>
-    <t>30449</t>
-  </si>
-  <si>
-    <t>31407</t>
-  </si>
-  <si>
-    <t>30443</t>
-  </si>
-  <si>
-    <t>34280</t>
-  </si>
-  <si>
-    <t>35014</t>
-  </si>
-  <si>
-    <t>04254</t>
-  </si>
-  <si>
-    <t>35268</t>
-  </si>
-  <si>
-    <t>23660</t>
-  </si>
-  <si>
-    <t>12798</t>
-  </si>
-  <si>
-    <t>05752</t>
-  </si>
-  <si>
-    <t>07070</t>
-  </si>
-  <si>
-    <t>10467</t>
-  </si>
-  <si>
-    <t>02962</t>
-  </si>
-  <si>
-    <t>07603</t>
-  </si>
-  <si>
-    <t>06184</t>
-  </si>
-  <si>
-    <t>13769</t>
-  </si>
-  <si>
-    <t>18958</t>
-  </si>
-  <si>
-    <t>19781</t>
-  </si>
-  <si>
-    <t>19758</t>
-  </si>
-  <si>
-    <t>01194</t>
-  </si>
-  <si>
-    <t>03400</t>
-  </si>
-  <si>
-    <t>05444</t>
-  </si>
-  <si>
-    <t>07050</t>
-  </si>
-  <si>
-    <t>07422</t>
-  </si>
-  <si>
-    <t>22492</t>
-  </si>
-  <si>
-    <t>24495</t>
-  </si>
-  <si>
-    <t>01863</t>
-  </si>
-  <si>
-    <t>03056</t>
-  </si>
-  <si>
-    <t>13027</t>
-  </si>
-  <si>
-    <t>24327</t>
-  </si>
-  <si>
-    <t>36024</t>
-  </si>
-  <si>
-    <t>36025</t>
-  </si>
-  <si>
-    <t>31441</t>
-  </si>
-  <si>
-    <t>36739</t>
-  </si>
-  <si>
-    <t>24565</t>
-  </si>
-  <si>
-    <t>32392</t>
-  </si>
-  <si>
-    <t>03001</t>
-  </si>
-  <si>
-    <t>05347</t>
-  </si>
-  <si>
-    <t>02490</t>
-  </si>
-  <si>
-    <t>36029</t>
   </si>
 </sst>
 </file>
@@ -935,15 +928,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1349,7 +1339,7 @@
         <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
@@ -1381,7 +1371,7 @@
         <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H3" t="s">
         <v>18</v>
@@ -1413,7 +1403,7 @@
         <v>21</v>
       </c>
       <c r="G4" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="H4" t="s">
         <v>22</v>
@@ -1445,7 +1435,7 @@
         <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="H5" t="s">
         <v>24</v>
@@ -1477,7 +1467,7 @@
         <v>21</v>
       </c>
       <c r="G6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="H6" t="s">
         <v>25</v>
@@ -1509,7 +1499,7 @@
         <v>21</v>
       </c>
       <c r="G7" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="H7" t="s">
         <v>26</v>
@@ -1541,7 +1531,7 @@
         <v>21</v>
       </c>
       <c r="G8" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="H8" t="s">
         <v>27</v>
@@ -1573,7 +1563,7 @@
         <v>21</v>
       </c>
       <c r="G9" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="H9" t="s">
         <v>28</v>
@@ -1605,7 +1595,7 @@
         <v>21</v>
       </c>
       <c r="G10" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H10" t="s">
         <v>29</v>
@@ -1637,7 +1627,7 @@
         <v>21</v>
       </c>
       <c r="G11" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H11" t="s">
         <v>30</v>
@@ -1669,7 +1659,7 @@
         <v>21</v>
       </c>
       <c r="G12" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="H12" t="s">
         <v>31</v>
@@ -1701,7 +1691,7 @@
         <v>21</v>
       </c>
       <c r="G13" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="H13" t="s">
         <v>32</v>
@@ -1733,7 +1723,7 @@
         <v>21</v>
       </c>
       <c r="G14" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="H14" t="s">
         <v>33</v>
@@ -1765,7 +1755,7 @@
         <v>21</v>
       </c>
       <c r="G15" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H15" t="s">
         <v>34</v>
@@ -1797,7 +1787,7 @@
         <v>21</v>
       </c>
       <c r="G16" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="H16" t="s">
         <v>35</v>
@@ -1829,7 +1819,7 @@
         <v>21</v>
       </c>
       <c r="G17" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="H17" t="s">
         <v>36</v>
@@ -1861,7 +1851,7 @@
         <v>21</v>
       </c>
       <c r="G18" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="H18" t="s">
         <v>37</v>
@@ -1893,7 +1883,7 @@
         <v>21</v>
       </c>
       <c r="G19" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="H19" t="s">
         <v>38</v>
@@ -1925,7 +1915,7 @@
         <v>21</v>
       </c>
       <c r="G20" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H20" t="s">
         <v>39</v>
@@ -1957,7 +1947,7 @@
         <v>21</v>
       </c>
       <c r="G21" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="H21" t="s">
         <v>40</v>
@@ -1989,7 +1979,7 @@
         <v>21</v>
       </c>
       <c r="G22" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H22" t="s">
         <v>41</v>
@@ -2021,7 +2011,7 @@
         <v>21</v>
       </c>
       <c r="G23" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H23" t="s">
         <v>42</v>
@@ -2053,7 +2043,7 @@
         <v>21</v>
       </c>
       <c r="G24" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="H24" t="s">
         <v>43</v>
@@ -2085,7 +2075,7 @@
         <v>21</v>
       </c>
       <c r="G25" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="H25" t="s">
         <v>44</v>
@@ -2117,7 +2107,7 @@
         <v>21</v>
       </c>
       <c r="G26" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="H26" t="s">
         <v>45</v>
@@ -2149,7 +2139,7 @@
         <v>21</v>
       </c>
       <c r="G27" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="H27" t="s">
         <v>46</v>
@@ -2181,7 +2171,7 @@
         <v>21</v>
       </c>
       <c r="G28" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="H28" t="s">
         <v>47</v>
@@ -2213,7 +2203,7 @@
         <v>21</v>
       </c>
       <c r="G29" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="H29" t="s">
         <v>48</v>
@@ -2245,7 +2235,7 @@
         <v>21</v>
       </c>
       <c r="G30" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="H30" t="s">
         <v>49</v>
@@ -2277,7 +2267,7 @@
         <v>21</v>
       </c>
       <c r="G31" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="H31" t="s">
         <v>50</v>
@@ -2309,7 +2299,7 @@
         <v>21</v>
       </c>
       <c r="G32" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="H32" t="s">
         <v>51</v>
@@ -2341,7 +2331,7 @@
         <v>21</v>
       </c>
       <c r="G33" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="H33" t="s">
         <v>52</v>
@@ -2373,7 +2363,7 @@
         <v>21</v>
       </c>
       <c r="G34" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="H34" t="s">
         <v>53</v>
@@ -2405,7 +2395,7 @@
         <v>21</v>
       </c>
       <c r="G35" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="H35" t="s">
         <v>54</v>
@@ -2437,7 +2427,7 @@
         <v>21</v>
       </c>
       <c r="G36" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="H36" t="s">
         <v>56</v>
@@ -2469,7 +2459,7 @@
         <v>21</v>
       </c>
       <c r="G37" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="H37" t="s">
         <v>58</v>
@@ -2501,7 +2491,7 @@
         <v>21</v>
       </c>
       <c r="G38" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="H38" t="s">
         <v>59</v>
@@ -2533,7 +2523,7 @@
         <v>21</v>
       </c>
       <c r="G39" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="H39" t="s">
         <v>60</v>
@@ -2565,7 +2555,7 @@
         <v>21</v>
       </c>
       <c r="G40" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="H40" t="s">
         <v>61</v>
@@ -2600,7 +2590,7 @@
         <v>21</v>
       </c>
       <c r="G41" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="H41" t="s">
         <v>63</v>
@@ -2635,7 +2625,7 @@
         <v>21</v>
       </c>
       <c r="G42" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="H42" t="s">
         <v>64</v>
@@ -2667,7 +2657,7 @@
         <v>21</v>
       </c>
       <c r="G43" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="H43" t="s">
         <v>65</v>
@@ -2699,7 +2689,7 @@
         <v>21</v>
       </c>
       <c r="G44" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="H44" t="s">
         <v>66</v>
@@ -2734,7 +2724,7 @@
         <v>21</v>
       </c>
       <c r="G45" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="H45" t="s">
         <v>68</v>
@@ -2769,7 +2759,7 @@
         <v>21</v>
       </c>
       <c r="G46" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H46" t="s">
         <v>69</v>
@@ -2804,7 +2794,7 @@
         <v>21</v>
       </c>
       <c r="G47" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="H47" t="s">
         <v>71</v>
@@ -2839,7 +2829,7 @@
         <v>21</v>
       </c>
       <c r="G48" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H48" t="s">
         <v>72</v>
@@ -2871,7 +2861,7 @@
         <v>21</v>
       </c>
       <c r="G49" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="H49" t="s">
         <v>74</v>
@@ -2903,7 +2893,7 @@
         <v>21</v>
       </c>
       <c r="G50" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="H50" t="s">
         <v>75</v>
@@ -2935,7 +2925,7 @@
         <v>21</v>
       </c>
       <c r="G51" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="H51" t="s">
         <v>76</v>
@@ -2967,7 +2957,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="H52" t="s">
         <v>81</v>
@@ -2999,7 +2989,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="H53" t="s">
         <v>82</v>
@@ -3031,7 +3021,7 @@
         <v>80</v>
       </c>
       <c r="G54" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H54" t="s">
         <v>83</v>
@@ -3063,7 +3053,7 @@
         <v>85</v>
       </c>
       <c r="G55" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="H55" t="s">
         <v>86</v>
@@ -3095,7 +3085,7 @@
         <v>85</v>
       </c>
       <c r="G56" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="H56" t="s">
         <v>87</v>
@@ -3127,7 +3117,7 @@
         <v>85</v>
       </c>
       <c r="G57" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="H57" t="s">
         <v>88</v>
@@ -3159,7 +3149,7 @@
         <v>85</v>
       </c>
       <c r="G58" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="H58" t="s">
         <v>89</v>
@@ -3191,7 +3181,7 @@
         <v>85</v>
       </c>
       <c r="G59" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="H59" t="s">
         <v>90</v>
@@ -3223,7 +3213,7 @@
         <v>85</v>
       </c>
       <c r="G60" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="H60" t="s">
         <v>91</v>
@@ -3255,7 +3245,7 @@
         <v>85</v>
       </c>
       <c r="G61" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="H61" t="s">
         <v>92</v>
@@ -3287,7 +3277,7 @@
         <v>85</v>
       </c>
       <c r="G62" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="H62" t="s">
         <v>93</v>
@@ -3319,7 +3309,7 @@
         <v>85</v>
       </c>
       <c r="G63" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="H63" t="s">
         <v>94</v>
@@ -3351,7 +3341,7 @@
         <v>85</v>
       </c>
       <c r="G64" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="H64" t="s">
         <v>95</v>
@@ -3383,7 +3373,7 @@
         <v>85</v>
       </c>
       <c r="G65" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="H65" t="s">
         <v>96</v>
@@ -3415,7 +3405,7 @@
         <v>85</v>
       </c>
       <c r="G66" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="H66" t="s">
         <v>97</v>
@@ -3447,7 +3437,7 @@
         <v>85</v>
       </c>
       <c r="G67" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="H67" t="s">
         <v>98</v>
@@ -3479,7 +3469,7 @@
         <v>85</v>
       </c>
       <c r="G68" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="H68" t="s">
         <v>99</v>
@@ -3511,7 +3501,7 @@
         <v>85</v>
       </c>
       <c r="G69" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>100</v>
@@ -3543,7 +3533,7 @@
         <v>85</v>
       </c>
       <c r="G70" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="H70" t="s">
         <v>101</v>
@@ -3575,7 +3565,7 @@
         <v>85</v>
       </c>
       <c r="G71" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>102</v>
@@ -3607,7 +3597,7 @@
         <v>85</v>
       </c>
       <c r="G72" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="H72" t="s">
         <v>103</v>
@@ -3639,7 +3629,7 @@
         <v>85</v>
       </c>
       <c r="G73" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H73" t="s">
         <v>104</v>
@@ -3671,7 +3661,7 @@
         <v>85</v>
       </c>
       <c r="G74" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="H74" t="s">
         <v>105</v>
@@ -3703,7 +3693,7 @@
         <v>85</v>
       </c>
       <c r="G75" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="H75" t="s">
         <v>106</v>
@@ -3735,7 +3725,7 @@
         <v>85</v>
       </c>
       <c r="G76" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>107</v>
@@ -3767,7 +3757,7 @@
         <v>85</v>
       </c>
       <c r="G77" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="H77" t="s">
         <v>109</v>
@@ -3799,7 +3789,7 @@
         <v>85</v>
       </c>
       <c r="G78" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="H78" t="s">
         <v>110</v>
@@ -3831,7 +3821,7 @@
         <v>85</v>
       </c>
       <c r="G79" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H79" t="s">
         <v>111</v>
@@ -3863,7 +3853,7 @@
         <v>85</v>
       </c>
       <c r="G80" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="H80" t="s">
         <v>112</v>
@@ -3895,7 +3885,7 @@
         <v>85</v>
       </c>
       <c r="G81" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="H81" t="s">
         <v>113</v>
@@ -3927,7 +3917,7 @@
         <v>85</v>
       </c>
       <c r="G82" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H82" t="s">
         <v>114</v>
@@ -3959,7 +3949,7 @@
         <v>85</v>
       </c>
       <c r="G83" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H83" t="s">
         <v>115</v>
@@ -3991,7 +3981,7 @@
         <v>85</v>
       </c>
       <c r="G84" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="H84" t="s">
         <v>116</v>
@@ -4023,7 +4013,7 @@
         <v>85</v>
       </c>
       <c r="G85" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="H85" t="s">
         <v>117</v>
@@ -4055,7 +4045,7 @@
         <v>85</v>
       </c>
       <c r="G86" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="H86" t="s">
         <v>118</v>
@@ -4087,7 +4077,7 @@
         <v>85</v>
       </c>
       <c r="G87" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="H87" t="s">
         <v>119</v>
@@ -4119,7 +4109,7 @@
         <v>85</v>
       </c>
       <c r="G88" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="H88" t="s">
         <v>121</v>
@@ -4151,7 +4141,7 @@
         <v>85</v>
       </c>
       <c r="G89" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H89" t="s">
         <v>122</v>
@@ -4183,7 +4173,7 @@
         <v>85</v>
       </c>
       <c r="G90" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="H90" t="s">
         <v>123</v>
@@ -4215,7 +4205,7 @@
         <v>85</v>
       </c>
       <c r="G91" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="H91" t="s">
         <v>124</v>
@@ -4247,7 +4237,7 @@
         <v>85</v>
       </c>
       <c r="G92" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="H92" t="s">
         <v>125</v>
@@ -4279,7 +4269,7 @@
         <v>129</v>
       </c>
       <c r="G93" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H93" t="s">
         <v>130</v>
@@ -4311,7 +4301,7 @@
         <v>129</v>
       </c>
       <c r="G94" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="H94" t="s">
         <v>132</v>
@@ -4343,7 +4333,7 @@
         <v>129</v>
       </c>
       <c r="G95" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="H95" t="s">
         <v>133</v>
@@ -4375,7 +4365,7 @@
         <v>135</v>
       </c>
       <c r="G96" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="H96" t="s">
         <v>136</v>
@@ -4407,7 +4397,7 @@
         <v>135</v>
       </c>
       <c r="G97" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H97" t="s">
         <v>137</v>
@@ -4439,7 +4429,7 @@
         <v>138</v>
       </c>
       <c r="G98" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H98" t="s">
         <v>139</v>
@@ -4471,7 +4461,7 @@
         <v>138</v>
       </c>
       <c r="G99" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="H99" t="s">
         <v>140</v>
@@ -4503,7 +4493,7 @@
         <v>138</v>
       </c>
       <c r="G100" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="H100" t="s">
         <v>141</v>
@@ -4535,7 +4525,7 @@
         <v>138</v>
       </c>
       <c r="G101" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="H101" t="s">
         <v>143</v>
@@ -4567,7 +4557,7 @@
         <v>138</v>
       </c>
       <c r="G102" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="H102" t="s">
         <v>145</v>
@@ -4599,7 +4589,7 @@
         <v>138</v>
       </c>
       <c r="G103" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="H103" t="s">
         <v>147</v>
@@ -4631,7 +4621,7 @@
         <v>138</v>
       </c>
       <c r="G104" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="H104" t="s">
         <v>149</v>
@@ -4663,7 +4653,7 @@
         <v>138</v>
       </c>
       <c r="G105" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H105" t="s">
         <v>151</v>
@@ -4695,7 +4685,7 @@
         <v>138</v>
       </c>
       <c r="G106" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="H106" t="s">
         <v>153</v>
@@ -4727,7 +4717,7 @@
         <v>155</v>
       </c>
       <c r="G107" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="H107" t="s">
         <v>156</v>
@@ -4740,22 +4730,18 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K107" xr:uid="{9D10CD69-4BB0-4CE2-BE79-D66EB69BEEA1}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DDE97CF-3E99-45D7-8AB9-CFC98FACF223}">
-  <dimension ref="A1:K106"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2CF5EF1-7FEB-43D6-B456-CF0AF6E5C949}">
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="22.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4801,10 +4787,10 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>77</v>
       </c>
@@ -4823,8 +4809,8 @@
       <c r="F3">
         <v>20</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>162</v>
+      <c r="G3" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -4847,423 +4833,11 @@
         <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="51" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K51">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="52" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K52">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K53">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>126</v>
-      </c>
-      <c r="B92" t="s">
-        <v>127</v>
-      </c>
-      <c r="C92" t="s">
-        <v>128</v>
-      </c>
-      <c r="D92">
-        <v>114</v>
-      </c>
-      <c r="G92" t="s">
-        <v>130</v>
-      </c>
-      <c r="H92">
-        <v>3</v>
-      </c>
-      <c r="I92" t="s">
-        <v>131</v>
-      </c>
-      <c r="K92">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>126</v>
-      </c>
-      <c r="B93" t="s">
-        <v>127</v>
-      </c>
-      <c r="C93" t="s">
-        <v>128</v>
-      </c>
-      <c r="D93">
-        <v>114</v>
-      </c>
-      <c r="G93" t="s">
-        <v>132</v>
-      </c>
-      <c r="H93">
-        <v>6</v>
-      </c>
-      <c r="I93" t="s">
-        <v>17</v>
-      </c>
-      <c r="K93">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>126</v>
-      </c>
-      <c r="B94" t="s">
-        <v>127</v>
-      </c>
-      <c r="C94" t="s">
-        <v>128</v>
-      </c>
-      <c r="D94">
-        <v>114</v>
-      </c>
-      <c r="G94" t="s">
-        <v>133</v>
-      </c>
-      <c r="H94">
-        <v>6</v>
-      </c>
-      <c r="I94" t="s">
-        <v>134</v>
-      </c>
-      <c r="K94">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>126</v>
-      </c>
-      <c r="B95" t="s">
-        <v>127</v>
-      </c>
-      <c r="C95" t="s">
-        <v>128</v>
-      </c>
-      <c r="D95">
-        <v>114</v>
-      </c>
-      <c r="E95" t="s">
-        <v>79</v>
-      </c>
-      <c r="G95" t="s">
-        <v>136</v>
-      </c>
-      <c r="H95">
-        <v>3</v>
-      </c>
-      <c r="I95" t="s">
-        <v>126</v>
-      </c>
-      <c r="K95">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>126</v>
-      </c>
-      <c r="B96" t="s">
-        <v>127</v>
-      </c>
-      <c r="C96" t="s">
-        <v>128</v>
-      </c>
-      <c r="D96">
-        <v>114</v>
-      </c>
-      <c r="E96" t="s">
-        <v>79</v>
-      </c>
-      <c r="G96" t="s">
-        <v>137</v>
-      </c>
-      <c r="H96">
-        <v>3</v>
-      </c>
-      <c r="I96" t="s">
-        <v>126</v>
-      </c>
-      <c r="K96">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>126</v>
-      </c>
-      <c r="B97" t="s">
-        <v>127</v>
-      </c>
-      <c r="C97" t="s">
-        <v>128</v>
-      </c>
-      <c r="D97">
-        <v>114</v>
-      </c>
-      <c r="G97" t="s">
-        <v>139</v>
-      </c>
-      <c r="H97">
-        <v>2</v>
-      </c>
-      <c r="I97" t="s">
-        <v>126</v>
-      </c>
-      <c r="K97">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>126</v>
-      </c>
-      <c r="B98" t="s">
-        <v>127</v>
-      </c>
-      <c r="C98" t="s">
-        <v>128</v>
-      </c>
-      <c r="D98">
-        <v>114</v>
-      </c>
-      <c r="G98" t="s">
-        <v>140</v>
-      </c>
-      <c r="H98">
-        <v>2</v>
-      </c>
-      <c r="I98" t="s">
-        <v>126</v>
-      </c>
-      <c r="K98">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>126</v>
-      </c>
-      <c r="B99" t="s">
-        <v>127</v>
-      </c>
-      <c r="C99" t="s">
-        <v>128</v>
-      </c>
-      <c r="D99">
-        <v>114</v>
-      </c>
-      <c r="G99" t="s">
-        <v>141</v>
-      </c>
-      <c r="H99">
-        <v>3</v>
-      </c>
-      <c r="I99" t="s">
-        <v>142</v>
-      </c>
-      <c r="K99">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>126</v>
-      </c>
-      <c r="B100" t="s">
-        <v>127</v>
-      </c>
-      <c r="C100" t="s">
-        <v>128</v>
-      </c>
-      <c r="D100">
-        <v>114</v>
-      </c>
-      <c r="G100" t="s">
-        <v>143</v>
-      </c>
-      <c r="H100">
-        <v>2</v>
-      </c>
-      <c r="I100" t="s">
-        <v>144</v>
-      </c>
-      <c r="K100">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>126</v>
-      </c>
-      <c r="B101" t="s">
-        <v>127</v>
-      </c>
-      <c r="C101" t="s">
-        <v>128</v>
-      </c>
-      <c r="D101">
-        <v>114</v>
-      </c>
-      <c r="G101" t="s">
-        <v>145</v>
-      </c>
-      <c r="H101">
-        <v>2</v>
-      </c>
-      <c r="I101" t="s">
-        <v>146</v>
-      </c>
-      <c r="K101">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>126</v>
-      </c>
-      <c r="B102" t="s">
-        <v>127</v>
-      </c>
-      <c r="C102" t="s">
-        <v>128</v>
-      </c>
-      <c r="D102">
-        <v>114</v>
-      </c>
-      <c r="G102" t="s">
-        <v>164</v>
-      </c>
-      <c r="H102">
-        <v>3</v>
-      </c>
-      <c r="I102" t="s">
-        <v>148</v>
-      </c>
-      <c r="K102">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>126</v>
-      </c>
-      <c r="B103" t="s">
-        <v>127</v>
-      </c>
-      <c r="C103" t="s">
-        <v>128</v>
-      </c>
-      <c r="D103">
-        <v>114</v>
-      </c>
-      <c r="G103" t="s">
-        <v>149</v>
-      </c>
-      <c r="H103">
-        <v>3</v>
-      </c>
-      <c r="I103" t="s">
-        <v>150</v>
-      </c>
-      <c r="K103">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>126</v>
-      </c>
-      <c r="B104" t="s">
-        <v>127</v>
-      </c>
-      <c r="C104" t="s">
-        <v>128</v>
-      </c>
-      <c r="D104">
-        <v>114</v>
-      </c>
-      <c r="G104" t="s">
-        <v>151</v>
-      </c>
-      <c r="H104">
-        <v>3</v>
-      </c>
-      <c r="I104" t="s">
-        <v>152</v>
-      </c>
-      <c r="K104">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>126</v>
-      </c>
-      <c r="B105" t="s">
-        <v>127</v>
-      </c>
-      <c r="C105" t="s">
-        <v>128</v>
-      </c>
-      <c r="D105">
-        <v>114</v>
-      </c>
-      <c r="G105" t="s">
-        <v>153</v>
-      </c>
-      <c r="H105">
-        <v>3</v>
-      </c>
-      <c r="I105" t="s">
-        <v>154</v>
-      </c>
-      <c r="K105">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>126</v>
-      </c>
-      <c r="B106" t="s">
-        <v>127</v>
-      </c>
-      <c r="C106" t="s">
-        <v>128</v>
-      </c>
-      <c r="D106">
-        <v>114</v>
-      </c>
-      <c r="G106" t="s">
-        <v>156</v>
-      </c>
-      <c r="H106">
-        <v>3</v>
-      </c>
-      <c r="I106" t="s">
-        <v>126</v>
-      </c>
-      <c r="K106">
-        <v>2</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/master_data.xlsx
+++ b/master_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\000_專案計畫\20260107_學分學程查詢功能\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70C8A36E-D882-4479-902A-3D176D27F7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88545AC4-6A30-4398-8D7A-6BC7E320244A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{08D0A2CF-AB20-4F18-B6B3-AB47673F728A}"/>
+    <workbookView xWindow="1965" yWindow="1575" windowWidth="21600" windowHeight="11295" xr2:uid="{08D0A2CF-AB20-4F18-B6B3-AB47673F728A}"/>
   </bookViews>
   <sheets>
     <sheet name="科目表" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="271">
   <si>
     <t>學院</t>
   </si>
@@ -874,7 +874,16 @@
 開設課程及開放選修名額以當年度課表為準</t>
   </si>
   <si>
+    <t>K860</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>教育大數據微學程</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>本微學程應修學分數 12 學分。包括基礎課程(2 學分)、重點課程(6 學分)、專業/進階課程(2 學分)、總整課程(2 學分)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1272,7 +1281,7 @@
   <dimension ref="A1:K107"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.75" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="9.5" bestFit="1" customWidth="1"/>
@@ -4254,10 +4263,10 @@
         <v>126</v>
       </c>
       <c r="B93" t="s">
-        <v>127</v>
+        <v>268</v>
       </c>
       <c r="C93" t="s">
-        <v>128</v>
+        <v>269</v>
       </c>
       <c r="D93">
         <v>114</v>
@@ -4730,7 +4739,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K107" xr:uid="{9D10CD69-4BB0-4CE2-BE79-D66EB69BEEA1}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4815,10 +4823,10 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>127</v>
+        <v>268</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>269</v>
       </c>
       <c r="C4">
         <v>114</v>
@@ -4833,7 +4841,7 @@
         <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>

--- a/master_data.xlsx
+++ b/master_data.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\000_專案計畫\20260107_學分學程查詢功能\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88545AC4-6A30-4398-8D7A-6BC7E320244A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8CF664C-9DDE-46A0-BF5D-17A83B886959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1965" yWindow="1575" windowWidth="21600" windowHeight="11295" xr2:uid="{08D0A2CF-AB20-4F18-B6B3-AB47673F728A}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3796A25F-1F4D-4179-BD9A-8404DC01DA19}"/>
   </bookViews>
   <sheets>
     <sheet name="科目表" sheetId="1" r:id="rId1"/>
-    <sheet name="學程規範總額" sheetId="3" r:id="rId2"/>
+    <sheet name="學程規範總額" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">科目表!$A$1:$K$107</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">科目表!$A$1:$L$108</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="290">
   <si>
     <t>學院</t>
   </si>
@@ -73,7 +73,12 @@
     <t>學分數</t>
   </si>
   <si>
-    <t>課程認抵範圍</t>
+    <t>認抵單位代碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>備註</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>互斥代碼</t>
@@ -98,10 +103,18 @@
     <t>書目學理論與實務</t>
   </si>
   <si>
+    <t>D10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>圖資系</t>
   </si>
   <si>
     <t>國學導讀</t>
+  </si>
+  <si>
+    <t>D01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>中文系</t>
@@ -117,6 +130,10 @@
     <t>古籍資源管理</t>
   </si>
   <si>
+    <t>D106</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>圖資系碩士班</t>
   </si>
   <si>
@@ -213,10 +230,18 @@
     <t>易經</t>
   </si>
   <si>
+    <t>D01,D03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>中文系or哲學系</t>
   </si>
   <si>
     <t>先秦諸子哲學</t>
+  </si>
+  <si>
+    <t>D03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>哲學系</t>
@@ -270,6 +295,10 @@
     <t>西洋博物館史</t>
   </si>
   <si>
+    <t>D02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>歷史系</t>
   </si>
   <si>
@@ -383,6 +412,10 @@
     <t>敘說、反映與實踐導論</t>
   </si>
   <si>
+    <t>D39</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>心理系</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -420,6 +453,10 @@
     <t>心理衛生</t>
   </si>
   <si>
+    <t>D95</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>臨心系</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -455,6 +492,10 @@
     <t>程式設計概論</t>
   </si>
   <si>
+    <t>D65,D74,D0F,D0E,D76</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>經濟系、資管系、金企系、企管系、統資系</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -465,6 +506,10 @@
     <t>程式設計</t>
   </si>
   <si>
+    <t>D55,D56</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>物理系</t>
   </si>
   <si>
@@ -475,6 +520,10 @@
     <t>機器學習</t>
   </si>
   <si>
+    <t>DTG,GTG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>資料探索及資訊視覺化</t>
   </si>
   <si>
@@ -491,16 +540,29 @@
     <t>大數據資料分析與應用</t>
   </si>
   <si>
+    <t>CQ1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>AI學士後系</t>
   </si>
   <si>
     <t>生成式AI與生活</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C1T</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>資創學程</t>
   </si>
   <si>
     <t>教育科技發展趨勢</t>
+  </si>
+  <si>
+    <t>D0V</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>領科學程三</t>
@@ -510,16 +572,28 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>DE1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>中等教育學程</t>
   </si>
   <si>
     <t>資料庫系統概論</t>
   </si>
   <si>
+    <t>D51</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>資工系</t>
   </si>
   <si>
     <t>資料庫</t>
+  </si>
+  <si>
+    <t>D1B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>資數系</t>
@@ -529,6 +603,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>D71,D74,D76</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>會計系、資管系、統資系</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -552,338 +630,339 @@
     <t>備註 (模組要求)</t>
   </si>
   <si>
-    <t>17624</t>
-  </si>
-  <si>
-    <t>02109</t>
-  </si>
-  <si>
-    <t>18087</t>
-  </si>
-  <si>
-    <t>18981</t>
-  </si>
-  <si>
-    <t>21877</t>
-  </si>
-  <si>
-    <t>32707</t>
-  </si>
-  <si>
-    <t>21256</t>
-  </si>
-  <si>
-    <t>31502</t>
-  </si>
-  <si>
-    <t>11230</t>
-  </si>
-  <si>
-    <t>11059</t>
-  </si>
-  <si>
-    <t>07253</t>
-  </si>
-  <si>
-    <t>07254</t>
-  </si>
-  <si>
-    <t>07269</t>
-  </si>
-  <si>
-    <t>07272</t>
-  </si>
-  <si>
-    <t>10035</t>
-  </si>
-  <si>
-    <t>08021</t>
-  </si>
-  <si>
-    <t>07268</t>
-  </si>
-  <si>
-    <t>02905</t>
-  </si>
-  <si>
-    <t>01625</t>
-  </si>
-  <si>
-    <t>01466</t>
-  </si>
-  <si>
-    <t>02243</t>
-  </si>
-  <si>
-    <t>02480</t>
-  </si>
-  <si>
-    <t>01977</t>
-  </si>
-  <si>
-    <t>01313</t>
-  </si>
-  <si>
-    <t>21269</t>
-  </si>
-  <si>
-    <t>22433</t>
-  </si>
-  <si>
-    <t>02894</t>
-  </si>
-  <si>
-    <t>01979</t>
-  </si>
-  <si>
-    <t>01203</t>
-  </si>
-  <si>
-    <t>01146</t>
-  </si>
-  <si>
-    <t>01119</t>
-  </si>
-  <si>
-    <t>01113</t>
-  </si>
-  <si>
-    <t>01299</t>
-  </si>
-  <si>
-    <t>01635</t>
-  </si>
-  <si>
-    <t>15998</t>
-  </si>
-  <si>
-    <t>02938</t>
-  </si>
-  <si>
-    <t>04534</t>
-  </si>
-  <si>
-    <t>01608</t>
-  </si>
-  <si>
-    <t>12724</t>
-  </si>
-  <si>
-    <t>22515</t>
-  </si>
-  <si>
-    <t>01556</t>
-  </si>
-  <si>
-    <t>01565</t>
-  </si>
-  <si>
-    <t>04538</t>
-  </si>
-  <si>
-    <t>15903</t>
-  </si>
-  <si>
-    <t>05163</t>
-  </si>
-  <si>
-    <t>23401</t>
-  </si>
-  <si>
-    <t>20178</t>
-  </si>
-  <si>
-    <t>20179</t>
-  </si>
-  <si>
-    <t>16324</t>
-  </si>
-  <si>
-    <t>01121</t>
-  </si>
-  <si>
-    <t>12728</t>
-  </si>
-  <si>
-    <t>15294</t>
-  </si>
-  <si>
-    <t>13644</t>
-  </si>
-  <si>
-    <t>01699</t>
-  </si>
-  <si>
-    <t>01913</t>
-  </si>
-  <si>
-    <t>09994</t>
-  </si>
-  <si>
-    <t>01600</t>
-  </si>
-  <si>
-    <t>17555</t>
-  </si>
-  <si>
-    <t>04868</t>
-  </si>
-  <si>
-    <t>16261</t>
-  </si>
-  <si>
-    <t>04189</t>
-  </si>
-  <si>
-    <t>01221</t>
-  </si>
-  <si>
-    <t>16785</t>
-  </si>
-  <si>
-    <t>03940</t>
-  </si>
-  <si>
-    <t>13737</t>
-  </si>
-  <si>
-    <t>30449</t>
-  </si>
-  <si>
-    <t>31407</t>
-  </si>
-  <si>
-    <t>30443</t>
-  </si>
-  <si>
-    <t>34280</t>
-  </si>
-  <si>
-    <t>35014</t>
-  </si>
-  <si>
-    <t>04254</t>
-  </si>
-  <si>
-    <t>35268</t>
-  </si>
-  <si>
-    <t>23660</t>
-  </si>
-  <si>
-    <t>12798</t>
-  </si>
-  <si>
-    <t>05752</t>
-  </si>
-  <si>
-    <t>07070</t>
-  </si>
-  <si>
-    <t>10467</t>
-  </si>
-  <si>
-    <t>02962</t>
-  </si>
-  <si>
-    <t>07603</t>
-  </si>
-  <si>
-    <t>06184</t>
-  </si>
-  <si>
-    <t>13769</t>
-  </si>
-  <si>
-    <t>18958</t>
-  </si>
-  <si>
-    <t>19781</t>
-  </si>
-  <si>
-    <t>19758</t>
-  </si>
-  <si>
-    <t>01194</t>
-  </si>
-  <si>
-    <t>03400</t>
-  </si>
-  <si>
-    <t>05444</t>
-  </si>
-  <si>
-    <t>07050</t>
-  </si>
-  <si>
-    <t>07422</t>
-  </si>
-  <si>
-    <t>22492</t>
-  </si>
-  <si>
-    <t>24495</t>
-  </si>
-  <si>
-    <t>01863</t>
-  </si>
-  <si>
-    <t>03056</t>
-  </si>
-  <si>
-    <t>13027</t>
-  </si>
-  <si>
-    <t>24327</t>
-  </si>
-  <si>
-    <t>36024</t>
-  </si>
-  <si>
-    <t>36025</t>
-  </si>
-  <si>
-    <t>31441</t>
-  </si>
-  <si>
-    <t>36739</t>
-  </si>
-  <si>
-    <t>24565</t>
-  </si>
-  <si>
-    <t>32392</t>
-  </si>
-  <si>
-    <t>03001</t>
-  </si>
-  <si>
-    <t>05347</t>
-  </si>
-  <si>
-    <t>02490</t>
-  </si>
-  <si>
-    <t>36029</t>
-  </si>
-  <si>
     <t>必修8學分，選修12學分</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>必修核心課程(共十學分) ,選修課程(至少須修讀十學分) ,
 開設課程及開放選修名額以當年度課表為準</t>
-  </si>
-  <si>
-    <t>K860</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>教育大數據微學程</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>本微學程應修學分數 12 學分。包括基礎課程(2 學分)、重點課程(6 學分)、專業/進階課程(2 學分)、總整課程(2 學分)</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>生成式AI與生活</t>
+  </si>
+  <si>
+    <t xml:space="preserve">特殊教育與適性教學
+</t>
+  </si>
+  <si>
+    <t>17624</t>
+  </si>
+  <si>
+    <t>02109</t>
+  </si>
+  <si>
+    <t>18087</t>
+  </si>
+  <si>
+    <t>18981</t>
+  </si>
+  <si>
+    <t>21877</t>
+  </si>
+  <si>
+    <t>32707</t>
+  </si>
+  <si>
+    <t>21256</t>
+  </si>
+  <si>
+    <t>31502</t>
+  </si>
+  <si>
+    <t>11230</t>
+  </si>
+  <si>
+    <t>11059</t>
+  </si>
+  <si>
+    <t>07253</t>
+  </si>
+  <si>
+    <t>07254</t>
+  </si>
+  <si>
+    <t>07269</t>
+  </si>
+  <si>
+    <t>07272</t>
+  </si>
+  <si>
+    <t>10035</t>
+  </si>
+  <si>
+    <t>08021</t>
+  </si>
+  <si>
+    <t>07268</t>
+  </si>
+  <si>
+    <t>02905</t>
+  </si>
+  <si>
+    <t>01625</t>
+  </si>
+  <si>
+    <t>01466</t>
+  </si>
+  <si>
+    <t>02243</t>
+  </si>
+  <si>
+    <t>02480</t>
+  </si>
+  <si>
+    <t>01977</t>
+  </si>
+  <si>
+    <t>01313</t>
+  </si>
+  <si>
+    <t>21269</t>
+  </si>
+  <si>
+    <t>22433</t>
+  </si>
+  <si>
+    <t>02894</t>
+  </si>
+  <si>
+    <t>01979</t>
+  </si>
+  <si>
+    <t>01203</t>
+  </si>
+  <si>
+    <t>01146</t>
+  </si>
+  <si>
+    <t>01119</t>
+  </si>
+  <si>
+    <t>01113</t>
+  </si>
+  <si>
+    <t>01299</t>
+  </si>
+  <si>
+    <t>01635</t>
+  </si>
+  <si>
+    <t>15998</t>
+  </si>
+  <si>
+    <t>02938</t>
+  </si>
+  <si>
+    <t>04534</t>
+  </si>
+  <si>
+    <t>01608</t>
+  </si>
+  <si>
+    <t>12724</t>
+  </si>
+  <si>
+    <t>22515</t>
+  </si>
+  <si>
+    <t>01556</t>
+  </si>
+  <si>
+    <t>01565</t>
+  </si>
+  <si>
+    <t>04538</t>
+  </si>
+  <si>
+    <t>15903</t>
+  </si>
+  <si>
+    <t>05163</t>
+  </si>
+  <si>
+    <t>23401</t>
+  </si>
+  <si>
+    <t>20178</t>
+  </si>
+  <si>
+    <t>20179</t>
+  </si>
+  <si>
+    <t>16324</t>
+  </si>
+  <si>
+    <t>01121</t>
+  </si>
+  <si>
+    <t>12728</t>
+  </si>
+  <si>
+    <t>15294</t>
+  </si>
+  <si>
+    <t>13644</t>
+  </si>
+  <si>
+    <t>01699</t>
+  </si>
+  <si>
+    <t>01913</t>
+  </si>
+  <si>
+    <t>09994</t>
+  </si>
+  <si>
+    <t>01600</t>
+  </si>
+  <si>
+    <t>17555</t>
+  </si>
+  <si>
+    <t>04868</t>
+  </si>
+  <si>
+    <t>16261</t>
+  </si>
+  <si>
+    <t>04189</t>
+  </si>
+  <si>
+    <t>01221</t>
+  </si>
+  <si>
+    <t>16785</t>
+  </si>
+  <si>
+    <t>03940</t>
+  </si>
+  <si>
+    <t>13737</t>
+  </si>
+  <si>
+    <t>30449</t>
+  </si>
+  <si>
+    <t>31407</t>
+  </si>
+  <si>
+    <t>30443</t>
+  </si>
+  <si>
+    <t>34280</t>
+  </si>
+  <si>
+    <t>35014</t>
+  </si>
+  <si>
+    <t>04254</t>
+  </si>
+  <si>
+    <t>35268</t>
+  </si>
+  <si>
+    <t>23660</t>
+  </si>
+  <si>
+    <t>12798</t>
+  </si>
+  <si>
+    <t>05752</t>
+  </si>
+  <si>
+    <t>07070</t>
+  </si>
+  <si>
+    <t>10467</t>
+  </si>
+  <si>
+    <t>02962</t>
+  </si>
+  <si>
+    <t>07603</t>
+  </si>
+  <si>
+    <t>06184</t>
+  </si>
+  <si>
+    <t>13769</t>
+  </si>
+  <si>
+    <t>18958</t>
+  </si>
+  <si>
+    <t>19781</t>
+  </si>
+  <si>
+    <t>19758</t>
+  </si>
+  <si>
+    <t>01194</t>
+  </si>
+  <si>
+    <t>03400</t>
+  </si>
+  <si>
+    <t>05444</t>
+  </si>
+  <si>
+    <t>07050</t>
+  </si>
+  <si>
+    <t>07422</t>
+  </si>
+  <si>
+    <t>22492</t>
+  </si>
+  <si>
+    <t>24495</t>
+  </si>
+  <si>
+    <t>01863</t>
+  </si>
+  <si>
+    <t>03056</t>
+  </si>
+  <si>
+    <t>13027</t>
+  </si>
+  <si>
+    <t>24327</t>
+  </si>
+  <si>
+    <t>36024</t>
+  </si>
+  <si>
+    <t>36025</t>
+  </si>
+  <si>
+    <t>31441</t>
+  </si>
+  <si>
+    <t>36739</t>
+  </si>
+  <si>
+    <t>24565</t>
+  </si>
+  <si>
+    <t>32392</t>
+  </si>
+  <si>
+    <t>03001</t>
+  </si>
+  <si>
+    <t>05347</t>
+  </si>
+  <si>
+    <t>02490</t>
+  </si>
+  <si>
+    <t>36029</t>
   </si>
 </sst>
 </file>
@@ -937,12 +1016,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1277,11 +1359,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D10CD69-4BB0-4CE2-BE79-D66EB69BEEA1}">
-  <dimension ref="A1:K107"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{321D3090-431E-4533-AB60-1226A3D839D2}">
+  <dimension ref="A1:L107"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.75" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="9.5" bestFit="1" customWidth="1"/>
@@ -1289,11 +1371,12 @@
     <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="25.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1327,3415 +1410,3736 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D2">
         <v>114</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2">
         <v>4</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>114</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>162</v>
+        <v>186</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I3">
         <v>4</v>
       </c>
       <c r="J3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4">
         <v>114</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>163</v>
+        <v>187</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I4">
         <v>2</v>
       </c>
       <c r="J4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="K4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5">
         <v>114</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G5" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I5">
         <v>2</v>
       </c>
       <c r="J5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="K5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6">
         <v>114</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="H6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I6">
         <v>2</v>
       </c>
       <c r="J6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="K6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7">
         <v>114</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="H7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I7">
         <v>4</v>
       </c>
       <c r="J7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8">
         <v>114</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G8" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="H8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
       <c r="J8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9">
         <v>114</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="H9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I9">
         <v>4</v>
       </c>
       <c r="J9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D10">
         <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G10" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="H10" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I10">
         <v>4</v>
       </c>
       <c r="J10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11">
         <v>114</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G11" t="s">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="H11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I11">
         <v>4</v>
       </c>
       <c r="J11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K11" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12">
         <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G12" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="H12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I12">
         <v>4</v>
       </c>
       <c r="J12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K12" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D13">
         <v>114</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F13" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G13" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I13">
         <v>4</v>
       </c>
       <c r="J13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D14">
         <v>114</v>
       </c>
       <c r="E14" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F14" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G14" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="H14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I14">
         <v>4</v>
       </c>
       <c r="J14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K14" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15">
         <v>114</v>
       </c>
       <c r="E15" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F15" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G15" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="H15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I15">
         <v>4</v>
       </c>
       <c r="J15" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K15" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D16">
         <v>114</v>
       </c>
       <c r="E16" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F16" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G16" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="H16" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I16">
         <v>4</v>
       </c>
       <c r="J16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D17">
         <v>114</v>
       </c>
       <c r="E17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F17" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G17" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="H17" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="I17">
         <v>4</v>
       </c>
       <c r="J17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D18">
         <v>114</v>
       </c>
       <c r="E18" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F18" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G18" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="H18" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I18">
         <v>2</v>
       </c>
       <c r="J18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K18" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D19">
         <v>114</v>
       </c>
       <c r="E19" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F19" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G19" t="s">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="H19" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="I19">
         <v>4</v>
       </c>
       <c r="J19" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="K19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D20">
         <v>114</v>
       </c>
       <c r="E20" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F20" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G20" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="H20" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I20">
         <v>4</v>
       </c>
       <c r="J20" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="K20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D21">
         <v>114</v>
       </c>
       <c r="E21" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F21" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G21" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="H21" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I21">
         <v>4</v>
       </c>
       <c r="J21" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="K21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D22">
         <v>114</v>
       </c>
       <c r="E22" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F22" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G22" t="s">
-        <v>181</v>
+        <v>205</v>
       </c>
       <c r="H22" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I22">
         <v>4</v>
       </c>
       <c r="J22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="K22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D23">
         <v>114</v>
       </c>
       <c r="E23" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G23" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="H23" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I23">
         <v>4</v>
       </c>
       <c r="J23" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="K23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D24">
         <v>114</v>
       </c>
       <c r="E24" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F24" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G24" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="H24" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I24">
         <v>4</v>
       </c>
       <c r="J24" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="K24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D25">
         <v>114</v>
       </c>
       <c r="E25" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F25" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G25" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="H25" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I25">
         <v>4</v>
       </c>
       <c r="J25" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="K25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D26">
         <v>114</v>
       </c>
       <c r="E26" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F26" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G26" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="H26" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I26">
         <v>4</v>
       </c>
       <c r="J26" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="K26" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D27">
         <v>114</v>
       </c>
       <c r="E27" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F27" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G27" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="H27" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I27">
         <v>4</v>
       </c>
       <c r="J27" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="K27" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D28">
         <v>114</v>
       </c>
       <c r="E28" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F28" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G28" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="H28" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I28">
         <v>4</v>
       </c>
       <c r="J28" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="K28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C29" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D29">
         <v>114</v>
       </c>
       <c r="E29" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F29" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G29" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="H29" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="I29">
         <v>4</v>
       </c>
       <c r="J29" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="K29" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D30">
         <v>114</v>
       </c>
       <c r="E30" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F30" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G30" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="H30" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I30">
         <v>4</v>
       </c>
       <c r="J30" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="K30" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D31">
         <v>114</v>
       </c>
       <c r="E31" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F31" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G31" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="H31" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="I31">
         <v>4</v>
       </c>
       <c r="J31" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="K31" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D32">
         <v>114</v>
       </c>
       <c r="E32" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F32" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G32" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="H32" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="I32">
         <v>4</v>
       </c>
       <c r="J32" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="K32" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D33">
         <v>114</v>
       </c>
       <c r="E33" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F33" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G33" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="H33" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I33">
         <v>6</v>
       </c>
       <c r="J33" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="K33" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D34">
         <v>114</v>
       </c>
       <c r="E34" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F34" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G34" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="H34" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I34">
         <v>4</v>
       </c>
       <c r="J34" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+      <c r="K34" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D35">
         <v>114</v>
       </c>
       <c r="E35" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F35" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G35" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="H35" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I35">
         <v>4</v>
       </c>
       <c r="J35" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="K35" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D36">
         <v>114</v>
       </c>
       <c r="E36" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F36" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G36" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="H36" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="I36">
         <v>4</v>
       </c>
       <c r="J36" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K36" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D37">
         <v>114</v>
       </c>
       <c r="E37" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F37" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G37" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="H37" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="I37">
         <v>4</v>
       </c>
       <c r="J37" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K37" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D38">
         <v>114</v>
       </c>
       <c r="E38" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F38" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G38" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="H38" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="I38">
         <v>4</v>
       </c>
       <c r="J38" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K38" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D39">
         <v>114</v>
       </c>
       <c r="E39" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F39" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G39" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="H39" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="I39">
         <v>4</v>
       </c>
       <c r="J39" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K39" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D40">
         <v>114</v>
       </c>
       <c r="E40" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F40" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G40" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="H40" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="I40">
         <v>4</v>
       </c>
       <c r="J40" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K40" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="L40" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D41">
         <v>114</v>
       </c>
       <c r="E41" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F41" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G41" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="H41" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="I41">
         <v>4</v>
       </c>
       <c r="J41" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K41" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="L41" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D42">
         <v>114</v>
       </c>
       <c r="E42" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F42" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G42" t="s">
-        <v>201</v>
+        <v>225</v>
       </c>
       <c r="H42" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="I42">
         <v>4</v>
       </c>
       <c r="J42" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K42" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D43">
         <v>114</v>
       </c>
       <c r="E43" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F43" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G43" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
       <c r="H43" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="I43">
         <v>4</v>
       </c>
       <c r="J43" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K43" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D44">
         <v>114</v>
       </c>
       <c r="E44" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F44" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G44" t="s">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="H44" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I44">
         <v>4</v>
       </c>
       <c r="J44" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K44" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="L44" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D45">
         <v>114</v>
       </c>
       <c r="E45" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F45" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G45" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="H45" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="I45">
         <v>4</v>
       </c>
       <c r="J45" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K45" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="L45" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D46">
         <v>114</v>
       </c>
       <c r="E46" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F46" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G46" t="s">
-        <v>205</v>
+        <v>229</v>
       </c>
       <c r="H46" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="I46">
         <v>4</v>
       </c>
       <c r="J46" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K46" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="L46" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D47">
         <v>114</v>
       </c>
       <c r="E47" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F47" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G47" t="s">
-        <v>206</v>
+        <v>230</v>
       </c>
       <c r="H47" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="I47">
         <v>4</v>
       </c>
       <c r="J47" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K47" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+      <c r="L47" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D48">
         <v>114</v>
       </c>
       <c r="E48" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F48" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G48" t="s">
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="H48" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I48">
         <v>2</v>
       </c>
       <c r="J48" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="K48" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D49">
         <v>114</v>
       </c>
       <c r="E49" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F49" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G49" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="H49" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I49">
         <v>2</v>
       </c>
       <c r="J49" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="K49" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D50">
         <v>114</v>
       </c>
       <c r="E50" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F50" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G50" t="s">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="H50" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I50">
         <v>2</v>
       </c>
       <c r="J50" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="K50" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D51">
         <v>114</v>
       </c>
       <c r="E51" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F51" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G51" t="s">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="H51" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I51">
         <v>4</v>
       </c>
       <c r="J51" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="K51" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C52" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D52">
         <v>114</v>
       </c>
       <c r="E52" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F52" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G52" t="s">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="H52" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="I52">
         <v>4</v>
       </c>
       <c r="J52" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K52" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C53" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D53">
         <v>114</v>
       </c>
       <c r="E53" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F53" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G53" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="H53" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="I53">
         <v>4</v>
       </c>
       <c r="J53" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K53" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C54" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D54">
         <v>114</v>
       </c>
       <c r="E54" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F54" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G54" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="H54" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="I54">
         <v>2</v>
       </c>
       <c r="J54" t="s">
+        <v>62</v>
+      </c>
+      <c r="K54" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>12</v>
+      </c>
+      <c r="B55" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>11</v>
-      </c>
-      <c r="B55" t="s">
-        <v>77</v>
-      </c>
       <c r="C55" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D55">
         <v>114</v>
       </c>
       <c r="E55" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F55" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G55" t="s">
-        <v>214</v>
+        <v>238</v>
       </c>
       <c r="H55" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="I55">
         <v>4</v>
       </c>
       <c r="J55" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K55" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C56" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D56">
         <v>114</v>
       </c>
       <c r="E56" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F56" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G56" t="s">
-        <v>215</v>
+        <v>239</v>
       </c>
       <c r="H56" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="I56">
         <v>4</v>
       </c>
       <c r="J56" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K56" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C57" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D57">
         <v>114</v>
       </c>
       <c r="E57" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F57" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G57" t="s">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="H57" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="I57">
         <v>4</v>
       </c>
       <c r="J57" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K57" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C58" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D58">
         <v>114</v>
       </c>
       <c r="E58" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F58" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G58" t="s">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="H58" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="I58">
         <v>2</v>
       </c>
       <c r="J58" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K58" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C59" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D59">
         <v>114</v>
       </c>
       <c r="E59" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F59" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G59" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="H59" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="I59">
         <v>2</v>
       </c>
       <c r="J59" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K59" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C60" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D60">
         <v>114</v>
       </c>
       <c r="E60" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F60" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G60" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="H60" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="I60">
         <v>2</v>
       </c>
       <c r="J60" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K60" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C61" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D61">
         <v>114</v>
       </c>
       <c r="E61" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F61" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G61" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="H61" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="I61">
         <v>2</v>
       </c>
       <c r="J61" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K61" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C62" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D62">
         <v>114</v>
       </c>
       <c r="E62" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F62" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G62" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="H62" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="I62">
         <v>2</v>
       </c>
       <c r="J62" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K62" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C63" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D63">
         <v>114</v>
       </c>
       <c r="E63" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F63" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G63" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="H63" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="I63">
         <v>4</v>
       </c>
       <c r="J63" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K63" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C64" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D64">
         <v>114</v>
       </c>
       <c r="E64" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F64" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G64" t="s">
-        <v>223</v>
+        <v>247</v>
       </c>
       <c r="H64" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="I64">
         <v>2</v>
       </c>
       <c r="J64" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K64" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C65" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D65">
         <v>114</v>
       </c>
       <c r="E65" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F65" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G65" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="H65" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="I65">
         <v>4</v>
       </c>
       <c r="J65" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K65" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C66" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D66">
         <v>114</v>
       </c>
       <c r="E66" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F66" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G66" t="s">
-        <v>225</v>
+        <v>249</v>
       </c>
       <c r="H66" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="I66">
         <v>4</v>
       </c>
       <c r="J66" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K66" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C67" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D67">
         <v>114</v>
       </c>
       <c r="E67" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F67" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G67" t="s">
-        <v>226</v>
+        <v>250</v>
       </c>
       <c r="H67" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="I67">
         <v>2</v>
       </c>
       <c r="J67" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K67" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C68" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D68">
         <v>114</v>
       </c>
       <c r="E68" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F68" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G68" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="H68" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="I68">
         <v>2</v>
       </c>
       <c r="J68" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K68" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C69" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D69">
         <v>114</v>
       </c>
       <c r="E69" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F69" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G69" t="s">
-        <v>228</v>
+        <v>252</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="I69">
         <v>2</v>
       </c>
       <c r="J69" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K69" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C70" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D70">
         <v>114</v>
       </c>
       <c r="E70" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F70" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G70" t="s">
-        <v>229</v>
+        <v>253</v>
       </c>
       <c r="H70" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="I70">
         <v>2</v>
       </c>
       <c r="J70" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K70" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C71" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D71">
         <v>114</v>
       </c>
       <c r="E71" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F71" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G71" t="s">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="I71">
         <v>2</v>
       </c>
       <c r="J71" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K71" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C72" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D72">
         <v>114</v>
       </c>
       <c r="E72" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F72" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G72" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="H72" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="I72">
         <v>4</v>
       </c>
       <c r="J72" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K72" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C73" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D73">
         <v>114</v>
       </c>
       <c r="E73" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F73" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G73" t="s">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="H73" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="I73">
         <v>4</v>
       </c>
       <c r="J73" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K73" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C74" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D74">
         <v>114</v>
       </c>
       <c r="E74" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F74" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G74" t="s">
-        <v>232</v>
+        <v>256</v>
       </c>
       <c r="H74" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="I74">
         <v>2</v>
       </c>
       <c r="J74" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K74" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C75" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D75">
         <v>114</v>
       </c>
       <c r="E75" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F75" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G75" t="s">
-        <v>233</v>
+        <v>257</v>
       </c>
       <c r="H75" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="I75">
         <v>2</v>
       </c>
       <c r="J75" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+      <c r="K75" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C76" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D76">
         <v>114</v>
       </c>
       <c r="E76" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F76" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G76" t="s">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="I76">
         <v>3</v>
       </c>
       <c r="J76" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="K76" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C77" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D77">
         <v>114</v>
       </c>
       <c r="E77" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F77" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G77" t="s">
-        <v>235</v>
+        <v>259</v>
       </c>
       <c r="H77" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="I77">
         <v>3</v>
       </c>
       <c r="J77" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="K77" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C78" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D78">
         <v>114</v>
       </c>
       <c r="E78" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F78" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G78" t="s">
-        <v>236</v>
+        <v>260</v>
       </c>
       <c r="H78" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="I78">
         <v>3</v>
       </c>
       <c r="J78" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="K78" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C79" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D79">
         <v>114</v>
       </c>
       <c r="E79" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F79" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G79" t="s">
-        <v>237</v>
+        <v>261</v>
       </c>
       <c r="H79" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="I79">
         <v>3</v>
       </c>
       <c r="J79" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="K79" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D80">
         <v>114</v>
       </c>
       <c r="E80" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F80" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G80" t="s">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="H80" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="I80">
         <v>3</v>
       </c>
       <c r="J80" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="K80" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C81" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D81">
         <v>114</v>
       </c>
       <c r="E81" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F81" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G81" t="s">
-        <v>239</v>
+        <v>263</v>
       </c>
       <c r="H81" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="I81">
         <v>3</v>
       </c>
       <c r="J81" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="K81" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C82" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D82">
         <v>114</v>
       </c>
       <c r="E82" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F82" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G82" t="s">
-        <v>240</v>
+        <v>264</v>
       </c>
       <c r="H82" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="I82">
         <v>3</v>
       </c>
       <c r="J82" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="K82" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C83" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D83">
         <v>114</v>
       </c>
       <c r="E83" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F83" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G83" t="s">
-        <v>241</v>
+        <v>265</v>
       </c>
       <c r="H83" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="I83">
         <v>3</v>
       </c>
       <c r="J83" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="K83" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C84" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D84">
         <v>114</v>
       </c>
       <c r="E84" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F84" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G84" t="s">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="H84" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="I84">
         <v>3</v>
       </c>
       <c r="J84" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="K84" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C85" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D85">
         <v>114</v>
       </c>
       <c r="E85" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F85" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G85" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="H85" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="I85">
         <v>3</v>
       </c>
       <c r="J85" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="K85" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D86">
         <v>114</v>
       </c>
       <c r="E86" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F86" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G86" t="s">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="H86" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="I86">
         <v>3</v>
       </c>
       <c r="J86" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="K86" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C87" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D87">
         <v>114</v>
       </c>
       <c r="E87" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F87" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G87" t="s">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="H87" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="I87">
         <v>2</v>
       </c>
       <c r="J87" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+      <c r="K87" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C88" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D88">
         <v>114</v>
       </c>
       <c r="E88" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F88" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G88" t="s">
-        <v>246</v>
+        <v>270</v>
       </c>
       <c r="H88" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="I88">
         <v>2</v>
       </c>
       <c r="J88" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+      <c r="K88" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C89" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D89">
         <v>114</v>
       </c>
       <c r="E89" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F89" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G89" t="s">
-        <v>247</v>
+        <v>271</v>
       </c>
       <c r="H89" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="I89">
         <v>2</v>
       </c>
       <c r="J89" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+      <c r="K89" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C90" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D90">
         <v>114</v>
       </c>
       <c r="E90" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F90" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G90" t="s">
-        <v>248</v>
+        <v>272</v>
       </c>
       <c r="H90" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="I90">
         <v>2</v>
       </c>
       <c r="J90" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+      <c r="K90" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C91" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D91">
         <v>114</v>
       </c>
       <c r="E91" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F91" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G91" t="s">
-        <v>249</v>
+        <v>273</v>
       </c>
       <c r="H91" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="I91">
         <v>2</v>
       </c>
       <c r="J91" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+      <c r="K91" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C92" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D92">
         <v>114</v>
       </c>
       <c r="E92" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F92" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G92" t="s">
-        <v>250</v>
+        <v>274</v>
       </c>
       <c r="H92" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="I92">
         <v>2</v>
       </c>
       <c r="J92" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+      <c r="K92" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B93" t="s">
-        <v>268</v>
+        <v>136</v>
       </c>
       <c r="C93" t="s">
-        <v>269</v>
+        <v>137</v>
       </c>
       <c r="D93">
         <v>114</v>
       </c>
       <c r="E93" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F93" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="G93" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="H93" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="I93">
         <v>3</v>
       </c>
       <c r="J93" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+      <c r="K93" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B94" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C94" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D94">
         <v>114</v>
       </c>
       <c r="E94" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F94" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="G94" t="s">
-        <v>252</v>
+        <v>276</v>
       </c>
       <c r="H94" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="I94">
         <v>6</v>
       </c>
       <c r="J94" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K94" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B95" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C95" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D95">
         <v>114</v>
       </c>
       <c r="E95" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F95" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="G95" t="s">
-        <v>253</v>
+        <v>277</v>
       </c>
       <c r="H95" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="I95">
         <v>6</v>
       </c>
       <c r="J95" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+      <c r="K95" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B96" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C96" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D96">
         <v>114</v>
       </c>
       <c r="E96" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F96" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="G96" t="s">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="H96" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="I96">
         <v>3</v>
       </c>
       <c r="J96" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+      <c r="K96" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B97" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C97" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D97">
         <v>114</v>
       </c>
       <c r="E97" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F97" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="G97" t="s">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="H97" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="I97">
         <v>3</v>
       </c>
       <c r="J97" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+      <c r="K97" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B98" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C98" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D98">
         <v>114</v>
       </c>
       <c r="E98" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F98" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="G98" t="s">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="H98" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="I98">
         <v>2</v>
       </c>
       <c r="J98" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+      <c r="K98" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B99" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C99" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D99">
         <v>114</v>
       </c>
       <c r="E99" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F99" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="G99" t="s">
-        <v>257</v>
+        <v>281</v>
       </c>
       <c r="H99" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="I99">
         <v>2</v>
       </c>
       <c r="J99" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+      <c r="K99" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B100" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C100" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D100">
         <v>114</v>
       </c>
       <c r="E100" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F100" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="G100" t="s">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="H100" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="I100">
         <v>3</v>
       </c>
       <c r="J100" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+      <c r="K100" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B101" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C101" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D101">
         <v>114</v>
       </c>
       <c r="E101" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F101" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="G101" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="H101" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="I101">
         <v>2</v>
       </c>
       <c r="J101" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+      <c r="K101" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B102" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C102" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D102">
         <v>114</v>
       </c>
       <c r="E102" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F102" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="G102" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="H102" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="I102">
         <v>2</v>
       </c>
       <c r="J102" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+      <c r="K102" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B103" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C103" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D103">
         <v>114</v>
       </c>
       <c r="E103" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F103" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="G103" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="H103" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="I103">
         <v>3</v>
       </c>
       <c r="J103" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="K103" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B104" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C104" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D104">
         <v>114</v>
       </c>
       <c r="E104" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F104" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="G104" t="s">
-        <v>262</v>
+        <v>286</v>
       </c>
       <c r="H104" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="I104">
         <v>3</v>
       </c>
       <c r="J104" t="s">
+        <v>166</v>
+      </c>
+      <c r="K104" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>135</v>
+      </c>
+      <c r="B105" t="s">
+        <v>136</v>
+      </c>
+      <c r="C105" t="s">
+        <v>137</v>
+      </c>
+      <c r="D105">
+        <v>114</v>
+      </c>
+      <c r="E105" t="s">
+        <v>23</v>
+      </c>
+      <c r="F105" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>126</v>
-      </c>
-      <c r="B105" t="s">
-        <v>127</v>
-      </c>
-      <c r="C105" t="s">
-        <v>128</v>
-      </c>
-      <c r="D105">
-        <v>114</v>
-      </c>
-      <c r="E105" t="s">
-        <v>20</v>
-      </c>
-      <c r="F105" t="s">
-        <v>138</v>
-      </c>
       <c r="G105" t="s">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="H105" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="I105">
         <v>3</v>
       </c>
       <c r="J105" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+      <c r="K105" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B106" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C106" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D106">
         <v>114</v>
       </c>
       <c r="E106" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F106" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="G106" t="s">
-        <v>264</v>
+        <v>288</v>
       </c>
       <c r="H106" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="I106">
         <v>3</v>
       </c>
       <c r="J106" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+      <c r="K106" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="B107" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="C107" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D107">
         <v>114</v>
       </c>
       <c r="E107" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F107" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="G107" t="s">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="H107" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="I107">
         <v>3</v>
       </c>
       <c r="J107" t="s">
-        <v>126</v>
+        <v>148</v>
+      </c>
+      <c r="K107" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -4745,11 +5149,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2CF5EF1-7FEB-43D6-B456-CF0AF6E5C949}">
-  <dimension ref="A1:G4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E09D0B36-23A9-4193-B5C2-804643840ECE}">
+  <dimension ref="A1:K106"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -4763,24 +5172,24 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="E1" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="F1" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="G1" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2">
         <v>114</v>
@@ -4795,15 +5204,15 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="66" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C3">
         <v>114</v>
@@ -4817,16 +5226,16 @@
       <c r="F3">
         <v>20</v>
       </c>
-      <c r="G3" t="s">
-        <v>267</v>
+      <c r="G3" s="2" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>268</v>
+        <v>136</v>
       </c>
       <c r="B4" t="s">
-        <v>269</v>
+        <v>137</v>
       </c>
       <c r="C4">
         <v>114</v>
@@ -4841,11 +5250,423 @@
         <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>270</v>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="51" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K51">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K52">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="11:11" x14ac:dyDescent="0.25">
+      <c r="K53">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>135</v>
+      </c>
+      <c r="B92" t="s">
+        <v>136</v>
+      </c>
+      <c r="C92" t="s">
+        <v>137</v>
+      </c>
+      <c r="D92">
+        <v>114</v>
+      </c>
+      <c r="G92" t="s">
+        <v>139</v>
+      </c>
+      <c r="H92">
+        <v>3</v>
+      </c>
+      <c r="I92" t="s">
+        <v>141</v>
+      </c>
+      <c r="K92">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>135</v>
+      </c>
+      <c r="B93" t="s">
+        <v>136</v>
+      </c>
+      <c r="C93" t="s">
+        <v>137</v>
+      </c>
+      <c r="D93">
+        <v>114</v>
+      </c>
+      <c r="G93" t="s">
+        <v>142</v>
+      </c>
+      <c r="H93">
+        <v>6</v>
+      </c>
+      <c r="I93" t="s">
+        <v>19</v>
+      </c>
+      <c r="K93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>135</v>
+      </c>
+      <c r="B94" t="s">
+        <v>136</v>
+      </c>
+      <c r="C94" t="s">
+        <v>137</v>
+      </c>
+      <c r="D94">
+        <v>114</v>
+      </c>
+      <c r="G94" t="s">
+        <v>143</v>
+      </c>
+      <c r="H94">
+        <v>6</v>
+      </c>
+      <c r="I94" t="s">
+        <v>145</v>
+      </c>
+      <c r="K94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>135</v>
+      </c>
+      <c r="B95" t="s">
+        <v>136</v>
+      </c>
+      <c r="C95" t="s">
+        <v>137</v>
+      </c>
+      <c r="D95">
+        <v>114</v>
+      </c>
+      <c r="E95" t="s">
+        <v>86</v>
+      </c>
+      <c r="G95" t="s">
+        <v>147</v>
+      </c>
+      <c r="H95">
+        <v>3</v>
+      </c>
+      <c r="I95" t="s">
+        <v>135</v>
+      </c>
+      <c r="K95">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>135</v>
+      </c>
+      <c r="B96" t="s">
+        <v>136</v>
+      </c>
+      <c r="C96" t="s">
+        <v>137</v>
+      </c>
+      <c r="D96">
+        <v>114</v>
+      </c>
+      <c r="E96" t="s">
+        <v>86</v>
+      </c>
+      <c r="G96" t="s">
+        <v>149</v>
+      </c>
+      <c r="H96">
+        <v>3</v>
+      </c>
+      <c r="I96" t="s">
+        <v>135</v>
+      </c>
+      <c r="K96">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>135</v>
+      </c>
+      <c r="B97" t="s">
+        <v>136</v>
+      </c>
+      <c r="C97" t="s">
+        <v>137</v>
+      </c>
+      <c r="D97">
+        <v>114</v>
+      </c>
+      <c r="G97" t="s">
+        <v>151</v>
+      </c>
+      <c r="H97">
+        <v>2</v>
+      </c>
+      <c r="I97" t="s">
+        <v>135</v>
+      </c>
+      <c r="K97">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>135</v>
+      </c>
+      <c r="B98" t="s">
+        <v>136</v>
+      </c>
+      <c r="C98" t="s">
+        <v>137</v>
+      </c>
+      <c r="D98">
+        <v>114</v>
+      </c>
+      <c r="G98" t="s">
+        <v>152</v>
+      </c>
+      <c r="H98">
+        <v>2</v>
+      </c>
+      <c r="I98" t="s">
+        <v>135</v>
+      </c>
+      <c r="K98">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>135</v>
+      </c>
+      <c r="B99" t="s">
+        <v>136</v>
+      </c>
+      <c r="C99" t="s">
+        <v>137</v>
+      </c>
+      <c r="D99">
+        <v>114</v>
+      </c>
+      <c r="G99" t="s">
+        <v>153</v>
+      </c>
+      <c r="H99">
+        <v>3</v>
+      </c>
+      <c r="I99" t="s">
+        <v>155</v>
+      </c>
+      <c r="K99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>135</v>
+      </c>
+      <c r="B100" t="s">
+        <v>136</v>
+      </c>
+      <c r="C100" t="s">
+        <v>137</v>
+      </c>
+      <c r="D100">
+        <v>114</v>
+      </c>
+      <c r="G100" t="s">
+        <v>183</v>
+      </c>
+      <c r="H100">
+        <v>2</v>
+      </c>
+      <c r="I100" t="s">
+        <v>158</v>
+      </c>
+      <c r="K100">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>135</v>
+      </c>
+      <c r="B101" t="s">
+        <v>136</v>
+      </c>
+      <c r="C101" t="s">
+        <v>137</v>
+      </c>
+      <c r="D101">
+        <v>114</v>
+      </c>
+      <c r="G101" t="s">
+        <v>159</v>
+      </c>
+      <c r="H101">
+        <v>2</v>
+      </c>
+      <c r="I101" t="s">
+        <v>161</v>
+      </c>
+      <c r="K101">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>135</v>
+      </c>
+      <c r="B102" t="s">
+        <v>136</v>
+      </c>
+      <c r="C102" t="s">
+        <v>137</v>
+      </c>
+      <c r="D102">
+        <v>114</v>
+      </c>
+      <c r="G102" t="s">
+        <v>184</v>
+      </c>
+      <c r="H102">
+        <v>3</v>
+      </c>
+      <c r="I102" t="s">
+        <v>164</v>
+      </c>
+      <c r="K102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>135</v>
+      </c>
+      <c r="B103" t="s">
+        <v>136</v>
+      </c>
+      <c r="C103" t="s">
+        <v>137</v>
+      </c>
+      <c r="D103">
+        <v>114</v>
+      </c>
+      <c r="G103" t="s">
+        <v>165</v>
+      </c>
+      <c r="H103">
+        <v>3</v>
+      </c>
+      <c r="I103" t="s">
+        <v>167</v>
+      </c>
+      <c r="K103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>135</v>
+      </c>
+      <c r="B104" t="s">
+        <v>136</v>
+      </c>
+      <c r="C104" t="s">
+        <v>137</v>
+      </c>
+      <c r="D104">
+        <v>114</v>
+      </c>
+      <c r="G104" t="s">
+        <v>168</v>
+      </c>
+      <c r="H104">
+        <v>3</v>
+      </c>
+      <c r="I104" t="s">
+        <v>170</v>
+      </c>
+      <c r="K104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>135</v>
+      </c>
+      <c r="B105" t="s">
+        <v>136</v>
+      </c>
+      <c r="C105" t="s">
+        <v>137</v>
+      </c>
+      <c r="D105">
+        <v>114</v>
+      </c>
+      <c r="G105" t="s">
+        <v>171</v>
+      </c>
+      <c r="H105">
+        <v>3</v>
+      </c>
+      <c r="I105" t="s">
+        <v>173</v>
+      </c>
+      <c r="K105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>135</v>
+      </c>
+      <c r="B106" t="s">
+        <v>136</v>
+      </c>
+      <c r="C106" t="s">
+        <v>137</v>
+      </c>
+      <c r="D106">
+        <v>114</v>
+      </c>
+      <c r="G106" t="s">
+        <v>175</v>
+      </c>
+      <c r="H106">
+        <v>3</v>
+      </c>
+      <c r="I106" t="s">
+        <v>135</v>
+      </c>
+      <c r="K106">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/master_data.xlsx
+++ b/master_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\000_專案計畫\20260107_學分學程查詢功能\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8CF664C-9DDE-46A0-BF5D-17A83B886959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE7A10BE-4031-4EA8-A2E8-737CEAA7EDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3796A25F-1F4D-4179-BD9A-8404DC01DA19}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{5C756728-D7FE-4632-9F6E-380DC409B664}"/>
   </bookViews>
   <sheets>
     <sheet name="科目表" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">科目表!$A$1:$L$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">學程規範總額!$A$1:$G$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,611 +44,609 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="290">
-  <si>
-    <t>學院</t>
-  </si>
-  <si>
-    <t>學程代碼</t>
-  </si>
-  <si>
-    <t>學程名稱</t>
-  </si>
-  <si>
-    <t>適用年度</t>
-  </si>
-  <si>
-    <t>科目類別</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="290">
+  <si>
+    <t>跨領域學院</t>
+  </si>
+  <si>
+    <t>DTG,GTG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>教育大數據專題</t>
+  </si>
+  <si>
+    <t>總整課程(至少2學分)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>選修</t>
+  </si>
+  <si>
+    <t>教育大數據微學程</t>
+  </si>
+  <si>
+    <t>K860</t>
+  </si>
+  <si>
+    <t>會計系、資管系、統資系</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D71,D74,D76</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>資料庫管理</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>專業/進階課程(至少2學分)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>資數系</t>
+  </si>
+  <si>
+    <t>D1B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>資料庫</t>
+  </si>
+  <si>
+    <t>資工系</t>
+  </si>
+  <si>
+    <t>D51</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>資料庫系統概論</t>
+  </si>
+  <si>
+    <t>中等教育學程</t>
+  </si>
+  <si>
+    <t>DE1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>特殊教育與適性教學</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>領科學程三</t>
+  </si>
+  <si>
+    <t>D0V</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>教育科技發展趨勢</t>
+  </si>
+  <si>
+    <t>資創學程</t>
+  </si>
+  <si>
+    <t>C1T</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>生成式AI與生活</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI學士後系</t>
+  </si>
+  <si>
+    <t>CQ1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>大數據資料分析與應用</t>
+  </si>
+  <si>
+    <t>AI與永續</t>
+  </si>
+  <si>
+    <t>資料庫系統設計</t>
+  </si>
+  <si>
+    <t>資料探索及資訊視覺化</t>
+  </si>
+  <si>
+    <t>重點(至少6學分)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>必修</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>機器學習</t>
+  </si>
+  <si>
+    <t>物理系</t>
+  </si>
+  <si>
+    <t>D55,D56</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>程式設計</t>
+  </si>
+  <si>
+    <t>基礎(至少2學分)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>圖資系</t>
+  </si>
+  <si>
+    <t>D10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>計算機概論</t>
+  </si>
+  <si>
+    <t>經濟系、資管系、金企系、企管系、統資系</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D65,D74,D0F,D0E,D76</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>程式設計概論</t>
+  </si>
+  <si>
+    <t>臨心系</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D95</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>舞蹈治療實務</t>
+  </si>
+  <si>
+    <t>選修模組(10)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>哲學諮商與輔導學分學程</t>
+  </si>
+  <si>
+    <t>K260</t>
+  </si>
+  <si>
+    <t>文學院</t>
+  </si>
+  <si>
+    <t>遊戲治療法</t>
+  </si>
+  <si>
+    <t>完形治療法</t>
+  </si>
+  <si>
+    <t>人本心理學</t>
+  </si>
+  <si>
+    <t>團體諮商</t>
+  </si>
+  <si>
+    <t>心理衛生</t>
+  </si>
+  <si>
+    <t>心理系</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D39</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>社會生活與社會治療</t>
+  </si>
+  <si>
+    <t>戲劇治療</t>
+  </si>
+  <si>
+    <t>生命敘說與自我發展</t>
+  </si>
+  <si>
+    <t>批判心理學導論</t>
+  </si>
+  <si>
+    <t>諮商與心理治療理論</t>
+  </si>
+  <si>
+    <t>家庭關係與個人發展</t>
+  </si>
+  <si>
+    <t>變態心理學</t>
+  </si>
+  <si>
+    <t>性別經驗與心理學</t>
+  </si>
+  <si>
+    <t>電影、心理與人生</t>
+  </si>
+  <si>
+    <t>輔導與諮商概論</t>
+  </si>
+  <si>
+    <t>敘說、反映與實踐導論</t>
+  </si>
+  <si>
+    <t>哲學系</t>
+  </si>
+  <si>
+    <t>D03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中國哲學專題：人性論</t>
+  </si>
+  <si>
+    <t>先秦儒家與情感哲學</t>
+  </si>
+  <si>
+    <t>中國哲學的方法論</t>
+  </si>
+  <si>
+    <t>五經思想：易經</t>
+  </si>
+  <si>
+    <t>哲學諮商的批判思考</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>哲學諮商實務</t>
+  </si>
+  <si>
+    <t>亞里斯多德式的哲學諮商</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>哲學諮商的倫理學基礎</t>
+  </si>
+  <si>
+    <t>哲學諮商與社會實踐</t>
+  </si>
+  <si>
+    <t>兒童哲學：理論與實務</t>
+  </si>
+  <si>
+    <t>存在主義</t>
+  </si>
+  <si>
+    <t>行動哲學</t>
+  </si>
+  <si>
+    <t>方法論</t>
+  </si>
+  <si>
+    <t>詮釋學</t>
+  </si>
+  <si>
+    <t>敘事符號學</t>
+  </si>
+  <si>
+    <t>現象學導論</t>
+  </si>
+  <si>
+    <t>蘇格拉底對話</t>
+  </si>
+  <si>
+    <t>兒童哲學</t>
+  </si>
+  <si>
+    <t>哲學人學</t>
+  </si>
+  <si>
+    <t>倫理學</t>
+  </si>
+  <si>
+    <t>知識論</t>
+  </si>
+  <si>
+    <t>哲學系、心理學系、臨床心理學系共同負責</t>
+  </si>
+  <si>
+    <t>哲學諮商:實習</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>必修模組(10)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>哲學諮商方法論</t>
+  </si>
+  <si>
+    <t>哲學諮商:理論與實務</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>歷史系</t>
+  </si>
+  <si>
+    <t>D02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中國史學史</t>
+  </si>
+  <si>
+    <t>選修模組(12)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中國古籍整理學分學程</t>
+  </si>
+  <si>
+    <t>K060</t>
+  </si>
+  <si>
+    <t>檔案與口述歷史</t>
+  </si>
+  <si>
+    <t>臺灣博物館史</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>西洋博物館史</t>
+  </si>
+  <si>
+    <t>dao_ph</t>
+  </si>
+  <si>
+    <t>先秦道家哲學</t>
+  </si>
+  <si>
+    <t>道家哲學</t>
+  </si>
+  <si>
+    <t>chin_ph</t>
+  </si>
+  <si>
+    <t>清代哲學研究</t>
+  </si>
+  <si>
+    <t>清代哲學</t>
+  </si>
+  <si>
+    <t>宋明理學</t>
+  </si>
+  <si>
+    <t>佛學概論</t>
+  </si>
+  <si>
+    <t>five_classics</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>五經思想：易經</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>五經思想</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>兩漢哲學</t>
+  </si>
+  <si>
+    <t>儒家哲學</t>
+  </si>
+  <si>
+    <t>魏晉哲學</t>
+  </si>
+  <si>
+    <t>先秦諸子哲學</t>
+  </si>
+  <si>
+    <t>中文系or哲學系</t>
+  </si>
+  <si>
+    <t>D01,D03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>易經</t>
+  </si>
+  <si>
+    <t>中文系</t>
+  </si>
+  <si>
+    <t>D01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>史記</t>
+  </si>
+  <si>
+    <t>中國文學史</t>
+  </si>
+  <si>
+    <t>中國古典戲曲</t>
+  </si>
+  <si>
+    <t>中國傳統小說</t>
+  </si>
+  <si>
+    <t>文字學</t>
+  </si>
+  <si>
+    <t>訓詁學</t>
+  </si>
+  <si>
+    <t>聲韻學</t>
+  </si>
+  <si>
+    <t>文獻知識</t>
+  </si>
+  <si>
+    <t>語法修辭學</t>
+  </si>
+  <si>
+    <t>左傳</t>
+  </si>
+  <si>
+    <t>荀子</t>
+  </si>
+  <si>
+    <t>詩經</t>
+  </si>
+  <si>
+    <t>莊子</t>
+  </si>
+  <si>
+    <t>老子</t>
+  </si>
+  <si>
+    <t>尚書</t>
+  </si>
+  <si>
+    <t>禮記</t>
+  </si>
+  <si>
+    <t>圖書館實務</t>
+  </si>
+  <si>
+    <t>社會科學資源</t>
+  </si>
+  <si>
+    <t>人文學資源</t>
+  </si>
+  <si>
+    <t>館藏發展</t>
+  </si>
+  <si>
+    <t>主題分析</t>
+  </si>
+  <si>
+    <t>資訊組織</t>
+  </si>
+  <si>
+    <t>參考資源</t>
+  </si>
+  <si>
+    <t>圖書資訊學導論</t>
+  </si>
+  <si>
+    <t>圖書館推廣與行銷</t>
+  </si>
+  <si>
+    <t>檔案管理與加值行銷</t>
+  </si>
+  <si>
+    <t>數位典藏與數位學習</t>
+  </si>
+  <si>
+    <t>版本學與古籍保護</t>
+  </si>
+  <si>
+    <t>圖資系碩士班</t>
+  </si>
+  <si>
+    <t>D106</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>數位典藏理論與實務專題</t>
+  </si>
+  <si>
+    <t>古籍整理與利用</t>
+  </si>
+  <si>
+    <t>古籍資源管理</t>
+  </si>
+  <si>
+    <t>國學導讀</t>
+  </si>
+  <si>
+    <t>必修模組(8)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>必修</t>
+  </si>
+  <si>
+    <t>書目學理論與實務</t>
+  </si>
+  <si>
+    <t>互斥代碼</t>
+  </si>
+  <si>
+    <t>備註</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>認抵單位代碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>學分數</t>
+  </si>
+  <si>
+    <t>課程名稱</t>
+  </si>
+  <si>
+    <t>課程代碼</t>
   </si>
   <si>
     <t>模組名稱</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>課程代碼</t>
-  </si>
-  <si>
-    <t>課程名稱</t>
-  </si>
-  <si>
-    <t>學分數</t>
-  </si>
-  <si>
-    <t>認抵單位代碼</t>
+    <t>科目類別</t>
+  </si>
+  <si>
+    <t>適用年度</t>
+  </si>
+  <si>
+    <t>學程名稱</t>
+  </si>
+  <si>
+    <t>學程代碼</t>
+  </si>
+  <si>
+    <t>學院</t>
+  </si>
+  <si>
+    <t>本微學程應修學分數 12 學分。包括基礎課程(2 學分)、重點課程(6 學分)、專業/進階課程(2 學分)、總整課程(2 學分)</t>
+  </si>
+  <si>
+    <t>教育大數據微學程</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>備註</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>互斥代碼</t>
-  </si>
-  <si>
-    <t>文學院</t>
-  </si>
-  <si>
-    <t>K060</t>
-  </si>
-  <si>
-    <t>中國古籍整理學分學程</t>
-  </si>
-  <si>
-    <t>必修</t>
-  </si>
-  <si>
-    <t>必修模組(8)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>書目學理論與實務</t>
-  </si>
-  <si>
-    <t>D10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>圖資系</t>
-  </si>
-  <si>
-    <t>國學導讀</t>
-  </si>
-  <si>
-    <t>D01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中文系</t>
-  </si>
-  <si>
-    <t>選修</t>
-  </si>
-  <si>
-    <t>選修模組(12)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>古籍資源管理</t>
-  </si>
-  <si>
-    <t>D106</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>圖資系碩士班</t>
-  </si>
-  <si>
-    <t>古籍整理與利用</t>
-  </si>
-  <si>
-    <t>數位典藏理論與實務專題</t>
-  </si>
-  <si>
-    <t>版本學與古籍保護</t>
-  </si>
-  <si>
-    <t>數位典藏與數位學習</t>
-  </si>
-  <si>
-    <t>檔案管理與加值行銷</t>
-  </si>
-  <si>
-    <t>圖書館推廣與行銷</t>
-  </si>
-  <si>
-    <t>圖書資訊學導論</t>
-  </si>
-  <si>
-    <t>參考資源</t>
-  </si>
-  <si>
-    <t>資訊組織</t>
-  </si>
-  <si>
-    <t>主題分析</t>
-  </si>
-  <si>
-    <t>館藏發展</t>
-  </si>
-  <si>
-    <t>人文學資源</t>
-  </si>
-  <si>
-    <t>社會科學資源</t>
-  </si>
-  <si>
-    <t>圖書館實務</t>
-  </si>
-  <si>
-    <t>禮記</t>
-  </si>
-  <si>
-    <t>尚書</t>
-  </si>
-  <si>
-    <t>老子</t>
-  </si>
-  <si>
-    <t>莊子</t>
-  </si>
-  <si>
-    <t>詩經</t>
-  </si>
-  <si>
-    <t>荀子</t>
-  </si>
-  <si>
-    <t>左傳</t>
-  </si>
-  <si>
-    <t>語法修辭學</t>
-  </si>
-  <si>
-    <t>文獻知識</t>
-  </si>
-  <si>
-    <t>聲韻學</t>
-  </si>
-  <si>
-    <t>訓詁學</t>
-  </si>
-  <si>
-    <t>文字學</t>
-  </si>
-  <si>
-    <t>中國傳統小說</t>
-  </si>
-  <si>
-    <t>中國古典戲曲</t>
-  </si>
-  <si>
-    <t>中國文學史</t>
-  </si>
-  <si>
-    <t>史記</t>
-  </si>
-  <si>
-    <t>易經</t>
-  </si>
-  <si>
-    <t>D01,D03</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中文系or哲學系</t>
-  </si>
-  <si>
-    <t>先秦諸子哲學</t>
-  </si>
-  <si>
-    <t>D03</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>哲學系</t>
-  </si>
-  <si>
-    <t>魏晉哲學</t>
-  </si>
-  <si>
-    <t>儒家哲學</t>
-  </si>
-  <si>
-    <t>兩漢哲學</t>
-  </si>
-  <si>
-    <t>五經思想</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>five_classics</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>五經思想：易經</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>佛學概論</t>
-  </si>
-  <si>
-    <t>宋明理學</t>
-  </si>
-  <si>
-    <t>清代哲學</t>
-  </si>
-  <si>
-    <t>chin_ph</t>
-  </si>
-  <si>
-    <t>清代哲學研究</t>
-  </si>
-  <si>
-    <t>道家哲學</t>
-  </si>
-  <si>
-    <t>dao_ph</t>
-  </si>
-  <si>
-    <t>先秦道家哲學</t>
-  </si>
-  <si>
-    <t>西洋博物館史</t>
-  </si>
-  <si>
-    <t>D02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>歷史系</t>
-  </si>
-  <si>
-    <t>臺灣博物館史</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>檔案與口述歷史</t>
-  </si>
-  <si>
-    <t>中國史學史</t>
-  </si>
-  <si>
-    <t>K260</t>
-  </si>
-  <si>
-    <t>哲學諮商與輔導學分學程</t>
-  </si>
-  <si>
-    <t>必修</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>必修模組(10)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>哲學諮商:理論與實務</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>哲學諮商方法論</t>
-  </si>
-  <si>
-    <t>哲學諮商:實習</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>哲學系、心理學系、臨床心理學系共同負責</t>
-  </si>
-  <si>
-    <t>選修模組(10)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>知識論</t>
-  </si>
-  <si>
-    <t>倫理學</t>
-  </si>
-  <si>
-    <t>哲學人學</t>
-  </si>
-  <si>
-    <t>兒童哲學</t>
-  </si>
-  <si>
-    <t>蘇格拉底對話</t>
-  </si>
-  <si>
-    <t>現象學導論</t>
-  </si>
-  <si>
-    <t>敘事符號學</t>
-  </si>
-  <si>
-    <t>詮釋學</t>
-  </si>
-  <si>
-    <t>方法論</t>
-  </si>
-  <si>
-    <t>行動哲學</t>
-  </si>
-  <si>
-    <t>存在主義</t>
-  </si>
-  <si>
-    <t>兒童哲學：理論與實務</t>
-  </si>
-  <si>
-    <t>哲學諮商與社會實踐</t>
-  </si>
-  <si>
-    <t>哲學諮商的倫理學基礎</t>
-  </si>
-  <si>
-    <t>亞里斯多德式的哲學諮商</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>哲學諮商實務</t>
-  </si>
-  <si>
-    <t>哲學諮商的批判思考</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>五經思想：易經</t>
-  </si>
-  <si>
-    <t>中國哲學的方法論</t>
-  </si>
-  <si>
-    <t>先秦儒家與情感哲學</t>
-  </si>
-  <si>
-    <t>中國哲學專題：人性論</t>
-  </si>
-  <si>
-    <t>敘說、反映與實踐導論</t>
-  </si>
-  <si>
-    <t>D39</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>心理系</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>輔導與諮商概論</t>
-  </si>
-  <si>
-    <t>電影、心理與人生</t>
-  </si>
-  <si>
-    <t>性別經驗與心理學</t>
-  </si>
-  <si>
-    <t>變態心理學</t>
-  </si>
-  <si>
-    <t>家庭關係與個人發展</t>
-  </si>
-  <si>
-    <t>諮商與心理治療理論</t>
-  </si>
-  <si>
-    <t>批判心理學導論</t>
-  </si>
-  <si>
-    <t>生命敘說與自我發展</t>
-  </si>
-  <si>
-    <t>戲劇治療</t>
-  </si>
-  <si>
-    <t>社會生活與社會治療</t>
-  </si>
-  <si>
-    <t>心理衛生</t>
-  </si>
-  <si>
-    <t>D95</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>臨心系</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>團體諮商</t>
-  </si>
-  <si>
-    <t>人本心理學</t>
-  </si>
-  <si>
-    <t>完形治療法</t>
-  </si>
-  <si>
-    <t>遊戲治療法</t>
-  </si>
-  <si>
-    <t>舞蹈治療實務</t>
-  </si>
-  <si>
-    <t>跨領域學院</t>
-  </si>
-  <si>
     <t>K860</t>
-  </si>
-  <si>
-    <t>教育大數據微學程</t>
-  </si>
-  <si>
-    <t>基礎(至少2學分)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>程式設計概論</t>
-  </si>
-  <si>
-    <t>D65,D74,D0F,D0E,D76</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>經濟系、資管系、金企系、企管系、統資系</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>計算機概論</t>
-  </si>
-  <si>
-    <t>程式設計</t>
-  </si>
-  <si>
-    <t>D55,D56</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>物理系</t>
-  </si>
-  <si>
-    <t>重點(至少6學分)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>機器學習</t>
-  </si>
-  <si>
-    <t>DTG,GTG</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>資料探索及資訊視覺化</t>
-  </si>
-  <si>
-    <t>專業/進階課程(至少2學分)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>資料庫系統設計</t>
-  </si>
-  <si>
-    <t>AI與永續</t>
-  </si>
-  <si>
-    <t>大數據資料分析與應用</t>
-  </si>
-  <si>
-    <t>CQ1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AI學士後系</t>
-  </si>
-  <si>
-    <t>生成式AI與生活</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>C1T</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>資創學程</t>
-  </si>
-  <si>
-    <t>教育科技發展趨勢</t>
-  </si>
-  <si>
-    <t>D0V</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>領科學程三</t>
-  </si>
-  <si>
-    <t>特殊教育與適性教學</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DE1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中等教育學程</t>
-  </si>
-  <si>
-    <t>資料庫系統概論</t>
-  </si>
-  <si>
-    <t>D51</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>資工系</t>
-  </si>
-  <si>
-    <t>資料庫</t>
-  </si>
-  <si>
-    <t>D1B</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>資數系</t>
-  </si>
-  <si>
-    <t>資料庫管理</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>D71,D74,D76</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>會計系、資管系、統資系</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>總整課程(至少2學分)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>教育大數據專題</t>
-  </si>
-  <si>
-    <t>必修總學分</t>
-  </si>
-  <si>
-    <t>選修總學分</t>
-  </si>
-  <si>
-    <t>總計應修學分</t>
-  </si>
-  <si>
-    <t>備註 (模組要求)</t>
-  </si>
-  <si>
-    <t>必修8學分，選修12學分</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>必修核心課程(共十學分) ,選修課程(至少須修讀十學分) ,
 開設課程及開放選修名額以當年度課表為準</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>本微學程應修學分數 12 學分。包括基礎課程(2 學分)、重點課程(6 學分)、專業/進階課程(2 學分)、總整課程(2 學分)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>生成式AI與生活</t>
-  </si>
-  <si>
-    <t xml:space="preserve">特殊教育與適性教學
-</t>
+  </si>
+  <si>
+    <t>必修8學分，選修12學分</t>
+  </si>
+  <si>
+    <t>備註 (模組要求)</t>
+  </si>
+  <si>
+    <t>總計應修學分</t>
+  </si>
+  <si>
+    <t>選修總學分</t>
+  </si>
+  <si>
+    <t>必修總學分</t>
   </si>
   <si>
     <t>17624</t>
@@ -1016,15 +1015,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1359,7 +1355,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{321D3090-431E-4533-AB60-1226A3D839D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41A0537A-F1D1-4B6B-B8E7-906C63A687B2}">
   <dimension ref="A1:L107"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1378,3768 +1374,3768 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>174</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>173</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>172</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>171</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>170</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>169</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>168</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>167</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>166</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
+        <v>165</v>
       </c>
       <c r="L1" t="s">
-        <v>11</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D2">
         <v>114</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>162</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>161</v>
       </c>
       <c r="G2" t="s">
         <v>185</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>163</v>
       </c>
       <c r="I2">
         <v>4</v>
       </c>
       <c r="J2" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="K2" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D3">
         <v>114</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>162</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>161</v>
       </c>
       <c r="G3" t="s">
         <v>186</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="I3">
         <v>4</v>
       </c>
       <c r="J3" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="K3" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D4">
         <v>114</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G4" t="s">
         <v>187</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>159</v>
       </c>
       <c r="I4">
         <v>2</v>
       </c>
       <c r="J4" t="s">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="K4" t="s">
-        <v>27</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D5">
         <v>114</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G5" t="s">
         <v>188</v>
       </c>
       <c r="H5" t="s">
-        <v>28</v>
+        <v>158</v>
       </c>
       <c r="I5">
         <v>2</v>
       </c>
       <c r="J5" t="s">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="K5" t="s">
-        <v>27</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D6">
         <v>114</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G6" t="s">
         <v>189</v>
       </c>
       <c r="H6" t="s">
-        <v>29</v>
+        <v>157</v>
       </c>
       <c r="I6">
         <v>2</v>
       </c>
       <c r="J6" t="s">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="K6" t="s">
-        <v>27</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D7">
         <v>114</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G7" t="s">
         <v>190</v>
       </c>
       <c r="H7" t="s">
-        <v>30</v>
+        <v>154</v>
       </c>
       <c r="I7">
         <v>4</v>
       </c>
       <c r="J7" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="K7" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D8">
         <v>114</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G8" t="s">
         <v>191</v>
       </c>
       <c r="H8" t="s">
-        <v>31</v>
+        <v>153</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
       <c r="J8" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="K8" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D9">
         <v>114</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G9" t="s">
         <v>192</v>
       </c>
       <c r="H9" t="s">
-        <v>32</v>
+        <v>152</v>
       </c>
       <c r="I9">
         <v>4</v>
       </c>
       <c r="J9" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="K9" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D10">
         <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G10" t="s">
         <v>193</v>
       </c>
       <c r="H10" t="s">
-        <v>33</v>
+        <v>151</v>
       </c>
       <c r="I10">
         <v>4</v>
       </c>
       <c r="J10" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="K10" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D11">
         <v>114</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G11" t="s">
         <v>194</v>
       </c>
       <c r="H11" t="s">
-        <v>34</v>
+        <v>150</v>
       </c>
       <c r="I11">
         <v>4</v>
       </c>
       <c r="J11" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="K11" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D12">
         <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F12" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G12" t="s">
         <v>195</v>
       </c>
       <c r="H12" t="s">
-        <v>35</v>
+        <v>149</v>
       </c>
       <c r="I12">
         <v>4</v>
       </c>
       <c r="J12" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="K12" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C13" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D13">
         <v>114</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G13" t="s">
         <v>196</v>
       </c>
       <c r="H13" t="s">
-        <v>36</v>
+        <v>148</v>
       </c>
       <c r="I13">
         <v>4</v>
       </c>
       <c r="J13" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="K13" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D14">
         <v>114</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F14" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G14" t="s">
         <v>197</v>
       </c>
       <c r="H14" t="s">
-        <v>37</v>
+        <v>147</v>
       </c>
       <c r="I14">
         <v>4</v>
       </c>
       <c r="J14" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="K14" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D15">
         <v>114</v>
       </c>
       <c r="E15" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F15" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G15" t="s">
         <v>198</v>
       </c>
       <c r="H15" t="s">
-        <v>38</v>
+        <v>146</v>
       </c>
       <c r="I15">
         <v>4</v>
       </c>
       <c r="J15" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="K15" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D16">
         <v>114</v>
       </c>
       <c r="E16" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F16" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G16" t="s">
         <v>199</v>
       </c>
       <c r="H16" t="s">
+        <v>145</v>
+      </c>
+      <c r="I16">
+        <v>4</v>
+      </c>
+      <c r="J16" t="s">
+        <v>40</v>
+      </c>
+      <c r="K16" t="s">
         <v>39</v>
-      </c>
-      <c r="I16">
-        <v>4</v>
-      </c>
-      <c r="J16" t="s">
-        <v>18</v>
-      </c>
-      <c r="K16" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D17">
         <v>114</v>
       </c>
       <c r="E17" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F17" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G17" t="s">
         <v>200</v>
       </c>
       <c r="H17" t="s">
+        <v>144</v>
+      </c>
+      <c r="I17">
+        <v>4</v>
+      </c>
+      <c r="J17" t="s">
         <v>40</v>
       </c>
-      <c r="I17">
-        <v>4</v>
-      </c>
-      <c r="J17" t="s">
-        <v>18</v>
-      </c>
       <c r="K17" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D18">
         <v>114</v>
       </c>
       <c r="E18" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F18" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G18" t="s">
         <v>201</v>
       </c>
       <c r="H18" t="s">
-        <v>41</v>
+        <v>143</v>
       </c>
       <c r="I18">
         <v>2</v>
       </c>
       <c r="J18" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="K18" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D19">
         <v>114</v>
       </c>
       <c r="E19" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F19" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G19" t="s">
         <v>202</v>
       </c>
       <c r="H19" t="s">
-        <v>42</v>
+        <v>142</v>
       </c>
       <c r="I19">
         <v>4</v>
       </c>
       <c r="J19" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="K19" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D20">
         <v>114</v>
       </c>
       <c r="E20" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F20" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G20" t="s">
         <v>203</v>
       </c>
       <c r="H20" t="s">
-        <v>43</v>
+        <v>141</v>
       </c>
       <c r="I20">
         <v>4</v>
       </c>
       <c r="J20" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="K20" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D21">
         <v>114</v>
       </c>
       <c r="E21" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F21" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G21" t="s">
         <v>204</v>
       </c>
       <c r="H21" t="s">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="I21">
         <v>4</v>
       </c>
       <c r="J21" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="K21" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D22">
         <v>114</v>
       </c>
       <c r="E22" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F22" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G22" t="s">
         <v>205</v>
       </c>
       <c r="H22" t="s">
-        <v>45</v>
+        <v>139</v>
       </c>
       <c r="I22">
         <v>4</v>
       </c>
       <c r="J22" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="K22" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C23" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D23">
         <v>114</v>
       </c>
       <c r="E23" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F23" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G23" t="s">
         <v>206</v>
       </c>
       <c r="H23" t="s">
-        <v>46</v>
+        <v>138</v>
       </c>
       <c r="I23">
         <v>4</v>
       </c>
       <c r="J23" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="K23" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D24">
         <v>114</v>
       </c>
       <c r="E24" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F24" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G24" t="s">
         <v>207</v>
       </c>
       <c r="H24" t="s">
-        <v>47</v>
+        <v>137</v>
       </c>
       <c r="I24">
         <v>4</v>
       </c>
       <c r="J24" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="K24" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D25">
         <v>114</v>
       </c>
       <c r="E25" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F25" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G25" t="s">
         <v>208</v>
       </c>
       <c r="H25" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="I25">
         <v>4</v>
       </c>
       <c r="J25" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="K25" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C26" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D26">
         <v>114</v>
       </c>
       <c r="E26" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F26" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G26" t="s">
         <v>209</v>
       </c>
       <c r="H26" t="s">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="I26">
         <v>4</v>
       </c>
       <c r="J26" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="K26" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C27" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D27">
         <v>114</v>
       </c>
       <c r="E27" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F27" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G27" t="s">
         <v>210</v>
       </c>
       <c r="H27" t="s">
-        <v>50</v>
+        <v>134</v>
       </c>
       <c r="I27">
         <v>4</v>
       </c>
       <c r="J27" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="K27" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D28">
         <v>114</v>
       </c>
       <c r="E28" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F28" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G28" t="s">
         <v>211</v>
       </c>
       <c r="H28" t="s">
-        <v>51</v>
+        <v>133</v>
       </c>
       <c r="I28">
         <v>4</v>
       </c>
       <c r="J28" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="K28" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C29" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D29">
         <v>114</v>
       </c>
       <c r="E29" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F29" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G29" t="s">
         <v>212</v>
       </c>
       <c r="H29" t="s">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="I29">
         <v>4</v>
       </c>
       <c r="J29" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="K29" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C30" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D30">
         <v>114</v>
       </c>
       <c r="E30" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F30" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G30" t="s">
         <v>213</v>
       </c>
       <c r="H30" t="s">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="I30">
         <v>4</v>
       </c>
       <c r="J30" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="K30" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D31">
         <v>114</v>
       </c>
       <c r="E31" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F31" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G31" t="s">
         <v>214</v>
       </c>
       <c r="H31" t="s">
-        <v>54</v>
+        <v>130</v>
       </c>
       <c r="I31">
         <v>4</v>
       </c>
       <c r="J31" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="K31" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D32">
         <v>114</v>
       </c>
       <c r="E32" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F32" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G32" t="s">
         <v>215</v>
       </c>
       <c r="H32" t="s">
-        <v>55</v>
+        <v>129</v>
       </c>
       <c r="I32">
         <v>4</v>
       </c>
       <c r="J32" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="K32" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C33" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D33">
         <v>114</v>
       </c>
       <c r="E33" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F33" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G33" t="s">
         <v>216</v>
       </c>
       <c r="H33" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="I33">
         <v>6</v>
       </c>
       <c r="J33" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="K33" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C34" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D34">
         <v>114</v>
       </c>
       <c r="E34" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F34" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G34" t="s">
         <v>217</v>
       </c>
       <c r="H34" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="I34">
         <v>4</v>
       </c>
       <c r="J34" t="s">
-        <v>21</v>
+        <v>126</v>
       </c>
       <c r="K34" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D35">
         <v>114</v>
       </c>
       <c r="E35" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F35" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G35" t="s">
         <v>218</v>
       </c>
       <c r="H35" t="s">
-        <v>58</v>
+        <v>124</v>
       </c>
       <c r="I35">
         <v>4</v>
       </c>
       <c r="J35" t="s">
-        <v>59</v>
+        <v>123</v>
       </c>
       <c r="K35" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D36">
         <v>114</v>
       </c>
       <c r="E36" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F36" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G36" t="s">
         <v>219</v>
       </c>
       <c r="H36" t="s">
-        <v>61</v>
+        <v>121</v>
       </c>
       <c r="I36">
         <v>4</v>
       </c>
       <c r="J36" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K36" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C37" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D37">
         <v>114</v>
       </c>
       <c r="E37" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F37" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G37" t="s">
         <v>220</v>
       </c>
       <c r="H37" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="I37">
         <v>4</v>
       </c>
       <c r="J37" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K37" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B38" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C38" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D38">
         <v>114</v>
       </c>
       <c r="E38" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F38" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G38" t="s">
         <v>221</v>
       </c>
       <c r="H38" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
       <c r="I38">
         <v>4</v>
       </c>
       <c r="J38" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K38" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C39" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D39">
         <v>114</v>
       </c>
       <c r="E39" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F39" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G39" t="s">
         <v>222</v>
       </c>
       <c r="H39" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="I39">
         <v>4</v>
       </c>
       <c r="J39" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K39" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B40" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C40" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D40">
         <v>114</v>
       </c>
       <c r="E40" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F40" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G40" t="s">
         <v>223</v>
       </c>
       <c r="H40" t="s">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="I40">
         <v>4</v>
       </c>
       <c r="J40" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K40" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L40" t="s">
-        <v>68</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C41" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D41">
         <v>114</v>
       </c>
       <c r="E41" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F41" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G41" t="s">
         <v>224</v>
       </c>
       <c r="H41" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="I41">
         <v>4</v>
       </c>
       <c r="J41" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K41" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L41" t="s">
-        <v>68</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C42" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D42">
         <v>114</v>
       </c>
       <c r="E42" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F42" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G42" t="s">
         <v>225</v>
       </c>
       <c r="H42" t="s">
+        <v>114</v>
+      </c>
+      <c r="I42">
+        <v>4</v>
+      </c>
+      <c r="J42" t="s">
+        <v>71</v>
+      </c>
+      <c r="K42" t="s">
         <v>70</v>
-      </c>
-      <c r="I42">
-        <v>4</v>
-      </c>
-      <c r="J42" t="s">
-        <v>62</v>
-      </c>
-      <c r="K42" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B43" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C43" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D43">
         <v>114</v>
       </c>
       <c r="E43" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F43" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G43" t="s">
         <v>226</v>
       </c>
       <c r="H43" t="s">
+        <v>113</v>
+      </c>
+      <c r="I43">
+        <v>4</v>
+      </c>
+      <c r="J43" t="s">
         <v>71</v>
       </c>
-      <c r="I43">
-        <v>4</v>
-      </c>
-      <c r="J43" t="s">
-        <v>62</v>
-      </c>
       <c r="K43" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C44" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D44">
         <v>114</v>
       </c>
       <c r="E44" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F44" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G44" t="s">
         <v>227</v>
       </c>
       <c r="H44" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="I44">
         <v>4</v>
       </c>
       <c r="J44" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K44" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L44" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C45" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D45">
         <v>114</v>
       </c>
       <c r="E45" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F45" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G45" t="s">
         <v>228</v>
       </c>
       <c r="H45" t="s">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="I45">
         <v>4</v>
       </c>
       <c r="J45" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K45" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L45" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C46" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D46">
         <v>114</v>
       </c>
       <c r="E46" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F46" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G46" t="s">
         <v>229</v>
       </c>
       <c r="H46" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="I46">
         <v>4</v>
       </c>
       <c r="J46" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K46" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L46" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B47" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C47" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D47">
         <v>114</v>
       </c>
       <c r="E47" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F47" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G47" t="s">
         <v>230</v>
       </c>
       <c r="H47" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="I47">
         <v>4</v>
       </c>
       <c r="J47" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K47" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L47" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C48" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D48">
         <v>114</v>
       </c>
       <c r="E48" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F48" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G48" t="s">
         <v>231</v>
       </c>
       <c r="H48" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="I48">
         <v>2</v>
       </c>
       <c r="J48" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="K48" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C49" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D49">
         <v>114</v>
       </c>
       <c r="E49" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F49" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G49" t="s">
         <v>232</v>
       </c>
       <c r="H49" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="I49">
         <v>2</v>
       </c>
       <c r="J49" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="K49" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B50" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C50" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D50">
         <v>114</v>
       </c>
       <c r="E50" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F50" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G50" t="s">
         <v>233</v>
       </c>
       <c r="H50" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="I50">
         <v>2</v>
       </c>
       <c r="J50" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="K50" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B51" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="C51" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D51">
         <v>114</v>
       </c>
       <c r="E51" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F51" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="G51" t="s">
         <v>234</v>
       </c>
       <c r="H51" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="I51">
         <v>4</v>
       </c>
       <c r="J51" t="s">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="K51" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D52">
         <v>114</v>
       </c>
       <c r="E52" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="F52" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="G52" t="s">
         <v>235</v>
       </c>
       <c r="H52" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I52">
         <v>4</v>
       </c>
       <c r="J52" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K52" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C53" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D53">
         <v>114</v>
       </c>
       <c r="E53" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="F53" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="G53" t="s">
         <v>236</v>
       </c>
       <c r="H53" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="I53">
         <v>4</v>
       </c>
       <c r="J53" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K53" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B54" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C54" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D54">
         <v>114</v>
       </c>
       <c r="E54" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="F54" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="G54" t="s">
         <v>237</v>
       </c>
       <c r="H54" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I54">
         <v>2</v>
       </c>
       <c r="J54" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K54" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B55" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C55" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D55">
         <v>114</v>
       </c>
       <c r="E55" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F55" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G55" t="s">
         <v>238</v>
       </c>
       <c r="H55" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I55">
         <v>4</v>
       </c>
       <c r="J55" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K55" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B56" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C56" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D56">
         <v>114</v>
       </c>
       <c r="E56" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F56" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G56" t="s">
         <v>239</v>
       </c>
       <c r="H56" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="I56">
         <v>4</v>
       </c>
       <c r="J56" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K56" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B57" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C57" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D57">
         <v>114</v>
       </c>
       <c r="E57" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F57" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G57" t="s">
         <v>240</v>
       </c>
       <c r="H57" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="I57">
         <v>4</v>
       </c>
       <c r="J57" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K57" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B58" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C58" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D58">
         <v>114</v>
       </c>
       <c r="E58" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F58" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G58" t="s">
         <v>241</v>
       </c>
       <c r="H58" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="I58">
         <v>2</v>
       </c>
       <c r="J58" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K58" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B59" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C59" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D59">
         <v>114</v>
       </c>
       <c r="E59" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F59" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G59" t="s">
         <v>242</v>
       </c>
       <c r="H59" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I59">
         <v>2</v>
       </c>
       <c r="J59" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K59" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B60" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C60" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D60">
         <v>114</v>
       </c>
       <c r="E60" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F60" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G60" t="s">
         <v>243</v>
       </c>
       <c r="H60" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="I60">
         <v>2</v>
       </c>
       <c r="J60" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K60" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B61" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C61" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D61">
         <v>114</v>
       </c>
       <c r="E61" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F61" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G61" t="s">
         <v>244</v>
       </c>
       <c r="H61" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="I61">
         <v>2</v>
       </c>
       <c r="J61" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K61" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B62" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C62" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D62">
         <v>114</v>
       </c>
       <c r="E62" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F62" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G62" t="s">
         <v>245</v>
       </c>
       <c r="H62" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="I62">
         <v>2</v>
       </c>
       <c r="J62" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K62" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B63" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C63" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D63">
         <v>114</v>
       </c>
       <c r="E63" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F63" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G63" t="s">
         <v>246</v>
       </c>
       <c r="H63" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I63">
         <v>4</v>
       </c>
       <c r="J63" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K63" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B64" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C64" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D64">
         <v>114</v>
       </c>
       <c r="E64" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F64" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G64" t="s">
         <v>247</v>
       </c>
       <c r="H64" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="I64">
         <v>2</v>
       </c>
       <c r="J64" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K64" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B65" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C65" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D65">
         <v>114</v>
       </c>
       <c r="E65" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F65" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G65" t="s">
         <v>248</v>
       </c>
       <c r="H65" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="I65">
         <v>4</v>
       </c>
       <c r="J65" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K65" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B66" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C66" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D66">
         <v>114</v>
       </c>
       <c r="E66" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F66" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G66" t="s">
         <v>249</v>
       </c>
       <c r="H66" t="s">
-        <v>104</v>
+        <v>81</v>
       </c>
       <c r="I66">
         <v>4</v>
       </c>
       <c r="J66" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K66" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B67" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C67" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D67">
         <v>114</v>
       </c>
       <c r="E67" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F67" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G67" t="s">
         <v>250</v>
       </c>
       <c r="H67" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="I67">
         <v>2</v>
       </c>
       <c r="J67" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K67" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B68" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C68" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D68">
         <v>114</v>
       </c>
       <c r="E68" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F68" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G68" t="s">
         <v>251</v>
       </c>
       <c r="H68" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="I68">
         <v>2</v>
       </c>
       <c r="J68" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K68" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B69" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C69" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D69">
         <v>114</v>
       </c>
       <c r="E69" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F69" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G69" t="s">
         <v>252</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="I69">
         <v>2</v>
       </c>
       <c r="J69" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K69" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B70" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C70" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D70">
         <v>114</v>
       </c>
       <c r="E70" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F70" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G70" t="s">
         <v>253</v>
       </c>
       <c r="H70" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="I70">
         <v>2</v>
       </c>
       <c r="J70" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K70" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B71" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C71" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D71">
         <v>114</v>
       </c>
       <c r="E71" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F71" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G71" t="s">
         <v>254</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="I71">
         <v>2</v>
       </c>
       <c r="J71" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K71" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B72" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C72" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D72">
         <v>114</v>
       </c>
       <c r="E72" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F72" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G72" t="s">
         <v>224</v>
       </c>
       <c r="H72" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="I72">
         <v>4</v>
       </c>
       <c r="J72" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K72" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B73" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C73" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D73">
         <v>114</v>
       </c>
       <c r="E73" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F73" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G73" t="s">
         <v>255</v>
       </c>
       <c r="H73" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="I73">
         <v>4</v>
       </c>
       <c r="J73" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K73" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B74" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C74" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D74">
         <v>114</v>
       </c>
       <c r="E74" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F74" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G74" t="s">
         <v>256</v>
       </c>
       <c r="H74" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="I74">
         <v>2</v>
       </c>
       <c r="J74" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K74" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B75" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C75" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D75">
         <v>114</v>
       </c>
       <c r="E75" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F75" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G75" t="s">
         <v>257</v>
       </c>
       <c r="H75" t="s">
-        <v>113</v>
+        <v>72</v>
       </c>
       <c r="I75">
         <v>2</v>
       </c>
       <c r="J75" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K75" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B76" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C76" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D76">
         <v>114</v>
       </c>
       <c r="E76" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F76" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G76" t="s">
         <v>258</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="I76">
         <v>3</v>
       </c>
       <c r="J76" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="K76" t="s">
-        <v>116</v>
+        <v>57</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B77" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C77" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D77">
         <v>114</v>
       </c>
       <c r="E77" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F77" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G77" t="s">
         <v>259</v>
       </c>
       <c r="H77" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="I77">
         <v>3</v>
       </c>
       <c r="J77" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="K77" t="s">
-        <v>116</v>
+        <v>57</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B78" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C78" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D78">
         <v>114</v>
       </c>
       <c r="E78" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F78" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G78" t="s">
         <v>260</v>
       </c>
       <c r="H78" t="s">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="I78">
         <v>3</v>
       </c>
       <c r="J78" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="K78" t="s">
-        <v>116</v>
+        <v>57</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B79" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C79" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D79">
         <v>114</v>
       </c>
       <c r="E79" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F79" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G79" t="s">
         <v>261</v>
       </c>
       <c r="H79" t="s">
-        <v>119</v>
+        <v>66</v>
       </c>
       <c r="I79">
         <v>3</v>
       </c>
       <c r="J79" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="K79" t="s">
-        <v>116</v>
+        <v>57</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B80" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C80" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D80">
         <v>114</v>
       </c>
       <c r="E80" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F80" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G80" t="s">
         <v>262</v>
       </c>
       <c r="H80" t="s">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="I80">
         <v>3</v>
       </c>
       <c r="J80" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="K80" t="s">
-        <v>116</v>
+        <v>57</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B81" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C81" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D81">
         <v>114</v>
       </c>
       <c r="E81" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F81" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G81" t="s">
         <v>263</v>
       </c>
       <c r="H81" t="s">
-        <v>121</v>
+        <v>64</v>
       </c>
       <c r="I81">
         <v>3</v>
       </c>
       <c r="J81" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="K81" t="s">
-        <v>116</v>
+        <v>57</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B82" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C82" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D82">
         <v>114</v>
       </c>
       <c r="E82" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F82" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G82" t="s">
         <v>264</v>
       </c>
       <c r="H82" t="s">
-        <v>122</v>
+        <v>63</v>
       </c>
       <c r="I82">
         <v>3</v>
       </c>
       <c r="J82" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="K82" t="s">
-        <v>116</v>
+        <v>57</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B83" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C83" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D83">
         <v>114</v>
       </c>
       <c r="E83" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F83" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G83" t="s">
         <v>265</v>
       </c>
       <c r="H83" t="s">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c r="I83">
         <v>3</v>
       </c>
       <c r="J83" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="K83" t="s">
-        <v>116</v>
+        <v>57</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C84" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D84">
         <v>114</v>
       </c>
       <c r="E84" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F84" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G84" t="s">
         <v>266</v>
       </c>
       <c r="H84" t="s">
-        <v>124</v>
+        <v>61</v>
       </c>
       <c r="I84">
         <v>3</v>
       </c>
       <c r="J84" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="K84" t="s">
-        <v>116</v>
+        <v>57</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B85" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C85" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D85">
         <v>114</v>
       </c>
       <c r="E85" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F85" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G85" t="s">
         <v>267</v>
       </c>
       <c r="H85" t="s">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="I85">
         <v>3</v>
       </c>
       <c r="J85" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="K85" t="s">
-        <v>116</v>
+        <v>57</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B86" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C86" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D86">
         <v>114</v>
       </c>
       <c r="E86" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F86" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G86" t="s">
         <v>268</v>
       </c>
       <c r="H86" t="s">
-        <v>126</v>
+        <v>59</v>
       </c>
       <c r="I86">
         <v>3</v>
       </c>
       <c r="J86" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="K86" t="s">
-        <v>116</v>
+        <v>57</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B87" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C87" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D87">
         <v>114</v>
       </c>
       <c r="E87" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F87" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G87" t="s">
         <v>269</v>
       </c>
       <c r="H87" t="s">
-        <v>127</v>
+        <v>56</v>
       </c>
       <c r="I87">
         <v>2</v>
       </c>
       <c r="J87" t="s">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="K87" t="s">
-        <v>129</v>
+        <v>45</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B88" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C88" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D88">
         <v>114</v>
       </c>
       <c r="E88" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F88" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G88" t="s">
         <v>270</v>
       </c>
       <c r="H88" t="s">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="I88">
         <v>2</v>
       </c>
       <c r="J88" t="s">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="K88" t="s">
-        <v>129</v>
+        <v>45</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B89" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C89" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D89">
         <v>114</v>
       </c>
       <c r="E89" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F89" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G89" t="s">
         <v>271</v>
       </c>
       <c r="H89" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="I89">
         <v>2</v>
       </c>
       <c r="J89" t="s">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="K89" t="s">
-        <v>129</v>
+        <v>45</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B90" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C90" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D90">
         <v>114</v>
       </c>
       <c r="E90" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F90" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G90" t="s">
         <v>272</v>
       </c>
       <c r="H90" t="s">
-        <v>132</v>
+        <v>53</v>
       </c>
       <c r="I90">
         <v>2</v>
       </c>
       <c r="J90" t="s">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="K90" t="s">
-        <v>129</v>
+        <v>45</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B91" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C91" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D91">
         <v>114</v>
       </c>
       <c r="E91" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F91" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G91" t="s">
         <v>273</v>
       </c>
       <c r="H91" t="s">
-        <v>133</v>
+        <v>52</v>
       </c>
       <c r="I91">
         <v>2</v>
       </c>
       <c r="J91" t="s">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="K91" t="s">
-        <v>129</v>
+        <v>45</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="B92" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="C92" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D92">
         <v>114</v>
       </c>
       <c r="E92" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F92" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="G92" t="s">
         <v>274</v>
       </c>
       <c r="H92" t="s">
-        <v>134</v>
+        <v>47</v>
       </c>
       <c r="I92">
         <v>2</v>
       </c>
       <c r="J92" t="s">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="K92" t="s">
-        <v>129</v>
+        <v>45</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="B93" t="s">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="C93" t="s">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="D93">
         <v>114</v>
       </c>
       <c r="E93" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F93" t="s">
-        <v>138</v>
+        <v>38</v>
       </c>
       <c r="G93" t="s">
         <v>275</v>
       </c>
       <c r="H93" t="s">
-        <v>139</v>
+        <v>44</v>
       </c>
       <c r="I93">
         <v>3</v>
       </c>
       <c r="J93" t="s">
-        <v>140</v>
+        <v>43</v>
       </c>
       <c r="K93" t="s">
-        <v>141</v>
+        <v>42</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="B94" t="s">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="C94" t="s">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="D94">
         <v>114</v>
       </c>
       <c r="E94" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F94" t="s">
-        <v>138</v>
+        <v>38</v>
       </c>
       <c r="G94" t="s">
         <v>276</v>
       </c>
       <c r="H94" t="s">
-        <v>142</v>
+        <v>41</v>
       </c>
       <c r="I94">
         <v>6</v>
       </c>
       <c r="J94" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="K94" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="B95" t="s">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="C95" t="s">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="D95">
         <v>114</v>
       </c>
       <c r="E95" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F95" t="s">
-        <v>138</v>
+        <v>38</v>
       </c>
       <c r="G95" t="s">
         <v>277</v>
       </c>
       <c r="H95" t="s">
-        <v>143</v>
+        <v>37</v>
       </c>
       <c r="I95">
         <v>6</v>
       </c>
       <c r="J95" t="s">
-        <v>144</v>
+        <v>36</v>
       </c>
       <c r="K95" t="s">
-        <v>145</v>
+        <v>35</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="B96" t="s">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="C96" t="s">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="D96">
         <v>114</v>
       </c>
       <c r="E96" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="F96" t="s">
-        <v>146</v>
+        <v>32</v>
       </c>
       <c r="G96" t="s">
         <v>278</v>
       </c>
       <c r="H96" t="s">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c r="I96">
         <v>3</v>
       </c>
       <c r="J96" t="s">
-        <v>148</v>
+        <v>1</v>
       </c>
       <c r="K96" t="s">
-        <v>135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="B97" t="s">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="C97" t="s">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="D97">
         <v>114</v>
       </c>
       <c r="E97" t="s">
-        <v>86</v>
+        <v>33</v>
       </c>
       <c r="F97" t="s">
-        <v>146</v>
+        <v>32</v>
       </c>
       <c r="G97" t="s">
         <v>279</v>
       </c>
       <c r="H97" t="s">
-        <v>149</v>
+        <v>31</v>
       </c>
       <c r="I97">
         <v>3</v>
       </c>
       <c r="J97" t="s">
-        <v>148</v>
+        <v>1</v>
       </c>
       <c r="K97" t="s">
-        <v>135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="C98" t="s">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="D98">
         <v>114</v>
       </c>
       <c r="E98" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F98" t="s">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="G98" t="s">
         <v>280</v>
       </c>
       <c r="H98" t="s">
-        <v>151</v>
+        <v>30</v>
       </c>
       <c r="I98">
         <v>2</v>
       </c>
       <c r="J98" t="s">
-        <v>148</v>
+        <v>1</v>
       </c>
       <c r="K98" t="s">
-        <v>135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="B99" t="s">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="C99" t="s">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="D99">
         <v>114</v>
       </c>
       <c r="E99" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F99" t="s">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="G99" t="s">
         <v>281</v>
       </c>
       <c r="H99" t="s">
-        <v>152</v>
+        <v>29</v>
       </c>
       <c r="I99">
         <v>2</v>
       </c>
       <c r="J99" t="s">
-        <v>148</v>
+        <v>1</v>
       </c>
       <c r="K99" t="s">
-        <v>135</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="C100" t="s">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="D100">
         <v>114</v>
       </c>
       <c r="E100" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F100" t="s">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="G100" t="s">
         <v>282</v>
       </c>
       <c r="H100" t="s">
-        <v>153</v>
+        <v>28</v>
       </c>
       <c r="I100">
         <v>3</v>
       </c>
       <c r="J100" t="s">
-        <v>154</v>
+        <v>27</v>
       </c>
       <c r="K100" t="s">
-        <v>155</v>
+        <v>26</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="C101" t="s">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="D101">
         <v>114</v>
       </c>
       <c r="E101" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F101" t="s">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="G101" t="s">
         <v>283</v>
       </c>
       <c r="H101" t="s">
-        <v>156</v>
+        <v>25</v>
       </c>
       <c r="I101">
         <v>2</v>
       </c>
       <c r="J101" t="s">
-        <v>157</v>
+        <v>24</v>
       </c>
       <c r="K101" t="s">
-        <v>158</v>
+        <v>23</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="B102" t="s">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="C102" t="s">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="D102">
         <v>114</v>
       </c>
       <c r="E102" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F102" t="s">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="G102" t="s">
         <v>284</v>
       </c>
       <c r="H102" t="s">
-        <v>159</v>
+        <v>22</v>
       </c>
       <c r="I102">
         <v>2</v>
       </c>
       <c r="J102" t="s">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="K102" t="s">
-        <v>161</v>
+        <v>20</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="B103" t="s">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="C103" t="s">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="D103">
         <v>114</v>
       </c>
       <c r="E103" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F103" t="s">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="G103" t="s">
         <v>285</v>
       </c>
       <c r="H103" t="s">
-        <v>162</v>
+        <v>19</v>
       </c>
       <c r="I103">
         <v>3</v>
       </c>
       <c r="J103" t="s">
-        <v>163</v>
+        <v>18</v>
       </c>
       <c r="K103" t="s">
-        <v>164</v>
+        <v>17</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="B104" t="s">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="C104" t="s">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="D104">
         <v>114</v>
       </c>
       <c r="E104" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F104" t="s">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="G104" t="s">
         <v>286</v>
       </c>
       <c r="H104" t="s">
-        <v>165</v>
+        <v>16</v>
       </c>
       <c r="I104">
         <v>3</v>
       </c>
       <c r="J104" t="s">
-        <v>166</v>
+        <v>15</v>
       </c>
       <c r="K104" t="s">
-        <v>167</v>
+        <v>14</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="B105" t="s">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="C105" t="s">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="D105">
         <v>114</v>
       </c>
       <c r="E105" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F105" t="s">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="G105" t="s">
         <v>287</v>
       </c>
       <c r="H105" t="s">
-        <v>168</v>
+        <v>13</v>
       </c>
       <c r="I105">
         <v>3</v>
       </c>
       <c r="J105" t="s">
-        <v>169</v>
+        <v>12</v>
       </c>
       <c r="K105" t="s">
-        <v>170</v>
+        <v>11</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="C106" t="s">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="D106">
         <v>114</v>
       </c>
       <c r="E106" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F106" t="s">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="G106" t="s">
         <v>288</v>
       </c>
       <c r="H106" t="s">
-        <v>171</v>
+        <v>9</v>
       </c>
       <c r="I106">
         <v>3</v>
       </c>
       <c r="J106" t="s">
-        <v>172</v>
+        <v>8</v>
       </c>
       <c r="K106" t="s">
-        <v>173</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="C107" t="s">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="D107">
         <v>114</v>
       </c>
       <c r="E107" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F107" t="s">
-        <v>174</v>
+        <v>3</v>
       </c>
       <c r="G107" t="s">
         <v>289</v>
       </c>
       <c r="H107" t="s">
-        <v>175</v>
+        <v>2</v>
       </c>
       <c r="I107">
         <v>3</v>
       </c>
       <c r="J107" t="s">
-        <v>148</v>
+        <v>1</v>
       </c>
       <c r="K107" t="s">
-        <v>135</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5149,47 +5145,39 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E09D0B36-23A9-4193-B5C2-804643840ECE}">
-  <dimension ref="A1:K106"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A48E5CAA-EB30-4C44-830B-2AE636C1BECE}">
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="22.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.75" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>174</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>173</v>
       </c>
       <c r="C1" t="s">
-        <v>3</v>
+        <v>172</v>
       </c>
       <c r="D1" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="E1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="F1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="G1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="C2">
         <v>114</v>
@@ -5207,12 +5195,12 @@
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="66" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="C3">
         <v>114</v>
@@ -5226,16 +5214,16 @@
       <c r="F3">
         <v>20</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>181</v>
+      <c r="G3" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="B4" t="s">
-        <v>137</v>
+        <v>177</v>
       </c>
       <c r="C4">
         <v>114</v>
@@ -5250,423 +5238,12 @@
         <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="51" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K51">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="52" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K52">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="11:11" x14ac:dyDescent="0.25">
-      <c r="K53">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>135</v>
-      </c>
-      <c r="B92" t="s">
-        <v>136</v>
-      </c>
-      <c r="C92" t="s">
-        <v>137</v>
-      </c>
-      <c r="D92">
-        <v>114</v>
-      </c>
-      <c r="G92" t="s">
-        <v>139</v>
-      </c>
-      <c r="H92">
-        <v>3</v>
-      </c>
-      <c r="I92" t="s">
-        <v>141</v>
-      </c>
-      <c r="K92">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>135</v>
-      </c>
-      <c r="B93" t="s">
-        <v>136</v>
-      </c>
-      <c r="C93" t="s">
-        <v>137</v>
-      </c>
-      <c r="D93">
-        <v>114</v>
-      </c>
-      <c r="G93" t="s">
-        <v>142</v>
-      </c>
-      <c r="H93">
-        <v>6</v>
-      </c>
-      <c r="I93" t="s">
-        <v>19</v>
-      </c>
-      <c r="K93">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>135</v>
-      </c>
-      <c r="B94" t="s">
-        <v>136</v>
-      </c>
-      <c r="C94" t="s">
-        <v>137</v>
-      </c>
-      <c r="D94">
-        <v>114</v>
-      </c>
-      <c r="G94" t="s">
-        <v>143</v>
-      </c>
-      <c r="H94">
-        <v>6</v>
-      </c>
-      <c r="I94" t="s">
-        <v>145</v>
-      </c>
-      <c r="K94">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>135</v>
-      </c>
-      <c r="B95" t="s">
-        <v>136</v>
-      </c>
-      <c r="C95" t="s">
-        <v>137</v>
-      </c>
-      <c r="D95">
-        <v>114</v>
-      </c>
-      <c r="E95" t="s">
-        <v>86</v>
-      </c>
-      <c r="G95" t="s">
-        <v>147</v>
-      </c>
-      <c r="H95">
-        <v>3</v>
-      </c>
-      <c r="I95" t="s">
-        <v>135</v>
-      </c>
-      <c r="K95">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>135</v>
-      </c>
-      <c r="B96" t="s">
-        <v>136</v>
-      </c>
-      <c r="C96" t="s">
-        <v>137</v>
-      </c>
-      <c r="D96">
-        <v>114</v>
-      </c>
-      <c r="E96" t="s">
-        <v>86</v>
-      </c>
-      <c r="G96" t="s">
-        <v>149</v>
-      </c>
-      <c r="H96">
-        <v>3</v>
-      </c>
-      <c r="I96" t="s">
-        <v>135</v>
-      </c>
-      <c r="K96">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>135</v>
-      </c>
-      <c r="B97" t="s">
-        <v>136</v>
-      </c>
-      <c r="C97" t="s">
-        <v>137</v>
-      </c>
-      <c r="D97">
-        <v>114</v>
-      </c>
-      <c r="G97" t="s">
-        <v>151</v>
-      </c>
-      <c r="H97">
-        <v>2</v>
-      </c>
-      <c r="I97" t="s">
-        <v>135</v>
-      </c>
-      <c r="K97">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>135</v>
-      </c>
-      <c r="B98" t="s">
-        <v>136</v>
-      </c>
-      <c r="C98" t="s">
-        <v>137</v>
-      </c>
-      <c r="D98">
-        <v>114</v>
-      </c>
-      <c r="G98" t="s">
-        <v>152</v>
-      </c>
-      <c r="H98">
-        <v>2</v>
-      </c>
-      <c r="I98" t="s">
-        <v>135</v>
-      </c>
-      <c r="K98">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>135</v>
-      </c>
-      <c r="B99" t="s">
-        <v>136</v>
-      </c>
-      <c r="C99" t="s">
-        <v>137</v>
-      </c>
-      <c r="D99">
-        <v>114</v>
-      </c>
-      <c r="G99" t="s">
-        <v>153</v>
-      </c>
-      <c r="H99">
-        <v>3</v>
-      </c>
-      <c r="I99" t="s">
-        <v>155</v>
-      </c>
-      <c r="K99">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>135</v>
-      </c>
-      <c r="B100" t="s">
-        <v>136</v>
-      </c>
-      <c r="C100" t="s">
-        <v>137</v>
-      </c>
-      <c r="D100">
-        <v>114</v>
-      </c>
-      <c r="G100" t="s">
-        <v>183</v>
-      </c>
-      <c r="H100">
-        <v>2</v>
-      </c>
-      <c r="I100" t="s">
-        <v>158</v>
-      </c>
-      <c r="K100">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>135</v>
-      </c>
-      <c r="B101" t="s">
-        <v>136</v>
-      </c>
-      <c r="C101" t="s">
-        <v>137</v>
-      </c>
-      <c r="D101">
-        <v>114</v>
-      </c>
-      <c r="G101" t="s">
-        <v>159</v>
-      </c>
-      <c r="H101">
-        <v>2</v>
-      </c>
-      <c r="I101" t="s">
-        <v>161</v>
-      </c>
-      <c r="K101">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>135</v>
-      </c>
-      <c r="B102" t="s">
-        <v>136</v>
-      </c>
-      <c r="C102" t="s">
-        <v>137</v>
-      </c>
-      <c r="D102">
-        <v>114</v>
-      </c>
-      <c r="G102" t="s">
-        <v>184</v>
-      </c>
-      <c r="H102">
-        <v>3</v>
-      </c>
-      <c r="I102" t="s">
-        <v>164</v>
-      </c>
-      <c r="K102">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>135</v>
-      </c>
-      <c r="B103" t="s">
-        <v>136</v>
-      </c>
-      <c r="C103" t="s">
-        <v>137</v>
-      </c>
-      <c r="D103">
-        <v>114</v>
-      </c>
-      <c r="G103" t="s">
-        <v>165</v>
-      </c>
-      <c r="H103">
-        <v>3</v>
-      </c>
-      <c r="I103" t="s">
-        <v>167</v>
-      </c>
-      <c r="K103">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>135</v>
-      </c>
-      <c r="B104" t="s">
-        <v>136</v>
-      </c>
-      <c r="C104" t="s">
-        <v>137</v>
-      </c>
-      <c r="D104">
-        <v>114</v>
-      </c>
-      <c r="G104" t="s">
-        <v>168</v>
-      </c>
-      <c r="H104">
-        <v>3</v>
-      </c>
-      <c r="I104" t="s">
-        <v>170</v>
-      </c>
-      <c r="K104">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>135</v>
-      </c>
-      <c r="B105" t="s">
-        <v>136</v>
-      </c>
-      <c r="C105" t="s">
-        <v>137</v>
-      </c>
-      <c r="D105">
-        <v>114</v>
-      </c>
-      <c r="G105" t="s">
-        <v>171</v>
-      </c>
-      <c r="H105">
-        <v>3</v>
-      </c>
-      <c r="I105" t="s">
-        <v>173</v>
-      </c>
-      <c r="K105">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>135</v>
-      </c>
-      <c r="B106" t="s">
-        <v>136</v>
-      </c>
-      <c r="C106" t="s">
-        <v>137</v>
-      </c>
-      <c r="D106">
-        <v>114</v>
-      </c>
-      <c r="G106" t="s">
-        <v>175</v>
-      </c>
-      <c r="H106">
-        <v>3</v>
-      </c>
-      <c r="I106" t="s">
-        <v>135</v>
-      </c>
-      <c r="K106">
-        <v>2</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G4" xr:uid="{A48E5CAA-EB30-4C44-830B-2AE636C1BECE}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/master_data.xlsx
+++ b/master_data.xlsx
@@ -8,17 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\000_專案計畫\20260107_學分學程查詢功能\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE7A10BE-4031-4EA8-A2E8-737CEAA7EDA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7345CE83-CEFE-47F9-BAAA-A580BF948832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{5C756728-D7FE-4632-9F6E-380DC409B664}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BF35B52C-D03C-44DF-89E9-E0C2470A9351}"/>
   </bookViews>
   <sheets>
     <sheet name="科目表" sheetId="1" r:id="rId1"/>
     <sheet name="學程規範總額" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">科目表!$A$1:$L$108</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">學程規範總額!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">科目表!$A$1:$L$135</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,609 +43,763 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="361">
+  <si>
+    <t>學院</t>
+  </si>
+  <si>
+    <t>學程代碼</t>
+  </si>
+  <si>
+    <t>學程名稱</t>
+  </si>
+  <si>
+    <t>適用年度</t>
+  </si>
+  <si>
+    <t>科目類別</t>
+  </si>
+  <si>
+    <t>模組名稱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>課程代碼</t>
+  </si>
+  <si>
+    <t>課程名稱</t>
+  </si>
+  <si>
+    <t>學分數</t>
+  </si>
+  <si>
+    <t>認抵單位代碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>備註</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>互斥代碼</t>
+  </si>
+  <si>
+    <t>文學院</t>
+  </si>
+  <si>
+    <t>K060</t>
+  </si>
+  <si>
+    <t>中國古籍整理學分學程</t>
+  </si>
+  <si>
+    <t>必修</t>
+  </si>
+  <si>
+    <t>必修模組(8)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>書目學理論與實務</t>
+  </si>
+  <si>
+    <t>D10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>圖資系</t>
+  </si>
+  <si>
+    <t>國學導讀</t>
+  </si>
+  <si>
+    <t>D01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中文系</t>
+  </si>
+  <si>
+    <t>選修</t>
+  </si>
+  <si>
+    <t>選修模組(12)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>古籍資源管理</t>
+  </si>
+  <si>
+    <t>D106</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>圖資系碩士班</t>
+  </si>
+  <si>
+    <t>古籍整理與利用</t>
+  </si>
+  <si>
+    <t>數位典藏理論與實務專題</t>
+  </si>
+  <si>
+    <t>版本學與古籍保護</t>
+  </si>
+  <si>
+    <t>數位典藏與數位學習</t>
+  </si>
+  <si>
+    <t>檔案管理與加值行銷</t>
+  </si>
+  <si>
+    <t>圖書館推廣與行銷</t>
+  </si>
+  <si>
+    <t>圖書資訊學導論</t>
+  </si>
+  <si>
+    <t>參考資源</t>
+  </si>
+  <si>
+    <t>資訊組織</t>
+  </si>
+  <si>
+    <t>主題分析</t>
+  </si>
+  <si>
+    <t>館藏發展</t>
+  </si>
+  <si>
+    <t>人文學資源</t>
+  </si>
+  <si>
+    <t>社會科學資源</t>
+  </si>
+  <si>
+    <t>圖書館實務</t>
+  </si>
+  <si>
+    <t>禮記</t>
+  </si>
+  <si>
+    <t>尚書</t>
+  </si>
+  <si>
+    <t>老子</t>
+  </si>
+  <si>
+    <t>莊子</t>
+  </si>
+  <si>
+    <t>詩經</t>
+  </si>
+  <si>
+    <t>荀子</t>
+  </si>
+  <si>
+    <t>左傳</t>
+  </si>
+  <si>
+    <t>語法修辭學</t>
+  </si>
+  <si>
+    <t>文獻知識</t>
+  </si>
+  <si>
+    <t>聲韻學</t>
+  </si>
+  <si>
+    <t>訓詁學</t>
+  </si>
+  <si>
+    <t>文字學</t>
+  </si>
+  <si>
+    <t>中國傳統小說</t>
+  </si>
+  <si>
+    <t>中國古典戲曲</t>
+  </si>
+  <si>
+    <t>中國文學史</t>
+  </si>
+  <si>
+    <t>史記</t>
+  </si>
+  <si>
+    <t>易經</t>
+  </si>
+  <si>
+    <t>D01,D03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中文系or哲學系</t>
+  </si>
+  <si>
+    <t>先秦諸子哲學</t>
+  </si>
+  <si>
+    <t>D03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>哲學系</t>
+  </si>
+  <si>
+    <t>魏晉哲學</t>
+  </si>
+  <si>
+    <t>儒家哲學</t>
+  </si>
+  <si>
+    <t>兩漢哲學</t>
+  </si>
+  <si>
+    <t>五經思想</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>five_classics</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>五經思想：易經</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>佛學概論</t>
+  </si>
+  <si>
+    <t>宋明理學</t>
+  </si>
+  <si>
+    <t>清代哲學</t>
+  </si>
+  <si>
+    <t>chin_ph</t>
+  </si>
+  <si>
+    <t>清代哲學研究</t>
+  </si>
+  <si>
+    <t>道家哲學</t>
+  </si>
+  <si>
+    <t>dao_ph</t>
+  </si>
+  <si>
+    <t>先秦道家哲學</t>
+  </si>
+  <si>
+    <t>西洋博物館史</t>
+  </si>
+  <si>
+    <t>D02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>歷史系</t>
+  </si>
+  <si>
+    <t>臺灣博物館史</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>檔案與口述歷史</t>
+  </si>
+  <si>
+    <t>中國史學史</t>
+  </si>
+  <si>
+    <t>K260</t>
+  </si>
+  <si>
+    <t>哲學諮商與輔導學分學程</t>
+  </si>
+  <si>
+    <t>必修</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>必修模組(10)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>哲學諮商:理論與實務</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>哲學諮商方法論</t>
+  </si>
+  <si>
+    <t>哲學諮商:實習</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>哲學系、心理學系、臨床心理學系共同負責</t>
+  </si>
+  <si>
+    <t>選修模組(10)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>知識論</t>
+  </si>
+  <si>
+    <t>倫理學</t>
+  </si>
+  <si>
+    <t>哲學人學</t>
+  </si>
+  <si>
+    <t>兒童哲學</t>
+  </si>
+  <si>
+    <t>蘇格拉底對話</t>
+  </si>
+  <si>
+    <t>現象學導論</t>
+  </si>
+  <si>
+    <t>敘事符號學</t>
+  </si>
+  <si>
+    <t>詮釋學</t>
+  </si>
+  <si>
+    <t>方法論</t>
+  </si>
+  <si>
+    <t>行動哲學</t>
+  </si>
+  <si>
+    <t>存在主義</t>
+  </si>
+  <si>
+    <t>兒童哲學：理論與實務</t>
+  </si>
+  <si>
+    <t>哲學諮商與社會實踐</t>
+  </si>
+  <si>
+    <t>哲學諮商的倫理學基礎</t>
+  </si>
+  <si>
+    <t>亞里斯多德式的哲學諮商</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>哲學諮商實務</t>
+  </si>
+  <si>
+    <t>哲學諮商的批判思考</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>五經思想：易經</t>
+  </si>
+  <si>
+    <t>中國哲學的方法論</t>
+  </si>
+  <si>
+    <t>先秦儒家與情感哲學</t>
+  </si>
+  <si>
+    <t>中國哲學專題：人性論</t>
+  </si>
+  <si>
+    <t>敘說、反映與實踐導論</t>
+  </si>
+  <si>
+    <t>D39</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>心理系</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>輔導與諮商概論</t>
+  </si>
+  <si>
+    <t>電影、心理與人生</t>
+  </si>
+  <si>
+    <t>性別經驗與心理學</t>
+  </si>
+  <si>
+    <t>變態心理學</t>
+  </si>
+  <si>
+    <t>家庭關係與個人發展</t>
+  </si>
+  <si>
+    <t>諮商與心理治療理論</t>
+  </si>
+  <si>
+    <t>批判心理學導論</t>
+  </si>
+  <si>
+    <t>生命敘說與自我發展</t>
+  </si>
+  <si>
+    <t>戲劇治療</t>
+  </si>
+  <si>
+    <t>社會生活與社會治療</t>
+  </si>
+  <si>
+    <t>心理衛生</t>
+  </si>
+  <si>
+    <t>D95</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>臨心系</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>團體諮商</t>
+  </si>
+  <si>
+    <t>人本心理學</t>
+  </si>
+  <si>
+    <t>完形治療法</t>
+  </si>
+  <si>
+    <t>遊戲治療法</t>
+  </si>
+  <si>
+    <t>舞蹈治療實務</t>
+  </si>
   <si>
     <t>跨領域學院</t>
+  </si>
+  <si>
+    <t>K860</t>
+  </si>
+  <si>
+    <t>教育大數據微學程</t>
+  </si>
+  <si>
+    <t>基礎(至少2學分)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>程式設計概論</t>
+  </si>
+  <si>
+    <t>D65,D74,D0F,D0E,D76</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>經濟系、資管系、金企系、企管系、統資系</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>計算機概論</t>
+  </si>
+  <si>
+    <t>程式設計</t>
+  </si>
+  <si>
+    <t>D55,D56</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理系</t>
+  </si>
+  <si>
+    <t>重點(至少6學分)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>機器學習</t>
   </si>
   <si>
     <t>DTG,GTG</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>教育大數據專題</t>
+    <t>資料探索及資訊視覺化</t>
+  </si>
+  <si>
+    <t>專業/進階課程(至少2學分)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>資料庫系統設計</t>
+  </si>
+  <si>
+    <t>AI與永續</t>
+  </si>
+  <si>
+    <t>大數據資料分析與應用</t>
+  </si>
+  <si>
+    <t>CQ1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI學士後系</t>
+  </si>
+  <si>
+    <t>生成式AI與生活</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>C1T</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>資創學程</t>
+  </si>
+  <si>
+    <t>教育科技發展趨勢</t>
+  </si>
+  <si>
+    <t>D0V</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>領科學程三</t>
+  </si>
+  <si>
+    <t>特殊教育與適性教學</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DE1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中等教育學程</t>
+  </si>
+  <si>
+    <t>資料庫系統概論</t>
+  </si>
+  <si>
+    <t>D51</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>資工系</t>
+  </si>
+  <si>
+    <t>資料庫</t>
+  </si>
+  <si>
+    <t>D1B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>資數系</t>
+  </si>
+  <si>
+    <t>資料庫管理</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>D71,D74,D76</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>會計系、資管系、統資系</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>總整課程(至少2學分)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>教育大數據專題</t>
+  </si>
+  <si>
+    <t>創新跨領域學院</t>
+  </si>
+  <si>
+    <t>K890</t>
+  </si>
+  <si>
+    <t>新莊好學跨領域學分學程</t>
+  </si>
+  <si>
     <t>選修</t>
-  </si>
-  <si>
-    <t>教育大數據微學程</t>
-  </si>
-  <si>
-    <t>K860</t>
-  </si>
-  <si>
-    <t>會計系、資管系、統資系</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>D71,D74,D76</t>
+    <t>基礎課程(2)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>資料庫管理</t>
+    <t>教育與大學社會責任-〈新莊學〉啟航</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>專業/進階課程(至少2學分)</t>
+    <t>大學與社區的連結-新莊對話</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>資數系</t>
-  </si>
-  <si>
-    <t>D1B</t>
+    <t>全人教育課程中心</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>資料庫</t>
-  </si>
-  <si>
-    <t>資工系</t>
-  </si>
-  <si>
-    <t>D51</t>
+    <t>訓練課程(4)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>資料庫系統概論</t>
-  </si>
-  <si>
-    <t>中等教育學程</t>
-  </si>
-  <si>
-    <t>DE1</t>
+    <t>地方想像</t>
+  </si>
+  <si>
+    <t>社創學程</t>
+  </si>
+  <si>
+    <t>新莊學文史實作</t>
+  </si>
+  <si>
+    <t>博物館展覽實作</t>
+  </si>
+  <si>
+    <t>台灣社會史</t>
+  </si>
+  <si>
+    <t>文化人類學</t>
+  </si>
+  <si>
+    <t>新莊文化景觀之保存與活化</t>
+  </si>
+  <si>
+    <t>景觀設計（一）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>特殊教育與適性教學</t>
+    <t>多了空格</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>領科學程三</t>
-  </si>
-  <si>
-    <t>D0V</t>
+    <t>景觀設計系</t>
+  </si>
+  <si>
+    <t>景觀設計（二）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>教育科技發展趨勢</t>
-  </si>
-  <si>
-    <t>資創學程</t>
-  </si>
-  <si>
-    <t>C1T</t>
+    <t>植栽設計(一)</t>
+  </si>
+  <si>
+    <t>英語教學與跨文化溝通服務學習</t>
+  </si>
+  <si>
+    <t>英文系</t>
+  </si>
+  <si>
+    <t>英語教學與兒童文學:故事與繪本</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>生成式AI與生活</t>
+    <t>冒號小寫</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>AI學士後系</t>
-  </si>
-  <si>
-    <t>CQ1</t>
+    <t>英語教學與教育心理</t>
+  </si>
+  <si>
+    <t>文化產業經營與管理</t>
+  </si>
+  <si>
+    <t>藝術與文化創意學士學位學程</t>
+  </si>
+  <si>
+    <t>實踐課程(10)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>大數據資料分析與應用</t>
-  </si>
-  <si>
-    <t>AI與永續</t>
-  </si>
-  <si>
-    <t>資料庫系統設計</t>
-  </si>
-  <si>
-    <t>資料探索及資訊視覺化</t>
-  </si>
-  <si>
-    <t>重點(至少6學分)</t>
+    <t>臺灣古蹟導覽</t>
+  </si>
+  <si>
+    <t>紀錄片與影像敘事</t>
+  </si>
+  <si>
+    <t>文化資產與歷史素養</t>
+  </si>
+  <si>
+    <t>歷史系/文服學程系</t>
+  </si>
+  <si>
+    <t>景觀英文</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>必修</t>
+    <t>沒這科目</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>機器學習</t>
-  </si>
-  <si>
-    <t>物理系</t>
-  </si>
-  <si>
-    <t>D55,D56</t>
+    <t>自主學習學分：數位人文創新行動計畫</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>程式設計</t>
-  </si>
-  <si>
-    <t>基礎(至少2學分)</t>
+    <t>自主學習-數位人文創新行動計畫</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>圖資系</t>
-  </si>
-  <si>
-    <t>D10</t>
+    <t>景觀工程</t>
+  </si>
+  <si>
+    <t>生態設計</t>
+  </si>
+  <si>
+    <t>植栽設計(二)</t>
+  </si>
+  <si>
+    <t>造園景觀施工實務</t>
+  </si>
+  <si>
+    <t>跨文化翻轉教學法</t>
+  </si>
+  <si>
+    <t>跨文化外語翻轉教學法??</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>計算機概論</t>
-  </si>
-  <si>
-    <t>經濟系、資管系、金企系、企管系、統資系</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>D65,D74,D0F,D0E,D76</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>程式設計概論</t>
-  </si>
-  <si>
-    <t>臨心系</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>D95</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>舞蹈治療實務</t>
-  </si>
-  <si>
-    <t>選修模組(10)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>哲學諮商與輔導學分學程</t>
-  </si>
-  <si>
-    <t>K260</t>
-  </si>
-  <si>
-    <t>文學院</t>
-  </si>
-  <si>
-    <t>遊戲治療法</t>
-  </si>
-  <si>
-    <t>完形治療法</t>
-  </si>
-  <si>
-    <t>人本心理學</t>
-  </si>
-  <si>
-    <t>團體諮商</t>
-  </si>
-  <si>
-    <t>心理衛生</t>
-  </si>
-  <si>
-    <t>心理系</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>D39</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>社會生活與社會治療</t>
-  </si>
-  <si>
-    <t>戲劇治療</t>
-  </si>
-  <si>
-    <t>生命敘說與自我發展</t>
-  </si>
-  <si>
-    <t>批判心理學導論</t>
-  </si>
-  <si>
-    <t>諮商與心理治療理論</t>
-  </si>
-  <si>
-    <t>家庭關係與個人發展</t>
-  </si>
-  <si>
-    <t>變態心理學</t>
-  </si>
-  <si>
-    <t>性別經驗與心理學</t>
-  </si>
-  <si>
-    <t>電影、心理與人生</t>
-  </si>
-  <si>
-    <t>輔導與諮商概論</t>
-  </si>
-  <si>
-    <t>敘說、反映與實踐導論</t>
-  </si>
-  <si>
-    <t>哲學系</t>
-  </si>
-  <si>
-    <t>D03</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中國哲學專題：人性論</t>
-  </si>
-  <si>
-    <t>先秦儒家與情感哲學</t>
-  </si>
-  <si>
-    <t>中國哲學的方法論</t>
-  </si>
-  <si>
-    <t>五經思想：易經</t>
-  </si>
-  <si>
-    <t>哲學諮商的批判思考</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>哲學諮商實務</t>
-  </si>
-  <si>
-    <t>亞里斯多德式的哲學諮商</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>哲學諮商的倫理學基礎</t>
-  </si>
-  <si>
-    <t>哲學諮商與社會實踐</t>
-  </si>
-  <si>
-    <t>兒童哲學：理論與實務</t>
-  </si>
-  <si>
-    <t>存在主義</t>
-  </si>
-  <si>
-    <t>行動哲學</t>
-  </si>
-  <si>
-    <t>方法論</t>
-  </si>
-  <si>
-    <t>詮釋學</t>
-  </si>
-  <si>
-    <t>敘事符號學</t>
-  </si>
-  <si>
-    <t>現象學導論</t>
-  </si>
-  <si>
-    <t>蘇格拉底對話</t>
-  </si>
-  <si>
-    <t>兒童哲學</t>
-  </si>
-  <si>
-    <t>哲學人學</t>
-  </si>
-  <si>
-    <t>倫理學</t>
-  </si>
-  <si>
-    <t>知識論</t>
-  </si>
-  <si>
-    <t>哲學系、心理學系、臨床心理學系共同負責</t>
-  </si>
-  <si>
-    <t>哲學諮商:實習</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>必修模組(10)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>哲學諮商方法論</t>
-  </si>
-  <si>
-    <t>哲學諮商:理論與實務</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>歷史系</t>
-  </si>
-  <si>
-    <t>D02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中國史學史</t>
-  </si>
-  <si>
-    <t>選修模組(12)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>中國古籍整理學分學程</t>
-  </si>
-  <si>
-    <t>K060</t>
-  </si>
-  <si>
-    <t>檔案與口述歷史</t>
-  </si>
-  <si>
-    <t>臺灣博物館史</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>西洋博物館史</t>
-  </si>
-  <si>
-    <t>dao_ph</t>
-  </si>
-  <si>
-    <t>先秦道家哲學</t>
-  </si>
-  <si>
-    <t>道家哲學</t>
-  </si>
-  <si>
-    <t>chin_ph</t>
-  </si>
-  <si>
-    <t>清代哲學研究</t>
-  </si>
-  <si>
-    <t>清代哲學</t>
-  </si>
-  <si>
-    <t>宋明理學</t>
-  </si>
-  <si>
-    <t>佛學概論</t>
-  </si>
-  <si>
-    <t>five_classics</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>五經思想：易經</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>五經思想</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>兩漢哲學</t>
-  </si>
-  <si>
-    <t>儒家哲學</t>
-  </si>
-  <si>
-    <t>魏晉哲學</t>
-  </si>
-  <si>
-    <t>先秦諸子哲學</t>
-  </si>
-  <si>
-    <t>中文系or哲學系</t>
-  </si>
-  <si>
-    <t>D01,D03</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>易經</t>
-  </si>
-  <si>
-    <t>中文系</t>
-  </si>
-  <si>
-    <t>D01</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>史記</t>
-  </si>
-  <si>
-    <t>中國文學史</t>
-  </si>
-  <si>
-    <t>中國古典戲曲</t>
-  </si>
-  <si>
-    <t>中國傳統小說</t>
-  </si>
-  <si>
-    <t>文字學</t>
-  </si>
-  <si>
-    <t>訓詁學</t>
-  </si>
-  <si>
-    <t>聲韻學</t>
-  </si>
-  <si>
-    <t>文獻知識</t>
-  </si>
-  <si>
-    <t>語法修辭學</t>
-  </si>
-  <si>
-    <t>左傳</t>
-  </si>
-  <si>
-    <t>荀子</t>
-  </si>
-  <si>
-    <t>詩經</t>
-  </si>
-  <si>
-    <t>莊子</t>
-  </si>
-  <si>
-    <t>老子</t>
-  </si>
-  <si>
-    <t>尚書</t>
-  </si>
-  <si>
-    <t>禮記</t>
-  </si>
-  <si>
-    <t>圖書館實務</t>
-  </si>
-  <si>
-    <t>社會科學資源</t>
-  </si>
-  <si>
-    <t>人文學資源</t>
-  </si>
-  <si>
-    <t>館藏發展</t>
-  </si>
-  <si>
-    <t>主題分析</t>
-  </si>
-  <si>
-    <t>資訊組織</t>
-  </si>
-  <si>
-    <t>參考資源</t>
-  </si>
-  <si>
-    <t>圖書資訊學導論</t>
-  </si>
-  <si>
-    <t>圖書館推廣與行銷</t>
-  </si>
-  <si>
-    <t>檔案管理與加值行銷</t>
-  </si>
-  <si>
-    <t>數位典藏與數位學習</t>
-  </si>
-  <si>
-    <t>版本學與古籍保護</t>
-  </si>
-  <si>
-    <t>圖資系碩士班</t>
-  </si>
-  <si>
-    <t>D106</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>數位典藏理論與實務專題</t>
-  </si>
-  <si>
-    <t>古籍整理與利用</t>
-  </si>
-  <si>
-    <t>古籍資源管理</t>
-  </si>
-  <si>
-    <t>國學導讀</t>
-  </si>
-  <si>
-    <t>必修模組(8)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>必修</t>
-  </si>
-  <si>
-    <t>書目學理論與實務</t>
-  </si>
-  <si>
-    <t>互斥代碼</t>
-  </si>
-  <si>
-    <t>備註</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>認抵單位代碼</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>學分數</t>
-  </si>
-  <si>
-    <t>課程名稱</t>
-  </si>
-  <si>
-    <t>課程代碼</t>
-  </si>
-  <si>
-    <t>模組名稱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>科目類別</t>
-  </si>
-  <si>
-    <t>適用年度</t>
-  </si>
-  <si>
-    <t>學程名稱</t>
-  </si>
-  <si>
-    <t>學程代碼</t>
-  </si>
-  <si>
-    <t>學院</t>
-  </si>
-  <si>
-    <t>本微學程應修學分數 12 學分。包括基礎課程(2 學分)、重點課程(6 學分)、專業/進階課程(2 學分)、總整課程(2 學分)</t>
-  </si>
-  <si>
-    <t>教育大數據微學程</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>K860</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>畢業製作</t>
+  </si>
+  <si>
+    <t>進修部英文系</t>
+  </si>
+  <si>
+    <t>插畫應用</t>
+  </si>
+  <si>
+    <t>創意商品設計</t>
+  </si>
+  <si>
+    <t>必修總學分</t>
+  </si>
+  <si>
+    <t>選修總學分</t>
+  </si>
+  <si>
+    <t>總計應修學分</t>
+  </si>
+  <si>
+    <t>備註 (模組要求)</t>
+  </si>
+  <si>
+    <t>必修8學分，選修12學分</t>
   </si>
   <si>
     <t>必修核心課程(共十學分) ,選修課程(至少須修讀十學分) ,
 開設課程及開放選修名額以當年度課表為準</t>
   </si>
   <si>
-    <t>必修8學分，選修12學分</t>
-  </si>
-  <si>
-    <t>備註 (模組要求)</t>
-  </si>
-  <si>
-    <t>總計應修學分</t>
-  </si>
-  <si>
-    <t>選修總學分</t>
-  </si>
-  <si>
-    <t>必修總學分</t>
+    <t>本微學程應修學分數 12 學分。包括基礎課程(2 學分)、重點課程(6 學分)、專業/進階課程(2 學分)、總整課程(2 學分)</t>
+  </si>
+  <si>
+    <t>本學程應修學分數 16 學分。包括基礎課程(2 學分)、訓練課程(4 學分)、實踐課程(10 學分)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>17624</t>
@@ -962,6 +1115,81 @@
   </si>
   <si>
     <t>36029</t>
+  </si>
+  <si>
+    <t>34685</t>
+  </si>
+  <si>
+    <t>35135</t>
+  </si>
+  <si>
+    <t>36863</t>
+  </si>
+  <si>
+    <t>36155</t>
+  </si>
+  <si>
+    <t>20388</t>
+  </si>
+  <si>
+    <t>15833</t>
+  </si>
+  <si>
+    <t>01199</t>
+  </si>
+  <si>
+    <t>36679</t>
+  </si>
+  <si>
+    <t>03867</t>
+  </si>
+  <si>
+    <t>03868</t>
+  </si>
+  <si>
+    <t>11078</t>
+  </si>
+  <si>
+    <t>24119</t>
+  </si>
+  <si>
+    <t>21036</t>
+  </si>
+  <si>
+    <t>30392</t>
+  </si>
+  <si>
+    <t>18830</t>
+  </si>
+  <si>
+    <t>21293</t>
+  </si>
+  <si>
+    <t>36915</t>
+  </si>
+  <si>
+    <t>35161</t>
+  </si>
+  <si>
+    <t>03876</t>
+  </si>
+  <si>
+    <t>35531</t>
+  </si>
+  <si>
+    <t>11281</t>
+  </si>
+  <si>
+    <t>14846</t>
+  </si>
+  <si>
+    <t>02213</t>
+  </si>
+  <si>
+    <t>35851</t>
+  </si>
+  <si>
+    <t>18843</t>
   </si>
 </sst>
 </file>
@@ -1355,3787 +1583,4701 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41A0537A-F1D1-4B6B-B8E7-906C63A687B2}">
-  <dimension ref="A1:L107"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5BBB722-6DB7-463D-AC03-0DD96DAA2023}">
+  <dimension ref="A1:L135"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.25" customWidth="1"/>
     <col min="2" max="2" width="9.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22.75" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="36.75" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="32.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="32" customWidth="1"/>
     <col min="12" max="12" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>175</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>174</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>173</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>172</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>171</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>170</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>169</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>168</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>167</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>166</v>
+        <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>165</v>
+        <v>10</v>
       </c>
       <c r="L1" t="s">
-        <v>164</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D2">
         <v>114</v>
       </c>
       <c r="E2" t="s">
-        <v>162</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>161</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>185</v>
+        <v>231</v>
       </c>
       <c r="H2" t="s">
-        <v>163</v>
+        <v>17</v>
       </c>
       <c r="I2">
         <v>4</v>
       </c>
       <c r="J2" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>114</v>
       </c>
       <c r="E3" t="s">
-        <v>162</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>161</v>
+        <v>16</v>
       </c>
       <c r="G3" t="s">
-        <v>186</v>
+        <v>232</v>
       </c>
       <c r="H3" t="s">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="I3">
         <v>4</v>
       </c>
       <c r="J3" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="K3" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D4">
         <v>114</v>
       </c>
       <c r="E4" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>187</v>
+        <v>233</v>
       </c>
       <c r="H4" t="s">
-        <v>159</v>
+        <v>25</v>
       </c>
       <c r="I4">
         <v>2</v>
       </c>
       <c r="J4" t="s">
-        <v>156</v>
+        <v>26</v>
       </c>
       <c r="K4" t="s">
-        <v>155</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D5">
         <v>114</v>
       </c>
       <c r="E5" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G5" t="s">
-        <v>188</v>
+        <v>234</v>
       </c>
       <c r="H5" t="s">
-        <v>158</v>
+        <v>28</v>
       </c>
       <c r="I5">
         <v>2</v>
       </c>
       <c r="J5" t="s">
-        <v>156</v>
+        <v>26</v>
       </c>
       <c r="K5" t="s">
-        <v>155</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D6">
         <v>114</v>
       </c>
       <c r="E6" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F6" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G6" t="s">
-        <v>189</v>
+        <v>235</v>
       </c>
       <c r="H6" t="s">
-        <v>157</v>
+        <v>29</v>
       </c>
       <c r="I6">
         <v>2</v>
       </c>
       <c r="J6" t="s">
-        <v>156</v>
+        <v>26</v>
       </c>
       <c r="K6" t="s">
-        <v>155</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D7">
         <v>114</v>
       </c>
       <c r="E7" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F7" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G7" t="s">
-        <v>190</v>
+        <v>236</v>
       </c>
       <c r="H7" t="s">
-        <v>154</v>
+        <v>30</v>
       </c>
       <c r="I7">
         <v>4</v>
       </c>
       <c r="J7" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="K7" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D8">
         <v>114</v>
       </c>
       <c r="E8" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F8" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G8" t="s">
-        <v>191</v>
+        <v>237</v>
       </c>
       <c r="H8" t="s">
-        <v>153</v>
+        <v>31</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
       <c r="J8" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="K8" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D9">
         <v>114</v>
       </c>
       <c r="E9" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G9" t="s">
-        <v>192</v>
+        <v>238</v>
       </c>
       <c r="H9" t="s">
-        <v>152</v>
+        <v>32</v>
       </c>
       <c r="I9">
         <v>4</v>
       </c>
       <c r="J9" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="K9" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D10">
         <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F10" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G10" t="s">
-        <v>193</v>
+        <v>239</v>
       </c>
       <c r="H10" t="s">
-        <v>151</v>
+        <v>33</v>
       </c>
       <c r="I10">
         <v>4</v>
       </c>
       <c r="J10" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="K10" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D11">
         <v>114</v>
       </c>
       <c r="E11" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F11" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G11" t="s">
-        <v>194</v>
+        <v>240</v>
       </c>
       <c r="H11" t="s">
-        <v>150</v>
+        <v>34</v>
       </c>
       <c r="I11">
         <v>4</v>
       </c>
       <c r="J11" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="K11" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D12">
         <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F12" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G12" t="s">
-        <v>195</v>
+        <v>241</v>
       </c>
       <c r="H12" t="s">
-        <v>149</v>
+        <v>35</v>
       </c>
       <c r="I12">
         <v>4</v>
       </c>
       <c r="J12" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="K12" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D13">
         <v>114</v>
       </c>
       <c r="E13" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F13" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G13" t="s">
-        <v>196</v>
+        <v>242</v>
       </c>
       <c r="H13" t="s">
-        <v>148</v>
+        <v>36</v>
       </c>
       <c r="I13">
         <v>4</v>
       </c>
       <c r="J13" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="K13" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D14">
         <v>114</v>
       </c>
       <c r="E14" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F14" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G14" t="s">
-        <v>197</v>
+        <v>243</v>
       </c>
       <c r="H14" t="s">
-        <v>147</v>
+        <v>37</v>
       </c>
       <c r="I14">
         <v>4</v>
       </c>
       <c r="J14" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="K14" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D15">
         <v>114</v>
       </c>
       <c r="E15" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F15" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G15" t="s">
-        <v>198</v>
+        <v>244</v>
       </c>
       <c r="H15" t="s">
-        <v>146</v>
+        <v>38</v>
       </c>
       <c r="I15">
         <v>4</v>
       </c>
       <c r="J15" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="K15" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D16">
         <v>114</v>
       </c>
       <c r="E16" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F16" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G16" t="s">
-        <v>199</v>
+        <v>245</v>
       </c>
       <c r="H16" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="I16">
         <v>4</v>
       </c>
       <c r="J16" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="K16" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D17">
         <v>114</v>
       </c>
       <c r="E17" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F17" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G17" t="s">
-        <v>200</v>
+        <v>246</v>
       </c>
       <c r="H17" t="s">
-        <v>144</v>
+        <v>40</v>
       </c>
       <c r="I17">
         <v>4</v>
       </c>
       <c r="J17" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="K17" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D18">
         <v>114</v>
       </c>
       <c r="E18" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F18" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G18" t="s">
-        <v>201</v>
+        <v>247</v>
       </c>
       <c r="H18" t="s">
-        <v>143</v>
+        <v>41</v>
       </c>
       <c r="I18">
         <v>2</v>
       </c>
       <c r="J18" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="K18" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D19">
         <v>114</v>
       </c>
       <c r="E19" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F19" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G19" t="s">
-        <v>202</v>
+        <v>248</v>
       </c>
       <c r="H19" t="s">
-        <v>142</v>
+        <v>42</v>
       </c>
       <c r="I19">
         <v>4</v>
       </c>
       <c r="J19" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="K19" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D20">
         <v>114</v>
       </c>
       <c r="E20" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F20" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G20" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="H20" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="I20">
         <v>4</v>
       </c>
       <c r="J20" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="K20" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D21">
         <v>114</v>
       </c>
       <c r="E21" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F21" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G21" t="s">
-        <v>204</v>
+        <v>250</v>
       </c>
       <c r="H21" t="s">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="I21">
         <v>4</v>
       </c>
       <c r="J21" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="K21" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D22">
         <v>114</v>
       </c>
       <c r="E22" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F22" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G22" t="s">
-        <v>205</v>
+        <v>251</v>
       </c>
       <c r="H22" t="s">
-        <v>139</v>
+        <v>45</v>
       </c>
       <c r="I22">
         <v>4</v>
       </c>
       <c r="J22" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="K22" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B23" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D23">
         <v>114</v>
       </c>
       <c r="E23" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G23" t="s">
-        <v>206</v>
+        <v>252</v>
       </c>
       <c r="H23" t="s">
-        <v>138</v>
+        <v>46</v>
       </c>
       <c r="I23">
         <v>4</v>
       </c>
       <c r="J23" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="K23" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C24" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D24">
         <v>114</v>
       </c>
       <c r="E24" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F24" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G24" t="s">
-        <v>207</v>
+        <v>253</v>
       </c>
       <c r="H24" t="s">
-        <v>137</v>
+        <v>47</v>
       </c>
       <c r="I24">
         <v>4</v>
       </c>
       <c r="J24" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="K24" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C25" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D25">
         <v>114</v>
       </c>
       <c r="E25" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F25" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G25" t="s">
-        <v>208</v>
+        <v>254</v>
       </c>
       <c r="H25" t="s">
-        <v>136</v>
+        <v>48</v>
       </c>
       <c r="I25">
         <v>4</v>
       </c>
       <c r="J25" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="K25" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D26">
         <v>114</v>
       </c>
       <c r="E26" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F26" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G26" t="s">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="H26" t="s">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="I26">
         <v>4</v>
       </c>
       <c r="J26" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="K26" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C27" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D27">
         <v>114</v>
       </c>
       <c r="E27" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F27" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G27" t="s">
-        <v>210</v>
+        <v>256</v>
       </c>
       <c r="H27" t="s">
-        <v>134</v>
+        <v>50</v>
       </c>
       <c r="I27">
         <v>4</v>
       </c>
       <c r="J27" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="K27" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28">
+        <v>114</v>
+      </c>
+      <c r="E28" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" t="s">
+        <v>24</v>
+      </c>
+      <c r="G28" t="s">
+        <v>257</v>
+      </c>
+      <c r="H28" t="s">
         <v>51</v>
-      </c>
-      <c r="B28" t="s">
-        <v>103</v>
-      </c>
-      <c r="C28" t="s">
-        <v>102</v>
-      </c>
-      <c r="D28">
-        <v>114</v>
-      </c>
-      <c r="E28" t="s">
-        <v>4</v>
-      </c>
-      <c r="F28" t="s">
-        <v>101</v>
-      </c>
-      <c r="G28" t="s">
-        <v>211</v>
-      </c>
-      <c r="H28" t="s">
-        <v>133</v>
       </c>
       <c r="I28">
         <v>4</v>
       </c>
       <c r="J28" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="K28" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C29" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D29">
         <v>114</v>
       </c>
       <c r="E29" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F29" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G29" t="s">
-        <v>212</v>
+        <v>258</v>
       </c>
       <c r="H29" t="s">
-        <v>132</v>
+        <v>52</v>
       </c>
       <c r="I29">
         <v>4</v>
       </c>
       <c r="J29" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="K29" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C30" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D30">
         <v>114</v>
       </c>
       <c r="E30" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F30" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G30" t="s">
-        <v>213</v>
+        <v>259</v>
       </c>
       <c r="H30" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="I30">
         <v>4</v>
       </c>
       <c r="J30" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="K30" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D31">
         <v>114</v>
       </c>
       <c r="E31" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F31" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G31" t="s">
-        <v>214</v>
+        <v>260</v>
       </c>
       <c r="H31" t="s">
-        <v>130</v>
+        <v>54</v>
       </c>
       <c r="I31">
         <v>4</v>
       </c>
       <c r="J31" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="K31" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D32">
         <v>114</v>
       </c>
       <c r="E32" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F32" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G32" t="s">
-        <v>215</v>
+        <v>261</v>
       </c>
       <c r="H32" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
       <c r="I32">
         <v>4</v>
       </c>
       <c r="J32" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="K32" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D33">
         <v>114</v>
       </c>
       <c r="E33" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F33" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G33" t="s">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="H33" t="s">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="I33">
         <v>6</v>
       </c>
       <c r="J33" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="K33" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C34" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D34">
         <v>114</v>
       </c>
       <c r="E34" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F34" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G34" t="s">
-        <v>217</v>
+        <v>263</v>
       </c>
       <c r="H34" t="s">
-        <v>127</v>
+        <v>57</v>
       </c>
       <c r="I34">
         <v>4</v>
       </c>
       <c r="J34" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="K34" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D35">
         <v>114</v>
       </c>
       <c r="E35" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F35" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G35" t="s">
-        <v>218</v>
+        <v>264</v>
       </c>
       <c r="H35" t="s">
-        <v>124</v>
+        <v>58</v>
       </c>
       <c r="I35">
         <v>4</v>
       </c>
       <c r="J35" t="s">
-        <v>123</v>
+        <v>59</v>
       </c>
       <c r="K35" t="s">
-        <v>122</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D36">
         <v>114</v>
       </c>
       <c r="E36" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F36" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G36" t="s">
-        <v>219</v>
+        <v>265</v>
       </c>
       <c r="H36" t="s">
-        <v>121</v>
+        <v>61</v>
       </c>
       <c r="I36">
         <v>4</v>
       </c>
       <c r="J36" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K36" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C37" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D37">
         <v>114</v>
       </c>
       <c r="E37" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F37" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G37" t="s">
-        <v>220</v>
+        <v>266</v>
       </c>
       <c r="H37" t="s">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="I37">
         <v>4</v>
       </c>
       <c r="J37" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K37" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B38" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C38" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D38">
         <v>114</v>
       </c>
       <c r="E38" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F38" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G38" t="s">
-        <v>221</v>
+        <v>267</v>
       </c>
       <c r="H38" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="I38">
         <v>4</v>
       </c>
       <c r="J38" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K38" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D39">
         <v>114</v>
       </c>
       <c r="E39" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F39" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G39" t="s">
-        <v>222</v>
+        <v>268</v>
       </c>
       <c r="H39" t="s">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="I39">
         <v>4</v>
       </c>
       <c r="J39" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K39" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C40" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D40">
         <v>114</v>
       </c>
       <c r="E40" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F40" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G40" t="s">
-        <v>223</v>
+        <v>269</v>
       </c>
       <c r="H40" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="I40">
         <v>4</v>
       </c>
       <c r="J40" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K40" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L40" t="s">
-        <v>115</v>
+        <v>68</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C41" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D41">
         <v>114</v>
       </c>
       <c r="E41" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F41" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G41" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="H41" t="s">
-        <v>116</v>
+        <v>69</v>
       </c>
       <c r="I41">
         <v>4</v>
       </c>
       <c r="J41" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K41" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L41" t="s">
-        <v>115</v>
+        <v>68</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C42" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D42">
         <v>114</v>
       </c>
       <c r="E42" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F42" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G42" t="s">
-        <v>225</v>
+        <v>271</v>
       </c>
       <c r="H42" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="I42">
         <v>4</v>
       </c>
       <c r="J42" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K42" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C43" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D43">
         <v>114</v>
       </c>
       <c r="E43" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F43" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G43" t="s">
-        <v>226</v>
+        <v>272</v>
       </c>
       <c r="H43" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="I43">
         <v>4</v>
       </c>
       <c r="J43" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K43" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D44">
         <v>114</v>
       </c>
       <c r="E44" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F44" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G44" t="s">
-        <v>227</v>
+        <v>273</v>
       </c>
       <c r="H44" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="I44">
         <v>4</v>
       </c>
       <c r="J44" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K44" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L44" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D45">
         <v>114</v>
       </c>
       <c r="E45" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F45" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G45" t="s">
-        <v>228</v>
+        <v>274</v>
       </c>
       <c r="H45" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="I45">
         <v>4</v>
       </c>
       <c r="J45" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K45" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L45" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D46">
         <v>114</v>
       </c>
       <c r="E46" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F46" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G46" t="s">
-        <v>229</v>
+        <v>275</v>
       </c>
       <c r="H46" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="I46">
         <v>4</v>
       </c>
       <c r="J46" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K46" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L46" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D47">
         <v>114</v>
       </c>
       <c r="E47" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F47" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G47" t="s">
-        <v>230</v>
+        <v>276</v>
       </c>
       <c r="H47" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="I47">
         <v>4</v>
       </c>
       <c r="J47" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K47" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L47" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D48">
         <v>114</v>
       </c>
       <c r="E48" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F48" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G48" t="s">
-        <v>231</v>
+        <v>277</v>
       </c>
       <c r="H48" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="I48">
         <v>2</v>
       </c>
       <c r="J48" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="K48" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D49">
         <v>114</v>
       </c>
       <c r="E49" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F49" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G49" t="s">
-        <v>232</v>
+        <v>278</v>
       </c>
       <c r="H49" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="I49">
         <v>2</v>
       </c>
       <c r="J49" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="K49" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C50" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D50">
         <v>114</v>
       </c>
       <c r="E50" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F50" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G50" t="s">
-        <v>233</v>
+        <v>279</v>
       </c>
       <c r="H50" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="I50">
         <v>2</v>
       </c>
       <c r="J50" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="K50" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="C51" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="D51">
         <v>114</v>
       </c>
       <c r="E51" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F51" t="s">
-        <v>101</v>
+        <v>24</v>
       </c>
       <c r="G51" t="s">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="H51" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="I51">
         <v>4</v>
       </c>
       <c r="J51" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="K51" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C52" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D52">
         <v>114</v>
       </c>
       <c r="E52" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="F52" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G52" t="s">
-        <v>235</v>
+        <v>281</v>
       </c>
       <c r="H52" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I52">
         <v>4</v>
       </c>
       <c r="J52" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K52" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C53" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D53">
         <v>114</v>
       </c>
       <c r="E53" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="F53" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G53" t="s">
-        <v>236</v>
+        <v>282</v>
       </c>
       <c r="H53" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="I53">
         <v>4</v>
       </c>
       <c r="J53" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K53" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B54" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C54" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D54">
         <v>114</v>
       </c>
       <c r="E54" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="F54" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G54" t="s">
-        <v>237</v>
+        <v>283</v>
       </c>
       <c r="H54" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I54">
         <v>2</v>
       </c>
       <c r="J54" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K54" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C55" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D55">
         <v>114</v>
       </c>
       <c r="E55" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F55" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G55" t="s">
-        <v>238</v>
+        <v>284</v>
       </c>
       <c r="H55" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I55">
         <v>4</v>
       </c>
       <c r="J55" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K55" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C56" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D56">
         <v>114</v>
       </c>
       <c r="E56" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F56" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G56" t="s">
-        <v>239</v>
+        <v>285</v>
       </c>
       <c r="H56" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="I56">
         <v>4</v>
       </c>
       <c r="J56" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K56" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C57" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D57">
         <v>114</v>
       </c>
       <c r="E57" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F57" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G57" t="s">
-        <v>240</v>
+        <v>286</v>
       </c>
       <c r="H57" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I57">
         <v>4</v>
       </c>
       <c r="J57" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K57" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C58" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D58">
         <v>114</v>
       </c>
       <c r="E58" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F58" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G58" t="s">
-        <v>241</v>
+        <v>287</v>
       </c>
       <c r="H58" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="I58">
         <v>2</v>
       </c>
       <c r="J58" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K58" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C59" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D59">
         <v>114</v>
       </c>
       <c r="E59" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F59" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G59" t="s">
-        <v>242</v>
+        <v>288</v>
       </c>
       <c r="H59" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="I59">
         <v>2</v>
       </c>
       <c r="J59" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K59" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C60" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D60">
         <v>114</v>
       </c>
       <c r="E60" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F60" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G60" t="s">
-        <v>243</v>
+        <v>289</v>
       </c>
       <c r="H60" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="I60">
         <v>2</v>
       </c>
       <c r="J60" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K60" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C61" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D61">
         <v>114</v>
       </c>
       <c r="E61" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F61" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G61" t="s">
-        <v>244</v>
+        <v>290</v>
       </c>
       <c r="H61" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="I61">
         <v>2</v>
       </c>
       <c r="J61" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K61" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C62" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D62">
         <v>114</v>
       </c>
       <c r="E62" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F62" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G62" t="s">
-        <v>245</v>
+        <v>291</v>
       </c>
       <c r="H62" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="I62">
         <v>2</v>
       </c>
       <c r="J62" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K62" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C63" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D63">
         <v>114</v>
       </c>
       <c r="E63" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F63" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G63" t="s">
-        <v>246</v>
+        <v>292</v>
       </c>
       <c r="H63" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="I63">
         <v>4</v>
       </c>
       <c r="J63" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K63" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C64" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D64">
         <v>114</v>
       </c>
       <c r="E64" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F64" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G64" t="s">
-        <v>247</v>
+        <v>293</v>
       </c>
       <c r="H64" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="I64">
         <v>2</v>
       </c>
       <c r="J64" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K64" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C65" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D65">
         <v>114</v>
       </c>
       <c r="E65" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F65" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G65" t="s">
-        <v>248</v>
+        <v>294</v>
       </c>
       <c r="H65" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="I65">
         <v>4</v>
       </c>
       <c r="J65" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K65" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C66" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D66">
         <v>114</v>
       </c>
       <c r="E66" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F66" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G66" t="s">
-        <v>249</v>
+        <v>295</v>
       </c>
       <c r="H66" t="s">
-        <v>81</v>
+        <v>104</v>
       </c>
       <c r="I66">
         <v>4</v>
       </c>
       <c r="J66" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K66" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C67" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D67">
         <v>114</v>
       </c>
       <c r="E67" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F67" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G67" t="s">
-        <v>250</v>
+        <v>296</v>
       </c>
       <c r="H67" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="I67">
         <v>2</v>
       </c>
       <c r="J67" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K67" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C68" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D68">
         <v>114</v>
       </c>
       <c r="E68" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F68" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G68" t="s">
-        <v>251</v>
+        <v>297</v>
       </c>
       <c r="H68" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="I68">
         <v>2</v>
       </c>
       <c r="J68" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K68" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C69" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D69">
         <v>114</v>
       </c>
       <c r="E69" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F69" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G69" t="s">
-        <v>252</v>
+        <v>298</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="I69">
         <v>2</v>
       </c>
       <c r="J69" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K69" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C70" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D70">
         <v>114</v>
       </c>
       <c r="E70" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F70" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G70" t="s">
-        <v>253</v>
+        <v>299</v>
       </c>
       <c r="H70" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="I70">
         <v>2</v>
       </c>
       <c r="J70" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K70" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C71" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D71">
         <v>114</v>
       </c>
       <c r="E71" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F71" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G71" t="s">
-        <v>254</v>
+        <v>300</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="I71">
         <v>2</v>
       </c>
       <c r="J71" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K71" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C72" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D72">
         <v>114</v>
       </c>
       <c r="E72" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F72" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G72" t="s">
-        <v>224</v>
+        <v>270</v>
       </c>
       <c r="H72" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="I72">
         <v>4</v>
       </c>
       <c r="J72" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K72" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C73" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D73">
         <v>114</v>
       </c>
       <c r="E73" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F73" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G73" t="s">
-        <v>255</v>
+        <v>301</v>
       </c>
       <c r="H73" t="s">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="I73">
         <v>4</v>
       </c>
       <c r="J73" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K73" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C74" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D74">
         <v>114</v>
       </c>
       <c r="E74" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F74" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G74" t="s">
-        <v>256</v>
+        <v>302</v>
       </c>
       <c r="H74" t="s">
-        <v>73</v>
+        <v>112</v>
       </c>
       <c r="I74">
         <v>2</v>
       </c>
       <c r="J74" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K74" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C75" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D75">
         <v>114</v>
       </c>
       <c r="E75" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F75" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G75" t="s">
-        <v>257</v>
+        <v>303</v>
       </c>
       <c r="H75" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="I75">
         <v>2</v>
       </c>
       <c r="J75" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="K75" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C76" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D76">
         <v>114</v>
       </c>
       <c r="E76" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F76" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G76" t="s">
-        <v>258</v>
+        <v>304</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>69</v>
+        <v>114</v>
       </c>
       <c r="I76">
         <v>3</v>
       </c>
       <c r="J76" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="K76" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C77" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D77">
         <v>114</v>
       </c>
       <c r="E77" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F77" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G77" t="s">
-        <v>259</v>
+        <v>305</v>
       </c>
       <c r="H77" t="s">
-        <v>68</v>
+        <v>117</v>
       </c>
       <c r="I77">
         <v>3</v>
       </c>
       <c r="J77" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="K77" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C78" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D78">
         <v>114</v>
       </c>
       <c r="E78" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F78" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G78" t="s">
-        <v>260</v>
+        <v>306</v>
       </c>
       <c r="H78" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="I78">
         <v>3</v>
       </c>
       <c r="J78" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="K78" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C79" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D79">
         <v>114</v>
       </c>
       <c r="E79" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F79" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G79" t="s">
-        <v>261</v>
+        <v>307</v>
       </c>
       <c r="H79" t="s">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="I79">
         <v>3</v>
       </c>
       <c r="J79" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="K79" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C80" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D80">
         <v>114</v>
       </c>
       <c r="E80" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F80" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G80" t="s">
-        <v>262</v>
+        <v>308</v>
       </c>
       <c r="H80" t="s">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="I80">
         <v>3</v>
       </c>
       <c r="J80" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="K80" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C81" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D81">
         <v>114</v>
       </c>
       <c r="E81" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F81" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G81" t="s">
-        <v>263</v>
+        <v>309</v>
       </c>
       <c r="H81" t="s">
-        <v>64</v>
+        <v>121</v>
       </c>
       <c r="I81">
         <v>3</v>
       </c>
       <c r="J81" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="K81" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C82" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D82">
         <v>114</v>
       </c>
       <c r="E82" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F82" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G82" t="s">
-        <v>264</v>
+        <v>310</v>
       </c>
       <c r="H82" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="I82">
         <v>3</v>
       </c>
       <c r="J82" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="K82" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C83" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D83">
         <v>114</v>
       </c>
       <c r="E83" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F83" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G83" t="s">
-        <v>265</v>
+        <v>311</v>
       </c>
       <c r="H83" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="I83">
         <v>3</v>
       </c>
       <c r="J83" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="K83" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C84" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D84">
         <v>114</v>
       </c>
       <c r="E84" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F84" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G84" t="s">
-        <v>266</v>
+        <v>312</v>
       </c>
       <c r="H84" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="I84">
         <v>3</v>
       </c>
       <c r="J84" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="K84" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C85" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D85">
         <v>114</v>
       </c>
       <c r="E85" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F85" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G85" t="s">
-        <v>267</v>
+        <v>313</v>
       </c>
       <c r="H85" t="s">
-        <v>60</v>
+        <v>125</v>
       </c>
       <c r="I85">
         <v>3</v>
       </c>
       <c r="J85" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="K85" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D86">
         <v>114</v>
       </c>
       <c r="E86" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F86" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G86" t="s">
-        <v>268</v>
+        <v>314</v>
       </c>
       <c r="H86" t="s">
-        <v>59</v>
+        <v>126</v>
       </c>
       <c r="I86">
         <v>3</v>
       </c>
       <c r="J86" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="K86" t="s">
-        <v>57</v>
+        <v>116</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C87" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D87">
         <v>114</v>
       </c>
       <c r="E87" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F87" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G87" t="s">
-        <v>269</v>
+        <v>315</v>
       </c>
       <c r="H87" t="s">
-        <v>56</v>
+        <v>127</v>
       </c>
       <c r="I87">
         <v>2</v>
       </c>
       <c r="J87" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="K87" t="s">
-        <v>45</v>
+        <v>129</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C88" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D88">
         <v>114</v>
       </c>
       <c r="E88" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F88" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G88" t="s">
-        <v>270</v>
+        <v>316</v>
       </c>
       <c r="H88" t="s">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="I88">
         <v>2</v>
       </c>
       <c r="J88" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="K88" t="s">
-        <v>45</v>
+        <v>129</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C89" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D89">
         <v>114</v>
       </c>
       <c r="E89" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F89" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G89" t="s">
-        <v>271</v>
+        <v>317</v>
       </c>
       <c r="H89" t="s">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c r="I89">
         <v>2</v>
       </c>
       <c r="J89" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="K89" t="s">
-        <v>45</v>
+        <v>129</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C90" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D90">
         <v>114</v>
       </c>
       <c r="E90" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F90" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G90" t="s">
-        <v>272</v>
+        <v>318</v>
       </c>
       <c r="H90" t="s">
-        <v>53</v>
+        <v>132</v>
       </c>
       <c r="I90">
         <v>2</v>
       </c>
       <c r="J90" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="K90" t="s">
-        <v>45</v>
+        <v>129</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C91" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D91">
         <v>114</v>
       </c>
       <c r="E91" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F91" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G91" t="s">
-        <v>273</v>
+        <v>319</v>
       </c>
       <c r="H91" t="s">
-        <v>52</v>
+        <v>133</v>
       </c>
       <c r="I91">
         <v>2</v>
       </c>
       <c r="J91" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="K91" t="s">
-        <v>45</v>
+        <v>129</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C92" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="D92">
         <v>114</v>
       </c>
       <c r="E92" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F92" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G92" t="s">
-        <v>274</v>
+        <v>320</v>
       </c>
       <c r="H92" t="s">
-        <v>47</v>
+        <v>134</v>
       </c>
       <c r="I92">
         <v>2</v>
       </c>
       <c r="J92" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="K92" t="s">
-        <v>45</v>
+        <v>129</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="B93" t="s">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="C93" t="s">
-        <v>5</v>
+        <v>137</v>
       </c>
       <c r="D93">
         <v>114</v>
       </c>
       <c r="E93" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F93" t="s">
-        <v>38</v>
+        <v>138</v>
       </c>
       <c r="G93" t="s">
-        <v>275</v>
+        <v>321</v>
       </c>
       <c r="H93" t="s">
-        <v>44</v>
+        <v>139</v>
       </c>
       <c r="I93">
         <v>3</v>
       </c>
       <c r="J93" t="s">
-        <v>43</v>
+        <v>140</v>
       </c>
       <c r="K93" t="s">
-        <v>42</v>
+        <v>141</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="B94" t="s">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="C94" t="s">
-        <v>5</v>
+        <v>137</v>
       </c>
       <c r="D94">
         <v>114</v>
       </c>
       <c r="E94" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F94" t="s">
-        <v>38</v>
+        <v>138</v>
       </c>
       <c r="G94" t="s">
-        <v>276</v>
+        <v>322</v>
       </c>
       <c r="H94" t="s">
-        <v>41</v>
+        <v>142</v>
       </c>
       <c r="I94">
         <v>6</v>
       </c>
       <c r="J94" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="K94" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="B95" t="s">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="C95" t="s">
-        <v>5</v>
+        <v>137</v>
       </c>
       <c r="D95">
         <v>114</v>
       </c>
       <c r="E95" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F95" t="s">
-        <v>38</v>
+        <v>138</v>
       </c>
       <c r="G95" t="s">
-        <v>277</v>
+        <v>323</v>
       </c>
       <c r="H95" t="s">
-        <v>37</v>
+        <v>143</v>
       </c>
       <c r="I95">
         <v>6</v>
       </c>
       <c r="J95" t="s">
-        <v>36</v>
+        <v>144</v>
       </c>
       <c r="K95" t="s">
-        <v>35</v>
+        <v>145</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="B96" t="s">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="C96" t="s">
-        <v>5</v>
+        <v>137</v>
       </c>
       <c r="D96">
         <v>114</v>
       </c>
       <c r="E96" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="F96" t="s">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="G96" t="s">
-        <v>278</v>
+        <v>324</v>
       </c>
       <c r="H96" t="s">
-        <v>34</v>
+        <v>147</v>
       </c>
       <c r="I96">
         <v>3</v>
       </c>
       <c r="J96" t="s">
-        <v>1</v>
+        <v>148</v>
       </c>
       <c r="K96" t="s">
-        <v>0</v>
+        <v>135</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="B97" t="s">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="C97" t="s">
-        <v>5</v>
+        <v>137</v>
       </c>
       <c r="D97">
         <v>114</v>
       </c>
       <c r="E97" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="F97" t="s">
-        <v>32</v>
+        <v>146</v>
       </c>
       <c r="G97" t="s">
-        <v>279</v>
+        <v>325</v>
       </c>
       <c r="H97" t="s">
-        <v>31</v>
+        <v>149</v>
       </c>
       <c r="I97">
         <v>3</v>
       </c>
       <c r="J97" t="s">
-        <v>1</v>
+        <v>148</v>
       </c>
       <c r="K97" t="s">
-        <v>0</v>
+        <v>135</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="B98" t="s">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="C98" t="s">
-        <v>5</v>
+        <v>137</v>
       </c>
       <c r="D98">
         <v>114</v>
       </c>
       <c r="E98" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F98" t="s">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="G98" t="s">
-        <v>280</v>
+        <v>326</v>
       </c>
       <c r="H98" t="s">
-        <v>30</v>
+        <v>151</v>
       </c>
       <c r="I98">
         <v>2</v>
       </c>
       <c r="J98" t="s">
-        <v>1</v>
+        <v>148</v>
       </c>
       <c r="K98" t="s">
-        <v>0</v>
+        <v>135</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="B99" t="s">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="C99" t="s">
-        <v>5</v>
+        <v>137</v>
       </c>
       <c r="D99">
         <v>114</v>
       </c>
       <c r="E99" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F99" t="s">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="G99" t="s">
-        <v>281</v>
+        <v>327</v>
       </c>
       <c r="H99" t="s">
-        <v>29</v>
+        <v>152</v>
       </c>
       <c r="I99">
         <v>2</v>
       </c>
       <c r="J99" t="s">
-        <v>1</v>
+        <v>148</v>
       </c>
       <c r="K99" t="s">
-        <v>0</v>
+        <v>135</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="B100" t="s">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="C100" t="s">
-        <v>5</v>
+        <v>137</v>
       </c>
       <c r="D100">
         <v>114</v>
       </c>
       <c r="E100" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F100" t="s">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="G100" t="s">
-        <v>282</v>
+        <v>328</v>
       </c>
       <c r="H100" t="s">
-        <v>28</v>
+        <v>153</v>
       </c>
       <c r="I100">
         <v>3</v>
       </c>
       <c r="J100" t="s">
-        <v>27</v>
+        <v>154</v>
       </c>
       <c r="K100" t="s">
-        <v>26</v>
+        <v>155</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="B101" t="s">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="C101" t="s">
-        <v>5</v>
+        <v>137</v>
       </c>
       <c r="D101">
         <v>114</v>
       </c>
       <c r="E101" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F101" t="s">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="G101" t="s">
-        <v>283</v>
+        <v>329</v>
       </c>
       <c r="H101" t="s">
-        <v>25</v>
+        <v>156</v>
       </c>
       <c r="I101">
         <v>2</v>
       </c>
       <c r="J101" t="s">
-        <v>24</v>
+        <v>157</v>
       </c>
       <c r="K101" t="s">
-        <v>23</v>
+        <v>158</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="B102" t="s">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="C102" t="s">
-        <v>5</v>
+        <v>137</v>
       </c>
       <c r="D102">
         <v>114</v>
       </c>
       <c r="E102" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F102" t="s">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="G102" t="s">
-        <v>284</v>
+        <v>330</v>
       </c>
       <c r="H102" t="s">
-        <v>22</v>
+        <v>159</v>
       </c>
       <c r="I102">
         <v>2</v>
       </c>
       <c r="J102" t="s">
-        <v>21</v>
+        <v>160</v>
       </c>
       <c r="K102" t="s">
-        <v>20</v>
+        <v>161</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="B103" t="s">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="C103" t="s">
-        <v>5</v>
+        <v>137</v>
       </c>
       <c r="D103">
         <v>114</v>
       </c>
       <c r="E103" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F103" t="s">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="G103" t="s">
-        <v>285</v>
+        <v>331</v>
       </c>
       <c r="H103" t="s">
-        <v>19</v>
+        <v>162</v>
       </c>
       <c r="I103">
         <v>3</v>
       </c>
       <c r="J103" t="s">
-        <v>18</v>
+        <v>163</v>
       </c>
       <c r="K103" t="s">
-        <v>17</v>
+        <v>164</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="B104" t="s">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="C104" t="s">
-        <v>5</v>
+        <v>137</v>
       </c>
       <c r="D104">
         <v>114</v>
       </c>
       <c r="E104" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F104" t="s">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="G104" t="s">
-        <v>286</v>
+        <v>332</v>
       </c>
       <c r="H104" t="s">
-        <v>16</v>
+        <v>165</v>
       </c>
       <c r="I104">
         <v>3</v>
       </c>
       <c r="J104" t="s">
-        <v>15</v>
+        <v>166</v>
       </c>
       <c r="K104" t="s">
-        <v>14</v>
+        <v>167</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="B105" t="s">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="C105" t="s">
-        <v>5</v>
+        <v>137</v>
       </c>
       <c r="D105">
         <v>114</v>
       </c>
       <c r="E105" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F105" t="s">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="G105" t="s">
-        <v>287</v>
+        <v>333</v>
       </c>
       <c r="H105" t="s">
-        <v>13</v>
+        <v>168</v>
       </c>
       <c r="I105">
         <v>3</v>
       </c>
       <c r="J105" t="s">
-        <v>12</v>
+        <v>169</v>
       </c>
       <c r="K105" t="s">
-        <v>11</v>
+        <v>170</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="B106" t="s">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="C106" t="s">
-        <v>5</v>
+        <v>137</v>
       </c>
       <c r="D106">
         <v>114</v>
       </c>
       <c r="E106" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F106" t="s">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="G106" t="s">
-        <v>288</v>
+        <v>334</v>
       </c>
       <c r="H106" t="s">
-        <v>9</v>
+        <v>171</v>
       </c>
       <c r="I106">
         <v>3</v>
       </c>
       <c r="J106" t="s">
-        <v>8</v>
+        <v>172</v>
       </c>
       <c r="K106" t="s">
-        <v>7</v>
+        <v>173</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="B107" t="s">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="C107" t="s">
-        <v>5</v>
+        <v>137</v>
       </c>
       <c r="D107">
         <v>114</v>
       </c>
       <c r="E107" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F107" t="s">
-        <v>3</v>
+        <v>174</v>
       </c>
       <c r="G107" t="s">
-        <v>289</v>
+        <v>335</v>
       </c>
       <c r="H107" t="s">
-        <v>2</v>
+        <v>175</v>
       </c>
       <c r="I107">
         <v>3</v>
       </c>
       <c r="J107" t="s">
-        <v>1</v>
+        <v>148</v>
       </c>
       <c r="K107" t="s">
-        <v>0</v>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>176</v>
+      </c>
+      <c r="B108" t="s">
+        <v>177</v>
+      </c>
+      <c r="C108" t="s">
+        <v>178</v>
+      </c>
+      <c r="D108">
+        <v>114</v>
+      </c>
+      <c r="E108" t="s">
+        <v>179</v>
+      </c>
+      <c r="F108" t="s">
+        <v>180</v>
+      </c>
+      <c r="G108" t="s">
+        <v>336</v>
+      </c>
+      <c r="H108" t="s">
+        <v>181</v>
+      </c>
+      <c r="I108">
+        <v>2</v>
+      </c>
+      <c r="K108" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>176</v>
+      </c>
+      <c r="B109" t="s">
+        <v>177</v>
+      </c>
+      <c r="C109" t="s">
+        <v>178</v>
+      </c>
+      <c r="D109">
+        <v>114</v>
+      </c>
+      <c r="E109" t="s">
+        <v>179</v>
+      </c>
+      <c r="F109" t="s">
+        <v>180</v>
+      </c>
+      <c r="G109" t="s">
+        <v>337</v>
+      </c>
+      <c r="H109" t="s">
+        <v>182</v>
+      </c>
+      <c r="I109">
+        <v>2</v>
+      </c>
+      <c r="K109" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>176</v>
+      </c>
+      <c r="B110" t="s">
+        <v>177</v>
+      </c>
+      <c r="C110" t="s">
+        <v>178</v>
+      </c>
+      <c r="D110">
+        <v>114</v>
+      </c>
+      <c r="E110" t="s">
+        <v>179</v>
+      </c>
+      <c r="F110" t="s">
+        <v>184</v>
+      </c>
+      <c r="G110" t="s">
+        <v>338</v>
+      </c>
+      <c r="H110" t="s">
+        <v>185</v>
+      </c>
+      <c r="I110">
+        <v>2</v>
+      </c>
+      <c r="K110" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>176</v>
+      </c>
+      <c r="B111" t="s">
+        <v>177</v>
+      </c>
+      <c r="C111" t="s">
+        <v>178</v>
+      </c>
+      <c r="D111">
+        <v>114</v>
+      </c>
+      <c r="E111" t="s">
+        <v>179</v>
+      </c>
+      <c r="F111" t="s">
+        <v>184</v>
+      </c>
+      <c r="G111" t="s">
+        <v>339</v>
+      </c>
+      <c r="H111" t="s">
+        <v>187</v>
+      </c>
+      <c r="I111">
+        <v>2</v>
+      </c>
+      <c r="K111" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>176</v>
+      </c>
+      <c r="B112" t="s">
+        <v>177</v>
+      </c>
+      <c r="C112" t="s">
+        <v>178</v>
+      </c>
+      <c r="D112">
+        <v>114</v>
+      </c>
+      <c r="E112" t="s">
+        <v>179</v>
+      </c>
+      <c r="F112" t="s">
+        <v>184</v>
+      </c>
+      <c r="G112" t="s">
+        <v>340</v>
+      </c>
+      <c r="H112" t="s">
+        <v>188</v>
+      </c>
+      <c r="I112">
+        <v>2</v>
+      </c>
+      <c r="K112" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>176</v>
+      </c>
+      <c r="B113" t="s">
+        <v>177</v>
+      </c>
+      <c r="C113" t="s">
+        <v>178</v>
+      </c>
+      <c r="D113">
+        <v>114</v>
+      </c>
+      <c r="E113" t="s">
+        <v>179</v>
+      </c>
+      <c r="F113" t="s">
+        <v>184</v>
+      </c>
+      <c r="G113" t="s">
+        <v>341</v>
+      </c>
+      <c r="H113" t="s">
+        <v>189</v>
+      </c>
+      <c r="I113">
+        <v>2</v>
+      </c>
+      <c r="K113" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>176</v>
+      </c>
+      <c r="B114" t="s">
+        <v>177</v>
+      </c>
+      <c r="C114" t="s">
+        <v>178</v>
+      </c>
+      <c r="D114">
+        <v>114</v>
+      </c>
+      <c r="E114" t="s">
+        <v>179</v>
+      </c>
+      <c r="F114" t="s">
+        <v>184</v>
+      </c>
+      <c r="G114" t="s">
+        <v>342</v>
+      </c>
+      <c r="H114" t="s">
+        <v>190</v>
+      </c>
+      <c r="I114">
+        <v>2</v>
+      </c>
+      <c r="K114" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>176</v>
+      </c>
+      <c r="B115" t="s">
+        <v>177</v>
+      </c>
+      <c r="C115" t="s">
+        <v>178</v>
+      </c>
+      <c r="D115">
+        <v>114</v>
+      </c>
+      <c r="E115" t="s">
+        <v>179</v>
+      </c>
+      <c r="F115" t="s">
+        <v>184</v>
+      </c>
+      <c r="G115" t="s">
+        <v>343</v>
+      </c>
+      <c r="H115" t="s">
+        <v>191</v>
+      </c>
+      <c r="I115">
+        <v>2</v>
+      </c>
+      <c r="K115" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>176</v>
+      </c>
+      <c r="B116" t="s">
+        <v>177</v>
+      </c>
+      <c r="C116" t="s">
+        <v>178</v>
+      </c>
+      <c r="D116">
+        <v>114</v>
+      </c>
+      <c r="E116" t="s">
+        <v>179</v>
+      </c>
+      <c r="F116" t="s">
+        <v>184</v>
+      </c>
+      <c r="G116" t="s">
+        <v>344</v>
+      </c>
+      <c r="H116" t="s">
+        <v>192</v>
+      </c>
+      <c r="I116">
+        <v>4</v>
+      </c>
+      <c r="J116" t="s">
+        <v>193</v>
+      </c>
+      <c r="K116" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>176</v>
+      </c>
+      <c r="B117" t="s">
+        <v>177</v>
+      </c>
+      <c r="C117" t="s">
+        <v>178</v>
+      </c>
+      <c r="D117">
+        <v>114</v>
+      </c>
+      <c r="E117" t="s">
+        <v>179</v>
+      </c>
+      <c r="F117" t="s">
+        <v>184</v>
+      </c>
+      <c r="G117" t="s">
+        <v>345</v>
+      </c>
+      <c r="H117" t="s">
+        <v>195</v>
+      </c>
+      <c r="I117">
+        <v>4</v>
+      </c>
+      <c r="J117" t="s">
+        <v>193</v>
+      </c>
+      <c r="K117" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>176</v>
+      </c>
+      <c r="B118" t="s">
+        <v>177</v>
+      </c>
+      <c r="C118" t="s">
+        <v>178</v>
+      </c>
+      <c r="D118">
+        <v>114</v>
+      </c>
+      <c r="E118" t="s">
+        <v>179</v>
+      </c>
+      <c r="F118" t="s">
+        <v>184</v>
+      </c>
+      <c r="G118" t="s">
+        <v>346</v>
+      </c>
+      <c r="H118" t="s">
+        <v>196</v>
+      </c>
+      <c r="I118">
+        <v>3</v>
+      </c>
+      <c r="K118" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>176</v>
+      </c>
+      <c r="B119" t="s">
+        <v>177</v>
+      </c>
+      <c r="C119" t="s">
+        <v>178</v>
+      </c>
+      <c r="D119">
+        <v>114</v>
+      </c>
+      <c r="E119" t="s">
+        <v>179</v>
+      </c>
+      <c r="F119" t="s">
+        <v>184</v>
+      </c>
+      <c r="G119" t="s">
+        <v>347</v>
+      </c>
+      <c r="H119" t="s">
+        <v>197</v>
+      </c>
+      <c r="I119">
+        <v>2</v>
+      </c>
+      <c r="K119" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>176</v>
+      </c>
+      <c r="B120" t="s">
+        <v>177</v>
+      </c>
+      <c r="C120" t="s">
+        <v>178</v>
+      </c>
+      <c r="D120">
+        <v>114</v>
+      </c>
+      <c r="E120" t="s">
+        <v>179</v>
+      </c>
+      <c r="F120" t="s">
+        <v>184</v>
+      </c>
+      <c r="G120" t="s">
+        <v>348</v>
+      </c>
+      <c r="H120" t="s">
+        <v>199</v>
+      </c>
+      <c r="I120">
+        <v>3</v>
+      </c>
+      <c r="J120" t="s">
+        <v>200</v>
+      </c>
+      <c r="K120" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>176</v>
+      </c>
+      <c r="B121" t="s">
+        <v>177</v>
+      </c>
+      <c r="C121" t="s">
+        <v>178</v>
+      </c>
+      <c r="D121">
+        <v>114</v>
+      </c>
+      <c r="E121" t="s">
+        <v>179</v>
+      </c>
+      <c r="F121" t="s">
+        <v>184</v>
+      </c>
+      <c r="G121" t="s">
+        <v>349</v>
+      </c>
+      <c r="H121" t="s">
+        <v>201</v>
+      </c>
+      <c r="I121">
+        <v>2</v>
+      </c>
+      <c r="K121" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>176</v>
+      </c>
+      <c r="B122" t="s">
+        <v>177</v>
+      </c>
+      <c r="C122" t="s">
+        <v>178</v>
+      </c>
+      <c r="D122">
+        <v>114</v>
+      </c>
+      <c r="E122" t="s">
+        <v>179</v>
+      </c>
+      <c r="F122" t="s">
+        <v>184</v>
+      </c>
+      <c r="G122" t="s">
+        <v>350</v>
+      </c>
+      <c r="H122" t="s">
+        <v>202</v>
+      </c>
+      <c r="I122">
+        <v>2</v>
+      </c>
+      <c r="K122" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>176</v>
+      </c>
+      <c r="B123" t="s">
+        <v>177</v>
+      </c>
+      <c r="C123" t="s">
+        <v>178</v>
+      </c>
+      <c r="D123">
+        <v>114</v>
+      </c>
+      <c r="E123" t="s">
+        <v>179</v>
+      </c>
+      <c r="F123" t="s">
+        <v>204</v>
+      </c>
+      <c r="G123" t="s">
+        <v>351</v>
+      </c>
+      <c r="H123" t="s">
+        <v>205</v>
+      </c>
+      <c r="I123">
+        <v>2</v>
+      </c>
+      <c r="K123" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>176</v>
+      </c>
+      <c r="B124" t="s">
+        <v>177</v>
+      </c>
+      <c r="C124" t="s">
+        <v>178</v>
+      </c>
+      <c r="D124">
+        <v>114</v>
+      </c>
+      <c r="E124" t="s">
+        <v>179</v>
+      </c>
+      <c r="F124" t="s">
+        <v>204</v>
+      </c>
+      <c r="G124" t="s">
+        <v>352</v>
+      </c>
+      <c r="H124" t="s">
+        <v>206</v>
+      </c>
+      <c r="I124">
+        <v>2</v>
+      </c>
+      <c r="K124" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>176</v>
+      </c>
+      <c r="B125" t="s">
+        <v>177</v>
+      </c>
+      <c r="C125" t="s">
+        <v>178</v>
+      </c>
+      <c r="D125">
+        <v>114</v>
+      </c>
+      <c r="E125" t="s">
+        <v>179</v>
+      </c>
+      <c r="F125" t="s">
+        <v>204</v>
+      </c>
+      <c r="G125" t="s">
+        <v>353</v>
+      </c>
+      <c r="H125" t="s">
+        <v>207</v>
+      </c>
+      <c r="I125">
+        <v>2</v>
+      </c>
+      <c r="K125" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>176</v>
+      </c>
+      <c r="B126" t="s">
+        <v>177</v>
+      </c>
+      <c r="C126" t="s">
+        <v>178</v>
+      </c>
+      <c r="D126">
+        <v>114</v>
+      </c>
+      <c r="E126" t="s">
+        <v>179</v>
+      </c>
+      <c r="F126" t="s">
+        <v>204</v>
+      </c>
+      <c r="G126" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H126" t="s">
+        <v>209</v>
+      </c>
+      <c r="I126">
+        <v>2</v>
+      </c>
+      <c r="J126" t="s">
+        <v>210</v>
+      </c>
+      <c r="K126" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>176</v>
+      </c>
+      <c r="B127" t="s">
+        <v>177</v>
+      </c>
+      <c r="C127" t="s">
+        <v>178</v>
+      </c>
+      <c r="D127">
+        <v>114</v>
+      </c>
+      <c r="E127" t="s">
+        <v>179</v>
+      </c>
+      <c r="F127" t="s">
+        <v>204</v>
+      </c>
+      <c r="G127" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H127" t="s">
+        <v>211</v>
+      </c>
+      <c r="I127">
+        <v>2</v>
+      </c>
+      <c r="J127" t="s">
+        <v>212</v>
+      </c>
+      <c r="K127" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>176</v>
+      </c>
+      <c r="B128" t="s">
+        <v>177</v>
+      </c>
+      <c r="C128" t="s">
+        <v>178</v>
+      </c>
+      <c r="D128">
+        <v>114</v>
+      </c>
+      <c r="E128" t="s">
+        <v>179</v>
+      </c>
+      <c r="F128" t="s">
+        <v>204</v>
+      </c>
+      <c r="G128" t="s">
+        <v>354</v>
+      </c>
+      <c r="H128" t="s">
+        <v>213</v>
+      </c>
+      <c r="I128">
+        <v>2</v>
+      </c>
+      <c r="K128" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>176</v>
+      </c>
+      <c r="B129" t="s">
+        <v>177</v>
+      </c>
+      <c r="C129" t="s">
+        <v>178</v>
+      </c>
+      <c r="D129">
+        <v>114</v>
+      </c>
+      <c r="E129" t="s">
+        <v>179</v>
+      </c>
+      <c r="F129" t="s">
+        <v>204</v>
+      </c>
+      <c r="G129" t="s">
+        <v>355</v>
+      </c>
+      <c r="H129" t="s">
+        <v>214</v>
+      </c>
+      <c r="I129">
+        <v>2</v>
+      </c>
+      <c r="K129" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>176</v>
+      </c>
+      <c r="B130" t="s">
+        <v>177</v>
+      </c>
+      <c r="C130" t="s">
+        <v>178</v>
+      </c>
+      <c r="D130">
+        <v>114</v>
+      </c>
+      <c r="E130" t="s">
+        <v>179</v>
+      </c>
+      <c r="F130" t="s">
+        <v>204</v>
+      </c>
+      <c r="G130" t="s">
+        <v>356</v>
+      </c>
+      <c r="H130" t="s">
+        <v>215</v>
+      </c>
+      <c r="I130">
+        <v>3</v>
+      </c>
+      <c r="K130" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>176</v>
+      </c>
+      <c r="B131" t="s">
+        <v>177</v>
+      </c>
+      <c r="C131" t="s">
+        <v>178</v>
+      </c>
+      <c r="D131">
+        <v>114</v>
+      </c>
+      <c r="E131" t="s">
+        <v>179</v>
+      </c>
+      <c r="F131" t="s">
+        <v>204</v>
+      </c>
+      <c r="G131" t="s">
+        <v>357</v>
+      </c>
+      <c r="H131" t="s">
+        <v>216</v>
+      </c>
+      <c r="I131">
+        <v>2</v>
+      </c>
+      <c r="K131" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>176</v>
+      </c>
+      <c r="B132" t="s">
+        <v>177</v>
+      </c>
+      <c r="C132" t="s">
+        <v>178</v>
+      </c>
+      <c r="D132">
+        <v>114</v>
+      </c>
+      <c r="E132" t="s">
+        <v>179</v>
+      </c>
+      <c r="F132" t="s">
+        <v>204</v>
+      </c>
+      <c r="G132" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H132" t="s">
+        <v>217</v>
+      </c>
+      <c r="I132">
+        <v>2</v>
+      </c>
+      <c r="J132" t="s">
+        <v>218</v>
+      </c>
+      <c r="K132" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>176</v>
+      </c>
+      <c r="B133" t="s">
+        <v>177</v>
+      </c>
+      <c r="C133" t="s">
+        <v>178</v>
+      </c>
+      <c r="D133">
+        <v>114</v>
+      </c>
+      <c r="E133" t="s">
+        <v>179</v>
+      </c>
+      <c r="F133" t="s">
+        <v>204</v>
+      </c>
+      <c r="G133" t="s">
+        <v>358</v>
+      </c>
+      <c r="H133" t="s">
+        <v>219</v>
+      </c>
+      <c r="I133">
+        <v>2</v>
+      </c>
+      <c r="K133" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>176</v>
+      </c>
+      <c r="B134" t="s">
+        <v>177</v>
+      </c>
+      <c r="C134" t="s">
+        <v>178</v>
+      </c>
+      <c r="D134">
+        <v>114</v>
+      </c>
+      <c r="E134" t="s">
+        <v>179</v>
+      </c>
+      <c r="F134" t="s">
+        <v>204</v>
+      </c>
+      <c r="G134" t="s">
+        <v>359</v>
+      </c>
+      <c r="H134" t="s">
+        <v>221</v>
+      </c>
+      <c r="I134">
+        <v>2</v>
+      </c>
+      <c r="K134" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>176</v>
+      </c>
+      <c r="B135" t="s">
+        <v>177</v>
+      </c>
+      <c r="C135" t="s">
+        <v>178</v>
+      </c>
+      <c r="D135">
+        <v>114</v>
+      </c>
+      <c r="E135" t="s">
+        <v>179</v>
+      </c>
+      <c r="F135" t="s">
+        <v>204</v>
+      </c>
+      <c r="G135" t="s">
+        <v>360</v>
+      </c>
+      <c r="H135" t="s">
+        <v>222</v>
+      </c>
+      <c r="I135">
+        <v>2</v>
+      </c>
+      <c r="K135" t="s">
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -5145,39 +6287,39 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A48E5CAA-EB30-4C44-830B-2AE636C1BECE}">
-  <dimension ref="A1:G4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4DCFC30-4D5C-4C4D-99C2-BB1D05E9719E}">
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>174</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>173</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>172</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>184</v>
+        <v>223</v>
       </c>
       <c r="E1" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="F1" t="s">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="G1" t="s">
-        <v>181</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="C2">
         <v>114</v>
@@ -5192,15 +6334,15 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>180</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="C3">
         <v>114</v>
@@ -5215,15 +6357,15 @@
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>179</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="B4" t="s">
-        <v>177</v>
+        <v>137</v>
       </c>
       <c r="C4">
         <v>114</v>
@@ -5238,11 +6380,33 @@
         <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>176</v>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C5">
+        <v>114</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>16</v>
+      </c>
+      <c r="F5">
+        <v>16</v>
+      </c>
+      <c r="G5" t="s">
+        <v>230</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{A48E5CAA-EB30-4C44-830B-2AE636C1BECE}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/master_data.xlsx
+++ b/master_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\000_專案計畫\20260107_學分學程查詢功能\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7345CE83-CEFE-47F9-BAAA-A580BF948832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73E8D2A7-2D8B-4580-92AF-E1E3B960353D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BF35B52C-D03C-44DF-89E9-E0C2470A9351}"/>
   </bookViews>
@@ -4843,7 +4843,7 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="B93" t="s">
         <v>136</v>
@@ -4878,7 +4878,7 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="B94" t="s">
         <v>136</v>
@@ -4913,7 +4913,7 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="B95" t="s">
         <v>136</v>
@@ -4948,7 +4948,7 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="B96" t="s">
         <v>136</v>
@@ -4983,7 +4983,7 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="B97" t="s">
         <v>136</v>
@@ -5018,7 +5018,7 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="B98" t="s">
         <v>136</v>
@@ -5053,7 +5053,7 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="B99" t="s">
         <v>136</v>
@@ -5088,7 +5088,7 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="B100" t="s">
         <v>136</v>
@@ -5123,7 +5123,7 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="B101" t="s">
         <v>136</v>
@@ -5158,7 +5158,7 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="B102" t="s">
         <v>136</v>
@@ -5193,7 +5193,7 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="B103" t="s">
         <v>136</v>
@@ -5228,7 +5228,7 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="B104" t="s">
         <v>136</v>
@@ -5263,7 +5263,7 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="B105" t="s">
         <v>136</v>
@@ -5298,7 +5298,7 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="B106" t="s">
         <v>136</v>
@@ -5333,7 +5333,7 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="B107" t="s">
         <v>136</v>

--- a/master_data.xlsx
+++ b/master_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\000_專案計畫\20260107_學分學程查詢功能\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73E8D2A7-2D8B-4580-92AF-E1E3B960353D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB3F154-E060-4209-906C-7876847E4CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BF35B52C-D03C-44DF-89E9-E0C2470A9351}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BF35B52C-D03C-44DF-89E9-E0C2470A9351}"/>
   </bookViews>
   <sheets>
     <sheet name="科目表" sheetId="1" r:id="rId1"/>
@@ -73,10 +73,6 @@
     <t>學分數</t>
   </si>
   <si>
-    <t>認抵單位代碼</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>備註</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1190,6 +1186,9 @@
   </si>
   <si>
     <t>18843</t>
+  </si>
+  <si>
+    <t>課程認抵範圍</t>
   </si>
 </sst>
 </file>
@@ -1629,4655 +1628,4655 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
+        <v>360</v>
+      </c>
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2">
+        <v>114</v>
+      </c>
+      <c r="E2" t="s">
         <v>14</v>
       </c>
-      <c r="D2">
-        <v>114</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>230</v>
+      </c>
+      <c r="H2" t="s">
         <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H2" t="s">
-        <v>17</v>
       </c>
       <c r="I2">
         <v>4</v>
       </c>
       <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" t="s">
         <v>18</v>
-      </c>
-      <c r="K2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3">
+        <v>114</v>
+      </c>
+      <c r="E3" t="s">
         <v>14</v>
       </c>
-      <c r="D3">
-        <v>114</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
       <c r="G3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I3">
         <v>4</v>
       </c>
       <c r="J3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" t="s">
         <v>21</v>
-      </c>
-      <c r="K3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
       <c r="D4">
         <v>114</v>
       </c>
       <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
         <v>23</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
+        <v>232</v>
+      </c>
+      <c r="H4" t="s">
         <v>24</v>
-      </c>
-      <c r="G4" t="s">
-        <v>233</v>
-      </c>
-      <c r="H4" t="s">
-        <v>25</v>
       </c>
       <c r="I4">
         <v>2</v>
       </c>
       <c r="J4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" t="s">
         <v>26</v>
-      </c>
-      <c r="K4" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
       <c r="D5">
         <v>114</v>
       </c>
       <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
         <v>23</v>
       </c>
-      <c r="F5" t="s">
-        <v>24</v>
-      </c>
       <c r="G5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I5">
         <v>2</v>
       </c>
       <c r="J5" t="s">
+        <v>25</v>
+      </c>
+      <c r="K5" t="s">
         <v>26</v>
-      </c>
-      <c r="K5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
       <c r="D6">
         <v>114</v>
       </c>
       <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s">
         <v>23</v>
       </c>
-      <c r="F6" t="s">
-        <v>24</v>
-      </c>
       <c r="G6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I6">
         <v>2</v>
       </c>
       <c r="J6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6" t="s">
         <v>26</v>
-      </c>
-      <c r="K6" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>13</v>
       </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
       <c r="D7">
         <v>114</v>
       </c>
       <c r="E7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" t="s">
         <v>23</v>
       </c>
-      <c r="F7" t="s">
-        <v>24</v>
-      </c>
       <c r="G7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I7">
         <v>4</v>
       </c>
       <c r="J7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" t="s">
         <v>18</v>
-      </c>
-      <c r="K7" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
       <c r="D8">
         <v>114</v>
       </c>
       <c r="E8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" t="s">
         <v>23</v>
       </c>
-      <c r="F8" t="s">
-        <v>24</v>
-      </c>
       <c r="G8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
       <c r="J8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" t="s">
         <v>18</v>
-      </c>
-      <c r="K8" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>13</v>
       </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
       <c r="D9">
         <v>114</v>
       </c>
       <c r="E9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" t="s">
         <v>23</v>
       </c>
-      <c r="F9" t="s">
-        <v>24</v>
-      </c>
       <c r="G9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I9">
         <v>4</v>
       </c>
       <c r="J9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" t="s">
         <v>18</v>
-      </c>
-      <c r="K9" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
         <v>12</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>13</v>
       </c>
-      <c r="C10" t="s">
-        <v>14</v>
-      </c>
       <c r="D10">
         <v>114</v>
       </c>
       <c r="E10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" t="s">
         <v>23</v>
       </c>
-      <c r="F10" t="s">
-        <v>24</v>
-      </c>
       <c r="G10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I10">
         <v>4</v>
       </c>
       <c r="J10" t="s">
+        <v>17</v>
+      </c>
+      <c r="K10" t="s">
         <v>18</v>
-      </c>
-      <c r="K10" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
         <v>12</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>13</v>
       </c>
-      <c r="C11" t="s">
-        <v>14</v>
-      </c>
       <c r="D11">
         <v>114</v>
       </c>
       <c r="E11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" t="s">
         <v>23</v>
       </c>
-      <c r="F11" t="s">
-        <v>24</v>
-      </c>
       <c r="G11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I11">
         <v>4</v>
       </c>
       <c r="J11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K11" t="s">
         <v>18</v>
-      </c>
-      <c r="K11" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
         <v>12</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>13</v>
       </c>
-      <c r="C12" t="s">
-        <v>14</v>
-      </c>
       <c r="D12">
         <v>114</v>
       </c>
       <c r="E12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" t="s">
         <v>23</v>
       </c>
-      <c r="F12" t="s">
-        <v>24</v>
-      </c>
       <c r="G12" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I12">
         <v>4</v>
       </c>
       <c r="J12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12" t="s">
         <v>18</v>
-      </c>
-      <c r="K12" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>13</v>
       </c>
-      <c r="C13" t="s">
-        <v>14</v>
-      </c>
       <c r="D13">
         <v>114</v>
       </c>
       <c r="E13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" t="s">
         <v>23</v>
       </c>
-      <c r="F13" t="s">
-        <v>24</v>
-      </c>
       <c r="G13" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I13">
         <v>4</v>
       </c>
       <c r="J13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13" t="s">
         <v>18</v>
-      </c>
-      <c r="K13" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
         <v>12</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>13</v>
       </c>
-      <c r="C14" t="s">
-        <v>14</v>
-      </c>
       <c r="D14">
         <v>114</v>
       </c>
       <c r="E14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" t="s">
         <v>23</v>
       </c>
-      <c r="F14" t="s">
-        <v>24</v>
-      </c>
       <c r="G14" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I14">
         <v>4</v>
       </c>
       <c r="J14" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14" t="s">
         <v>18</v>
-      </c>
-      <c r="K14" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
         <v>12</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>13</v>
       </c>
-      <c r="C15" t="s">
-        <v>14</v>
-      </c>
       <c r="D15">
         <v>114</v>
       </c>
       <c r="E15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" t="s">
         <v>23</v>
       </c>
-      <c r="F15" t="s">
-        <v>24</v>
-      </c>
       <c r="G15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I15">
         <v>4</v>
       </c>
       <c r="J15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K15" t="s">
         <v>18</v>
-      </c>
-      <c r="K15" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
         <v>12</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>13</v>
       </c>
-      <c r="C16" t="s">
-        <v>14</v>
-      </c>
       <c r="D16">
         <v>114</v>
       </c>
       <c r="E16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" t="s">
         <v>23</v>
       </c>
-      <c r="F16" t="s">
-        <v>24</v>
-      </c>
       <c r="G16" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I16">
         <v>4</v>
       </c>
       <c r="J16" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16" t="s">
         <v>18</v>
-      </c>
-      <c r="K16" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
         <v>12</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>13</v>
       </c>
-      <c r="C17" t="s">
-        <v>14</v>
-      </c>
       <c r="D17">
         <v>114</v>
       </c>
       <c r="E17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" t="s">
         <v>23</v>
       </c>
-      <c r="F17" t="s">
-        <v>24</v>
-      </c>
       <c r="G17" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I17">
         <v>4</v>
       </c>
       <c r="J17" t="s">
+        <v>17</v>
+      </c>
+      <c r="K17" t="s">
         <v>18</v>
-      </c>
-      <c r="K17" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" t="s">
         <v>12</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>13</v>
       </c>
-      <c r="C18" t="s">
-        <v>14</v>
-      </c>
       <c r="D18">
         <v>114</v>
       </c>
       <c r="E18" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" t="s">
         <v>23</v>
       </c>
-      <c r="F18" t="s">
-        <v>24</v>
-      </c>
       <c r="G18" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I18">
         <v>2</v>
       </c>
       <c r="J18" t="s">
+        <v>17</v>
+      </c>
+      <c r="K18" t="s">
         <v>18</v>
-      </c>
-      <c r="K18" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" t="s">
         <v>12</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>13</v>
       </c>
-      <c r="C19" t="s">
-        <v>14</v>
-      </c>
       <c r="D19">
         <v>114</v>
       </c>
       <c r="E19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" t="s">
         <v>23</v>
       </c>
-      <c r="F19" t="s">
-        <v>24</v>
-      </c>
       <c r="G19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I19">
         <v>4</v>
       </c>
       <c r="J19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" t="s">
         <v>21</v>
-      </c>
-      <c r="K19" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" t="s">
         <v>12</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>13</v>
       </c>
-      <c r="C20" t="s">
-        <v>14</v>
-      </c>
       <c r="D20">
         <v>114</v>
       </c>
       <c r="E20" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" t="s">
         <v>23</v>
       </c>
-      <c r="F20" t="s">
-        <v>24</v>
-      </c>
       <c r="G20" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I20">
         <v>4</v>
       </c>
       <c r="J20" t="s">
+        <v>20</v>
+      </c>
+      <c r="K20" t="s">
         <v>21</v>
-      </c>
-      <c r="K20" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" t="s">
         <v>12</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>13</v>
       </c>
-      <c r="C21" t="s">
-        <v>14</v>
-      </c>
       <c r="D21">
         <v>114</v>
       </c>
       <c r="E21" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" t="s">
         <v>23</v>
       </c>
-      <c r="F21" t="s">
-        <v>24</v>
-      </c>
       <c r="G21" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I21">
         <v>4</v>
       </c>
       <c r="J21" t="s">
+        <v>20</v>
+      </c>
+      <c r="K21" t="s">
         <v>21</v>
-      </c>
-      <c r="K21" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" t="s">
         <v>12</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>13</v>
       </c>
-      <c r="C22" t="s">
-        <v>14</v>
-      </c>
       <c r="D22">
         <v>114</v>
       </c>
       <c r="E22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" t="s">
         <v>23</v>
       </c>
-      <c r="F22" t="s">
-        <v>24</v>
-      </c>
       <c r="G22" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I22">
         <v>4</v>
       </c>
       <c r="J22" t="s">
+        <v>20</v>
+      </c>
+      <c r="K22" t="s">
         <v>21</v>
-      </c>
-      <c r="K22" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" t="s">
         <v>12</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>13</v>
       </c>
-      <c r="C23" t="s">
-        <v>14</v>
-      </c>
       <c r="D23">
         <v>114</v>
       </c>
       <c r="E23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" t="s">
         <v>23</v>
       </c>
-      <c r="F23" t="s">
-        <v>24</v>
-      </c>
       <c r="G23" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I23">
         <v>4</v>
       </c>
       <c r="J23" t="s">
+        <v>20</v>
+      </c>
+      <c r="K23" t="s">
         <v>21</v>
-      </c>
-      <c r="K23" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" t="s">
         <v>12</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>13</v>
       </c>
-      <c r="C24" t="s">
-        <v>14</v>
-      </c>
       <c r="D24">
         <v>114</v>
       </c>
       <c r="E24" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" t="s">
         <v>23</v>
       </c>
-      <c r="F24" t="s">
-        <v>24</v>
-      </c>
       <c r="G24" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I24">
         <v>4</v>
       </c>
       <c r="J24" t="s">
+        <v>20</v>
+      </c>
+      <c r="K24" t="s">
         <v>21</v>
-      </c>
-      <c r="K24" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" t="s">
         <v>12</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>13</v>
       </c>
-      <c r="C25" t="s">
-        <v>14</v>
-      </c>
       <c r="D25">
         <v>114</v>
       </c>
       <c r="E25" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" t="s">
         <v>23</v>
       </c>
-      <c r="F25" t="s">
-        <v>24</v>
-      </c>
       <c r="G25" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I25">
         <v>4</v>
       </c>
       <c r="J25" t="s">
+        <v>20</v>
+      </c>
+      <c r="K25" t="s">
         <v>21</v>
-      </c>
-      <c r="K25" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" t="s">
         <v>12</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>13</v>
       </c>
-      <c r="C26" t="s">
-        <v>14</v>
-      </c>
       <c r="D26">
         <v>114</v>
       </c>
       <c r="E26" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" t="s">
         <v>23</v>
       </c>
-      <c r="F26" t="s">
-        <v>24</v>
-      </c>
       <c r="G26" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I26">
         <v>4</v>
       </c>
       <c r="J26" t="s">
+        <v>20</v>
+      </c>
+      <c r="K26" t="s">
         <v>21</v>
-      </c>
-      <c r="K26" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" t="s">
         <v>12</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>13</v>
       </c>
-      <c r="C27" t="s">
-        <v>14</v>
-      </c>
       <c r="D27">
         <v>114</v>
       </c>
       <c r="E27" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" t="s">
         <v>23</v>
       </c>
-      <c r="F27" t="s">
-        <v>24</v>
-      </c>
       <c r="G27" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I27">
         <v>4</v>
       </c>
       <c r="J27" t="s">
+        <v>20</v>
+      </c>
+      <c r="K27" t="s">
         <v>21</v>
-      </c>
-      <c r="K27" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" t="s">
         <v>12</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>13</v>
       </c>
-      <c r="C28" t="s">
-        <v>14</v>
-      </c>
       <c r="D28">
         <v>114</v>
       </c>
       <c r="E28" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" t="s">
         <v>23</v>
       </c>
-      <c r="F28" t="s">
-        <v>24</v>
-      </c>
       <c r="G28" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I28">
         <v>4</v>
       </c>
       <c r="J28" t="s">
+        <v>20</v>
+      </c>
+      <c r="K28" t="s">
         <v>21</v>
-      </c>
-      <c r="K28" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" t="s">
         <v>12</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>13</v>
       </c>
-      <c r="C29" t="s">
-        <v>14</v>
-      </c>
       <c r="D29">
         <v>114</v>
       </c>
       <c r="E29" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" t="s">
         <v>23</v>
       </c>
-      <c r="F29" t="s">
-        <v>24</v>
-      </c>
       <c r="G29" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I29">
         <v>4</v>
       </c>
       <c r="J29" t="s">
+        <v>20</v>
+      </c>
+      <c r="K29" t="s">
         <v>21</v>
-      </c>
-      <c r="K29" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" t="s">
         <v>12</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>13</v>
       </c>
-      <c r="C30" t="s">
-        <v>14</v>
-      </c>
       <c r="D30">
         <v>114</v>
       </c>
       <c r="E30" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" t="s">
         <v>23</v>
       </c>
-      <c r="F30" t="s">
-        <v>24</v>
-      </c>
       <c r="G30" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I30">
         <v>4</v>
       </c>
       <c r="J30" t="s">
+        <v>20</v>
+      </c>
+      <c r="K30" t="s">
         <v>21</v>
-      </c>
-      <c r="K30" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" t="s">
         <v>12</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>13</v>
       </c>
-      <c r="C31" t="s">
-        <v>14</v>
-      </c>
       <c r="D31">
         <v>114</v>
       </c>
       <c r="E31" t="s">
+        <v>22</v>
+      </c>
+      <c r="F31" t="s">
         <v>23</v>
       </c>
-      <c r="F31" t="s">
-        <v>24</v>
-      </c>
       <c r="G31" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I31">
         <v>4</v>
       </c>
       <c r="J31" t="s">
+        <v>20</v>
+      </c>
+      <c r="K31" t="s">
         <v>21</v>
-      </c>
-      <c r="K31" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" t="s">
         <v>12</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>13</v>
       </c>
-      <c r="C32" t="s">
-        <v>14</v>
-      </c>
       <c r="D32">
         <v>114</v>
       </c>
       <c r="E32" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" t="s">
         <v>23</v>
       </c>
-      <c r="F32" t="s">
-        <v>24</v>
-      </c>
       <c r="G32" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I32">
         <v>4</v>
       </c>
       <c r="J32" t="s">
+        <v>20</v>
+      </c>
+      <c r="K32" t="s">
         <v>21</v>
-      </c>
-      <c r="K32" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" t="s">
         <v>12</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>13</v>
       </c>
-      <c r="C33" t="s">
-        <v>14</v>
-      </c>
       <c r="D33">
         <v>114</v>
       </c>
       <c r="E33" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" t="s">
         <v>23</v>
       </c>
-      <c r="F33" t="s">
-        <v>24</v>
-      </c>
       <c r="G33" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I33">
         <v>6</v>
       </c>
       <c r="J33" t="s">
+        <v>20</v>
+      </c>
+      <c r="K33" t="s">
         <v>21</v>
-      </c>
-      <c r="K33" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" t="s">
         <v>12</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>13</v>
       </c>
-      <c r="C34" t="s">
-        <v>14</v>
-      </c>
       <c r="D34">
         <v>114</v>
       </c>
       <c r="E34" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" t="s">
         <v>23</v>
       </c>
-      <c r="F34" t="s">
-        <v>24</v>
-      </c>
       <c r="G34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H34" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I34">
         <v>4</v>
       </c>
       <c r="J34" t="s">
+        <v>20</v>
+      </c>
+      <c r="K34" t="s">
         <v>21</v>
-      </c>
-      <c r="K34" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" t="s">
         <v>12</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>13</v>
       </c>
-      <c r="C35" t="s">
-        <v>14</v>
-      </c>
       <c r="D35">
         <v>114</v>
       </c>
       <c r="E35" t="s">
+        <v>22</v>
+      </c>
+      <c r="F35" t="s">
         <v>23</v>
       </c>
-      <c r="F35" t="s">
-        <v>24</v>
-      </c>
       <c r="G35" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I35">
         <v>4</v>
       </c>
       <c r="J35" t="s">
+        <v>58</v>
+      </c>
+      <c r="K35" t="s">
         <v>59</v>
-      </c>
-      <c r="K35" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" t="s">
         <v>12</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>13</v>
       </c>
-      <c r="C36" t="s">
-        <v>14</v>
-      </c>
       <c r="D36">
         <v>114</v>
       </c>
       <c r="E36" t="s">
+        <v>22</v>
+      </c>
+      <c r="F36" t="s">
         <v>23</v>
       </c>
-      <c r="F36" t="s">
-        <v>24</v>
-      </c>
       <c r="G36" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I36">
         <v>4</v>
       </c>
       <c r="J36" t="s">
+        <v>61</v>
+      </c>
+      <c r="K36" t="s">
         <v>62</v>
-      </c>
-      <c r="K36" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" t="s">
         <v>12</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>13</v>
       </c>
-      <c r="C37" t="s">
-        <v>14</v>
-      </c>
       <c r="D37">
         <v>114</v>
       </c>
       <c r="E37" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" t="s">
         <v>23</v>
       </c>
-      <c r="F37" t="s">
-        <v>24</v>
-      </c>
       <c r="G37" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I37">
         <v>4</v>
       </c>
       <c r="J37" t="s">
+        <v>61</v>
+      </c>
+      <c r="K37" t="s">
         <v>62</v>
-      </c>
-      <c r="K37" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" t="s">
         <v>12</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>13</v>
       </c>
-      <c r="C38" t="s">
-        <v>14</v>
-      </c>
       <c r="D38">
         <v>114</v>
       </c>
       <c r="E38" t="s">
+        <v>22</v>
+      </c>
+      <c r="F38" t="s">
         <v>23</v>
       </c>
-      <c r="F38" t="s">
-        <v>24</v>
-      </c>
       <c r="G38" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I38">
         <v>4</v>
       </c>
       <c r="J38" t="s">
+        <v>61</v>
+      </c>
+      <c r="K38" t="s">
         <v>62</v>
-      </c>
-      <c r="K38" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" t="s">
         <v>12</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>13</v>
       </c>
-      <c r="C39" t="s">
-        <v>14</v>
-      </c>
       <c r="D39">
         <v>114</v>
       </c>
       <c r="E39" t="s">
+        <v>22</v>
+      </c>
+      <c r="F39" t="s">
         <v>23</v>
       </c>
-      <c r="F39" t="s">
-        <v>24</v>
-      </c>
       <c r="G39" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I39">
         <v>4</v>
       </c>
       <c r="J39" t="s">
+        <v>61</v>
+      </c>
+      <c r="K39" t="s">
         <v>62</v>
-      </c>
-      <c r="K39" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" t="s">
         <v>12</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>13</v>
       </c>
-      <c r="C40" t="s">
-        <v>14</v>
-      </c>
       <c r="D40">
         <v>114</v>
       </c>
       <c r="E40" t="s">
+        <v>22</v>
+      </c>
+      <c r="F40" t="s">
         <v>23</v>
       </c>
-      <c r="F40" t="s">
-        <v>24</v>
-      </c>
       <c r="G40" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H40" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I40">
         <v>4</v>
       </c>
       <c r="J40" t="s">
+        <v>61</v>
+      </c>
+      <c r="K40" t="s">
         <v>62</v>
       </c>
-      <c r="K40" t="s">
-        <v>63</v>
-      </c>
       <c r="L40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" t="s">
         <v>12</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>13</v>
       </c>
-      <c r="C41" t="s">
-        <v>14</v>
-      </c>
       <c r="D41">
         <v>114</v>
       </c>
       <c r="E41" t="s">
+        <v>22</v>
+      </c>
+      <c r="F41" t="s">
         <v>23</v>
       </c>
-      <c r="F41" t="s">
-        <v>24</v>
-      </c>
       <c r="G41" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H41" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I41">
         <v>4</v>
       </c>
       <c r="J41" t="s">
+        <v>61</v>
+      </c>
+      <c r="K41" t="s">
         <v>62</v>
       </c>
-      <c r="K41" t="s">
-        <v>63</v>
-      </c>
       <c r="L41" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42" t="s">
         <v>12</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>13</v>
       </c>
-      <c r="C42" t="s">
-        <v>14</v>
-      </c>
       <c r="D42">
         <v>114</v>
       </c>
       <c r="E42" t="s">
+        <v>22</v>
+      </c>
+      <c r="F42" t="s">
         <v>23</v>
       </c>
-      <c r="F42" t="s">
-        <v>24</v>
-      </c>
       <c r="G42" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H42" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I42">
         <v>4</v>
       </c>
       <c r="J42" t="s">
+        <v>61</v>
+      </c>
+      <c r="K42" t="s">
         <v>62</v>
-      </c>
-      <c r="K42" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43" t="s">
         <v>12</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>13</v>
       </c>
-      <c r="C43" t="s">
-        <v>14</v>
-      </c>
       <c r="D43">
         <v>114</v>
       </c>
       <c r="E43" t="s">
+        <v>22</v>
+      </c>
+      <c r="F43" t="s">
         <v>23</v>
       </c>
-      <c r="F43" t="s">
-        <v>24</v>
-      </c>
       <c r="G43" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H43" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I43">
         <v>4</v>
       </c>
       <c r="J43" t="s">
+        <v>61</v>
+      </c>
+      <c r="K43" t="s">
         <v>62</v>
-      </c>
-      <c r="K43" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" t="s">
         <v>12</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>13</v>
       </c>
-      <c r="C44" t="s">
-        <v>14</v>
-      </c>
       <c r="D44">
         <v>114</v>
       </c>
       <c r="E44" t="s">
+        <v>22</v>
+      </c>
+      <c r="F44" t="s">
         <v>23</v>
       </c>
-      <c r="F44" t="s">
-        <v>24</v>
-      </c>
       <c r="G44" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I44">
         <v>4</v>
       </c>
       <c r="J44" t="s">
+        <v>61</v>
+      </c>
+      <c r="K44" t="s">
         <v>62</v>
       </c>
-      <c r="K44" t="s">
-        <v>63</v>
-      </c>
       <c r="L44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45" t="s">
         <v>12</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>13</v>
       </c>
-      <c r="C45" t="s">
-        <v>14</v>
-      </c>
       <c r="D45">
         <v>114</v>
       </c>
       <c r="E45" t="s">
+        <v>22</v>
+      </c>
+      <c r="F45" t="s">
         <v>23</v>
       </c>
-      <c r="F45" t="s">
-        <v>24</v>
-      </c>
       <c r="G45" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I45">
         <v>4</v>
       </c>
       <c r="J45" t="s">
+        <v>61</v>
+      </c>
+      <c r="K45" t="s">
         <v>62</v>
       </c>
-      <c r="K45" t="s">
-        <v>63</v>
-      </c>
       <c r="L45" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" t="s">
         <v>12</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>13</v>
       </c>
-      <c r="C46" t="s">
-        <v>14</v>
-      </c>
       <c r="D46">
         <v>114</v>
       </c>
       <c r="E46" t="s">
+        <v>22</v>
+      </c>
+      <c r="F46" t="s">
         <v>23</v>
       </c>
-      <c r="F46" t="s">
-        <v>24</v>
-      </c>
       <c r="G46" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I46">
         <v>4</v>
       </c>
       <c r="J46" t="s">
+        <v>61</v>
+      </c>
+      <c r="K46" t="s">
         <v>62</v>
       </c>
-      <c r="K46" t="s">
-        <v>63</v>
-      </c>
       <c r="L46" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" t="s">
         <v>12</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>13</v>
       </c>
-      <c r="C47" t="s">
-        <v>14</v>
-      </c>
       <c r="D47">
         <v>114</v>
       </c>
       <c r="E47" t="s">
+        <v>22</v>
+      </c>
+      <c r="F47" t="s">
         <v>23</v>
       </c>
-      <c r="F47" t="s">
-        <v>24</v>
-      </c>
       <c r="G47" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H47" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I47">
         <v>4</v>
       </c>
       <c r="J47" t="s">
+        <v>61</v>
+      </c>
+      <c r="K47" t="s">
         <v>62</v>
       </c>
-      <c r="K47" t="s">
-        <v>63</v>
-      </c>
       <c r="L47" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>11</v>
+      </c>
+      <c r="B48" t="s">
         <v>12</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>13</v>
       </c>
-      <c r="C48" t="s">
-        <v>14</v>
-      </c>
       <c r="D48">
         <v>114</v>
       </c>
       <c r="E48" t="s">
+        <v>22</v>
+      </c>
+      <c r="F48" t="s">
         <v>23</v>
       </c>
-      <c r="F48" t="s">
-        <v>24</v>
-      </c>
       <c r="G48" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I48">
         <v>2</v>
       </c>
       <c r="J48" t="s">
+        <v>78</v>
+      </c>
+      <c r="K48" t="s">
         <v>79</v>
-      </c>
-      <c r="K48" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>11</v>
+      </c>
+      <c r="B49" t="s">
         <v>12</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>13</v>
       </c>
-      <c r="C49" t="s">
-        <v>14</v>
-      </c>
       <c r="D49">
         <v>114</v>
       </c>
       <c r="E49" t="s">
+        <v>22</v>
+      </c>
+      <c r="F49" t="s">
         <v>23</v>
       </c>
-      <c r="F49" t="s">
-        <v>24</v>
-      </c>
       <c r="G49" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H49" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I49">
         <v>2</v>
       </c>
       <c r="J49" t="s">
+        <v>78</v>
+      </c>
+      <c r="K49" t="s">
         <v>79</v>
-      </c>
-      <c r="K49" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>11</v>
+      </c>
+      <c r="B50" t="s">
         <v>12</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>13</v>
       </c>
-      <c r="C50" t="s">
-        <v>14</v>
-      </c>
       <c r="D50">
         <v>114</v>
       </c>
       <c r="E50" t="s">
+        <v>22</v>
+      </c>
+      <c r="F50" t="s">
         <v>23</v>
       </c>
-      <c r="F50" t="s">
-        <v>24</v>
-      </c>
       <c r="G50" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I50">
         <v>2</v>
       </c>
       <c r="J50" t="s">
+        <v>78</v>
+      </c>
+      <c r="K50" t="s">
         <v>79</v>
-      </c>
-      <c r="K50" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51" t="s">
         <v>12</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>13</v>
       </c>
-      <c r="C51" t="s">
-        <v>14</v>
-      </c>
       <c r="D51">
         <v>114</v>
       </c>
       <c r="E51" t="s">
+        <v>22</v>
+      </c>
+      <c r="F51" t="s">
         <v>23</v>
       </c>
-      <c r="F51" t="s">
-        <v>24</v>
-      </c>
       <c r="G51" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H51" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I51">
         <v>4</v>
       </c>
       <c r="J51" t="s">
+        <v>78</v>
+      </c>
+      <c r="K51" t="s">
         <v>79</v>
-      </c>
-      <c r="K51" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B52" t="s">
+        <v>83</v>
+      </c>
+      <c r="C52" t="s">
         <v>84</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52">
+        <v>114</v>
+      </c>
+      <c r="E52" t="s">
         <v>85</v>
       </c>
-      <c r="D52">
-        <v>114</v>
-      </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>86</v>
       </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
+        <v>280</v>
+      </c>
+      <c r="H52" t="s">
         <v>87</v>
-      </c>
-      <c r="G52" t="s">
-        <v>281</v>
-      </c>
-      <c r="H52" t="s">
-        <v>88</v>
       </c>
       <c r="I52">
         <v>4</v>
       </c>
       <c r="J52" t="s">
+        <v>61</v>
+      </c>
+      <c r="K52" t="s">
         <v>62</v>
-      </c>
-      <c r="K52" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B53" t="s">
+        <v>83</v>
+      </c>
+      <c r="C53" t="s">
         <v>84</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53">
+        <v>114</v>
+      </c>
+      <c r="E53" t="s">
         <v>85</v>
       </c>
-      <c r="D53">
-        <v>114</v>
-      </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>86</v>
       </c>
-      <c r="F53" t="s">
-        <v>87</v>
-      </c>
       <c r="G53" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H53" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I53">
         <v>4</v>
       </c>
       <c r="J53" t="s">
+        <v>61</v>
+      </c>
+      <c r="K53" t="s">
         <v>62</v>
-      </c>
-      <c r="K53" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B54" t="s">
+        <v>83</v>
+      </c>
+      <c r="C54" t="s">
         <v>84</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54">
+        <v>114</v>
+      </c>
+      <c r="E54" t="s">
         <v>85</v>
       </c>
-      <c r="D54">
-        <v>114</v>
-      </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>86</v>
       </c>
-      <c r="F54" t="s">
-        <v>87</v>
-      </c>
       <c r="G54" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H54" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I54">
         <v>2</v>
       </c>
       <c r="J54" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K54" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B55" t="s">
+        <v>83</v>
+      </c>
+      <c r="C55" t="s">
         <v>84</v>
       </c>
-      <c r="C55" t="s">
-        <v>85</v>
-      </c>
       <c r="D55">
         <v>114</v>
       </c>
       <c r="E55" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F55" t="s">
+        <v>91</v>
+      </c>
+      <c r="G55" t="s">
+        <v>283</v>
+      </c>
+      <c r="H55" t="s">
         <v>92</v>
-      </c>
-      <c r="G55" t="s">
-        <v>284</v>
-      </c>
-      <c r="H55" t="s">
-        <v>93</v>
       </c>
       <c r="I55">
         <v>4</v>
       </c>
       <c r="J55" t="s">
+        <v>61</v>
+      </c>
+      <c r="K55" t="s">
         <v>62</v>
-      </c>
-      <c r="K55" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B56" t="s">
+        <v>83</v>
+      </c>
+      <c r="C56" t="s">
         <v>84</v>
       </c>
-      <c r="C56" t="s">
-        <v>85</v>
-      </c>
       <c r="D56">
         <v>114</v>
       </c>
       <c r="E56" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F56" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G56" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H56" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I56">
         <v>4</v>
       </c>
       <c r="J56" t="s">
+        <v>61</v>
+      </c>
+      <c r="K56" t="s">
         <v>62</v>
-      </c>
-      <c r="K56" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B57" t="s">
+        <v>83</v>
+      </c>
+      <c r="C57" t="s">
         <v>84</v>
       </c>
-      <c r="C57" t="s">
-        <v>85</v>
-      </c>
       <c r="D57">
         <v>114</v>
       </c>
       <c r="E57" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F57" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G57" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I57">
         <v>4</v>
       </c>
       <c r="J57" t="s">
+        <v>61</v>
+      </c>
+      <c r="K57" t="s">
         <v>62</v>
-      </c>
-      <c r="K57" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B58" t="s">
+        <v>83</v>
+      </c>
+      <c r="C58" t="s">
         <v>84</v>
       </c>
-      <c r="C58" t="s">
-        <v>85</v>
-      </c>
       <c r="D58">
         <v>114</v>
       </c>
       <c r="E58" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F58" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G58" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H58" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I58">
         <v>2</v>
       </c>
       <c r="J58" t="s">
+        <v>61</v>
+      </c>
+      <c r="K58" t="s">
         <v>62</v>
-      </c>
-      <c r="K58" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B59" t="s">
+        <v>83</v>
+      </c>
+      <c r="C59" t="s">
         <v>84</v>
       </c>
-      <c r="C59" t="s">
-        <v>85</v>
-      </c>
       <c r="D59">
         <v>114</v>
       </c>
       <c r="E59" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F59" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G59" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H59" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I59">
         <v>2</v>
       </c>
       <c r="J59" t="s">
+        <v>61</v>
+      </c>
+      <c r="K59" t="s">
         <v>62</v>
-      </c>
-      <c r="K59" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B60" t="s">
+        <v>83</v>
+      </c>
+      <c r="C60" t="s">
         <v>84</v>
       </c>
-      <c r="C60" t="s">
-        <v>85</v>
-      </c>
       <c r="D60">
         <v>114</v>
       </c>
       <c r="E60" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F60" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G60" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H60" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I60">
         <v>2</v>
       </c>
       <c r="J60" t="s">
+        <v>61</v>
+      </c>
+      <c r="K60" t="s">
         <v>62</v>
-      </c>
-      <c r="K60" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B61" t="s">
+        <v>83</v>
+      </c>
+      <c r="C61" t="s">
         <v>84</v>
       </c>
-      <c r="C61" t="s">
-        <v>85</v>
-      </c>
       <c r="D61">
         <v>114</v>
       </c>
       <c r="E61" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G61" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H61" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I61">
         <v>2</v>
       </c>
       <c r="J61" t="s">
+        <v>61</v>
+      </c>
+      <c r="K61" t="s">
         <v>62</v>
-      </c>
-      <c r="K61" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B62" t="s">
+        <v>83</v>
+      </c>
+      <c r="C62" t="s">
         <v>84</v>
       </c>
-      <c r="C62" t="s">
-        <v>85</v>
-      </c>
       <c r="D62">
         <v>114</v>
       </c>
       <c r="E62" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F62" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G62" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H62" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I62">
         <v>2</v>
       </c>
       <c r="J62" t="s">
+        <v>61</v>
+      </c>
+      <c r="K62" t="s">
         <v>62</v>
-      </c>
-      <c r="K62" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B63" t="s">
+        <v>83</v>
+      </c>
+      <c r="C63" t="s">
         <v>84</v>
       </c>
-      <c r="C63" t="s">
-        <v>85</v>
-      </c>
       <c r="D63">
         <v>114</v>
       </c>
       <c r="E63" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F63" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G63" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H63" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I63">
         <v>4</v>
       </c>
       <c r="J63" t="s">
+        <v>61</v>
+      </c>
+      <c r="K63" t="s">
         <v>62</v>
-      </c>
-      <c r="K63" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B64" t="s">
+        <v>83</v>
+      </c>
+      <c r="C64" t="s">
         <v>84</v>
       </c>
-      <c r="C64" t="s">
-        <v>85</v>
-      </c>
       <c r="D64">
         <v>114</v>
       </c>
       <c r="E64" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F64" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G64" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H64" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I64">
         <v>2</v>
       </c>
       <c r="J64" t="s">
+        <v>61</v>
+      </c>
+      <c r="K64" t="s">
         <v>62</v>
-      </c>
-      <c r="K64" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B65" t="s">
+        <v>83</v>
+      </c>
+      <c r="C65" t="s">
         <v>84</v>
       </c>
-      <c r="C65" t="s">
-        <v>85</v>
-      </c>
       <c r="D65">
         <v>114</v>
       </c>
       <c r="E65" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F65" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G65" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H65" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I65">
         <v>4</v>
       </c>
       <c r="J65" t="s">
+        <v>61</v>
+      </c>
+      <c r="K65" t="s">
         <v>62</v>
-      </c>
-      <c r="K65" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B66" t="s">
+        <v>83</v>
+      </c>
+      <c r="C66" t="s">
         <v>84</v>
       </c>
-      <c r="C66" t="s">
-        <v>85</v>
-      </c>
       <c r="D66">
         <v>114</v>
       </c>
       <c r="E66" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F66" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G66" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H66" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I66">
         <v>4</v>
       </c>
       <c r="J66" t="s">
+        <v>61</v>
+      </c>
+      <c r="K66" t="s">
         <v>62</v>
-      </c>
-      <c r="K66" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B67" t="s">
+        <v>83</v>
+      </c>
+      <c r="C67" t="s">
         <v>84</v>
       </c>
-      <c r="C67" t="s">
-        <v>85</v>
-      </c>
       <c r="D67">
         <v>114</v>
       </c>
       <c r="E67" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F67" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G67" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H67" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I67">
         <v>2</v>
       </c>
       <c r="J67" t="s">
+        <v>61</v>
+      </c>
+      <c r="K67" t="s">
         <v>62</v>
-      </c>
-      <c r="K67" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B68" t="s">
+        <v>83</v>
+      </c>
+      <c r="C68" t="s">
         <v>84</v>
       </c>
-      <c r="C68" t="s">
-        <v>85</v>
-      </c>
       <c r="D68">
         <v>114</v>
       </c>
       <c r="E68" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F68" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G68" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H68" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I68">
         <v>2</v>
       </c>
       <c r="J68" t="s">
+        <v>61</v>
+      </c>
+      <c r="K68" t="s">
         <v>62</v>
-      </c>
-      <c r="K68" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B69" t="s">
+        <v>83</v>
+      </c>
+      <c r="C69" t="s">
         <v>84</v>
       </c>
-      <c r="C69" t="s">
-        <v>85</v>
-      </c>
       <c r="D69">
         <v>114</v>
       </c>
       <c r="E69" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F69" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G69" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I69">
         <v>2</v>
       </c>
       <c r="J69" t="s">
+        <v>61</v>
+      </c>
+      <c r="K69" t="s">
         <v>62</v>
-      </c>
-      <c r="K69" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B70" t="s">
+        <v>83</v>
+      </c>
+      <c r="C70" t="s">
         <v>84</v>
       </c>
-      <c r="C70" t="s">
-        <v>85</v>
-      </c>
       <c r="D70">
         <v>114</v>
       </c>
       <c r="E70" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F70" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G70" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H70" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I70">
         <v>2</v>
       </c>
       <c r="J70" t="s">
+        <v>61</v>
+      </c>
+      <c r="K70" t="s">
         <v>62</v>
-      </c>
-      <c r="K70" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B71" t="s">
+        <v>83</v>
+      </c>
+      <c r="C71" t="s">
         <v>84</v>
       </c>
-      <c r="C71" t="s">
-        <v>85</v>
-      </c>
       <c r="D71">
         <v>114</v>
       </c>
       <c r="E71" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F71" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G71" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I71">
         <v>2</v>
       </c>
       <c r="J71" t="s">
+        <v>61</v>
+      </c>
+      <c r="K71" t="s">
         <v>62</v>
-      </c>
-      <c r="K71" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B72" t="s">
+        <v>83</v>
+      </c>
+      <c r="C72" t="s">
         <v>84</v>
       </c>
-      <c r="C72" t="s">
-        <v>85</v>
-      </c>
       <c r="D72">
         <v>114</v>
       </c>
       <c r="E72" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F72" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G72" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H72" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I72">
         <v>4</v>
       </c>
       <c r="J72" t="s">
+        <v>61</v>
+      </c>
+      <c r="K72" t="s">
         <v>62</v>
-      </c>
-      <c r="K72" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B73" t="s">
+        <v>83</v>
+      </c>
+      <c r="C73" t="s">
         <v>84</v>
       </c>
-      <c r="C73" t="s">
-        <v>85</v>
-      </c>
       <c r="D73">
         <v>114</v>
       </c>
       <c r="E73" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F73" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G73" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H73" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I73">
         <v>4</v>
       </c>
       <c r="J73" t="s">
+        <v>61</v>
+      </c>
+      <c r="K73" t="s">
         <v>62</v>
-      </c>
-      <c r="K73" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B74" t="s">
+        <v>83</v>
+      </c>
+      <c r="C74" t="s">
         <v>84</v>
       </c>
-      <c r="C74" t="s">
-        <v>85</v>
-      </c>
       <c r="D74">
         <v>114</v>
       </c>
       <c r="E74" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F74" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G74" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H74" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I74">
         <v>2</v>
       </c>
       <c r="J74" t="s">
+        <v>61</v>
+      </c>
+      <c r="K74" t="s">
         <v>62</v>
-      </c>
-      <c r="K74" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B75" t="s">
+        <v>83</v>
+      </c>
+      <c r="C75" t="s">
         <v>84</v>
       </c>
-      <c r="C75" t="s">
-        <v>85</v>
-      </c>
       <c r="D75">
         <v>114</v>
       </c>
       <c r="E75" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F75" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G75" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H75" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I75">
         <v>2</v>
       </c>
       <c r="J75" t="s">
+        <v>61</v>
+      </c>
+      <c r="K75" t="s">
         <v>62</v>
-      </c>
-      <c r="K75" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B76" t="s">
+        <v>83</v>
+      </c>
+      <c r="C76" t="s">
         <v>84</v>
       </c>
-      <c r="C76" t="s">
-        <v>85</v>
-      </c>
       <c r="D76">
         <v>114</v>
       </c>
       <c r="E76" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F76" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G76" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I76">
         <v>3</v>
       </c>
       <c r="J76" t="s">
+        <v>114</v>
+      </c>
+      <c r="K76" t="s">
         <v>115</v>
-      </c>
-      <c r="K76" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B77" t="s">
+        <v>83</v>
+      </c>
+      <c r="C77" t="s">
         <v>84</v>
       </c>
-      <c r="C77" t="s">
-        <v>85</v>
-      </c>
       <c r="D77">
         <v>114</v>
       </c>
       <c r="E77" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F77" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G77" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H77" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I77">
         <v>3</v>
       </c>
       <c r="J77" t="s">
+        <v>114</v>
+      </c>
+      <c r="K77" t="s">
         <v>115</v>
-      </c>
-      <c r="K77" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B78" t="s">
+        <v>83</v>
+      </c>
+      <c r="C78" t="s">
         <v>84</v>
       </c>
-      <c r="C78" t="s">
-        <v>85</v>
-      </c>
       <c r="D78">
         <v>114</v>
       </c>
       <c r="E78" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F78" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G78" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H78" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I78">
         <v>3</v>
       </c>
       <c r="J78" t="s">
+        <v>114</v>
+      </c>
+      <c r="K78" t="s">
         <v>115</v>
-      </c>
-      <c r="K78" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B79" t="s">
+        <v>83</v>
+      </c>
+      <c r="C79" t="s">
         <v>84</v>
       </c>
-      <c r="C79" t="s">
-        <v>85</v>
-      </c>
       <c r="D79">
         <v>114</v>
       </c>
       <c r="E79" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F79" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G79" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H79" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I79">
         <v>3</v>
       </c>
       <c r="J79" t="s">
+        <v>114</v>
+      </c>
+      <c r="K79" t="s">
         <v>115</v>
-      </c>
-      <c r="K79" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B80" t="s">
+        <v>83</v>
+      </c>
+      <c r="C80" t="s">
         <v>84</v>
       </c>
-      <c r="C80" t="s">
-        <v>85</v>
-      </c>
       <c r="D80">
         <v>114</v>
       </c>
       <c r="E80" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F80" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G80" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H80" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I80">
         <v>3</v>
       </c>
       <c r="J80" t="s">
+        <v>114</v>
+      </c>
+      <c r="K80" t="s">
         <v>115</v>
-      </c>
-      <c r="K80" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B81" t="s">
+        <v>83</v>
+      </c>
+      <c r="C81" t="s">
         <v>84</v>
       </c>
-      <c r="C81" t="s">
-        <v>85</v>
-      </c>
       <c r="D81">
         <v>114</v>
       </c>
       <c r="E81" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F81" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G81" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H81" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I81">
         <v>3</v>
       </c>
       <c r="J81" t="s">
+        <v>114</v>
+      </c>
+      <c r="K81" t="s">
         <v>115</v>
-      </c>
-      <c r="K81" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B82" t="s">
+        <v>83</v>
+      </c>
+      <c r="C82" t="s">
         <v>84</v>
       </c>
-      <c r="C82" t="s">
-        <v>85</v>
-      </c>
       <c r="D82">
         <v>114</v>
       </c>
       <c r="E82" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F82" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G82" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H82" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I82">
         <v>3</v>
       </c>
       <c r="J82" t="s">
+        <v>114</v>
+      </c>
+      <c r="K82" t="s">
         <v>115</v>
-      </c>
-      <c r="K82" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B83" t="s">
+        <v>83</v>
+      </c>
+      <c r="C83" t="s">
         <v>84</v>
       </c>
-      <c r="C83" t="s">
-        <v>85</v>
-      </c>
       <c r="D83">
         <v>114</v>
       </c>
       <c r="E83" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F83" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G83" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H83" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I83">
         <v>3</v>
       </c>
       <c r="J83" t="s">
+        <v>114</v>
+      </c>
+      <c r="K83" t="s">
         <v>115</v>
-      </c>
-      <c r="K83" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B84" t="s">
+        <v>83</v>
+      </c>
+      <c r="C84" t="s">
         <v>84</v>
       </c>
-      <c r="C84" t="s">
-        <v>85</v>
-      </c>
       <c r="D84">
         <v>114</v>
       </c>
       <c r="E84" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F84" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G84" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H84" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I84">
         <v>3</v>
       </c>
       <c r="J84" t="s">
+        <v>114</v>
+      </c>
+      <c r="K84" t="s">
         <v>115</v>
-      </c>
-      <c r="K84" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B85" t="s">
+        <v>83</v>
+      </c>
+      <c r="C85" t="s">
         <v>84</v>
       </c>
-      <c r="C85" t="s">
-        <v>85</v>
-      </c>
       <c r="D85">
         <v>114</v>
       </c>
       <c r="E85" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F85" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G85" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H85" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I85">
         <v>3</v>
       </c>
       <c r="J85" t="s">
+        <v>114</v>
+      </c>
+      <c r="K85" t="s">
         <v>115</v>
-      </c>
-      <c r="K85" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B86" t="s">
+        <v>83</v>
+      </c>
+      <c r="C86" t="s">
         <v>84</v>
       </c>
-      <c r="C86" t="s">
-        <v>85</v>
-      </c>
       <c r="D86">
         <v>114</v>
       </c>
       <c r="E86" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F86" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G86" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H86" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I86">
         <v>3</v>
       </c>
       <c r="J86" t="s">
+        <v>114</v>
+      </c>
+      <c r="K86" t="s">
         <v>115</v>
-      </c>
-      <c r="K86" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B87" t="s">
+        <v>83</v>
+      </c>
+      <c r="C87" t="s">
         <v>84</v>
       </c>
-      <c r="C87" t="s">
-        <v>85</v>
-      </c>
       <c r="D87">
         <v>114</v>
       </c>
       <c r="E87" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F87" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G87" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H87" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I87">
         <v>2</v>
       </c>
       <c r="J87" t="s">
+        <v>127</v>
+      </c>
+      <c r="K87" t="s">
         <v>128</v>
-      </c>
-      <c r="K87" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B88" t="s">
+        <v>83</v>
+      </c>
+      <c r="C88" t="s">
         <v>84</v>
       </c>
-      <c r="C88" t="s">
-        <v>85</v>
-      </c>
       <c r="D88">
         <v>114</v>
       </c>
       <c r="E88" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F88" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G88" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H88" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="I88">
         <v>2</v>
       </c>
       <c r="J88" t="s">
+        <v>127</v>
+      </c>
+      <c r="K88" t="s">
         <v>128</v>
-      </c>
-      <c r="K88" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B89" t="s">
+        <v>83</v>
+      </c>
+      <c r="C89" t="s">
         <v>84</v>
       </c>
-      <c r="C89" t="s">
-        <v>85</v>
-      </c>
       <c r="D89">
         <v>114</v>
       </c>
       <c r="E89" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F89" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G89" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H89" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I89">
         <v>2</v>
       </c>
       <c r="J89" t="s">
+        <v>127</v>
+      </c>
+      <c r="K89" t="s">
         <v>128</v>
-      </c>
-      <c r="K89" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B90" t="s">
+        <v>83</v>
+      </c>
+      <c r="C90" t="s">
         <v>84</v>
       </c>
-      <c r="C90" t="s">
-        <v>85</v>
-      </c>
       <c r="D90">
         <v>114</v>
       </c>
       <c r="E90" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F90" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G90" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H90" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="I90">
         <v>2</v>
       </c>
       <c r="J90" t="s">
+        <v>127</v>
+      </c>
+      <c r="K90" t="s">
         <v>128</v>
-      </c>
-      <c r="K90" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B91" t="s">
+        <v>83</v>
+      </c>
+      <c r="C91" t="s">
         <v>84</v>
       </c>
-      <c r="C91" t="s">
-        <v>85</v>
-      </c>
       <c r="D91">
         <v>114</v>
       </c>
       <c r="E91" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F91" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G91" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H91" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I91">
         <v>2</v>
       </c>
       <c r="J91" t="s">
+        <v>127</v>
+      </c>
+      <c r="K91" t="s">
         <v>128</v>
-      </c>
-      <c r="K91" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B92" t="s">
+        <v>83</v>
+      </c>
+      <c r="C92" t="s">
         <v>84</v>
       </c>
-      <c r="C92" t="s">
-        <v>85</v>
-      </c>
       <c r="D92">
         <v>114</v>
       </c>
       <c r="E92" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F92" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G92" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H92" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I92">
         <v>2</v>
       </c>
       <c r="J92" t="s">
+        <v>127</v>
+      </c>
+      <c r="K92" t="s">
         <v>128</v>
-      </c>
-      <c r="K92" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B93" t="s">
+        <v>135</v>
+      </c>
+      <c r="C93" t="s">
         <v>136</v>
       </c>
-      <c r="C93" t="s">
+      <c r="D93">
+        <v>114</v>
+      </c>
+      <c r="E93" t="s">
+        <v>22</v>
+      </c>
+      <c r="F93" t="s">
         <v>137</v>
       </c>
-      <c r="D93">
-        <v>114</v>
-      </c>
-      <c r="E93" t="s">
-        <v>23</v>
-      </c>
-      <c r="F93" t="s">
+      <c r="G93" t="s">
+        <v>320</v>
+      </c>
+      <c r="H93" t="s">
         <v>138</v>
-      </c>
-      <c r="G93" t="s">
-        <v>321</v>
-      </c>
-      <c r="H93" t="s">
-        <v>139</v>
       </c>
       <c r="I93">
         <v>3</v>
       </c>
       <c r="J93" t="s">
+        <v>139</v>
+      </c>
+      <c r="K93" t="s">
         <v>140</v>
-      </c>
-      <c r="K93" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B94" t="s">
+        <v>135</v>
+      </c>
+      <c r="C94" t="s">
         <v>136</v>
       </c>
-      <c r="C94" t="s">
+      <c r="D94">
+        <v>114</v>
+      </c>
+      <c r="E94" t="s">
+        <v>22</v>
+      </c>
+      <c r="F94" t="s">
         <v>137</v>
       </c>
-      <c r="D94">
-        <v>114</v>
-      </c>
-      <c r="E94" t="s">
-        <v>23</v>
-      </c>
-      <c r="F94" t="s">
-        <v>138</v>
-      </c>
       <c r="G94" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H94" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I94">
         <v>6</v>
       </c>
       <c r="J94" t="s">
+        <v>17</v>
+      </c>
+      <c r="K94" t="s">
         <v>18</v>
-      </c>
-      <c r="K94" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B95" t="s">
+        <v>135</v>
+      </c>
+      <c r="C95" t="s">
         <v>136</v>
       </c>
-      <c r="C95" t="s">
+      <c r="D95">
+        <v>114</v>
+      </c>
+      <c r="E95" t="s">
+        <v>22</v>
+      </c>
+      <c r="F95" t="s">
         <v>137</v>
       </c>
-      <c r="D95">
-        <v>114</v>
-      </c>
-      <c r="E95" t="s">
-        <v>23</v>
-      </c>
-      <c r="F95" t="s">
-        <v>138</v>
-      </c>
       <c r="G95" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H95" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I95">
         <v>6</v>
       </c>
       <c r="J95" t="s">
+        <v>143</v>
+      </c>
+      <c r="K95" t="s">
         <v>144</v>
-      </c>
-      <c r="K95" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B96" t="s">
+        <v>135</v>
+      </c>
+      <c r="C96" t="s">
         <v>136</v>
       </c>
-      <c r="C96" t="s">
-        <v>137</v>
-      </c>
       <c r="D96">
         <v>114</v>
       </c>
       <c r="E96" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F96" t="s">
+        <v>145</v>
+      </c>
+      <c r="G96" t="s">
+        <v>323</v>
+      </c>
+      <c r="H96" t="s">
         <v>146</v>
-      </c>
-      <c r="G96" t="s">
-        <v>324</v>
-      </c>
-      <c r="H96" t="s">
-        <v>147</v>
       </c>
       <c r="I96">
         <v>3</v>
       </c>
       <c r="J96" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K96" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B97" t="s">
+        <v>135</v>
+      </c>
+      <c r="C97" t="s">
         <v>136</v>
       </c>
-      <c r="C97" t="s">
-        <v>137</v>
-      </c>
       <c r="D97">
         <v>114</v>
       </c>
       <c r="E97" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F97" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G97" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H97" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I97">
         <v>3</v>
       </c>
       <c r="J97" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K97" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B98" t="s">
+        <v>135</v>
+      </c>
+      <c r="C98" t="s">
         <v>136</v>
       </c>
-      <c r="C98" t="s">
-        <v>137</v>
-      </c>
       <c r="D98">
         <v>114</v>
       </c>
       <c r="E98" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F98" t="s">
+        <v>149</v>
+      </c>
+      <c r="G98" t="s">
+        <v>325</v>
+      </c>
+      <c r="H98" t="s">
         <v>150</v>
-      </c>
-      <c r="G98" t="s">
-        <v>326</v>
-      </c>
-      <c r="H98" t="s">
-        <v>151</v>
       </c>
       <c r="I98">
         <v>2</v>
       </c>
       <c r="J98" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K98" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B99" t="s">
+        <v>135</v>
+      </c>
+      <c r="C99" t="s">
         <v>136</v>
       </c>
-      <c r="C99" t="s">
-        <v>137</v>
-      </c>
       <c r="D99">
         <v>114</v>
       </c>
       <c r="E99" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F99" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G99" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H99" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I99">
         <v>2</v>
       </c>
       <c r="J99" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K99" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B100" t="s">
+        <v>135</v>
+      </c>
+      <c r="C100" t="s">
         <v>136</v>
       </c>
-      <c r="C100" t="s">
-        <v>137</v>
-      </c>
       <c r="D100">
         <v>114</v>
       </c>
       <c r="E100" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F100" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G100" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H100" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I100">
         <v>3</v>
       </c>
       <c r="J100" t="s">
+        <v>153</v>
+      </c>
+      <c r="K100" t="s">
         <v>154</v>
-      </c>
-      <c r="K100" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B101" t="s">
+        <v>135</v>
+      </c>
+      <c r="C101" t="s">
         <v>136</v>
       </c>
-      <c r="C101" t="s">
-        <v>137</v>
-      </c>
       <c r="D101">
         <v>114</v>
       </c>
       <c r="E101" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F101" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G101" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H101" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I101">
         <v>2</v>
       </c>
       <c r="J101" t="s">
+        <v>156</v>
+      </c>
+      <c r="K101" t="s">
         <v>157</v>
-      </c>
-      <c r="K101" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B102" t="s">
+        <v>135</v>
+      </c>
+      <c r="C102" t="s">
         <v>136</v>
       </c>
-      <c r="C102" t="s">
-        <v>137</v>
-      </c>
       <c r="D102">
         <v>114</v>
       </c>
       <c r="E102" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F102" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G102" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H102" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I102">
         <v>2</v>
       </c>
       <c r="J102" t="s">
+        <v>159</v>
+      </c>
+      <c r="K102" t="s">
         <v>160</v>
-      </c>
-      <c r="K102" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B103" t="s">
+        <v>135</v>
+      </c>
+      <c r="C103" t="s">
         <v>136</v>
       </c>
-      <c r="C103" t="s">
-        <v>137</v>
-      </c>
       <c r="D103">
         <v>114</v>
       </c>
       <c r="E103" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F103" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G103" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H103" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I103">
         <v>3</v>
       </c>
       <c r="J103" t="s">
+        <v>162</v>
+      </c>
+      <c r="K103" t="s">
         <v>163</v>
-      </c>
-      <c r="K103" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B104" t="s">
+        <v>135</v>
+      </c>
+      <c r="C104" t="s">
         <v>136</v>
       </c>
-      <c r="C104" t="s">
-        <v>137</v>
-      </c>
       <c r="D104">
         <v>114</v>
       </c>
       <c r="E104" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F104" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G104" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H104" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I104">
         <v>3</v>
       </c>
       <c r="J104" t="s">
+        <v>165</v>
+      </c>
+      <c r="K104" t="s">
         <v>166</v>
-      </c>
-      <c r="K104" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B105" t="s">
+        <v>135</v>
+      </c>
+      <c r="C105" t="s">
         <v>136</v>
       </c>
-      <c r="C105" t="s">
-        <v>137</v>
-      </c>
       <c r="D105">
         <v>114</v>
       </c>
       <c r="E105" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F105" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G105" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H105" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I105">
         <v>3</v>
       </c>
       <c r="J105" t="s">
+        <v>168</v>
+      </c>
+      <c r="K105" t="s">
         <v>169</v>
-      </c>
-      <c r="K105" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B106" t="s">
+        <v>135</v>
+      </c>
+      <c r="C106" t="s">
         <v>136</v>
       </c>
-      <c r="C106" t="s">
-        <v>137</v>
-      </c>
       <c r="D106">
         <v>114</v>
       </c>
       <c r="E106" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F106" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G106" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H106" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I106">
         <v>3</v>
       </c>
       <c r="J106" t="s">
+        <v>171</v>
+      </c>
+      <c r="K106" t="s">
         <v>172</v>
-      </c>
-      <c r="K106" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B107" t="s">
+        <v>135</v>
+      </c>
+      <c r="C107" t="s">
         <v>136</v>
       </c>
-      <c r="C107" t="s">
-        <v>137</v>
-      </c>
       <c r="D107">
         <v>114</v>
       </c>
       <c r="E107" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F107" t="s">
+        <v>173</v>
+      </c>
+      <c r="G107" t="s">
+        <v>334</v>
+      </c>
+      <c r="H107" t="s">
         <v>174</v>
-      </c>
-      <c r="G107" t="s">
-        <v>335</v>
-      </c>
-      <c r="H107" t="s">
-        <v>175</v>
       </c>
       <c r="I107">
         <v>3</v>
       </c>
       <c r="J107" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K107" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>175</v>
+      </c>
+      <c r="B108" t="s">
         <v>176</v>
       </c>
-      <c r="B108" t="s">
+      <c r="C108" t="s">
         <v>177</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108">
+        <v>114</v>
+      </c>
+      <c r="E108" t="s">
         <v>178</v>
       </c>
-      <c r="D108">
-        <v>114</v>
-      </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
         <v>179</v>
       </c>
-      <c r="F108" t="s">
+      <c r="G108" t="s">
+        <v>335</v>
+      </c>
+      <c r="H108" t="s">
         <v>180</v>
-      </c>
-      <c r="G108" t="s">
-        <v>336</v>
-      </c>
-      <c r="H108" t="s">
-        <v>181</v>
       </c>
       <c r="I108">
         <v>2</v>
       </c>
       <c r="K108" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>175</v>
+      </c>
+      <c r="B109" t="s">
         <v>176</v>
       </c>
-      <c r="B109" t="s">
+      <c r="C109" t="s">
         <v>177</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109">
+        <v>114</v>
+      </c>
+      <c r="E109" t="s">
         <v>178</v>
       </c>
-      <c r="D109">
-        <v>114</v>
-      </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
         <v>179</v>
       </c>
-      <c r="F109" t="s">
-        <v>180</v>
-      </c>
       <c r="G109" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H109" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I109">
         <v>2</v>
       </c>
       <c r="K109" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>175</v>
+      </c>
+      <c r="B110" t="s">
         <v>176</v>
       </c>
-      <c r="B110" t="s">
+      <c r="C110" t="s">
         <v>177</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110">
+        <v>114</v>
+      </c>
+      <c r="E110" t="s">
         <v>178</v>
       </c>
-      <c r="D110">
-        <v>114</v>
-      </c>
-      <c r="E110" t="s">
-        <v>179</v>
-      </c>
       <c r="F110" t="s">
+        <v>183</v>
+      </c>
+      <c r="G110" t="s">
+        <v>337</v>
+      </c>
+      <c r="H110" t="s">
         <v>184</v>
-      </c>
-      <c r="G110" t="s">
-        <v>338</v>
-      </c>
-      <c r="H110" t="s">
-        <v>185</v>
       </c>
       <c r="I110">
         <v>2</v>
       </c>
       <c r="K110" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>175</v>
+      </c>
+      <c r="B111" t="s">
         <v>176</v>
       </c>
-      <c r="B111" t="s">
+      <c r="C111" t="s">
         <v>177</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111">
+        <v>114</v>
+      </c>
+      <c r="E111" t="s">
         <v>178</v>
       </c>
-      <c r="D111">
-        <v>114</v>
-      </c>
-      <c r="E111" t="s">
-        <v>179</v>
-      </c>
       <c r="F111" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G111" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H111" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I111">
         <v>2</v>
       </c>
       <c r="K111" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>175</v>
+      </c>
+      <c r="B112" t="s">
         <v>176</v>
       </c>
-      <c r="B112" t="s">
+      <c r="C112" t="s">
         <v>177</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112">
+        <v>114</v>
+      </c>
+      <c r="E112" t="s">
         <v>178</v>
       </c>
-      <c r="D112">
-        <v>114</v>
-      </c>
-      <c r="E112" t="s">
-        <v>179</v>
-      </c>
       <c r="F112" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G112" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H112" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I112">
         <v>2</v>
       </c>
       <c r="K112" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>175</v>
+      </c>
+      <c r="B113" t="s">
         <v>176</v>
       </c>
-      <c r="B113" t="s">
+      <c r="C113" t="s">
         <v>177</v>
       </c>
-      <c r="C113" t="s">
+      <c r="D113">
+        <v>114</v>
+      </c>
+      <c r="E113" t="s">
         <v>178</v>
       </c>
-      <c r="D113">
-        <v>114</v>
-      </c>
-      <c r="E113" t="s">
-        <v>179</v>
-      </c>
       <c r="F113" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G113" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H113" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I113">
         <v>2</v>
       </c>
       <c r="K113" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>175</v>
+      </c>
+      <c r="B114" t="s">
         <v>176</v>
       </c>
-      <c r="B114" t="s">
+      <c r="C114" t="s">
         <v>177</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114">
+        <v>114</v>
+      </c>
+      <c r="E114" t="s">
         <v>178</v>
       </c>
-      <c r="D114">
-        <v>114</v>
-      </c>
-      <c r="E114" t="s">
-        <v>179</v>
-      </c>
       <c r="F114" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G114" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H114" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I114">
         <v>2</v>
       </c>
       <c r="K114" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>175</v>
+      </c>
+      <c r="B115" t="s">
         <v>176</v>
       </c>
-      <c r="B115" t="s">
+      <c r="C115" t="s">
         <v>177</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115">
+        <v>114</v>
+      </c>
+      <c r="E115" t="s">
         <v>178</v>
       </c>
-      <c r="D115">
-        <v>114</v>
-      </c>
-      <c r="E115" t="s">
-        <v>179</v>
-      </c>
       <c r="F115" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G115" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H115" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I115">
         <v>2</v>
       </c>
       <c r="K115" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>175</v>
+      </c>
+      <c r="B116" t="s">
         <v>176</v>
       </c>
-      <c r="B116" t="s">
+      <c r="C116" t="s">
         <v>177</v>
       </c>
-      <c r="C116" t="s">
+      <c r="D116">
+        <v>114</v>
+      </c>
+      <c r="E116" t="s">
         <v>178</v>
       </c>
-      <c r="D116">
-        <v>114</v>
-      </c>
-      <c r="E116" t="s">
-        <v>179</v>
-      </c>
       <c r="F116" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G116" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H116" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I116">
         <v>4</v>
       </c>
       <c r="J116" t="s">
+        <v>192</v>
+      </c>
+      <c r="K116" t="s">
         <v>193</v>
-      </c>
-      <c r="K116" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>175</v>
+      </c>
+      <c r="B117" t="s">
         <v>176</v>
       </c>
-      <c r="B117" t="s">
+      <c r="C117" t="s">
         <v>177</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117">
+        <v>114</v>
+      </c>
+      <c r="E117" t="s">
         <v>178</v>
       </c>
-      <c r="D117">
-        <v>114</v>
-      </c>
-      <c r="E117" t="s">
-        <v>179</v>
-      </c>
       <c r="F117" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G117" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H117" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I117">
         <v>4</v>
       </c>
       <c r="J117" t="s">
+        <v>192</v>
+      </c>
+      <c r="K117" t="s">
         <v>193</v>
-      </c>
-      <c r="K117" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>175</v>
+      </c>
+      <c r="B118" t="s">
         <v>176</v>
       </c>
-      <c r="B118" t="s">
+      <c r="C118" t="s">
         <v>177</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118">
+        <v>114</v>
+      </c>
+      <c r="E118" t="s">
         <v>178</v>
       </c>
-      <c r="D118">
-        <v>114</v>
-      </c>
-      <c r="E118" t="s">
-        <v>179</v>
-      </c>
       <c r="F118" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G118" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H118" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I118">
         <v>3</v>
       </c>
       <c r="K118" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>175</v>
+      </c>
+      <c r="B119" t="s">
         <v>176</v>
       </c>
-      <c r="B119" t="s">
+      <c r="C119" t="s">
         <v>177</v>
       </c>
-      <c r="C119" t="s">
+      <c r="D119">
+        <v>114</v>
+      </c>
+      <c r="E119" t="s">
         <v>178</v>
       </c>
-      <c r="D119">
-        <v>114</v>
-      </c>
-      <c r="E119" t="s">
-        <v>179</v>
-      </c>
       <c r="F119" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G119" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H119" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I119">
         <v>2</v>
       </c>
       <c r="K119" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>175</v>
+      </c>
+      <c r="B120" t="s">
         <v>176</v>
       </c>
-      <c r="B120" t="s">
+      <c r="C120" t="s">
         <v>177</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120">
+        <v>114</v>
+      </c>
+      <c r="E120" t="s">
         <v>178</v>
       </c>
-      <c r="D120">
-        <v>114</v>
-      </c>
-      <c r="E120" t="s">
-        <v>179</v>
-      </c>
       <c r="F120" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G120" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H120" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I120">
         <v>3</v>
       </c>
       <c r="J120" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K120" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>175</v>
+      </c>
+      <c r="B121" t="s">
         <v>176</v>
       </c>
-      <c r="B121" t="s">
+      <c r="C121" t="s">
         <v>177</v>
       </c>
-      <c r="C121" t="s">
+      <c r="D121">
+        <v>114</v>
+      </c>
+      <c r="E121" t="s">
         <v>178</v>
       </c>
-      <c r="D121">
-        <v>114</v>
-      </c>
-      <c r="E121" t="s">
-        <v>179</v>
-      </c>
       <c r="F121" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G121" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H121" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I121">
         <v>2</v>
       </c>
       <c r="K121" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>175</v>
+      </c>
+      <c r="B122" t="s">
         <v>176</v>
       </c>
-      <c r="B122" t="s">
+      <c r="C122" t="s">
         <v>177</v>
       </c>
-      <c r="C122" t="s">
+      <c r="D122">
+        <v>114</v>
+      </c>
+      <c r="E122" t="s">
         <v>178</v>
       </c>
-      <c r="D122">
-        <v>114</v>
-      </c>
-      <c r="E122" t="s">
-        <v>179</v>
-      </c>
       <c r="F122" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G122" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H122" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I122">
         <v>2</v>
       </c>
       <c r="K122" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>175</v>
+      </c>
+      <c r="B123" t="s">
         <v>176</v>
       </c>
-      <c r="B123" t="s">
+      <c r="C123" t="s">
         <v>177</v>
       </c>
-      <c r="C123" t="s">
+      <c r="D123">
+        <v>114</v>
+      </c>
+      <c r="E123" t="s">
         <v>178</v>
       </c>
-      <c r="D123">
-        <v>114</v>
-      </c>
-      <c r="E123" t="s">
-        <v>179</v>
-      </c>
       <c r="F123" t="s">
+        <v>203</v>
+      </c>
+      <c r="G123" t="s">
+        <v>350</v>
+      </c>
+      <c r="H123" t="s">
         <v>204</v>
-      </c>
-      <c r="G123" t="s">
-        <v>351</v>
-      </c>
-      <c r="H123" t="s">
-        <v>205</v>
       </c>
       <c r="I123">
         <v>2</v>
       </c>
       <c r="K123" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>175</v>
+      </c>
+      <c r="B124" t="s">
         <v>176</v>
       </c>
-      <c r="B124" t="s">
+      <c r="C124" t="s">
         <v>177</v>
       </c>
-      <c r="C124" t="s">
+      <c r="D124">
+        <v>114</v>
+      </c>
+      <c r="E124" t="s">
         <v>178</v>
       </c>
-      <c r="D124">
-        <v>114</v>
-      </c>
-      <c r="E124" t="s">
-        <v>179</v>
-      </c>
       <c r="F124" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G124" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H124" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I124">
         <v>2</v>
       </c>
       <c r="K124" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>175</v>
+      </c>
+      <c r="B125" t="s">
         <v>176</v>
       </c>
-      <c r="B125" t="s">
+      <c r="C125" t="s">
         <v>177</v>
       </c>
-      <c r="C125" t="s">
+      <c r="D125">
+        <v>114</v>
+      </c>
+      <c r="E125" t="s">
         <v>178</v>
       </c>
-      <c r="D125">
-        <v>114</v>
-      </c>
-      <c r="E125" t="s">
-        <v>179</v>
-      </c>
       <c r="F125" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G125" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H125" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I125">
         <v>2</v>
       </c>
       <c r="K125" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>175</v>
+      </c>
+      <c r="B126" t="s">
         <v>176</v>
       </c>
-      <c r="B126" t="s">
+      <c r="C126" t="s">
         <v>177</v>
       </c>
-      <c r="C126" t="s">
+      <c r="D126">
+        <v>114</v>
+      </c>
+      <c r="E126" t="s">
         <v>178</v>
       </c>
-      <c r="D126">
-        <v>114</v>
-      </c>
-      <c r="E126" t="s">
-        <v>179</v>
-      </c>
       <c r="F126" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G126" t="e">
         <v>#N/A</v>
       </c>
       <c r="H126" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I126">
         <v>2</v>
       </c>
       <c r="J126" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K126" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>175</v>
+      </c>
+      <c r="B127" t="s">
         <v>176</v>
       </c>
-      <c r="B127" t="s">
+      <c r="C127" t="s">
         <v>177</v>
       </c>
-      <c r="C127" t="s">
+      <c r="D127">
+        <v>114</v>
+      </c>
+      <c r="E127" t="s">
         <v>178</v>
       </c>
-      <c r="D127">
-        <v>114</v>
-      </c>
-      <c r="E127" t="s">
-        <v>179</v>
-      </c>
       <c r="F127" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G127" t="e">
         <v>#N/A</v>
       </c>
       <c r="H127" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I127">
         <v>2</v>
       </c>
       <c r="J127" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K127" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>175</v>
+      </c>
+      <c r="B128" t="s">
         <v>176</v>
       </c>
-      <c r="B128" t="s">
+      <c r="C128" t="s">
         <v>177</v>
       </c>
-      <c r="C128" t="s">
+      <c r="D128">
+        <v>114</v>
+      </c>
+      <c r="E128" t="s">
         <v>178</v>
       </c>
-      <c r="D128">
-        <v>114</v>
-      </c>
-      <c r="E128" t="s">
-        <v>179</v>
-      </c>
       <c r="F128" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G128" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H128" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I128">
         <v>2</v>
       </c>
       <c r="K128" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>175</v>
+      </c>
+      <c r="B129" t="s">
         <v>176</v>
       </c>
-      <c r="B129" t="s">
+      <c r="C129" t="s">
         <v>177</v>
       </c>
-      <c r="C129" t="s">
+      <c r="D129">
+        <v>114</v>
+      </c>
+      <c r="E129" t="s">
         <v>178</v>
       </c>
-      <c r="D129">
-        <v>114</v>
-      </c>
-      <c r="E129" t="s">
-        <v>179</v>
-      </c>
       <c r="F129" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G129" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H129" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I129">
         <v>2</v>
       </c>
       <c r="K129" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>175</v>
+      </c>
+      <c r="B130" t="s">
         <v>176</v>
       </c>
-      <c r="B130" t="s">
+      <c r="C130" t="s">
         <v>177</v>
       </c>
-      <c r="C130" t="s">
+      <c r="D130">
+        <v>114</v>
+      </c>
+      <c r="E130" t="s">
         <v>178</v>
       </c>
-      <c r="D130">
-        <v>114</v>
-      </c>
-      <c r="E130" t="s">
-        <v>179</v>
-      </c>
       <c r="F130" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G130" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H130" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I130">
         <v>3</v>
       </c>
       <c r="K130" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>175</v>
+      </c>
+      <c r="B131" t="s">
         <v>176</v>
       </c>
-      <c r="B131" t="s">
+      <c r="C131" t="s">
         <v>177</v>
       </c>
-      <c r="C131" t="s">
+      <c r="D131">
+        <v>114</v>
+      </c>
+      <c r="E131" t="s">
         <v>178</v>
       </c>
-      <c r="D131">
-        <v>114</v>
-      </c>
-      <c r="E131" t="s">
-        <v>179</v>
-      </c>
       <c r="F131" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G131" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H131" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I131">
         <v>2</v>
       </c>
       <c r="K131" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>175</v>
+      </c>
+      <c r="B132" t="s">
         <v>176</v>
       </c>
-      <c r="B132" t="s">
+      <c r="C132" t="s">
         <v>177</v>
       </c>
-      <c r="C132" t="s">
+      <c r="D132">
+        <v>114</v>
+      </c>
+      <c r="E132" t="s">
         <v>178</v>
       </c>
-      <c r="D132">
-        <v>114</v>
-      </c>
-      <c r="E132" t="s">
-        <v>179</v>
-      </c>
       <c r="F132" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G132" t="e">
         <v>#N/A</v>
       </c>
       <c r="H132" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I132">
         <v>2</v>
       </c>
       <c r="J132" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K132" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>175</v>
+      </c>
+      <c r="B133" t="s">
         <v>176</v>
       </c>
-      <c r="B133" t="s">
+      <c r="C133" t="s">
         <v>177</v>
       </c>
-      <c r="C133" t="s">
+      <c r="D133">
+        <v>114</v>
+      </c>
+      <c r="E133" t="s">
         <v>178</v>
       </c>
-      <c r="D133">
-        <v>114</v>
-      </c>
-      <c r="E133" t="s">
-        <v>179</v>
-      </c>
       <c r="F133" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G133" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H133" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I133">
         <v>2</v>
       </c>
       <c r="K133" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>175</v>
+      </c>
+      <c r="B134" t="s">
         <v>176</v>
       </c>
-      <c r="B134" t="s">
+      <c r="C134" t="s">
         <v>177</v>
       </c>
-      <c r="C134" t="s">
+      <c r="D134">
+        <v>114</v>
+      </c>
+      <c r="E134" t="s">
         <v>178</v>
       </c>
-      <c r="D134">
-        <v>114</v>
-      </c>
-      <c r="E134" t="s">
-        <v>179</v>
-      </c>
       <c r="F134" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G134" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H134" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I134">
         <v>2</v>
       </c>
       <c r="K134" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>175</v>
+      </c>
+      <c r="B135" t="s">
         <v>176</v>
       </c>
-      <c r="B135" t="s">
+      <c r="C135" t="s">
         <v>177</v>
       </c>
-      <c r="C135" t="s">
+      <c r="D135">
+        <v>114</v>
+      </c>
+      <c r="E135" t="s">
         <v>178</v>
       </c>
-      <c r="D135">
-        <v>114</v>
-      </c>
-      <c r="E135" t="s">
-        <v>179</v>
-      </c>
       <c r="F135" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G135" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H135" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I135">
         <v>2</v>
       </c>
       <c r="K135" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -6302,24 +6301,24 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E1" t="s">
         <v>223</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>224</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>225</v>
-      </c>
-      <c r="G1" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
       </c>
       <c r="C2">
         <v>114</v>
@@ -6334,15 +6333,15 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" t="s">
         <v>84</v>
-      </c>
-      <c r="B3" t="s">
-        <v>85</v>
       </c>
       <c r="C3">
         <v>114</v>
@@ -6357,15 +6356,15 @@
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" t="s">
         <v>136</v>
-      </c>
-      <c r="B4" t="s">
-        <v>137</v>
       </c>
       <c r="C4">
         <v>114</v>
@@ -6380,15 +6379,15 @@
         <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>176</v>
+      </c>
+      <c r="B5" t="s">
         <v>177</v>
-      </c>
-      <c r="B5" t="s">
-        <v>178</v>
       </c>
       <c r="C5">
         <v>114</v>
@@ -6403,7 +6402,7 @@
         <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>

--- a/master_data.xlsx
+++ b/master_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\000_專案計畫\20260107_學分學程查詢功能\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB3F154-E060-4209-906C-7876847E4CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4284CA15-44B5-4176-95C4-9D3923172B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BF35B52C-D03C-44DF-89E9-E0C2470A9351}"/>
+    <workbookView xWindow="345" yWindow="690" windowWidth="21165" windowHeight="11295" xr2:uid="{BF35B52C-D03C-44DF-89E9-E0C2470A9351}"/>
   </bookViews>
   <sheets>
     <sheet name="科目表" sheetId="1" r:id="rId1"/>
@@ -1188,7 +1188,8 @@
     <t>18843</t>
   </si>
   <si>
-    <t>課程認抵範圍</t>
+    <t>認抵單位代碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>

--- a/master_data.xlsx
+++ b/master_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\000_專案計畫\20260107_學分學程查詢功能\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4284CA15-44B5-4176-95C4-9D3923172B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E81F087E-FD19-4F0C-A78F-48DDD7943D38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="690" windowWidth="21165" windowHeight="11295" xr2:uid="{BF35B52C-D03C-44DF-89E9-E0C2470A9351}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BBEB6681-899A-4DDD-9172-823D6DCCA8ED}"/>
   </bookViews>
   <sheets>
     <sheet name="科目表" sheetId="1" r:id="rId1"/>
@@ -43,10 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1218" uniqueCount="361">
-  <si>
-    <t>學院</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="457">
   <si>
     <t>學程代碼</t>
   </si>
@@ -73,6 +70,10 @@
     <t>學分數</t>
   </si>
   <si>
+    <t>認抵單位代碼</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>備註</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -472,54 +473,57 @@
     <t>舞蹈治療實務</t>
   </si>
   <si>
+    <t>創新跨領域學院</t>
+  </si>
+  <si>
+    <t>K860</t>
+  </si>
+  <si>
+    <t>教育大數據微學程</t>
+  </si>
+  <si>
+    <t>基礎(至少2學分)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>程式設計概論</t>
+  </si>
+  <si>
+    <t>D65,D74,D0F,D0E,D76</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>經濟系、資管系、金企系、企管系、統資系</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>計算機概論</t>
+  </si>
+  <si>
+    <t>程式設計</t>
+  </si>
+  <si>
+    <t>D55,D56</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>物理系</t>
+  </si>
+  <si>
+    <t>重點(至少6學分)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>機器學習</t>
+  </si>
+  <si>
+    <t>DTG,GTG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>跨領域學院</t>
   </si>
   <si>
-    <t>K860</t>
-  </si>
-  <si>
-    <t>教育大數據微學程</t>
-  </si>
-  <si>
-    <t>基礎(至少2學分)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>程式設計概論</t>
-  </si>
-  <si>
-    <t>D65,D74,D0F,D0E,D76</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>經濟系、資管系、金企系、企管系、統資系</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>計算機概論</t>
-  </si>
-  <si>
-    <t>程式設計</t>
-  </si>
-  <si>
-    <t>D55,D56</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>物理系</t>
-  </si>
-  <si>
-    <t>重點(至少6學分)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>機器學習</t>
-  </si>
-  <si>
-    <t>DTG,GTG</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>資料探索及資訊視覺化</t>
   </si>
   <si>
@@ -614,9 +618,6 @@
     <t>教育大數據專題</t>
   </si>
   <si>
-    <t>創新跨領域學院</t>
-  </si>
-  <si>
     <t>K890</t>
   </si>
   <si>
@@ -639,6 +640,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>DDT</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>全人教育課程中心</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -650,6 +655,10 @@
     <t>地方想像</t>
   </si>
   <si>
+    <t>D1N</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>社創學程</t>
   </si>
   <si>
@@ -668,11 +677,15 @@
     <t>新莊文化景觀之保存與活化</t>
   </si>
   <si>
+    <t>跨領域學院</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>景觀設計（一）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>多了空格</t>
+    <t>D82</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -689,6 +702,10 @@
     <t>英語教學與跨文化溝通服務學習</t>
   </si>
   <si>
+    <t>D20</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>英文系</t>
   </si>
   <si>
@@ -696,16 +713,16 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>冒號小寫</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>英語教學與教育心理</t>
   </si>
   <si>
     <t>文化產業經營與管理</t>
   </si>
   <si>
+    <t>C0J</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>藝術與文化創意學士學位學程</t>
   </si>
   <si>
@@ -722,21 +739,18 @@
     <t>文化資產與歷史素養</t>
   </si>
   <si>
-    <t>歷史系/文服學程系</t>
+    <t>D02,C1D</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>歷史系、文服學程系</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>景觀英文</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>沒這科目</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>自主學習學分：數位人文創新行動計畫</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>自主學習-數位人文創新行動計畫</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -756,13 +770,13 @@
     <t>跨文化翻轉教學法</t>
   </si>
   <si>
-    <t>跨文化外語翻轉教學法??</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>畢業製作</t>
   </si>
   <si>
+    <t>C20</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>進修部英文系</t>
   </si>
   <si>
@@ -770,6 +784,201 @@
   </si>
   <si>
     <t>創意商品設計</t>
+  </si>
+  <si>
+    <t>K320</t>
+  </si>
+  <si>
+    <t>應用史學學分學程</t>
+  </si>
+  <si>
+    <t>必修(4)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>史學導論</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>歷史學系</t>
+  </si>
+  <si>
+    <t>共同必修(4)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>臺灣博物館史</t>
+  </si>
+  <si>
+    <t>影視史學</t>
+  </si>
+  <si>
+    <t>歷史與文創產業</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>史料數位化</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>歷史知識與時事評論</t>
+  </si>
+  <si>
+    <t>中國飲食文化史</t>
+  </si>
+  <si>
+    <t>臺灣飲食文化史</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>歷史普及實作</t>
+  </si>
+  <si>
+    <t>禮俗生活與歷史</t>
+  </si>
+  <si>
+    <t>選修(12)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>歐洲飲食文化史</t>
+  </si>
+  <si>
+    <t>C02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>歷史學系（進）</t>
+  </si>
+  <si>
+    <t>臺灣節慶祭典與歷史民俗</t>
+  </si>
+  <si>
+    <t>阿祖的日常生活：臺灣庶民生活史</t>
+  </si>
+  <si>
+    <t>摩登年代：臺灣庶民文化史</t>
+  </si>
+  <si>
+    <t>古蹟導覽與文化旅遊</t>
+  </si>
+  <si>
+    <t>口述歷史</t>
+  </si>
+  <si>
+    <t>旅行的文化與歷史</t>
+  </si>
+  <si>
+    <t>書寫文化與歷史</t>
+  </si>
+  <si>
+    <t>現代小說與習作</t>
+  </si>
+  <si>
+    <t>中國文學系</t>
+  </si>
+  <si>
+    <t>編輯與採訪</t>
+  </si>
+  <si>
+    <t>編纂實務</t>
+  </si>
+  <si>
+    <t>報導文學</t>
+  </si>
+  <si>
+    <t>採編寫作與出版實務</t>
+  </si>
+  <si>
+    <t>C01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中國文學系（進）</t>
+  </si>
+  <si>
+    <t>社會哲學</t>
+  </si>
+  <si>
+    <t>環境倫理學</t>
+  </si>
+  <si>
+    <t>中國建築與室內設計史</t>
+  </si>
+  <si>
+    <t>D81,G816</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>應用美術系所</t>
+  </si>
+  <si>
+    <t>西洋藝術史</t>
+  </si>
+  <si>
+    <t>D82,G826</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>景觀設計系所</t>
+  </si>
+  <si>
+    <t>中國園林藝術</t>
+  </si>
+  <si>
+    <t>電腦排版與設計</t>
+  </si>
+  <si>
+    <t>D12</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新聞傳播學系</t>
+  </si>
+  <si>
+    <t>G106</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>圖資所</t>
+  </si>
+  <si>
+    <t>公共圖書館</t>
+  </si>
+  <si>
+    <t>檔案管理</t>
+  </si>
+  <si>
+    <t>古籍保存與維護</t>
+  </si>
+  <si>
+    <t>博物館與文化政策</t>
+  </si>
+  <si>
+    <t>G156</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>博物館學研究所</t>
+  </si>
+  <si>
+    <t>博物館與文化資產</t>
+  </si>
+  <si>
+    <t>宗教與文化旅遊</t>
+  </si>
+  <si>
+    <t>D90</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>宗教學系</t>
+  </si>
+  <si>
+    <t>心理傳記與文化創新</t>
+  </si>
+  <si>
+    <t>心理學系</t>
   </si>
   <si>
     <t>必修總學分</t>
@@ -798,6 +1007,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>本學程應修學分數 20 學分。包括必修(4 學分)、共同必修(4 學分)、選修(12 學分)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>17624</t>
   </si>
   <si>
@@ -1167,6 +1380,9 @@
     <t>35161</t>
   </si>
   <si>
+    <t>35738</t>
+  </si>
+  <si>
     <t>03876</t>
   </si>
   <si>
@@ -1188,7 +1404,100 @@
     <t>18843</t>
   </si>
   <si>
-    <t>認抵單位代碼</t>
+    <t>01301</t>
+  </si>
+  <si>
+    <t>15917</t>
+  </si>
+  <si>
+    <t>22182</t>
+  </si>
+  <si>
+    <t>16776</t>
+  </si>
+  <si>
+    <t>24344</t>
+  </si>
+  <si>
+    <t>22934</t>
+  </si>
+  <si>
+    <t>22474</t>
+  </si>
+  <si>
+    <t>30363</t>
+  </si>
+  <si>
+    <t>30365</t>
+  </si>
+  <si>
+    <t>30366</t>
+  </si>
+  <si>
+    <t>24671</t>
+  </si>
+  <si>
+    <t>12459</t>
+  </si>
+  <si>
+    <t>30368</t>
+  </si>
+  <si>
+    <t>02190</t>
+  </si>
+  <si>
+    <t>02764</t>
+  </si>
+  <si>
+    <t>22426</t>
+  </si>
+  <si>
+    <t>04521</t>
+  </si>
+  <si>
+    <t>16035</t>
+  </si>
+  <si>
+    <t>01718</t>
+  </si>
+  <si>
+    <t>20860</t>
+  </si>
+  <si>
+    <t>16898</t>
+  </si>
+  <si>
+    <t>01527</t>
+  </si>
+  <si>
+    <t>03883</t>
+  </si>
+  <si>
+    <t>04978</t>
+  </si>
+  <si>
+    <t>01159</t>
+  </si>
+  <si>
+    <t>02865</t>
+  </si>
+  <si>
+    <t>24058</t>
+  </si>
+  <si>
+    <t>20389</t>
+  </si>
+  <si>
+    <t>18336</t>
+  </si>
+  <si>
+    <t>20438</t>
+  </si>
+  <si>
+    <t>19375</t>
+  </si>
+  <si>
+    <t>學院</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1583,8 +1892,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5BBB722-6DB7-463D-AC03-0DD96DAA2023}">
-  <dimension ref="A1:L135"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34EB9EDD-E590-48C3-BF14-EA18EBB37F39}">
+  <dimension ref="A1:L177"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.25" customWidth="1"/>
@@ -1602,34 +1911,34 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
       <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>360</v>
       </c>
       <c r="K1" t="s">
         <v>9</v>
@@ -1658,7 +1967,7 @@
         <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>230</v>
+        <v>294</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
@@ -1693,7 +2002,7 @@
         <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>231</v>
+        <v>295</v>
       </c>
       <c r="H3" t="s">
         <v>19</v>
@@ -1728,7 +2037,7 @@
         <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>232</v>
+        <v>296</v>
       </c>
       <c r="H4" t="s">
         <v>24</v>
@@ -1763,7 +2072,7 @@
         <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>233</v>
+        <v>297</v>
       </c>
       <c r="H5" t="s">
         <v>27</v>
@@ -1798,7 +2107,7 @@
         <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>234</v>
+        <v>298</v>
       </c>
       <c r="H6" t="s">
         <v>28</v>
@@ -1833,7 +2142,7 @@
         <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>235</v>
+        <v>299</v>
       </c>
       <c r="H7" t="s">
         <v>29</v>
@@ -1868,7 +2177,7 @@
         <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>236</v>
+        <v>300</v>
       </c>
       <c r="H8" t="s">
         <v>30</v>
@@ -1903,7 +2212,7 @@
         <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>237</v>
+        <v>301</v>
       </c>
       <c r="H9" t="s">
         <v>31</v>
@@ -1938,7 +2247,7 @@
         <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>238</v>
+        <v>302</v>
       </c>
       <c r="H10" t="s">
         <v>32</v>
@@ -1973,7 +2282,7 @@
         <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>239</v>
+        <v>303</v>
       </c>
       <c r="H11" t="s">
         <v>33</v>
@@ -2008,7 +2317,7 @@
         <v>23</v>
       </c>
       <c r="G12" t="s">
-        <v>240</v>
+        <v>304</v>
       </c>
       <c r="H12" t="s">
         <v>34</v>
@@ -2043,7 +2352,7 @@
         <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>241</v>
+        <v>305</v>
       </c>
       <c r="H13" t="s">
         <v>35</v>
@@ -2078,7 +2387,7 @@
         <v>23</v>
       </c>
       <c r="G14" t="s">
-        <v>242</v>
+        <v>306</v>
       </c>
       <c r="H14" t="s">
         <v>36</v>
@@ -2113,7 +2422,7 @@
         <v>23</v>
       </c>
       <c r="G15" t="s">
-        <v>243</v>
+        <v>307</v>
       </c>
       <c r="H15" t="s">
         <v>37</v>
@@ -2148,7 +2457,7 @@
         <v>23</v>
       </c>
       <c r="G16" t="s">
-        <v>244</v>
+        <v>308</v>
       </c>
       <c r="H16" t="s">
         <v>38</v>
@@ -2183,7 +2492,7 @@
         <v>23</v>
       </c>
       <c r="G17" t="s">
-        <v>245</v>
+        <v>309</v>
       </c>
       <c r="H17" t="s">
         <v>39</v>
@@ -2218,7 +2527,7 @@
         <v>23</v>
       </c>
       <c r="G18" t="s">
-        <v>246</v>
+        <v>310</v>
       </c>
       <c r="H18" t="s">
         <v>40</v>
@@ -2253,7 +2562,7 @@
         <v>23</v>
       </c>
       <c r="G19" t="s">
-        <v>247</v>
+        <v>311</v>
       </c>
       <c r="H19" t="s">
         <v>41</v>
@@ -2288,7 +2597,7 @@
         <v>23</v>
       </c>
       <c r="G20" t="s">
-        <v>248</v>
+        <v>312</v>
       </c>
       <c r="H20" t="s">
         <v>42</v>
@@ -2323,7 +2632,7 @@
         <v>23</v>
       </c>
       <c r="G21" t="s">
-        <v>249</v>
+        <v>313</v>
       </c>
       <c r="H21" t="s">
         <v>43</v>
@@ -2358,7 +2667,7 @@
         <v>23</v>
       </c>
       <c r="G22" t="s">
-        <v>250</v>
+        <v>314</v>
       </c>
       <c r="H22" t="s">
         <v>44</v>
@@ -2393,7 +2702,7 @@
         <v>23</v>
       </c>
       <c r="G23" t="s">
-        <v>251</v>
+        <v>315</v>
       </c>
       <c r="H23" t="s">
         <v>45</v>
@@ -2428,7 +2737,7 @@
         <v>23</v>
       </c>
       <c r="G24" t="s">
-        <v>252</v>
+        <v>316</v>
       </c>
       <c r="H24" t="s">
         <v>46</v>
@@ -2463,7 +2772,7 @@
         <v>23</v>
       </c>
       <c r="G25" t="s">
-        <v>253</v>
+        <v>317</v>
       </c>
       <c r="H25" t="s">
         <v>47</v>
@@ -2498,7 +2807,7 @@
         <v>23</v>
       </c>
       <c r="G26" t="s">
-        <v>254</v>
+        <v>318</v>
       </c>
       <c r="H26" t="s">
         <v>48</v>
@@ -2533,7 +2842,7 @@
         <v>23</v>
       </c>
       <c r="G27" t="s">
-        <v>255</v>
+        <v>319</v>
       </c>
       <c r="H27" t="s">
         <v>49</v>
@@ -2568,7 +2877,7 @@
         <v>23</v>
       </c>
       <c r="G28" t="s">
-        <v>256</v>
+        <v>320</v>
       </c>
       <c r="H28" t="s">
         <v>50</v>
@@ -2603,7 +2912,7 @@
         <v>23</v>
       </c>
       <c r="G29" t="s">
-        <v>257</v>
+        <v>321</v>
       </c>
       <c r="H29" t="s">
         <v>51</v>
@@ -2638,7 +2947,7 @@
         <v>23</v>
       </c>
       <c r="G30" t="s">
-        <v>258</v>
+        <v>322</v>
       </c>
       <c r="H30" t="s">
         <v>52</v>
@@ -2673,7 +2982,7 @@
         <v>23</v>
       </c>
       <c r="G31" t="s">
-        <v>259</v>
+        <v>323</v>
       </c>
       <c r="H31" t="s">
         <v>53</v>
@@ -2708,7 +3017,7 @@
         <v>23</v>
       </c>
       <c r="G32" t="s">
-        <v>260</v>
+        <v>324</v>
       </c>
       <c r="H32" t="s">
         <v>54</v>
@@ -2743,7 +3052,7 @@
         <v>23</v>
       </c>
       <c r="G33" t="s">
-        <v>261</v>
+        <v>325</v>
       </c>
       <c r="H33" t="s">
         <v>55</v>
@@ -2778,7 +3087,7 @@
         <v>23</v>
       </c>
       <c r="G34" t="s">
-        <v>262</v>
+        <v>326</v>
       </c>
       <c r="H34" t="s">
         <v>56</v>
@@ -2813,7 +3122,7 @@
         <v>23</v>
       </c>
       <c r="G35" t="s">
-        <v>263</v>
+        <v>327</v>
       </c>
       <c r="H35" t="s">
         <v>57</v>
@@ -2848,7 +3157,7 @@
         <v>23</v>
       </c>
       <c r="G36" t="s">
-        <v>264</v>
+        <v>328</v>
       </c>
       <c r="H36" t="s">
         <v>60</v>
@@ -2883,7 +3192,7 @@
         <v>23</v>
       </c>
       <c r="G37" t="s">
-        <v>265</v>
+        <v>329</v>
       </c>
       <c r="H37" t="s">
         <v>63</v>
@@ -2918,7 +3227,7 @@
         <v>23</v>
       </c>
       <c r="G38" t="s">
-        <v>266</v>
+        <v>330</v>
       </c>
       <c r="H38" t="s">
         <v>64</v>
@@ -2953,7 +3262,7 @@
         <v>23</v>
       </c>
       <c r="G39" t="s">
-        <v>267</v>
+        <v>331</v>
       </c>
       <c r="H39" t="s">
         <v>65</v>
@@ -2988,7 +3297,7 @@
         <v>23</v>
       </c>
       <c r="G40" t="s">
-        <v>268</v>
+        <v>332</v>
       </c>
       <c r="H40" t="s">
         <v>66</v>
@@ -3026,7 +3335,7 @@
         <v>23</v>
       </c>
       <c r="G41" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="H41" t="s">
         <v>68</v>
@@ -3064,7 +3373,7 @@
         <v>23</v>
       </c>
       <c r="G42" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="H42" t="s">
         <v>69</v>
@@ -3099,7 +3408,7 @@
         <v>23</v>
       </c>
       <c r="G43" t="s">
-        <v>271</v>
+        <v>335</v>
       </c>
       <c r="H43" t="s">
         <v>70</v>
@@ -3134,7 +3443,7 @@
         <v>23</v>
       </c>
       <c r="G44" t="s">
-        <v>272</v>
+        <v>336</v>
       </c>
       <c r="H44" t="s">
         <v>71</v>
@@ -3172,7 +3481,7 @@
         <v>23</v>
       </c>
       <c r="G45" t="s">
-        <v>273</v>
+        <v>337</v>
       </c>
       <c r="H45" t="s">
         <v>73</v>
@@ -3210,7 +3519,7 @@
         <v>23</v>
       </c>
       <c r="G46" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="H46" t="s">
         <v>74</v>
@@ -3248,7 +3557,7 @@
         <v>23</v>
       </c>
       <c r="G47" t="s">
-        <v>275</v>
+        <v>339</v>
       </c>
       <c r="H47" t="s">
         <v>76</v>
@@ -3286,7 +3595,7 @@
         <v>23</v>
       </c>
       <c r="G48" t="s">
-        <v>276</v>
+        <v>340</v>
       </c>
       <c r="H48" t="s">
         <v>77</v>
@@ -3321,7 +3630,7 @@
         <v>23</v>
       </c>
       <c r="G49" t="s">
-        <v>277</v>
+        <v>341</v>
       </c>
       <c r="H49" t="s">
         <v>80</v>
@@ -3356,7 +3665,7 @@
         <v>23</v>
       </c>
       <c r="G50" t="s">
-        <v>278</v>
+        <v>342</v>
       </c>
       <c r="H50" t="s">
         <v>81</v>
@@ -3391,7 +3700,7 @@
         <v>23</v>
       </c>
       <c r="G51" t="s">
-        <v>279</v>
+        <v>343</v>
       </c>
       <c r="H51" t="s">
         <v>82</v>
@@ -3426,7 +3735,7 @@
         <v>86</v>
       </c>
       <c r="G52" t="s">
-        <v>280</v>
+        <v>344</v>
       </c>
       <c r="H52" t="s">
         <v>87</v>
@@ -3461,7 +3770,7 @@
         <v>86</v>
       </c>
       <c r="G53" t="s">
-        <v>281</v>
+        <v>345</v>
       </c>
       <c r="H53" t="s">
         <v>88</v>
@@ -3496,7 +3805,7 @@
         <v>86</v>
       </c>
       <c r="G54" t="s">
-        <v>282</v>
+        <v>346</v>
       </c>
       <c r="H54" t="s">
         <v>89</v>
@@ -3531,7 +3840,7 @@
         <v>91</v>
       </c>
       <c r="G55" t="s">
-        <v>283</v>
+        <v>347</v>
       </c>
       <c r="H55" t="s">
         <v>92</v>
@@ -3566,7 +3875,7 @@
         <v>91</v>
       </c>
       <c r="G56" t="s">
-        <v>284</v>
+        <v>348</v>
       </c>
       <c r="H56" t="s">
         <v>93</v>
@@ -3601,7 +3910,7 @@
         <v>91</v>
       </c>
       <c r="G57" t="s">
-        <v>285</v>
+        <v>349</v>
       </c>
       <c r="H57" t="s">
         <v>94</v>
@@ -3636,7 +3945,7 @@
         <v>91</v>
       </c>
       <c r="G58" t="s">
-        <v>286</v>
+        <v>350</v>
       </c>
       <c r="H58" t="s">
         <v>95</v>
@@ -3671,7 +3980,7 @@
         <v>91</v>
       </c>
       <c r="G59" t="s">
-        <v>287</v>
+        <v>351</v>
       </c>
       <c r="H59" t="s">
         <v>96</v>
@@ -3706,7 +4015,7 @@
         <v>91</v>
       </c>
       <c r="G60" t="s">
-        <v>288</v>
+        <v>352</v>
       </c>
       <c r="H60" t="s">
         <v>97</v>
@@ -3741,7 +4050,7 @@
         <v>91</v>
       </c>
       <c r="G61" t="s">
-        <v>289</v>
+        <v>353</v>
       </c>
       <c r="H61" t="s">
         <v>98</v>
@@ -3776,7 +4085,7 @@
         <v>91</v>
       </c>
       <c r="G62" t="s">
-        <v>290</v>
+        <v>354</v>
       </c>
       <c r="H62" t="s">
         <v>99</v>
@@ -3811,7 +4120,7 @@
         <v>91</v>
       </c>
       <c r="G63" t="s">
-        <v>291</v>
+        <v>355</v>
       </c>
       <c r="H63" t="s">
         <v>100</v>
@@ -3846,7 +4155,7 @@
         <v>91</v>
       </c>
       <c r="G64" t="s">
-        <v>292</v>
+        <v>356</v>
       </c>
       <c r="H64" t="s">
         <v>101</v>
@@ -3881,7 +4190,7 @@
         <v>91</v>
       </c>
       <c r="G65" t="s">
-        <v>293</v>
+        <v>357</v>
       </c>
       <c r="H65" t="s">
         <v>102</v>
@@ -3916,7 +4225,7 @@
         <v>91</v>
       </c>
       <c r="G66" t="s">
-        <v>294</v>
+        <v>358</v>
       </c>
       <c r="H66" t="s">
         <v>103</v>
@@ -3951,7 +4260,7 @@
         <v>91</v>
       </c>
       <c r="G67" t="s">
-        <v>295</v>
+        <v>359</v>
       </c>
       <c r="H67" t="s">
         <v>104</v>
@@ -3986,7 +4295,7 @@
         <v>91</v>
       </c>
       <c r="G68" t="s">
-        <v>296</v>
+        <v>360</v>
       </c>
       <c r="H68" t="s">
         <v>105</v>
@@ -4021,7 +4330,7 @@
         <v>91</v>
       </c>
       <c r="G69" t="s">
-        <v>297</v>
+        <v>361</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>106</v>
@@ -4056,7 +4365,7 @@
         <v>91</v>
       </c>
       <c r="G70" t="s">
-        <v>298</v>
+        <v>362</v>
       </c>
       <c r="H70" t="s">
         <v>107</v>
@@ -4091,7 +4400,7 @@
         <v>91</v>
       </c>
       <c r="G71" t="s">
-        <v>299</v>
+        <v>363</v>
       </c>
       <c r="H71" s="1" t="s">
         <v>108</v>
@@ -4126,7 +4435,7 @@
         <v>91</v>
       </c>
       <c r="G72" t="s">
-        <v>269</v>
+        <v>333</v>
       </c>
       <c r="H72" t="s">
         <v>109</v>
@@ -4161,7 +4470,7 @@
         <v>91</v>
       </c>
       <c r="G73" t="s">
-        <v>300</v>
+        <v>364</v>
       </c>
       <c r="H73" t="s">
         <v>110</v>
@@ -4196,7 +4505,7 @@
         <v>91</v>
       </c>
       <c r="G74" t="s">
-        <v>301</v>
+        <v>365</v>
       </c>
       <c r="H74" t="s">
         <v>111</v>
@@ -4231,7 +4540,7 @@
         <v>91</v>
       </c>
       <c r="G75" t="s">
-        <v>302</v>
+        <v>366</v>
       </c>
       <c r="H75" t="s">
         <v>112</v>
@@ -4266,7 +4575,7 @@
         <v>91</v>
       </c>
       <c r="G76" t="s">
-        <v>303</v>
+        <v>367</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>113</v>
@@ -4301,7 +4610,7 @@
         <v>91</v>
       </c>
       <c r="G77" t="s">
-        <v>304</v>
+        <v>368</v>
       </c>
       <c r="H77" t="s">
         <v>116</v>
@@ -4336,7 +4645,7 @@
         <v>91</v>
       </c>
       <c r="G78" t="s">
-        <v>305</v>
+        <v>369</v>
       </c>
       <c r="H78" t="s">
         <v>117</v>
@@ -4371,7 +4680,7 @@
         <v>91</v>
       </c>
       <c r="G79" t="s">
-        <v>306</v>
+        <v>370</v>
       </c>
       <c r="H79" t="s">
         <v>118</v>
@@ -4406,7 +4715,7 @@
         <v>91</v>
       </c>
       <c r="G80" t="s">
-        <v>307</v>
+        <v>371</v>
       </c>
       <c r="H80" t="s">
         <v>119</v>
@@ -4441,7 +4750,7 @@
         <v>91</v>
       </c>
       <c r="G81" t="s">
-        <v>308</v>
+        <v>372</v>
       </c>
       <c r="H81" t="s">
         <v>120</v>
@@ -4476,7 +4785,7 @@
         <v>91</v>
       </c>
       <c r="G82" t="s">
-        <v>309</v>
+        <v>373</v>
       </c>
       <c r="H82" t="s">
         <v>121</v>
@@ -4511,7 +4820,7 @@
         <v>91</v>
       </c>
       <c r="G83" t="s">
-        <v>310</v>
+        <v>374</v>
       </c>
       <c r="H83" t="s">
         <v>122</v>
@@ -4546,7 +4855,7 @@
         <v>91</v>
       </c>
       <c r="G84" t="s">
-        <v>311</v>
+        <v>375</v>
       </c>
       <c r="H84" t="s">
         <v>123</v>
@@ -4581,7 +4890,7 @@
         <v>91</v>
       </c>
       <c r="G85" t="s">
-        <v>312</v>
+        <v>376</v>
       </c>
       <c r="H85" t="s">
         <v>124</v>
@@ -4616,7 +4925,7 @@
         <v>91</v>
       </c>
       <c r="G86" t="s">
-        <v>313</v>
+        <v>377</v>
       </c>
       <c r="H86" t="s">
         <v>125</v>
@@ -4651,7 +4960,7 @@
         <v>91</v>
       </c>
       <c r="G87" t="s">
-        <v>314</v>
+        <v>378</v>
       </c>
       <c r="H87" t="s">
         <v>126</v>
@@ -4686,7 +4995,7 @@
         <v>91</v>
       </c>
       <c r="G88" t="s">
-        <v>315</v>
+        <v>379</v>
       </c>
       <c r="H88" t="s">
         <v>129</v>
@@ -4721,7 +5030,7 @@
         <v>91</v>
       </c>
       <c r="G89" t="s">
-        <v>316</v>
+        <v>380</v>
       </c>
       <c r="H89" t="s">
         <v>130</v>
@@ -4756,7 +5065,7 @@
         <v>91</v>
       </c>
       <c r="G90" t="s">
-        <v>317</v>
+        <v>381</v>
       </c>
       <c r="H90" t="s">
         <v>131</v>
@@ -4791,7 +5100,7 @@
         <v>91</v>
       </c>
       <c r="G91" t="s">
-        <v>318</v>
+        <v>382</v>
       </c>
       <c r="H91" t="s">
         <v>132</v>
@@ -4826,7 +5135,7 @@
         <v>91</v>
       </c>
       <c r="G92" t="s">
-        <v>319</v>
+        <v>383</v>
       </c>
       <c r="H92" t="s">
         <v>133</v>
@@ -4843,7 +5152,7 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B93" t="s">
         <v>135</v>
@@ -4861,7 +5170,7 @@
         <v>137</v>
       </c>
       <c r="G93" t="s">
-        <v>320</v>
+        <v>384</v>
       </c>
       <c r="H93" t="s">
         <v>138</v>
@@ -4878,7 +5187,7 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B94" t="s">
         <v>135</v>
@@ -4896,7 +5205,7 @@
         <v>137</v>
       </c>
       <c r="G94" t="s">
-        <v>321</v>
+        <v>385</v>
       </c>
       <c r="H94" t="s">
         <v>141</v>
@@ -4913,7 +5222,7 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B95" t="s">
         <v>135</v>
@@ -4931,7 +5240,7 @@
         <v>137</v>
       </c>
       <c r="G95" t="s">
-        <v>322</v>
+        <v>386</v>
       </c>
       <c r="H95" t="s">
         <v>142</v>
@@ -4948,7 +5257,7 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B96" t="s">
         <v>135</v>
@@ -4966,7 +5275,7 @@
         <v>145</v>
       </c>
       <c r="G96" t="s">
-        <v>323</v>
+        <v>387</v>
       </c>
       <c r="H96" t="s">
         <v>146</v>
@@ -4978,12 +5287,12 @@
         <v>147</v>
       </c>
       <c r="K96" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B97" t="s">
         <v>135</v>
@@ -5001,10 +5310,10 @@
         <v>145</v>
       </c>
       <c r="G97" t="s">
-        <v>324</v>
+        <v>388</v>
       </c>
       <c r="H97" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I97">
         <v>3</v>
@@ -5013,12 +5322,12 @@
         <v>147</v>
       </c>
       <c r="K97" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B98" t="s">
         <v>135</v>
@@ -5033,13 +5342,13 @@
         <v>22</v>
       </c>
       <c r="F98" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G98" t="s">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="H98" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I98">
         <v>2</v>
@@ -5048,12 +5357,12 @@
         <v>147</v>
       </c>
       <c r="K98" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B99" t="s">
         <v>135</v>
@@ -5068,13 +5377,13 @@
         <v>22</v>
       </c>
       <c r="F99" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G99" t="s">
-        <v>326</v>
+        <v>390</v>
       </c>
       <c r="H99" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I99">
         <v>2</v>
@@ -5083,12 +5392,12 @@
         <v>147</v>
       </c>
       <c r="K99" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B100" t="s">
         <v>135</v>
@@ -5103,27 +5412,27 @@
         <v>22</v>
       </c>
       <c r="F100" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G100" t="s">
-        <v>327</v>
+        <v>391</v>
       </c>
       <c r="H100" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I100">
         <v>3</v>
       </c>
       <c r="J100" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K100" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B101" t="s">
         <v>135</v>
@@ -5138,27 +5447,27 @@
         <v>22</v>
       </c>
       <c r="F101" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G101" t="s">
-        <v>328</v>
+        <v>392</v>
       </c>
       <c r="H101" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I101">
         <v>2</v>
       </c>
       <c r="J101" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K101" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B102" t="s">
         <v>135</v>
@@ -5173,27 +5482,27 @@
         <v>22</v>
       </c>
       <c r="F102" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G102" t="s">
-        <v>329</v>
+        <v>393</v>
       </c>
       <c r="H102" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I102">
         <v>2</v>
       </c>
       <c r="J102" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K102" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B103" t="s">
         <v>135</v>
@@ -5208,27 +5517,27 @@
         <v>22</v>
       </c>
       <c r="F103" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G103" t="s">
-        <v>330</v>
+        <v>394</v>
       </c>
       <c r="H103" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I103">
         <v>3</v>
       </c>
       <c r="J103" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K103" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B104" t="s">
         <v>135</v>
@@ -5243,27 +5552,27 @@
         <v>22</v>
       </c>
       <c r="F104" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G104" t="s">
-        <v>331</v>
+        <v>395</v>
       </c>
       <c r="H104" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I104">
         <v>3</v>
       </c>
       <c r="J104" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K104" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B105" t="s">
         <v>135</v>
@@ -5278,27 +5587,27 @@
         <v>22</v>
       </c>
       <c r="F105" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G105" t="s">
-        <v>332</v>
+        <v>396</v>
       </c>
       <c r="H105" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I105">
         <v>3</v>
       </c>
       <c r="J105" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K105" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B106" t="s">
         <v>135</v>
@@ -5313,27 +5622,27 @@
         <v>22</v>
       </c>
       <c r="F106" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G106" t="s">
-        <v>333</v>
+        <v>397</v>
       </c>
       <c r="H106" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I106">
         <v>3</v>
       </c>
       <c r="J106" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K106" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B107" t="s">
         <v>135</v>
@@ -5348,13 +5657,13 @@
         <v>22</v>
       </c>
       <c r="F107" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G107" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
       <c r="H107" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I107">
         <v>3</v>
@@ -5363,12 +5672,12 @@
         <v>147</v>
       </c>
       <c r="K107" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B108" t="s">
         <v>176</v>
@@ -5386,7 +5695,7 @@
         <v>179</v>
       </c>
       <c r="G108" t="s">
-        <v>335</v>
+        <v>399</v>
       </c>
       <c r="H108" t="s">
         <v>180</v>
@@ -5394,13 +5703,16 @@
       <c r="I108">
         <v>2</v>
       </c>
+      <c r="J108" t="s">
+        <v>147</v>
+      </c>
       <c r="K108" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B109" t="s">
         <v>176</v>
@@ -5418,7 +5730,7 @@
         <v>179</v>
       </c>
       <c r="G109" t="s">
-        <v>336</v>
+        <v>400</v>
       </c>
       <c r="H109" t="s">
         <v>181</v>
@@ -5426,13 +5738,16 @@
       <c r="I109">
         <v>2</v>
       </c>
+      <c r="J109" t="s">
+        <v>182</v>
+      </c>
       <c r="K109" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B110" t="s">
         <v>176</v>
@@ -5447,24 +5762,27 @@
         <v>178</v>
       </c>
       <c r="F110" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G110" t="s">
-        <v>337</v>
+        <v>401</v>
       </c>
       <c r="H110" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I110">
         <v>2</v>
       </c>
+      <c r="J110" t="s">
+        <v>186</v>
+      </c>
       <c r="K110" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B111" t="s">
         <v>176</v>
@@ -5479,16 +5797,19 @@
         <v>178</v>
       </c>
       <c r="F111" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G111" t="s">
-        <v>338</v>
+        <v>402</v>
       </c>
       <c r="H111" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I111">
         <v>2</v>
+      </c>
+      <c r="J111" t="s">
+        <v>78</v>
       </c>
       <c r="K111" t="s">
         <v>79</v>
@@ -5496,7 +5817,7 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B112" t="s">
         <v>176</v>
@@ -5511,16 +5832,19 @@
         <v>178</v>
       </c>
       <c r="F112" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G112" t="s">
-        <v>339</v>
+        <v>403</v>
       </c>
       <c r="H112" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="I112">
         <v>2</v>
+      </c>
+      <c r="J112" t="s">
+        <v>78</v>
       </c>
       <c r="K112" t="s">
         <v>79</v>
@@ -5528,7 +5852,7 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B113" t="s">
         <v>176</v>
@@ -5543,16 +5867,19 @@
         <v>178</v>
       </c>
       <c r="F113" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G113" t="s">
-        <v>340</v>
+        <v>404</v>
       </c>
       <c r="H113" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="I113">
         <v>2</v>
+      </c>
+      <c r="J113" t="s">
+        <v>78</v>
       </c>
       <c r="K113" t="s">
         <v>79</v>
@@ -5560,7 +5887,7 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B114" t="s">
         <v>176</v>
@@ -5575,16 +5902,19 @@
         <v>178</v>
       </c>
       <c r="F114" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G114" t="s">
-        <v>341</v>
+        <v>405</v>
       </c>
       <c r="H114" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I114">
         <v>2</v>
+      </c>
+      <c r="J114" t="s">
+        <v>78</v>
       </c>
       <c r="K114" t="s">
         <v>79</v>
@@ -5592,7 +5922,7 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B115" t="s">
         <v>176</v>
@@ -5607,24 +5937,27 @@
         <v>178</v>
       </c>
       <c r="F115" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G115" t="s">
-        <v>342</v>
+        <v>406</v>
       </c>
       <c r="H115" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I115">
         <v>2</v>
       </c>
+      <c r="J115" t="s">
+        <v>147</v>
+      </c>
       <c r="K115" t="s">
-        <v>134</v>
+        <v>193</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B116" t="s">
         <v>176</v>
@@ -5639,27 +5972,27 @@
         <v>178</v>
       </c>
       <c r="F116" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G116" t="s">
-        <v>343</v>
+        <v>407</v>
       </c>
       <c r="H116" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I116">
         <v>4</v>
       </c>
       <c r="J116" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K116" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B117" t="s">
         <v>176</v>
@@ -5674,27 +6007,27 @@
         <v>178</v>
       </c>
       <c r="F117" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G117" t="s">
-        <v>344</v>
+        <v>408</v>
       </c>
       <c r="H117" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="I117">
         <v>4</v>
       </c>
       <c r="J117" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K117" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B118" t="s">
         <v>176</v>
@@ -5709,24 +6042,27 @@
         <v>178</v>
       </c>
       <c r="F118" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G118" t="s">
-        <v>345</v>
+        <v>409</v>
       </c>
       <c r="H118" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="I118">
         <v>3</v>
       </c>
+      <c r="J118" t="s">
+        <v>195</v>
+      </c>
       <c r="K118" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B119" t="s">
         <v>176</v>
@@ -5741,24 +6077,27 @@
         <v>178</v>
       </c>
       <c r="F119" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G119" t="s">
-        <v>346</v>
+        <v>410</v>
       </c>
       <c r="H119" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I119">
         <v>2</v>
       </c>
+      <c r="J119" t="s">
+        <v>200</v>
+      </c>
       <c r="K119" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B120" t="s">
         <v>176</v>
@@ -5773,27 +6112,27 @@
         <v>178</v>
       </c>
       <c r="F120" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G120" t="s">
-        <v>347</v>
+        <v>411</v>
       </c>
       <c r="H120" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I120">
         <v>3</v>
       </c>
       <c r="J120" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K120" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B121" t="s">
         <v>176</v>
@@ -5808,24 +6147,27 @@
         <v>178</v>
       </c>
       <c r="F121" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G121" t="s">
-        <v>348</v>
+        <v>412</v>
       </c>
       <c r="H121" t="s">
+        <v>203</v>
+      </c>
+      <c r="I121">
+        <v>2</v>
+      </c>
+      <c r="J121" t="s">
         <v>200</v>
       </c>
-      <c r="I121">
-        <v>2</v>
-      </c>
       <c r="K121" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B122" t="s">
         <v>176</v>
@@ -5840,24 +6182,27 @@
         <v>178</v>
       </c>
       <c r="F122" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G122" t="s">
-        <v>349</v>
+        <v>413</v>
       </c>
       <c r="H122" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="I122">
         <v>2</v>
       </c>
+      <c r="J122" t="s">
+        <v>205</v>
+      </c>
       <c r="K122" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B123" t="s">
         <v>176</v>
@@ -5872,16 +6217,19 @@
         <v>178</v>
       </c>
       <c r="F123" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G123" t="s">
-        <v>350</v>
+        <v>414</v>
       </c>
       <c r="H123" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="I123">
         <v>2</v>
+      </c>
+      <c r="J123" t="s">
+        <v>78</v>
       </c>
       <c r="K123" t="s">
         <v>79</v>
@@ -5889,7 +6237,7 @@
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B124" t="s">
         <v>176</v>
@@ -5904,16 +6252,19 @@
         <v>178</v>
       </c>
       <c r="F124" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G124" t="s">
-        <v>351</v>
+        <v>415</v>
       </c>
       <c r="H124" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="I124">
         <v>2</v>
+      </c>
+      <c r="J124" t="s">
+        <v>78</v>
       </c>
       <c r="K124" t="s">
         <v>79</v>
@@ -5921,7 +6272,7 @@
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B125" t="s">
         <v>176</v>
@@ -5936,24 +6287,27 @@
         <v>178</v>
       </c>
       <c r="F125" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G125" t="s">
-        <v>352</v>
+        <v>416</v>
       </c>
       <c r="H125" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="I125">
         <v>2</v>
       </c>
+      <c r="J125" t="s">
+        <v>211</v>
+      </c>
       <c r="K125" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B126" t="s">
         <v>176</v>
@@ -5968,27 +6322,27 @@
         <v>178</v>
       </c>
       <c r="F126" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G126" t="e">
         <v>#N/A</v>
       </c>
       <c r="H126" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="I126">
         <v>2</v>
       </c>
       <c r="J126" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="K126" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B127" t="s">
         <v>176</v>
@@ -6003,27 +6357,27 @@
         <v>178</v>
       </c>
       <c r="F127" t="s">
-        <v>203</v>
-      </c>
-      <c r="G127" t="e">
-        <v>#N/A</v>
+        <v>207</v>
+      </c>
+      <c r="G127" t="s">
+        <v>417</v>
       </c>
       <c r="H127" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="I127">
         <v>2</v>
       </c>
       <c r="J127" t="s">
-        <v>211</v>
+        <v>147</v>
       </c>
       <c r="K127" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B128" t="s">
         <v>176</v>
@@ -6038,24 +6392,27 @@
         <v>178</v>
       </c>
       <c r="F128" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G128" t="s">
-        <v>353</v>
+        <v>418</v>
       </c>
       <c r="H128" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="I128">
         <v>2</v>
       </c>
+      <c r="J128" t="s">
+        <v>195</v>
+      </c>
       <c r="K128" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B129" t="s">
         <v>176</v>
@@ -6070,24 +6427,27 @@
         <v>178</v>
       </c>
       <c r="F129" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G129" t="s">
-        <v>354</v>
+        <v>419</v>
       </c>
       <c r="H129" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="I129">
         <v>2</v>
       </c>
+      <c r="J129" t="s">
+        <v>195</v>
+      </c>
       <c r="K129" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B130" t="s">
         <v>176</v>
@@ -6102,24 +6462,27 @@
         <v>178</v>
       </c>
       <c r="F130" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G130" t="s">
-        <v>355</v>
+        <v>420</v>
       </c>
       <c r="H130" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="I130">
         <v>3</v>
       </c>
+      <c r="J130" t="s">
+        <v>195</v>
+      </c>
       <c r="K130" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B131" t="s">
         <v>176</v>
@@ -6134,24 +6497,27 @@
         <v>178</v>
       </c>
       <c r="F131" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G131" t="s">
-        <v>356</v>
+        <v>421</v>
       </c>
       <c r="H131" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="I131">
         <v>2</v>
       </c>
+      <c r="J131" t="s">
+        <v>195</v>
+      </c>
       <c r="K131" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B132" t="s">
         <v>176</v>
@@ -6166,27 +6532,27 @@
         <v>178</v>
       </c>
       <c r="F132" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G132" t="e">
         <v>#N/A</v>
       </c>
       <c r="H132" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="I132">
         <v>2</v>
       </c>
       <c r="J132" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="K132" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B133" t="s">
         <v>176</v>
@@ -6201,24 +6567,27 @@
         <v>178</v>
       </c>
       <c r="F133" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G133" t="s">
-        <v>357</v>
+        <v>422</v>
       </c>
       <c r="H133" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I133">
         <v>2</v>
       </c>
+      <c r="J133" t="s">
+        <v>221</v>
+      </c>
       <c r="K133" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B134" t="s">
         <v>176</v>
@@ -6233,24 +6602,27 @@
         <v>178</v>
       </c>
       <c r="F134" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G134" t="s">
-        <v>358</v>
+        <v>423</v>
       </c>
       <c r="H134" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="I134">
         <v>2</v>
       </c>
+      <c r="J134" t="s">
+        <v>205</v>
+      </c>
       <c r="K134" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="B135" t="s">
         <v>176</v>
@@ -6265,19 +6637,1492 @@
         <v>178</v>
       </c>
       <c r="F135" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G135" t="s">
-        <v>359</v>
+        <v>424</v>
       </c>
       <c r="H135" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="I135">
         <v>2</v>
       </c>
+      <c r="J135" t="s">
+        <v>205</v>
+      </c>
       <c r="K135" t="s">
-        <v>202</v>
+        <v>206</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>11</v>
+      </c>
+      <c r="B136" t="s">
+        <v>225</v>
+      </c>
+      <c r="C136" t="s">
+        <v>226</v>
+      </c>
+      <c r="D136">
+        <v>114</v>
+      </c>
+      <c r="E136" t="s">
+        <v>85</v>
+      </c>
+      <c r="F136" t="s">
+        <v>227</v>
+      </c>
+      <c r="G136" t="s">
+        <v>425</v>
+      </c>
+      <c r="H136" t="s">
+        <v>228</v>
+      </c>
+      <c r="I136">
+        <v>4</v>
+      </c>
+      <c r="J136" t="s">
+        <v>78</v>
+      </c>
+      <c r="K136" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>11</v>
+      </c>
+      <c r="B137" t="s">
+        <v>225</v>
+      </c>
+      <c r="C137" t="s">
+        <v>226</v>
+      </c>
+      <c r="D137">
+        <v>114</v>
+      </c>
+      <c r="E137" t="s">
+        <v>85</v>
+      </c>
+      <c r="F137" t="s">
+        <v>230</v>
+      </c>
+      <c r="G137" t="s">
+        <v>342</v>
+      </c>
+      <c r="H137" t="s">
+        <v>81</v>
+      </c>
+      <c r="I137">
+        <v>2</v>
+      </c>
+      <c r="J137" t="s">
+        <v>78</v>
+      </c>
+      <c r="K137" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>11</v>
+      </c>
+      <c r="B138" t="s">
+        <v>225</v>
+      </c>
+      <c r="C138" t="s">
+        <v>226</v>
+      </c>
+      <c r="D138">
+        <v>114</v>
+      </c>
+      <c r="E138" t="s">
+        <v>85</v>
+      </c>
+      <c r="F138" t="s">
+        <v>230</v>
+      </c>
+      <c r="G138" t="s">
+        <v>340</v>
+      </c>
+      <c r="H138" t="s">
+        <v>77</v>
+      </c>
+      <c r="I138">
+        <v>2</v>
+      </c>
+      <c r="J138" t="s">
+        <v>78</v>
+      </c>
+      <c r="K138" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>11</v>
+      </c>
+      <c r="B139" t="s">
+        <v>225</v>
+      </c>
+      <c r="C139" t="s">
+        <v>226</v>
+      </c>
+      <c r="D139">
+        <v>114</v>
+      </c>
+      <c r="E139" t="s">
+        <v>85</v>
+      </c>
+      <c r="F139" t="s">
+        <v>230</v>
+      </c>
+      <c r="G139" t="s">
+        <v>341</v>
+      </c>
+      <c r="H139" t="s">
+        <v>231</v>
+      </c>
+      <c r="I139">
+        <v>2</v>
+      </c>
+      <c r="J139" t="s">
+        <v>78</v>
+      </c>
+      <c r="K139" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>11</v>
+      </c>
+      <c r="B140" t="s">
+        <v>225</v>
+      </c>
+      <c r="C140" t="s">
+        <v>226</v>
+      </c>
+      <c r="D140">
+        <v>114</v>
+      </c>
+      <c r="E140" t="s">
+        <v>85</v>
+      </c>
+      <c r="F140" t="s">
+        <v>230</v>
+      </c>
+      <c r="G140" t="s">
+        <v>426</v>
+      </c>
+      <c r="H140" t="s">
+        <v>232</v>
+      </c>
+      <c r="I140">
+        <v>4</v>
+      </c>
+      <c r="J140" t="s">
+        <v>78</v>
+      </c>
+      <c r="K140" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>11</v>
+      </c>
+      <c r="B141" t="s">
+        <v>225</v>
+      </c>
+      <c r="C141" t="s">
+        <v>226</v>
+      </c>
+      <c r="D141">
+        <v>114</v>
+      </c>
+      <c r="E141" t="s">
+        <v>85</v>
+      </c>
+      <c r="F141" t="s">
+        <v>230</v>
+      </c>
+      <c r="G141" t="s">
+        <v>414</v>
+      </c>
+      <c r="H141" t="s">
+        <v>208</v>
+      </c>
+      <c r="I141">
+        <v>4</v>
+      </c>
+      <c r="J141" t="s">
+        <v>78</v>
+      </c>
+      <c r="K141" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>11</v>
+      </c>
+      <c r="B142" t="s">
+        <v>225</v>
+      </c>
+      <c r="C142" t="s">
+        <v>226</v>
+      </c>
+      <c r="D142">
+        <v>114</v>
+      </c>
+      <c r="E142" t="s">
+        <v>85</v>
+      </c>
+      <c r="F142" t="s">
+        <v>230</v>
+      </c>
+      <c r="G142" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H142" t="s">
+        <v>233</v>
+      </c>
+      <c r="I142">
+        <v>2</v>
+      </c>
+      <c r="J142" t="s">
+        <v>78</v>
+      </c>
+      <c r="K142" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>11</v>
+      </c>
+      <c r="B143" t="s">
+        <v>225</v>
+      </c>
+      <c r="C143" t="s">
+        <v>226</v>
+      </c>
+      <c r="D143">
+        <v>114</v>
+      </c>
+      <c r="E143" t="s">
+        <v>85</v>
+      </c>
+      <c r="F143" t="s">
+        <v>230</v>
+      </c>
+      <c r="G143" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H143" t="s">
+        <v>234</v>
+      </c>
+      <c r="I143">
+        <v>2</v>
+      </c>
+      <c r="J143" t="s">
+        <v>78</v>
+      </c>
+      <c r="K143" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>11</v>
+      </c>
+      <c r="B144" t="s">
+        <v>225</v>
+      </c>
+      <c r="C144" t="s">
+        <v>226</v>
+      </c>
+      <c r="D144">
+        <v>114</v>
+      </c>
+      <c r="E144" t="s">
+        <v>85</v>
+      </c>
+      <c r="F144" t="s">
+        <v>230</v>
+      </c>
+      <c r="G144" t="s">
+        <v>427</v>
+      </c>
+      <c r="H144" t="s">
+        <v>235</v>
+      </c>
+      <c r="I144">
+        <v>2</v>
+      </c>
+      <c r="J144" t="s">
+        <v>78</v>
+      </c>
+      <c r="K144" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>11</v>
+      </c>
+      <c r="B145" t="s">
+        <v>225</v>
+      </c>
+      <c r="C145" t="s">
+        <v>226</v>
+      </c>
+      <c r="D145">
+        <v>114</v>
+      </c>
+      <c r="E145" t="s">
+        <v>85</v>
+      </c>
+      <c r="F145" t="s">
+        <v>230</v>
+      </c>
+      <c r="G145" t="s">
+        <v>428</v>
+      </c>
+      <c r="H145" t="s">
+        <v>236</v>
+      </c>
+      <c r="I145">
+        <v>4</v>
+      </c>
+      <c r="J145" t="s">
+        <v>78</v>
+      </c>
+      <c r="K145" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>11</v>
+      </c>
+      <c r="B146" t="s">
+        <v>225</v>
+      </c>
+      <c r="C146" t="s">
+        <v>226</v>
+      </c>
+      <c r="D146">
+        <v>114</v>
+      </c>
+      <c r="E146" t="s">
+        <v>85</v>
+      </c>
+      <c r="F146" t="s">
+        <v>230</v>
+      </c>
+      <c r="G146" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H146" t="s">
+        <v>237</v>
+      </c>
+      <c r="I146">
+        <v>2</v>
+      </c>
+      <c r="J146" t="s">
+        <v>78</v>
+      </c>
+      <c r="K146" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>11</v>
+      </c>
+      <c r="B147" t="s">
+        <v>225</v>
+      </c>
+      <c r="C147" t="s">
+        <v>226</v>
+      </c>
+      <c r="D147">
+        <v>114</v>
+      </c>
+      <c r="E147" t="s">
+        <v>85</v>
+      </c>
+      <c r="F147" t="s">
+        <v>230</v>
+      </c>
+      <c r="G147" t="s">
+        <v>429</v>
+      </c>
+      <c r="H147" t="s">
+        <v>238</v>
+      </c>
+      <c r="I147">
+        <v>2</v>
+      </c>
+      <c r="J147" t="s">
+        <v>78</v>
+      </c>
+      <c r="K147" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>11</v>
+      </c>
+      <c r="B148" t="s">
+        <v>225</v>
+      </c>
+      <c r="C148" t="s">
+        <v>226</v>
+      </c>
+      <c r="D148">
+        <v>114</v>
+      </c>
+      <c r="E148" t="s">
+        <v>85</v>
+      </c>
+      <c r="F148" t="s">
+        <v>230</v>
+      </c>
+      <c r="G148" t="s">
+        <v>430</v>
+      </c>
+      <c r="H148" t="s">
+        <v>239</v>
+      </c>
+      <c r="I148">
+        <v>2</v>
+      </c>
+      <c r="J148" t="s">
+        <v>78</v>
+      </c>
+      <c r="K148" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>11</v>
+      </c>
+      <c r="B149" t="s">
+        <v>225</v>
+      </c>
+      <c r="C149" t="s">
+        <v>226</v>
+      </c>
+      <c r="D149">
+        <v>114</v>
+      </c>
+      <c r="E149" t="s">
+        <v>178</v>
+      </c>
+      <c r="F149" t="s">
+        <v>240</v>
+      </c>
+      <c r="G149" t="s">
+        <v>431</v>
+      </c>
+      <c r="H149" t="s">
+        <v>241</v>
+      </c>
+      <c r="I149">
+        <v>2</v>
+      </c>
+      <c r="J149" t="s">
+        <v>242</v>
+      </c>
+      <c r="K149" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>11</v>
+      </c>
+      <c r="B150" t="s">
+        <v>225</v>
+      </c>
+      <c r="C150" t="s">
+        <v>226</v>
+      </c>
+      <c r="D150">
+        <v>114</v>
+      </c>
+      <c r="E150" t="s">
+        <v>178</v>
+      </c>
+      <c r="F150" t="s">
+        <v>240</v>
+      </c>
+      <c r="G150" t="s">
+        <v>432</v>
+      </c>
+      <c r="H150" t="s">
+        <v>244</v>
+      </c>
+      <c r="I150">
+        <v>2</v>
+      </c>
+      <c r="J150" t="s">
+        <v>242</v>
+      </c>
+      <c r="K150" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>11</v>
+      </c>
+      <c r="B151" t="s">
+        <v>225</v>
+      </c>
+      <c r="C151" t="s">
+        <v>226</v>
+      </c>
+      <c r="D151">
+        <v>114</v>
+      </c>
+      <c r="E151" t="s">
+        <v>178</v>
+      </c>
+      <c r="F151" t="s">
+        <v>240</v>
+      </c>
+      <c r="G151" t="s">
+        <v>433</v>
+      </c>
+      <c r="H151" t="s">
+        <v>245</v>
+      </c>
+      <c r="I151">
+        <v>2</v>
+      </c>
+      <c r="J151" t="s">
+        <v>242</v>
+      </c>
+      <c r="K151" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>11</v>
+      </c>
+      <c r="B152" t="s">
+        <v>225</v>
+      </c>
+      <c r="C152" t="s">
+        <v>226</v>
+      </c>
+      <c r="D152">
+        <v>114</v>
+      </c>
+      <c r="E152" t="s">
+        <v>178</v>
+      </c>
+      <c r="F152" t="s">
+        <v>240</v>
+      </c>
+      <c r="G152" t="s">
+        <v>434</v>
+      </c>
+      <c r="H152" t="s">
+        <v>246</v>
+      </c>
+      <c r="I152">
+        <v>2</v>
+      </c>
+      <c r="J152" t="s">
+        <v>242</v>
+      </c>
+      <c r="K152" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>11</v>
+      </c>
+      <c r="B153" t="s">
+        <v>225</v>
+      </c>
+      <c r="C153" t="s">
+        <v>226</v>
+      </c>
+      <c r="D153">
+        <v>114</v>
+      </c>
+      <c r="E153" t="s">
+        <v>178</v>
+      </c>
+      <c r="F153" t="s">
+        <v>240</v>
+      </c>
+      <c r="G153" t="s">
+        <v>435</v>
+      </c>
+      <c r="H153" t="s">
+        <v>247</v>
+      </c>
+      <c r="I153">
+        <v>2</v>
+      </c>
+      <c r="J153" t="s">
+        <v>242</v>
+      </c>
+      <c r="K153" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>11</v>
+      </c>
+      <c r="B154" t="s">
+        <v>225</v>
+      </c>
+      <c r="C154" t="s">
+        <v>226</v>
+      </c>
+      <c r="D154">
+        <v>114</v>
+      </c>
+      <c r="E154" t="s">
+        <v>178</v>
+      </c>
+      <c r="F154" t="s">
+        <v>240</v>
+      </c>
+      <c r="G154" t="s">
+        <v>436</v>
+      </c>
+      <c r="H154" t="s">
+        <v>248</v>
+      </c>
+      <c r="I154">
+        <v>2</v>
+      </c>
+      <c r="J154" t="s">
+        <v>242</v>
+      </c>
+      <c r="K154" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>11</v>
+      </c>
+      <c r="B155" t="s">
+        <v>225</v>
+      </c>
+      <c r="C155" t="s">
+        <v>226</v>
+      </c>
+      <c r="D155">
+        <v>114</v>
+      </c>
+      <c r="E155" t="s">
+        <v>178</v>
+      </c>
+      <c r="F155" t="s">
+        <v>240</v>
+      </c>
+      <c r="G155" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H155" t="s">
+        <v>249</v>
+      </c>
+      <c r="I155">
+        <v>2</v>
+      </c>
+      <c r="J155" t="s">
+        <v>242</v>
+      </c>
+      <c r="K155" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>11</v>
+      </c>
+      <c r="B156" t="s">
+        <v>225</v>
+      </c>
+      <c r="C156" t="s">
+        <v>226</v>
+      </c>
+      <c r="D156">
+        <v>114</v>
+      </c>
+      <c r="E156" t="s">
+        <v>178</v>
+      </c>
+      <c r="F156" t="s">
+        <v>240</v>
+      </c>
+      <c r="G156" t="s">
+        <v>437</v>
+      </c>
+      <c r="H156" t="s">
+        <v>250</v>
+      </c>
+      <c r="I156">
+        <v>2</v>
+      </c>
+      <c r="J156" t="s">
+        <v>242</v>
+      </c>
+      <c r="K156" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>11</v>
+      </c>
+      <c r="B157" t="s">
+        <v>225</v>
+      </c>
+      <c r="C157" t="s">
+        <v>226</v>
+      </c>
+      <c r="D157">
+        <v>114</v>
+      </c>
+      <c r="E157" t="s">
+        <v>178</v>
+      </c>
+      <c r="F157" t="s">
+        <v>240</v>
+      </c>
+      <c r="G157" t="s">
+        <v>438</v>
+      </c>
+      <c r="H157" t="s">
+        <v>251</v>
+      </c>
+      <c r="I157">
+        <v>4</v>
+      </c>
+      <c r="J157" t="s">
+        <v>20</v>
+      </c>
+      <c r="K157" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>11</v>
+      </c>
+      <c r="B158" t="s">
+        <v>225</v>
+      </c>
+      <c r="C158" t="s">
+        <v>226</v>
+      </c>
+      <c r="D158">
+        <v>114</v>
+      </c>
+      <c r="E158" t="s">
+        <v>178</v>
+      </c>
+      <c r="F158" t="s">
+        <v>240</v>
+      </c>
+      <c r="G158" t="s">
+        <v>439</v>
+      </c>
+      <c r="H158" t="s">
+        <v>253</v>
+      </c>
+      <c r="I158">
+        <v>4</v>
+      </c>
+      <c r="J158" t="s">
+        <v>20</v>
+      </c>
+      <c r="K158" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>11</v>
+      </c>
+      <c r="B159" t="s">
+        <v>225</v>
+      </c>
+      <c r="C159" t="s">
+        <v>226</v>
+      </c>
+      <c r="D159">
+        <v>114</v>
+      </c>
+      <c r="E159" t="s">
+        <v>178</v>
+      </c>
+      <c r="F159" t="s">
+        <v>240</v>
+      </c>
+      <c r="G159" t="s">
+        <v>440</v>
+      </c>
+      <c r="H159" t="s">
+        <v>254</v>
+      </c>
+      <c r="I159">
+        <v>4</v>
+      </c>
+      <c r="J159" t="s">
+        <v>20</v>
+      </c>
+      <c r="K159" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>11</v>
+      </c>
+      <c r="B160" t="s">
+        <v>225</v>
+      </c>
+      <c r="C160" t="s">
+        <v>226</v>
+      </c>
+      <c r="D160">
+        <v>114</v>
+      </c>
+      <c r="E160" t="s">
+        <v>178</v>
+      </c>
+      <c r="F160" t="s">
+        <v>240</v>
+      </c>
+      <c r="G160" t="s">
+        <v>441</v>
+      </c>
+      <c r="H160" t="s">
+        <v>255</v>
+      </c>
+      <c r="I160">
+        <v>2</v>
+      </c>
+      <c r="J160" t="s">
+        <v>20</v>
+      </c>
+      <c r="K160" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>11</v>
+      </c>
+      <c r="B161" t="s">
+        <v>225</v>
+      </c>
+      <c r="C161" t="s">
+        <v>226</v>
+      </c>
+      <c r="D161">
+        <v>114</v>
+      </c>
+      <c r="E161" t="s">
+        <v>178</v>
+      </c>
+      <c r="F161" t="s">
+        <v>240</v>
+      </c>
+      <c r="G161" t="s">
+        <v>442</v>
+      </c>
+      <c r="H161" t="s">
+        <v>256</v>
+      </c>
+      <c r="I161">
+        <v>4</v>
+      </c>
+      <c r="J161" t="s">
+        <v>257</v>
+      </c>
+      <c r="K161" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>11</v>
+      </c>
+      <c r="B162" t="s">
+        <v>225</v>
+      </c>
+      <c r="C162" t="s">
+        <v>226</v>
+      </c>
+      <c r="D162">
+        <v>114</v>
+      </c>
+      <c r="E162" t="s">
+        <v>178</v>
+      </c>
+      <c r="F162" t="s">
+        <v>240</v>
+      </c>
+      <c r="G162" t="s">
+        <v>443</v>
+      </c>
+      <c r="H162" t="s">
+        <v>259</v>
+      </c>
+      <c r="I162">
+        <v>4</v>
+      </c>
+      <c r="J162" t="s">
+        <v>61</v>
+      </c>
+      <c r="K162" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>11</v>
+      </c>
+      <c r="B163" t="s">
+        <v>225</v>
+      </c>
+      <c r="C163" t="s">
+        <v>226</v>
+      </c>
+      <c r="D163">
+        <v>114</v>
+      </c>
+      <c r="E163" t="s">
+        <v>178</v>
+      </c>
+      <c r="F163" t="s">
+        <v>240</v>
+      </c>
+      <c r="G163" t="s">
+        <v>444</v>
+      </c>
+      <c r="H163" t="s">
+        <v>260</v>
+      </c>
+      <c r="I163">
+        <v>2</v>
+      </c>
+      <c r="J163" t="s">
+        <v>61</v>
+      </c>
+      <c r="K163" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>11</v>
+      </c>
+      <c r="B164" t="s">
+        <v>225</v>
+      </c>
+      <c r="C164" t="s">
+        <v>226</v>
+      </c>
+      <c r="D164">
+        <v>114</v>
+      </c>
+      <c r="E164" t="s">
+        <v>178</v>
+      </c>
+      <c r="F164" t="s">
+        <v>240</v>
+      </c>
+      <c r="G164" t="s">
+        <v>445</v>
+      </c>
+      <c r="H164" t="s">
+        <v>261</v>
+      </c>
+      <c r="I164">
+        <v>2</v>
+      </c>
+      <c r="J164" t="s">
+        <v>262</v>
+      </c>
+      <c r="K164" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>11</v>
+      </c>
+      <c r="B165" t="s">
+        <v>225</v>
+      </c>
+      <c r="C165" t="s">
+        <v>226</v>
+      </c>
+      <c r="D165">
+        <v>114</v>
+      </c>
+      <c r="E165" t="s">
+        <v>178</v>
+      </c>
+      <c r="F165" t="s">
+        <v>240</v>
+      </c>
+      <c r="G165" t="s">
+        <v>446</v>
+      </c>
+      <c r="H165" t="s">
+        <v>264</v>
+      </c>
+      <c r="I165">
+        <v>2</v>
+      </c>
+      <c r="J165" t="s">
+        <v>265</v>
+      </c>
+      <c r="K165" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>11</v>
+      </c>
+      <c r="B166" t="s">
+        <v>225</v>
+      </c>
+      <c r="C166" t="s">
+        <v>226</v>
+      </c>
+      <c r="D166">
+        <v>114</v>
+      </c>
+      <c r="E166" t="s">
+        <v>178</v>
+      </c>
+      <c r="F166" t="s">
+        <v>240</v>
+      </c>
+      <c r="G166" t="s">
+        <v>447</v>
+      </c>
+      <c r="H166" t="s">
+        <v>267</v>
+      </c>
+      <c r="I166">
+        <v>2</v>
+      </c>
+      <c r="J166" t="s">
+        <v>265</v>
+      </c>
+      <c r="K166" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>11</v>
+      </c>
+      <c r="B167" t="s">
+        <v>225</v>
+      </c>
+      <c r="C167" t="s">
+        <v>226</v>
+      </c>
+      <c r="D167">
+        <v>114</v>
+      </c>
+      <c r="E167" t="s">
+        <v>178</v>
+      </c>
+      <c r="F167" t="s">
+        <v>240</v>
+      </c>
+      <c r="G167" t="s">
+        <v>448</v>
+      </c>
+      <c r="H167" t="s">
+        <v>268</v>
+      </c>
+      <c r="I167">
+        <v>2</v>
+      </c>
+      <c r="J167" t="s">
+        <v>269</v>
+      </c>
+      <c r="K167" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>11</v>
+      </c>
+      <c r="B168" t="s">
+        <v>225</v>
+      </c>
+      <c r="C168" t="s">
+        <v>226</v>
+      </c>
+      <c r="D168">
+        <v>114</v>
+      </c>
+      <c r="E168" t="s">
+        <v>178</v>
+      </c>
+      <c r="F168" t="s">
+        <v>240</v>
+      </c>
+      <c r="G168" t="s">
+        <v>296</v>
+      </c>
+      <c r="H168" t="s">
+        <v>24</v>
+      </c>
+      <c r="I168">
+        <v>2</v>
+      </c>
+      <c r="J168" t="s">
+        <v>271</v>
+      </c>
+      <c r="K168" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>11</v>
+      </c>
+      <c r="B169" t="s">
+        <v>225</v>
+      </c>
+      <c r="C169" t="s">
+        <v>226</v>
+      </c>
+      <c r="D169">
+        <v>114</v>
+      </c>
+      <c r="E169" t="s">
+        <v>178</v>
+      </c>
+      <c r="F169" t="s">
+        <v>240</v>
+      </c>
+      <c r="G169" t="s">
+        <v>297</v>
+      </c>
+      <c r="H169" t="s">
+        <v>27</v>
+      </c>
+      <c r="I169">
+        <v>2</v>
+      </c>
+      <c r="J169" t="s">
+        <v>271</v>
+      </c>
+      <c r="K169" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>11</v>
+      </c>
+      <c r="B170" t="s">
+        <v>225</v>
+      </c>
+      <c r="C170" t="s">
+        <v>226</v>
+      </c>
+      <c r="D170">
+        <v>114</v>
+      </c>
+      <c r="E170" t="s">
+        <v>178</v>
+      </c>
+      <c r="F170" t="s">
+        <v>240</v>
+      </c>
+      <c r="G170" t="s">
+        <v>449</v>
+      </c>
+      <c r="H170" t="s">
+        <v>273</v>
+      </c>
+      <c r="I170">
+        <v>2</v>
+      </c>
+      <c r="J170" t="s">
+        <v>17</v>
+      </c>
+      <c r="K170" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>11</v>
+      </c>
+      <c r="B171" t="s">
+        <v>225</v>
+      </c>
+      <c r="C171" t="s">
+        <v>226</v>
+      </c>
+      <c r="D171">
+        <v>114</v>
+      </c>
+      <c r="E171" t="s">
+        <v>178</v>
+      </c>
+      <c r="F171" t="s">
+        <v>240</v>
+      </c>
+      <c r="G171" t="s">
+        <v>450</v>
+      </c>
+      <c r="H171" t="s">
+        <v>274</v>
+      </c>
+      <c r="I171">
+        <v>4</v>
+      </c>
+      <c r="J171" t="s">
+        <v>17</v>
+      </c>
+      <c r="K171" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>11</v>
+      </c>
+      <c r="B172" t="s">
+        <v>225</v>
+      </c>
+      <c r="C172" t="s">
+        <v>226</v>
+      </c>
+      <c r="D172">
+        <v>114</v>
+      </c>
+      <c r="E172" t="s">
+        <v>178</v>
+      </c>
+      <c r="F172" t="s">
+        <v>240</v>
+      </c>
+      <c r="G172" t="s">
+        <v>294</v>
+      </c>
+      <c r="H172" t="s">
+        <v>16</v>
+      </c>
+      <c r="I172">
+        <v>4</v>
+      </c>
+      <c r="J172" t="s">
+        <v>17</v>
+      </c>
+      <c r="K172" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>11</v>
+      </c>
+      <c r="B173" t="s">
+        <v>225</v>
+      </c>
+      <c r="C173" t="s">
+        <v>226</v>
+      </c>
+      <c r="D173">
+        <v>114</v>
+      </c>
+      <c r="E173" t="s">
+        <v>178</v>
+      </c>
+      <c r="F173" t="s">
+        <v>240</v>
+      </c>
+      <c r="G173" t="s">
+        <v>451</v>
+      </c>
+      <c r="H173" t="s">
+        <v>275</v>
+      </c>
+      <c r="I173">
+        <v>2</v>
+      </c>
+      <c r="J173" t="s">
+        <v>17</v>
+      </c>
+      <c r="K173" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>11</v>
+      </c>
+      <c r="B174" t="s">
+        <v>225</v>
+      </c>
+      <c r="C174" t="s">
+        <v>226</v>
+      </c>
+      <c r="D174">
+        <v>114</v>
+      </c>
+      <c r="E174" t="s">
+        <v>178</v>
+      </c>
+      <c r="F174" t="s">
+        <v>240</v>
+      </c>
+      <c r="G174" t="s">
+        <v>452</v>
+      </c>
+      <c r="H174" t="s">
+        <v>276</v>
+      </c>
+      <c r="I174">
+        <v>2</v>
+      </c>
+      <c r="J174" t="s">
+        <v>277</v>
+      </c>
+      <c r="K174" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>11</v>
+      </c>
+      <c r="B175" t="s">
+        <v>225</v>
+      </c>
+      <c r="C175" t="s">
+        <v>226</v>
+      </c>
+      <c r="D175">
+        <v>114</v>
+      </c>
+      <c r="E175" t="s">
+        <v>178</v>
+      </c>
+      <c r="F175" t="s">
+        <v>240</v>
+      </c>
+      <c r="G175" t="s">
+        <v>453</v>
+      </c>
+      <c r="H175" t="s">
+        <v>279</v>
+      </c>
+      <c r="I175">
+        <v>2</v>
+      </c>
+      <c r="J175" t="s">
+        <v>277</v>
+      </c>
+      <c r="K175" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>11</v>
+      </c>
+      <c r="B176" t="s">
+        <v>225</v>
+      </c>
+      <c r="C176" t="s">
+        <v>226</v>
+      </c>
+      <c r="D176">
+        <v>114</v>
+      </c>
+      <c r="E176" t="s">
+        <v>178</v>
+      </c>
+      <c r="F176" t="s">
+        <v>240</v>
+      </c>
+      <c r="G176" t="s">
+        <v>454</v>
+      </c>
+      <c r="H176" t="s">
+        <v>280</v>
+      </c>
+      <c r="I176">
+        <v>2</v>
+      </c>
+      <c r="J176" t="s">
+        <v>281</v>
+      </c>
+      <c r="K176" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>11</v>
+      </c>
+      <c r="B177" t="s">
+        <v>225</v>
+      </c>
+      <c r="C177" t="s">
+        <v>226</v>
+      </c>
+      <c r="D177">
+        <v>114</v>
+      </c>
+      <c r="E177" t="s">
+        <v>178</v>
+      </c>
+      <c r="F177" t="s">
+        <v>240</v>
+      </c>
+      <c r="G177" t="s">
+        <v>455</v>
+      </c>
+      <c r="H177" t="s">
+        <v>283</v>
+      </c>
+      <c r="I177">
+        <v>3</v>
+      </c>
+      <c r="J177" t="s">
+        <v>114</v>
+      </c>
+      <c r="K177" t="s">
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -6287,31 +8132,31 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4DCFC30-4D5C-4C4D-99C2-BB1D05E9719E}">
-  <dimension ref="A1:G5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8549A938-95F2-4F8B-8CFA-A404657EE9C4}">
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
       <c r="C1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>222</v>
+        <v>285</v>
       </c>
       <c r="E1" t="s">
-        <v>223</v>
+        <v>286</v>
       </c>
       <c r="F1" t="s">
-        <v>224</v>
+        <v>287</v>
       </c>
       <c r="G1" t="s">
-        <v>225</v>
+        <v>288</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -6334,7 +8179,7 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>226</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -6357,7 +8202,7 @@
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>227</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -6380,7 +8225,7 @@
         <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>228</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -6403,7 +8248,30 @@
         <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>229</v>
+        <v>292</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>225</v>
+      </c>
+      <c r="B6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C6">
+        <v>114</v>
+      </c>
+      <c r="D6">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>20</v>
+      </c>
+      <c r="G6" t="s">
+        <v>293</v>
       </c>
     </row>
   </sheetData>
